--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN101"/>
+  <dimension ref="A1:BN105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22629,6 +22629,466 @@
         <v>238</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45508.65625</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="n">
+        <v>77</v>
+      </c>
+      <c r="X102" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr"/>
+      <c r="BA102" t="inlineStr"/>
+      <c r="BB102" t="inlineStr"/>
+      <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr"/>
+      <c r="BM102" t="inlineStr"/>
+      <c r="BN102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="n">
+        <v>77</v>
+      </c>
+      <c r="X103" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+      <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="inlineStr"/>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AU103" t="inlineStr"/>
+      <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr"/>
+      <c r="BA103" t="inlineStr"/>
+      <c r="BB103" t="inlineStr"/>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr"/>
+      <c r="BM103" t="inlineStr"/>
+      <c r="BN103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="n">
+        <v>77</v>
+      </c>
+      <c r="X104" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>587500</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA104" t="inlineStr"/>
+      <c r="BB104" t="inlineStr"/>
+      <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr"/>
+      <c r="BM104" t="inlineStr"/>
+      <c r="BN104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1707</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="n">
+        <v>77</v>
+      </c>
+      <c r="X105" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr"/>
+      <c r="BA105" t="inlineStr"/>
+      <c r="BB105" t="inlineStr"/>
+      <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr"/>
+      <c r="BM105" t="inlineStr"/>
+      <c r="BN105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN105"/>
+  <dimension ref="A1:BN109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23089,6 +23089,714 @@
       <c r="BM105" t="inlineStr"/>
       <c r="BN105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>16917</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>57</v>
+      </c>
+      <c r="N106" t="n">
+        <v>43</v>
+      </c>
+      <c r="O106" t="n">
+        <v>10</v>
+      </c>
+      <c r="P106" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>4</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="n">
+        <v>9</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W106" t="n">
+        <v>77</v>
+      </c>
+      <c r="X106" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>983500</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>72.29166666666667</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>5370833.333333333</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>185.3157894736842</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>1278947.368421053</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>71.36842105263158</v>
+      </c>
+      <c r="BA106" t="inlineStr"/>
+      <c r="BB106" t="inlineStr"/>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr"/>
+      <c r="BM106" t="inlineStr"/>
+      <c r="BN106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F107" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>54</v>
+      </c>
+      <c r="N107" t="n">
+        <v>46</v>
+      </c>
+      <c r="O107" t="n">
+        <v>19</v>
+      </c>
+      <c r="P107" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>13</v>
+      </c>
+      <c r="R107" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" t="n">
+        <v>16</v>
+      </c>
+      <c r="T107" t="n">
+        <v>11</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W107" t="n">
+        <v>77</v>
+      </c>
+      <c r="X107" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>4072500</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>781250</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>184.0666666666667</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>5316666.666666667</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>75.93333333333334</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>62.1875</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>718125</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr"/>
+      <c r="BM107" t="inlineStr"/>
+      <c r="BN107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>62</v>
+      </c>
+      <c r="N108" t="n">
+        <v>38</v>
+      </c>
+      <c r="O108" t="n">
+        <v>16</v>
+      </c>
+      <c r="P108" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="n">
+        <v>10</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="W108" t="n">
+        <v>77</v>
+      </c>
+      <c r="X108" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>4140909.090909091</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr"/>
+      <c r="BA108" t="inlineStr"/>
+      <c r="BB108" t="inlineStr"/>
+      <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="inlineStr"/>
+      <c r="BM108" t="inlineStr"/>
+      <c r="BN108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>49</v>
+      </c>
+      <c r="N109" t="n">
+        <v>51</v>
+      </c>
+      <c r="O109" t="n">
+        <v>15</v>
+      </c>
+      <c r="P109" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>9</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="n">
+        <v>9</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W109" t="n">
+        <v>77</v>
+      </c>
+      <c r="X109" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="n">
+        <v>21.60869565217391</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>184.2608695652174</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>68.08695652173913</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3495652.173913043</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1042954.545454545</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>69.13636363636364</v>
+      </c>
+      <c r="BA109" t="inlineStr"/>
+      <c r="BB109" t="inlineStr"/>
+      <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr"/>
+      <c r="BI109" t="inlineStr"/>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="inlineStr"/>
+      <c r="BM109" t="inlineStr"/>
+      <c r="BN109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN109"/>
+  <dimension ref="A1:BN139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23797,6 +23797,5700 @@
       <c r="BM109" t="inlineStr"/>
       <c r="BN109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M110" t="n">
+        <v>43</v>
+      </c>
+      <c r="N110" t="n">
+        <v>57</v>
+      </c>
+      <c r="O110" t="n">
+        <v>12</v>
+      </c>
+      <c r="P110" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>3</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="n">
+        <v>7</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="W110" t="n">
+        <v>77</v>
+      </c>
+      <c r="X110" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>4581818.181818182</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>19037500</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>81</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2293750</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>24.78947368421053</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>180.421052631579</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>77.21052631578948</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>24271052.63157895</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>82.21052631578948</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>288</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>292</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M111" t="n">
+        <v>67</v>
+      </c>
+      <c r="N111" t="n">
+        <v>33</v>
+      </c>
+      <c r="O111" t="n">
+        <v>13</v>
+      </c>
+      <c r="P111" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>6</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" t="n">
+        <v>14</v>
+      </c>
+      <c r="T111" t="n">
+        <v>11</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W111" t="n">
+        <v>77</v>
+      </c>
+      <c r="X111" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>20770000</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>74.45833333333333</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>11406250</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>24.47619047619047</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>181.7619047619048</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>66.52380952380952</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1505714.285714286</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>72.42857142857143</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>423</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F112" t="n">
+        <v>26418</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M112" t="n">
+        <v>74</v>
+      </c>
+      <c r="N112" t="n">
+        <v>26</v>
+      </c>
+      <c r="O112" t="n">
+        <v>22</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>7</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>15</v>
+      </c>
+      <c r="T112" t="n">
+        <v>13</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W112" t="n">
+        <v>77</v>
+      </c>
+      <c r="X112" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>8381818.181818182</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>5271250</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>3143750</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>37325000</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M113" t="n">
+        <v>32</v>
+      </c>
+      <c r="N113" t="n">
+        <v>68</v>
+      </c>
+      <c r="O113" t="n">
+        <v>8</v>
+      </c>
+      <c r="P113" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>5</v>
+      </c>
+      <c r="R113" t="n">
+        <v>5</v>
+      </c>
+      <c r="S113" t="n">
+        <v>15</v>
+      </c>
+      <c r="T113" t="n">
+        <v>13</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="W113" t="n">
+        <v>77</v>
+      </c>
+      <c r="X113" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>5012500</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>31620000</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>70.04761904761905</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>3560714.285714286</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>75.61904761904762</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>76.05882352941177</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>16613235.29411765</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>79.58823529411765</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH113" t="inlineStr"/>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
+      <c r="BM113" t="inlineStr"/>
+      <c r="BN113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M114" t="n">
+        <v>56</v>
+      </c>
+      <c r="N114" t="n">
+        <v>44</v>
+      </c>
+      <c r="O114" t="n">
+        <v>20</v>
+      </c>
+      <c r="P114" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>6</v>
+      </c>
+      <c r="R114" t="n">
+        <v>3</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="n">
+        <v>7</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W114" t="n">
+        <v>77</v>
+      </c>
+      <c r="X114" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>23.31578947368421</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>181.2631578947368</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>30031578.94736842</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>185.6315789473684</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>7406578.947368421</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>192</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>287</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>49600000</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M115" t="n">
+        <v>39</v>
+      </c>
+      <c r="N115" t="n">
+        <v>61</v>
+      </c>
+      <c r="O115" t="n">
+        <v>9</v>
+      </c>
+      <c r="P115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>16</v>
+      </c>
+      <c r="T115" t="n">
+        <v>19</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W115" t="n">
+        <v>77</v>
+      </c>
+      <c r="X115" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC115" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>3172727.272727273</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>2695416.666666667</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>75.20833333333333</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>72.47619047619048</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>5076190.476190476</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>75.80952380952381</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>347</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>224</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M116" t="n">
+        <v>32</v>
+      </c>
+      <c r="N116" t="n">
+        <v>68</v>
+      </c>
+      <c r="O116" t="n">
+        <v>10</v>
+      </c>
+      <c r="P116" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>6</v>
+      </c>
+      <c r="R116" t="n">
+        <v>9</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="n">
+        <v>14</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W116" t="n">
+        <v>77</v>
+      </c>
+      <c r="X116" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC116" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>43272727.27272727</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>3080882.352941176</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>78.95652173913044</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>26208695.65217391</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>258</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>236</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>53800000</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M117" t="n">
+        <v>39</v>
+      </c>
+      <c r="N117" t="n">
+        <v>61</v>
+      </c>
+      <c r="O117" t="n">
+        <v>13</v>
+      </c>
+      <c r="P117" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>5</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="n">
+        <v>9</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W117" t="n">
+        <v>77</v>
+      </c>
+      <c r="X117" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>13710000</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>2866956.52173913</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>22.68181818181818</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>73.13636363636364</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>80.77272727272727</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>355</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>53</v>
+      </c>
+      <c r="N118" t="n">
+        <v>47</v>
+      </c>
+      <c r="O118" t="n">
+        <v>21</v>
+      </c>
+      <c r="P118" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>8</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="n">
+        <v>11</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W118" t="n">
+        <v>77</v>
+      </c>
+      <c r="X118" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>4015909.090909091</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>68.42307692307692</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>3002884.615384615</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>74.65384615384616</v>
+      </c>
+      <c r="AU118" t="inlineStr"/>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr"/>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F119" t="n">
+        <v>6905</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>59</v>
+      </c>
+      <c r="N119" t="n">
+        <v>41</v>
+      </c>
+      <c r="O119" t="n">
+        <v>11</v>
+      </c>
+      <c r="P119" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>5</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7</v>
+      </c>
+      <c r="S119" t="n">
+        <v>13</v>
+      </c>
+      <c r="T119" t="n">
+        <v>17</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W119" t="n">
+        <v>77</v>
+      </c>
+      <c r="X119" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>4894444.444444444</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>24.10526315789474</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>182.8421052631579</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2236842.105263158</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>74.47368421052632</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1538888.888888889</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45516.5625</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>38</v>
+      </c>
+      <c r="N120" t="n">
+        <v>62</v>
+      </c>
+      <c r="O120" t="n">
+        <v>19</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>9</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>20</v>
+      </c>
+      <c r="T120" t="n">
+        <v>9</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W120" t="n">
+        <v>77</v>
+      </c>
+      <c r="X120" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2694444.444444444</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AU120" t="inlineStr"/>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr"/>
+      <c r="BA120" t="inlineStr"/>
+      <c r="BB120" t="inlineStr"/>
+      <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>59</v>
+      </c>
+      <c r="N121" t="n">
+        <v>41</v>
+      </c>
+      <c r="O121" t="n">
+        <v>5</v>
+      </c>
+      <c r="P121" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2</v>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="n">
+        <v>19</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W121" t="n">
+        <v>77</v>
+      </c>
+      <c r="X121" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1597222.222222222</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>980000</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BA121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr"/>
+      <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>60</v>
+      </c>
+      <c r="N122" t="n">
+        <v>40</v>
+      </c>
+      <c r="O122" t="n">
+        <v>8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="n">
+        <v>6</v>
+      </c>
+      <c r="T122" t="n">
+        <v>12</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W122" t="n">
+        <v>77</v>
+      </c>
+      <c r="X122" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>5423684.210526315</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>76.47368421052632</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F123" t="n">
+        <v>14196</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>43</v>
+      </c>
+      <c r="N123" t="n">
+        <v>57</v>
+      </c>
+      <c r="O123" t="n">
+        <v>11</v>
+      </c>
+      <c r="P123" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>3</v>
+      </c>
+      <c r="R123" t="n">
+        <v>5</v>
+      </c>
+      <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>13</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="W123" t="n">
+        <v>77</v>
+      </c>
+      <c r="X123" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2136111.111111111</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1749750</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>70.59090909090909</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>3314318.181818182</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="BA123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr"/>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
+      <c r="BI123" t="inlineStr"/>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
+      <c r="BM123" t="inlineStr"/>
+      <c r="BN123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>47</v>
+      </c>
+      <c r="N124" t="n">
+        <v>53</v>
+      </c>
+      <c r="O124" t="n">
+        <v>17</v>
+      </c>
+      <c r="P124" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>4</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4</v>
+      </c>
+      <c r="S124" t="n">
+        <v>7</v>
+      </c>
+      <c r="T124" t="n">
+        <v>12</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W124" t="n">
+        <v>77</v>
+      </c>
+      <c r="X124" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>22.95238095238095</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>67.04761904761905</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>2280476.19047619</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>24.82608695652174</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>2280434.782608696</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="BA124" t="inlineStr"/>
+      <c r="BB124" t="inlineStr"/>
+      <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+      <c r="BM124" t="inlineStr"/>
+      <c r="BN124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4310</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>38</v>
+      </c>
+      <c r="N125" t="n">
+        <v>62</v>
+      </c>
+      <c r="O125" t="n">
+        <v>9</v>
+      </c>
+      <c r="P125" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>5</v>
+      </c>
+      <c r="R125" t="n">
+        <v>8</v>
+      </c>
+      <c r="S125" t="n">
+        <v>14</v>
+      </c>
+      <c r="T125" t="n">
+        <v>12</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>77</v>
+      </c>
+      <c r="X125" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1888888.888888889</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1217777.777777778</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>66.78947368421052</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1748421.052631579</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BA125" t="inlineStr"/>
+      <c r="BB125" t="inlineStr"/>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F126" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>70</v>
+      </c>
+      <c r="N126" t="n">
+        <v>30</v>
+      </c>
+      <c r="O126" t="n">
+        <v>28</v>
+      </c>
+      <c r="P126" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>6</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W126" t="n">
+        <v>77</v>
+      </c>
+      <c r="X126" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>32290909.09090909</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>82.36363636363636</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>9576250</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>63.85714285714285</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1024642.857142857</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="BA126" t="inlineStr"/>
+      <c r="BB126" t="inlineStr"/>
+      <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
+        <v>57</v>
+      </c>
+      <c r="N127" t="n">
+        <v>43</v>
+      </c>
+      <c r="O127" t="n">
+        <v>22</v>
+      </c>
+      <c r="P127" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>9</v>
+      </c>
+      <c r="T127" t="n">
+        <v>10</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W127" t="n">
+        <v>77</v>
+      </c>
+      <c r="X127" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1133333.333333333</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>181.4090909090909</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2088181.818181818</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1014583.333333333</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+      <c r="BM127" t="inlineStr"/>
+      <c r="BN127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45514.5625</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7048</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>54</v>
+      </c>
+      <c r="N128" t="n">
+        <v>46</v>
+      </c>
+      <c r="O128" t="n">
+        <v>11</v>
+      </c>
+      <c r="P128" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>3</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4</v>
+      </c>
+      <c r="S128" t="n">
+        <v>14</v>
+      </c>
+      <c r="T128" t="n">
+        <v>7</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W128" t="n">
+        <v>77</v>
+      </c>
+      <c r="X128" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>5011111.111111111</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr"/>
+      <c r="AK128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>184.0555555555555</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2776388.888888889</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA128" t="inlineStr"/>
+      <c r="BB128" t="inlineStr"/>
+      <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+      <c r="BM128" t="inlineStr"/>
+      <c r="BN128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>58</v>
+      </c>
+      <c r="N129" t="n">
+        <v>42</v>
+      </c>
+      <c r="O129" t="n">
+        <v>13</v>
+      </c>
+      <c r="P129" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>3</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="n">
+        <v>12</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W129" t="n">
+        <v>77</v>
+      </c>
+      <c r="X129" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>2154545.454545455</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2065217.391304348</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1022500</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="BA129" t="inlineStr"/>
+      <c r="BB129" t="inlineStr"/>
+      <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+      <c r="BM129" t="inlineStr"/>
+      <c r="BN129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>49</v>
+      </c>
+      <c r="N130" t="n">
+        <v>51</v>
+      </c>
+      <c r="O130" t="n">
+        <v>9</v>
+      </c>
+      <c r="P130" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6</v>
+      </c>
+      <c r="S130" t="n">
+        <v>11</v>
+      </c>
+      <c r="T130" t="n">
+        <v>7</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W130" t="n">
+        <v>77</v>
+      </c>
+      <c r="X130" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="BA130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr"/>
+      <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
+      <c r="BM130" t="inlineStr"/>
+      <c r="BN130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11382</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>42</v>
+      </c>
+      <c r="N131" t="n">
+        <v>58</v>
+      </c>
+      <c r="O131" t="n">
+        <v>14</v>
+      </c>
+      <c r="P131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>8</v>
+      </c>
+      <c r="R131" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>13</v>
+      </c>
+      <c r="T131" t="n">
+        <v>14</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W131" t="n">
+        <v>77</v>
+      </c>
+      <c r="X131" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="inlineStr"/>
+      <c r="AK131" t="inlineStr"/>
+      <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr"/>
+      <c r="AN131" t="inlineStr"/>
+      <c r="AO131" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>3056250</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>871875</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
+      <c r="BM131" t="inlineStr"/>
+      <c r="BN131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6840</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>32</v>
+      </c>
+      <c r="N132" t="n">
+        <v>68</v>
+      </c>
+      <c r="O132" t="n">
+        <v>15</v>
+      </c>
+      <c r="P132" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>11</v>
+      </c>
+      <c r="T132" t="n">
+        <v>16</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="W132" t="n">
+        <v>77</v>
+      </c>
+      <c r="X132" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1909090.909090909</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1179687.5</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>23.91666666666667</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>2183333.333333333</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="inlineStr"/>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
+      <c r="BM132" t="inlineStr"/>
+      <c r="BN132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>45</v>
+      </c>
+      <c r="N133" t="n">
+        <v>55</v>
+      </c>
+      <c r="O133" t="n">
+        <v>20</v>
+      </c>
+      <c r="P133" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>12</v>
+      </c>
+      <c r="R133" t="n">
+        <v>4</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="n">
+        <v>13</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="W133" t="n">
+        <v>77</v>
+      </c>
+      <c r="X133" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1646875</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1680555.555555556</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>21.78260869565218</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>63.91304347826087</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1310869.565217391</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>24.42857142857143</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>67.76190476190476</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1782142.857142857</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="BA133" t="inlineStr"/>
+      <c r="BB133" t="inlineStr"/>
+      <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
+      <c r="BH133" t="inlineStr"/>
+      <c r="BI133" t="inlineStr"/>
+      <c r="BJ133" t="inlineStr"/>
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="inlineStr"/>
+      <c r="BM133" t="inlineStr"/>
+      <c r="BN133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>30</v>
+      </c>
+      <c r="N134" t="n">
+        <v>70</v>
+      </c>
+      <c r="O134" t="n">
+        <v>12</v>
+      </c>
+      <c r="P134" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="n">
+        <v>25</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W134" t="n">
+        <v>77</v>
+      </c>
+      <c r="X134" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="inlineStr"/>
+      <c r="AK134" t="inlineStr"/>
+      <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr"/>
+      <c r="AO134" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA134" t="inlineStr"/>
+      <c r="BB134" t="inlineStr"/>
+      <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
+      <c r="BI134" t="inlineStr"/>
+      <c r="BJ134" t="inlineStr"/>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="inlineStr"/>
+      <c r="BM134" t="inlineStr"/>
+      <c r="BN134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F135" t="n">
+        <v>20957</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>56</v>
+      </c>
+      <c r="N135" t="n">
+        <v>44</v>
+      </c>
+      <c r="O135" t="n">
+        <v>16</v>
+      </c>
+      <c r="P135" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>4</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
+        <v>20</v>
+      </c>
+      <c r="T135" t="n">
+        <v>14</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W135" t="n">
+        <v>77</v>
+      </c>
+      <c r="X135" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AI135" t="inlineStr"/>
+      <c r="AJ135" t="inlineStr"/>
+      <c r="AK135" t="inlineStr"/>
+      <c r="AL135" t="inlineStr"/>
+      <c r="AM135" t="inlineStr"/>
+      <c r="AN135" t="inlineStr"/>
+      <c r="AO135" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>181.68</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>934600</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="AU135" t="inlineStr"/>
+      <c r="AV135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr"/>
+      <c r="BA135" t="inlineStr"/>
+      <c r="BB135" t="inlineStr"/>
+      <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr"/>
+      <c r="BI135" t="inlineStr"/>
+      <c r="BJ135" t="inlineStr"/>
+      <c r="BK135" t="inlineStr"/>
+      <c r="BL135" t="inlineStr"/>
+      <c r="BM135" t="inlineStr"/>
+      <c r="BN135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F136" t="n">
+        <v>8770</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>54</v>
+      </c>
+      <c r="N136" t="n">
+        <v>46</v>
+      </c>
+      <c r="O136" t="n">
+        <v>19</v>
+      </c>
+      <c r="P136" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="n">
+        <v>22</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W136" t="n">
+        <v>77</v>
+      </c>
+      <c r="X136" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1563888.888888889</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>184.2380952380952</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>186.0588235294118</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1320588.235294118</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BA136" t="inlineStr"/>
+      <c r="BB136" t="inlineStr"/>
+      <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
+      <c r="BI136" t="inlineStr"/>
+      <c r="BJ136" t="inlineStr"/>
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="inlineStr"/>
+      <c r="BM136" t="inlineStr"/>
+      <c r="BN136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12509</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>70</v>
+      </c>
+      <c r="N137" t="n">
+        <v>30</v>
+      </c>
+      <c r="O137" t="n">
+        <v>15</v>
+      </c>
+      <c r="P137" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>7</v>
+      </c>
+      <c r="R137" t="n">
+        <v>3</v>
+      </c>
+      <c r="S137" t="n">
+        <v>23</v>
+      </c>
+      <c r="T137" t="n">
+        <v>12</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W137" t="n">
+        <v>77</v>
+      </c>
+      <c r="X137" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2572222.222222222</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>22.72222222222222</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>178.0555555555555</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1901388.888888889</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>74.61111111111111</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>844473.6842105263</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="BA137" t="inlineStr"/>
+      <c r="BB137" t="inlineStr"/>
+      <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
+      <c r="BI137" t="inlineStr"/>
+      <c r="BJ137" t="inlineStr"/>
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="inlineStr"/>
+      <c r="BM137" t="inlineStr"/>
+      <c r="BN137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>68</v>
+      </c>
+      <c r="N138" t="n">
+        <v>32</v>
+      </c>
+      <c r="O138" t="n">
+        <v>9</v>
+      </c>
+      <c r="P138" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="n">
+        <v>15</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W138" t="n">
+        <v>77</v>
+      </c>
+      <c r="X138" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1190909.090909091</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>65.44444444444444</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>65.61538461538461</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1168846.153846154</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>70.46153846153847</v>
+      </c>
+      <c r="BA138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr"/>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="inlineStr"/>
+      <c r="BJ138" t="inlineStr"/>
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="inlineStr"/>
+      <c r="BM138" t="inlineStr"/>
+      <c r="BN138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>37</v>
+      </c>
+      <c r="N139" t="n">
+        <v>63</v>
+      </c>
+      <c r="O139" t="n">
+        <v>18</v>
+      </c>
+      <c r="P139" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>6</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="n">
+        <v>10</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W139" t="n">
+        <v>77</v>
+      </c>
+      <c r="X139" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>181.2142857142857</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1164285.714285714</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA139" t="inlineStr"/>
+      <c r="BB139" t="inlineStr"/>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
+      <c r="BI139" t="inlineStr"/>
+      <c r="BJ139" t="inlineStr"/>
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="inlineStr"/>
+      <c r="BM139" t="inlineStr"/>
+      <c r="BN139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN109"/>
+  <dimension ref="A1:BN141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23797,6 +23797,6138 @@
       <c r="BM109" t="inlineStr"/>
       <c r="BN109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M110" t="n">
+        <v>43</v>
+      </c>
+      <c r="N110" t="n">
+        <v>57</v>
+      </c>
+      <c r="O110" t="n">
+        <v>12</v>
+      </c>
+      <c r="P110" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>3</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="n">
+        <v>7</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="W110" t="n">
+        <v>77</v>
+      </c>
+      <c r="X110" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>4581818.181818182</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>19037500</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>81</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2293750</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>24.78947368421053</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>180.421052631579</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>77.21052631578948</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>24271052.63157895</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>82.21052631578948</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>288</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>292</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M111" t="n">
+        <v>67</v>
+      </c>
+      <c r="N111" t="n">
+        <v>33</v>
+      </c>
+      <c r="O111" t="n">
+        <v>13</v>
+      </c>
+      <c r="P111" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>6</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" t="n">
+        <v>14</v>
+      </c>
+      <c r="T111" t="n">
+        <v>11</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W111" t="n">
+        <v>77</v>
+      </c>
+      <c r="X111" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>20770000</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>74.45833333333333</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>11406250</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>24.47619047619047</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>181.7619047619048</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>66.52380952380952</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1505714.285714286</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>72.42857142857143</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>423</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F112" t="n">
+        <v>26418</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M112" t="n">
+        <v>74</v>
+      </c>
+      <c r="N112" t="n">
+        <v>26</v>
+      </c>
+      <c r="O112" t="n">
+        <v>22</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>7</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>15</v>
+      </c>
+      <c r="T112" t="n">
+        <v>13</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W112" t="n">
+        <v>77</v>
+      </c>
+      <c r="X112" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>8381818.181818182</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>5271250</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>3143750</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>37325000</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M113" t="n">
+        <v>32</v>
+      </c>
+      <c r="N113" t="n">
+        <v>68</v>
+      </c>
+      <c r="O113" t="n">
+        <v>8</v>
+      </c>
+      <c r="P113" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>5</v>
+      </c>
+      <c r="R113" t="n">
+        <v>5</v>
+      </c>
+      <c r="S113" t="n">
+        <v>15</v>
+      </c>
+      <c r="T113" t="n">
+        <v>13</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="W113" t="n">
+        <v>77</v>
+      </c>
+      <c r="X113" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>5012500</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>31620000</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>70.04761904761905</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>3560714.285714286</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>75.61904761904762</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>76.05882352941177</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>16613235.29411765</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>79.58823529411765</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH113" t="inlineStr"/>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
+      <c r="BM113" t="inlineStr"/>
+      <c r="BN113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M114" t="n">
+        <v>56</v>
+      </c>
+      <c r="N114" t="n">
+        <v>44</v>
+      </c>
+      <c r="O114" t="n">
+        <v>20</v>
+      </c>
+      <c r="P114" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>6</v>
+      </c>
+      <c r="R114" t="n">
+        <v>3</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="n">
+        <v>7</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W114" t="n">
+        <v>77</v>
+      </c>
+      <c r="X114" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>23.31578947368421</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>181.2631578947368</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>30031578.94736842</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>185.6315789473684</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>7406578.947368421</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>192</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>287</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>49600000</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M115" t="n">
+        <v>39</v>
+      </c>
+      <c r="N115" t="n">
+        <v>61</v>
+      </c>
+      <c r="O115" t="n">
+        <v>9</v>
+      </c>
+      <c r="P115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>16</v>
+      </c>
+      <c r="T115" t="n">
+        <v>19</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W115" t="n">
+        <v>77</v>
+      </c>
+      <c r="X115" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC115" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>3172727.272727273</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>2695416.666666667</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>75.20833333333333</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>72.47619047619048</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>5076190.476190476</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>75.80952380952381</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>347</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>224</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M116" t="n">
+        <v>32</v>
+      </c>
+      <c r="N116" t="n">
+        <v>68</v>
+      </c>
+      <c r="O116" t="n">
+        <v>10</v>
+      </c>
+      <c r="P116" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>6</v>
+      </c>
+      <c r="R116" t="n">
+        <v>9</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="n">
+        <v>14</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W116" t="n">
+        <v>77</v>
+      </c>
+      <c r="X116" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC116" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>43272727.27272727</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>3080882.352941176</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>78.95652173913044</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>26208695.65217391</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>258</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>236</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>53800000</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M117" t="n">
+        <v>39</v>
+      </c>
+      <c r="N117" t="n">
+        <v>61</v>
+      </c>
+      <c r="O117" t="n">
+        <v>13</v>
+      </c>
+      <c r="P117" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>5</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="n">
+        <v>9</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W117" t="n">
+        <v>77</v>
+      </c>
+      <c r="X117" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>13710000</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>2866956.52173913</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>22.68181818181818</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>73.13636363636364</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>80.77272727272727</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>355</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>53</v>
+      </c>
+      <c r="N118" t="n">
+        <v>47</v>
+      </c>
+      <c r="O118" t="n">
+        <v>21</v>
+      </c>
+      <c r="P118" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>8</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="n">
+        <v>11</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W118" t="n">
+        <v>77</v>
+      </c>
+      <c r="X118" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>4015909.090909091</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>68.42307692307692</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>3002884.615384615</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>74.65384615384616</v>
+      </c>
+      <c r="AU118" t="inlineStr"/>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr"/>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F119" t="n">
+        <v>6905</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>59</v>
+      </c>
+      <c r="N119" t="n">
+        <v>41</v>
+      </c>
+      <c r="O119" t="n">
+        <v>11</v>
+      </c>
+      <c r="P119" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>5</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7</v>
+      </c>
+      <c r="S119" t="n">
+        <v>13</v>
+      </c>
+      <c r="T119" t="n">
+        <v>17</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W119" t="n">
+        <v>77</v>
+      </c>
+      <c r="X119" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>4894444.444444444</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>24.10526315789474</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>182.8421052631579</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2236842.105263158</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>74.47368421052632</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1538888.888888889</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45516.5625</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>38</v>
+      </c>
+      <c r="N120" t="n">
+        <v>62</v>
+      </c>
+      <c r="O120" t="n">
+        <v>19</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>9</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>20</v>
+      </c>
+      <c r="T120" t="n">
+        <v>9</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W120" t="n">
+        <v>77</v>
+      </c>
+      <c r="X120" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2694444.444444444</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AU120" t="inlineStr"/>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr"/>
+      <c r="BA120" t="inlineStr"/>
+      <c r="BB120" t="inlineStr"/>
+      <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>59</v>
+      </c>
+      <c r="N121" t="n">
+        <v>41</v>
+      </c>
+      <c r="O121" t="n">
+        <v>5</v>
+      </c>
+      <c r="P121" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2</v>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="n">
+        <v>19</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W121" t="n">
+        <v>77</v>
+      </c>
+      <c r="X121" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1597222.222222222</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>980000</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BA121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr"/>
+      <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>60</v>
+      </c>
+      <c r="N122" t="n">
+        <v>40</v>
+      </c>
+      <c r="O122" t="n">
+        <v>8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="n">
+        <v>6</v>
+      </c>
+      <c r="T122" t="n">
+        <v>12</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W122" t="n">
+        <v>77</v>
+      </c>
+      <c r="X122" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>5423684.210526315</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>76.47368421052632</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F123" t="n">
+        <v>14196</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>43</v>
+      </c>
+      <c r="N123" t="n">
+        <v>57</v>
+      </c>
+      <c r="O123" t="n">
+        <v>11</v>
+      </c>
+      <c r="P123" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>3</v>
+      </c>
+      <c r="R123" t="n">
+        <v>5</v>
+      </c>
+      <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>13</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="W123" t="n">
+        <v>77</v>
+      </c>
+      <c r="X123" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2136111.111111111</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1749750</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>70.59090909090909</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>3314318.181818182</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="BA123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr"/>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
+      <c r="BI123" t="inlineStr"/>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
+      <c r="BM123" t="inlineStr"/>
+      <c r="BN123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>47</v>
+      </c>
+      <c r="N124" t="n">
+        <v>53</v>
+      </c>
+      <c r="O124" t="n">
+        <v>17</v>
+      </c>
+      <c r="P124" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>4</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4</v>
+      </c>
+      <c r="S124" t="n">
+        <v>7</v>
+      </c>
+      <c r="T124" t="n">
+        <v>12</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W124" t="n">
+        <v>77</v>
+      </c>
+      <c r="X124" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>22.95238095238095</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>67.04761904761905</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>2280476.19047619</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>24.82608695652174</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>2280434.782608696</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="BA124" t="inlineStr"/>
+      <c r="BB124" t="inlineStr"/>
+      <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+      <c r="BM124" t="inlineStr"/>
+      <c r="BN124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4310</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>38</v>
+      </c>
+      <c r="N125" t="n">
+        <v>62</v>
+      </c>
+      <c r="O125" t="n">
+        <v>9</v>
+      </c>
+      <c r="P125" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>5</v>
+      </c>
+      <c r="R125" t="n">
+        <v>8</v>
+      </c>
+      <c r="S125" t="n">
+        <v>14</v>
+      </c>
+      <c r="T125" t="n">
+        <v>12</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>77</v>
+      </c>
+      <c r="X125" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1888888.888888889</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1217777.777777778</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>66.78947368421052</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1748421.052631579</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BA125" t="inlineStr"/>
+      <c r="BB125" t="inlineStr"/>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F126" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>70</v>
+      </c>
+      <c r="N126" t="n">
+        <v>30</v>
+      </c>
+      <c r="O126" t="n">
+        <v>28</v>
+      </c>
+      <c r="P126" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>6</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W126" t="n">
+        <v>77</v>
+      </c>
+      <c r="X126" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>32290909.09090909</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>82.36363636363636</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>9576250</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>63.85714285714285</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1024642.857142857</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="BA126" t="inlineStr"/>
+      <c r="BB126" t="inlineStr"/>
+      <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
+        <v>57</v>
+      </c>
+      <c r="N127" t="n">
+        <v>43</v>
+      </c>
+      <c r="O127" t="n">
+        <v>22</v>
+      </c>
+      <c r="P127" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>9</v>
+      </c>
+      <c r="T127" t="n">
+        <v>10</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W127" t="n">
+        <v>77</v>
+      </c>
+      <c r="X127" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1133333.333333333</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>181.4090909090909</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2088181.818181818</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1014583.333333333</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+      <c r="BM127" t="inlineStr"/>
+      <c r="BN127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45514.5625</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7048</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>54</v>
+      </c>
+      <c r="N128" t="n">
+        <v>46</v>
+      </c>
+      <c r="O128" t="n">
+        <v>11</v>
+      </c>
+      <c r="P128" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>3</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4</v>
+      </c>
+      <c r="S128" t="n">
+        <v>14</v>
+      </c>
+      <c r="T128" t="n">
+        <v>7</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W128" t="n">
+        <v>77</v>
+      </c>
+      <c r="X128" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>5011111.111111111</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr"/>
+      <c r="AK128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>184.0555555555555</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2776388.888888889</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA128" t="inlineStr"/>
+      <c r="BB128" t="inlineStr"/>
+      <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+      <c r="BM128" t="inlineStr"/>
+      <c r="BN128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>58</v>
+      </c>
+      <c r="N129" t="n">
+        <v>42</v>
+      </c>
+      <c r="O129" t="n">
+        <v>13</v>
+      </c>
+      <c r="P129" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>3</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="n">
+        <v>12</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W129" t="n">
+        <v>77</v>
+      </c>
+      <c r="X129" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>2154545.454545455</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2065217.391304348</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1022500</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="BA129" t="inlineStr"/>
+      <c r="BB129" t="inlineStr"/>
+      <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+      <c r="BM129" t="inlineStr"/>
+      <c r="BN129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>49</v>
+      </c>
+      <c r="N130" t="n">
+        <v>51</v>
+      </c>
+      <c r="O130" t="n">
+        <v>9</v>
+      </c>
+      <c r="P130" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6</v>
+      </c>
+      <c r="S130" t="n">
+        <v>11</v>
+      </c>
+      <c r="T130" t="n">
+        <v>7</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W130" t="n">
+        <v>77</v>
+      </c>
+      <c r="X130" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="BA130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr"/>
+      <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
+      <c r="BM130" t="inlineStr"/>
+      <c r="BN130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11382</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>42</v>
+      </c>
+      <c r="N131" t="n">
+        <v>58</v>
+      </c>
+      <c r="O131" t="n">
+        <v>14</v>
+      </c>
+      <c r="P131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>8</v>
+      </c>
+      <c r="R131" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>13</v>
+      </c>
+      <c r="T131" t="n">
+        <v>14</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W131" t="n">
+        <v>77</v>
+      </c>
+      <c r="X131" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="inlineStr"/>
+      <c r="AK131" t="inlineStr"/>
+      <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr"/>
+      <c r="AN131" t="inlineStr"/>
+      <c r="AO131" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>3056250</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>871875</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
+      <c r="BM131" t="inlineStr"/>
+      <c r="BN131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6840</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>32</v>
+      </c>
+      <c r="N132" t="n">
+        <v>68</v>
+      </c>
+      <c r="O132" t="n">
+        <v>15</v>
+      </c>
+      <c r="P132" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>11</v>
+      </c>
+      <c r="T132" t="n">
+        <v>16</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="W132" t="n">
+        <v>77</v>
+      </c>
+      <c r="X132" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1909090.909090909</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1179687.5</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>23.91666666666667</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>2183333.333333333</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="inlineStr"/>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
+      <c r="BM132" t="inlineStr"/>
+      <c r="BN132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>45</v>
+      </c>
+      <c r="N133" t="n">
+        <v>55</v>
+      </c>
+      <c r="O133" t="n">
+        <v>20</v>
+      </c>
+      <c r="P133" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>12</v>
+      </c>
+      <c r="R133" t="n">
+        <v>4</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="n">
+        <v>13</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="W133" t="n">
+        <v>77</v>
+      </c>
+      <c r="X133" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1646875</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1680555.555555556</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>21.78260869565218</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>63.91304347826087</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1310869.565217391</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>24.42857142857143</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>67.76190476190476</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1782142.857142857</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="BA133" t="inlineStr"/>
+      <c r="BB133" t="inlineStr"/>
+      <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
+      <c r="BH133" t="inlineStr"/>
+      <c r="BI133" t="inlineStr"/>
+      <c r="BJ133" t="inlineStr"/>
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="inlineStr"/>
+      <c r="BM133" t="inlineStr"/>
+      <c r="BN133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>30</v>
+      </c>
+      <c r="N134" t="n">
+        <v>70</v>
+      </c>
+      <c r="O134" t="n">
+        <v>12</v>
+      </c>
+      <c r="P134" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="n">
+        <v>25</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W134" t="n">
+        <v>77</v>
+      </c>
+      <c r="X134" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="inlineStr"/>
+      <c r="AK134" t="inlineStr"/>
+      <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr"/>
+      <c r="AO134" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA134" t="inlineStr"/>
+      <c r="BB134" t="inlineStr"/>
+      <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
+      <c r="BI134" t="inlineStr"/>
+      <c r="BJ134" t="inlineStr"/>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="inlineStr"/>
+      <c r="BM134" t="inlineStr"/>
+      <c r="BN134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F135" t="n">
+        <v>20957</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>56</v>
+      </c>
+      <c r="N135" t="n">
+        <v>44</v>
+      </c>
+      <c r="O135" t="n">
+        <v>16</v>
+      </c>
+      <c r="P135" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>4</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
+        <v>20</v>
+      </c>
+      <c r="T135" t="n">
+        <v>14</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W135" t="n">
+        <v>77</v>
+      </c>
+      <c r="X135" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AI135" t="inlineStr"/>
+      <c r="AJ135" t="inlineStr"/>
+      <c r="AK135" t="inlineStr"/>
+      <c r="AL135" t="inlineStr"/>
+      <c r="AM135" t="inlineStr"/>
+      <c r="AN135" t="inlineStr"/>
+      <c r="AO135" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>181.68</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>934600</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="AU135" t="inlineStr"/>
+      <c r="AV135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr"/>
+      <c r="BA135" t="inlineStr"/>
+      <c r="BB135" t="inlineStr"/>
+      <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr"/>
+      <c r="BI135" t="inlineStr"/>
+      <c r="BJ135" t="inlineStr"/>
+      <c r="BK135" t="inlineStr"/>
+      <c r="BL135" t="inlineStr"/>
+      <c r="BM135" t="inlineStr"/>
+      <c r="BN135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F136" t="n">
+        <v>8770</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>54</v>
+      </c>
+      <c r="N136" t="n">
+        <v>46</v>
+      </c>
+      <c r="O136" t="n">
+        <v>19</v>
+      </c>
+      <c r="P136" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="n">
+        <v>22</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W136" t="n">
+        <v>77</v>
+      </c>
+      <c r="X136" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1563888.888888889</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>184.2380952380952</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>186.0588235294118</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1320588.235294118</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BA136" t="inlineStr"/>
+      <c r="BB136" t="inlineStr"/>
+      <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
+      <c r="BI136" t="inlineStr"/>
+      <c r="BJ136" t="inlineStr"/>
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="inlineStr"/>
+      <c r="BM136" t="inlineStr"/>
+      <c r="BN136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12509</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>70</v>
+      </c>
+      <c r="N137" t="n">
+        <v>30</v>
+      </c>
+      <c r="O137" t="n">
+        <v>15</v>
+      </c>
+      <c r="P137" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>7</v>
+      </c>
+      <c r="R137" t="n">
+        <v>3</v>
+      </c>
+      <c r="S137" t="n">
+        <v>23</v>
+      </c>
+      <c r="T137" t="n">
+        <v>12</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W137" t="n">
+        <v>77</v>
+      </c>
+      <c r="X137" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2572222.222222222</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>22.72222222222222</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>178.0555555555555</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1901388.888888889</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>74.61111111111111</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>844473.6842105263</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="BA137" t="inlineStr"/>
+      <c r="BB137" t="inlineStr"/>
+      <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
+      <c r="BI137" t="inlineStr"/>
+      <c r="BJ137" t="inlineStr"/>
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="inlineStr"/>
+      <c r="BM137" t="inlineStr"/>
+      <c r="BN137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>68</v>
+      </c>
+      <c r="N138" t="n">
+        <v>32</v>
+      </c>
+      <c r="O138" t="n">
+        <v>9</v>
+      </c>
+      <c r="P138" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="n">
+        <v>15</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W138" t="n">
+        <v>77</v>
+      </c>
+      <c r="X138" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1190909.090909091</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>65.44444444444444</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>65.61538461538461</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1168846.153846154</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>70.46153846153847</v>
+      </c>
+      <c r="BA138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr"/>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="inlineStr"/>
+      <c r="BJ138" t="inlineStr"/>
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="inlineStr"/>
+      <c r="BM138" t="inlineStr"/>
+      <c r="BN138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>37</v>
+      </c>
+      <c r="N139" t="n">
+        <v>63</v>
+      </c>
+      <c r="O139" t="n">
+        <v>18</v>
+      </c>
+      <c r="P139" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>6</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="n">
+        <v>10</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W139" t="n">
+        <v>77</v>
+      </c>
+      <c r="X139" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>181.2142857142857</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1164285.714285714</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA139" t="inlineStr"/>
+      <c r="BB139" t="inlineStr"/>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
+      <c r="BI139" t="inlineStr"/>
+      <c r="BJ139" t="inlineStr"/>
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="inlineStr"/>
+      <c r="BM139" t="inlineStr"/>
+      <c r="BN139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M140" t="n">
+        <v>55</v>
+      </c>
+      <c r="N140" t="n">
+        <v>45</v>
+      </c>
+      <c r="O140" t="n">
+        <v>12</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>9</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>12</v>
+      </c>
+      <c r="T140" t="n">
+        <v>6</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="W140" t="n">
+        <v>77</v>
+      </c>
+      <c r="X140" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>28437500</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>5062500</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>18218750</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>185</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>3786250</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>321</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>45523.5625</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F141" t="n">
+        <v>28719</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M141" t="n">
+        <v>47</v>
+      </c>
+      <c r="N141" t="n">
+        <v>53</v>
+      </c>
+      <c r="O141" t="n">
+        <v>19</v>
+      </c>
+      <c r="P141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>5</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="n">
+        <v>24</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="W141" t="n">
+        <v>77</v>
+      </c>
+      <c r="X141" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC141" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>188</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>22.68421052631579</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>181.6842105263158</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2952631.578947369</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>75.31578947368421</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>185.7692307692308</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>9996923.076923076</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>78.76923076923077</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>215</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>314</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN141"/>
+  <dimension ref="A1:BN145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29929,6 +29929,804 @@
         <v>329</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L142" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M142" t="n">
+        <v>34</v>
+      </c>
+      <c r="N142" t="n">
+        <v>66</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7</v>
+      </c>
+      <c r="P142" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>6</v>
+      </c>
+      <c r="R142" t="n">
+        <v>5</v>
+      </c>
+      <c r="S142" t="n">
+        <v>8</v>
+      </c>
+      <c r="T142" t="n">
+        <v>10</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="W142" t="n">
+        <v>77</v>
+      </c>
+      <c r="X142" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>44650000</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>3159500</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>78.13333333333334</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>22640000</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>354</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>365</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>192</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>77</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M143" t="n">
+        <v>35</v>
+      </c>
+      <c r="N143" t="n">
+        <v>65</v>
+      </c>
+      <c r="O143" t="n">
+        <v>8</v>
+      </c>
+      <c r="P143" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>3</v>
+      </c>
+      <c r="R143" t="n">
+        <v>5</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="n">
+        <v>10</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="W143" t="n">
+        <v>77</v>
+      </c>
+      <c r="X143" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>4430000</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>19270000</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>71.82608695652173</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>3582608.695652174</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>75.04347826086956</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>25.04166666666667</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>182.0416666666667</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>74.54166666666667</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>11072916.66666667</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>78.70833333333333</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>45528.60416666666</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>40</v>
+      </c>
+      <c r="N144" t="n">
+        <v>60</v>
+      </c>
+      <c r="O144" t="n">
+        <v>17</v>
+      </c>
+      <c r="P144" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>7</v>
+      </c>
+      <c r="R144" t="n">
+        <v>3</v>
+      </c>
+      <c r="S144" t="n">
+        <v>15</v>
+      </c>
+      <c r="T144" t="n">
+        <v>9</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>77</v>
+      </c>
+      <c r="X144" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1108500</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="inlineStr"/>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="n">
+        <v>26.38095238095238</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>185.5238095238095</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>66.57142857142857</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1147619.047619048</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>23.23076923076923</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>178.3846153846154</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>67.07692307692308</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1959615.384615385</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>74.53846153846153</v>
+      </c>
+      <c r="BA144" t="inlineStr"/>
+      <c r="BB144" t="inlineStr"/>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
+      <c r="BI144" t="inlineStr"/>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="inlineStr"/>
+      <c r="BM144" t="inlineStr"/>
+      <c r="BN144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>21092</v>
+      </c>
+      <c r="F145" t="n">
+        <v>10248</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>41</v>
+      </c>
+      <c r="N145" t="n">
+        <v>59</v>
+      </c>
+      <c r="O145" t="n">
+        <v>16</v>
+      </c>
+      <c r="P145" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>5</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4</v>
+      </c>
+      <c r="S145" t="n">
+        <v>20</v>
+      </c>
+      <c r="T145" t="n">
+        <v>13</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W145" t="n">
+        <v>77</v>
+      </c>
+      <c r="X145" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC145" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>1387500</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>26.95454545454545</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1215681.818181818</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>181.7826086956522</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>64.73913043478261</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>1059347.826086957</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>69.47826086956522</v>
+      </c>
+      <c r="BA145" t="inlineStr"/>
+      <c r="BB145" t="inlineStr"/>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr"/>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="inlineStr"/>
+      <c r="BM145" t="inlineStr"/>
+      <c r="BN145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN145"/>
+  <dimension ref="A1:BN155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30727,6 +30727,1954 @@
       <c r="BM145" t="inlineStr"/>
       <c r="BN145" t="inlineStr"/>
     </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>45529.5625</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M146" t="n">
+        <v>56</v>
+      </c>
+      <c r="N146" t="n">
+        <v>44</v>
+      </c>
+      <c r="O146" t="n">
+        <v>12</v>
+      </c>
+      <c r="P146" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>8</v>
+      </c>
+      <c r="R146" t="n">
+        <v>4</v>
+      </c>
+      <c r="S146" t="n">
+        <v>13</v>
+      </c>
+      <c r="T146" t="n">
+        <v>19</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>77</v>
+      </c>
+      <c r="X146" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC146" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>13922222.22222222</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>80.33333333333333</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>74.63636363636364</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>23.60869565217391</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>182.0869565217391</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.347826086956522</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>74.21739130434783</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>11895652.17391304</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>80.56521739130434</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>23.52173913043478</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>184.1304347826087</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>66.47826086956522</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>1631304.347826087</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>73.65217391304348</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>155</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>284</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>14625000</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>45529.5625</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F147" t="n">
+        <v>20451</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L147" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M147" t="n">
+        <v>43</v>
+      </c>
+      <c r="N147" t="n">
+        <v>57</v>
+      </c>
+      <c r="O147" t="n">
+        <v>13</v>
+      </c>
+      <c r="P147" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>6</v>
+      </c>
+      <c r="R147" t="n">
+        <v>8</v>
+      </c>
+      <c r="S147" t="n">
+        <v>8</v>
+      </c>
+      <c r="T147" t="n">
+        <v>13</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>77</v>
+      </c>
+      <c r="X147" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>185.7777777777778</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>75.44444444444444</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>10711111.11111111</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>188</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>23.29411764705882</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>70.41176470588235</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>5413235.294117647</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>76.23529411764706</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>188.1111111111111</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>10795555.55555556</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>79.11111111111111</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>47500000</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>244</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>314</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45528.65625</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M148" t="n">
+        <v>61</v>
+      </c>
+      <c r="N148" t="n">
+        <v>39</v>
+      </c>
+      <c r="O148" t="n">
+        <v>11</v>
+      </c>
+      <c r="P148" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>3</v>
+      </c>
+      <c r="R148" t="n">
+        <v>4</v>
+      </c>
+      <c r="S148" t="n">
+        <v>9</v>
+      </c>
+      <c r="T148" t="n">
+        <v>12</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>77</v>
+      </c>
+      <c r="X148" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AC148" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>38100000</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>5477777.777777778</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>78.11111111111111</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>26.07692307692308</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>184.2692307692308</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.807692307692308</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>78.76923076923077</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>23684615.38461538</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>81.84615384615384</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>183.9375</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>2718750</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>242</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>140300000</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>249</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>215</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>45528.65625</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M149" t="n">
+        <v>70</v>
+      </c>
+      <c r="N149" t="n">
+        <v>30</v>
+      </c>
+      <c r="O149" t="n">
+        <v>9</v>
+      </c>
+      <c r="P149" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1</v>
+      </c>
+      <c r="S149" t="n">
+        <v>6</v>
+      </c>
+      <c r="T149" t="n">
+        <v>17</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="W149" t="n">
+        <v>77</v>
+      </c>
+      <c r="X149" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AC149" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>5230000</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>72.40909090909091</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>4209090.909090909</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>76.72727272727273</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>185.12</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>3603000</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>302</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>303</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>190</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>125</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>58</v>
+      </c>
+      <c r="N150" t="n">
+        <v>42</v>
+      </c>
+      <c r="O150" t="n">
+        <v>18</v>
+      </c>
+      <c r="P150" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>6</v>
+      </c>
+      <c r="R150" t="n">
+        <v>3</v>
+      </c>
+      <c r="S150" t="n">
+        <v>17</v>
+      </c>
+      <c r="T150" t="n">
+        <v>8</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W150" t="n">
+        <v>77</v>
+      </c>
+      <c r="X150" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC150" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>181.3809523809524</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1091666.666666667</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>65.53846153846153</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>909615.3846153846</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>69.92307692307692</v>
+      </c>
+      <c r="BA150" t="inlineStr"/>
+      <c r="BB150" t="inlineStr"/>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr"/>
+      <c r="BI150" t="inlineStr"/>
+      <c r="BJ150" t="inlineStr"/>
+      <c r="BK150" t="inlineStr"/>
+      <c r="BL150" t="inlineStr"/>
+      <c r="BM150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>63</v>
+      </c>
+      <c r="N151" t="n">
+        <v>37</v>
+      </c>
+      <c r="O151" t="n">
+        <v>16</v>
+      </c>
+      <c r="P151" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>4</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3</v>
+      </c>
+      <c r="S151" t="n">
+        <v>8</v>
+      </c>
+      <c r="T151" t="n">
+        <v>14</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W151" t="n">
+        <v>77</v>
+      </c>
+      <c r="X151" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1772727.272727273</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="n">
+        <v>24.54166666666667</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>69.04166666666667</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>2191666.666666667</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="BA151" t="inlineStr"/>
+      <c r="BB151" t="inlineStr"/>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
+      <c r="BI151" t="inlineStr"/>
+      <c r="BJ151" t="inlineStr"/>
+      <c r="BK151" t="inlineStr"/>
+      <c r="BL151" t="inlineStr"/>
+      <c r="BM151" t="inlineStr"/>
+      <c r="BN151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F152" t="n">
+        <v>8811</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>34</v>
+      </c>
+      <c r="N152" t="n">
+        <v>66</v>
+      </c>
+      <c r="O152" t="n">
+        <v>11</v>
+      </c>
+      <c r="P152" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>4</v>
+      </c>
+      <c r="R152" t="n">
+        <v>4</v>
+      </c>
+      <c r="S152" t="n">
+        <v>8</v>
+      </c>
+      <c r="T152" t="n">
+        <v>20</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W152" t="n">
+        <v>77</v>
+      </c>
+      <c r="X152" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC152" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>67.36363636363636</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1615909.090909091</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>66.40909090909091</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1995454.545454545</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>73.40909090909091</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>24.04545454545455</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>2620454.545454545</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>75.86363636363636</v>
+      </c>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
+      <c r="BI152" t="inlineStr"/>
+      <c r="BJ152" t="inlineStr"/>
+      <c r="BK152" t="inlineStr"/>
+      <c r="BL152" t="inlineStr"/>
+      <c r="BM152" t="inlineStr"/>
+      <c r="BN152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F153" t="n">
+        <v>23061</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>54</v>
+      </c>
+      <c r="N153" t="n">
+        <v>46</v>
+      </c>
+      <c r="O153" t="n">
+        <v>9</v>
+      </c>
+      <c r="P153" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>1</v>
+      </c>
+      <c r="R153" t="n">
+        <v>4</v>
+      </c>
+      <c r="S153" t="n">
+        <v>11</v>
+      </c>
+      <c r="T153" t="n">
+        <v>12</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W153" t="n">
+        <v>77</v>
+      </c>
+      <c r="X153" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>1658333.333333333</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>24.15789473684211</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>183.5263157894737</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>67.36842105263158</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1738157.894736842</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>65.93333333333334</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>1074333.333333333</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BA153" t="inlineStr"/>
+      <c r="BB153" t="inlineStr"/>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
+      <c r="BI153" t="inlineStr"/>
+      <c r="BJ153" t="inlineStr"/>
+      <c r="BK153" t="inlineStr"/>
+      <c r="BL153" t="inlineStr"/>
+      <c r="BM153" t="inlineStr"/>
+      <c r="BN153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F154" t="n">
+        <v>5017</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>36</v>
+      </c>
+      <c r="N154" t="n">
+        <v>64</v>
+      </c>
+      <c r="O154" t="n">
+        <v>13</v>
+      </c>
+      <c r="P154" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>6</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="n">
+        <v>14</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W154" t="n">
+        <v>77</v>
+      </c>
+      <c r="X154" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr"/>
+      <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr"/>
+      <c r="AO154" t="n">
+        <v>22.16666666666667</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1955555.555555556</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>76.72222222222223</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>1672222.222222222</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="BA154" t="inlineStr"/>
+      <c r="BB154" t="inlineStr"/>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
+      <c r="BI154" t="inlineStr"/>
+      <c r="BJ154" t="inlineStr"/>
+      <c r="BK154" t="inlineStr"/>
+      <c r="BL154" t="inlineStr"/>
+      <c r="BM154" t="inlineStr"/>
+      <c r="BN154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>52</v>
+      </c>
+      <c r="N155" t="n">
+        <v>48</v>
+      </c>
+      <c r="O155" t="n">
+        <v>12</v>
+      </c>
+      <c r="P155" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>6</v>
+      </c>
+      <c r="R155" t="n">
+        <v>3</v>
+      </c>
+      <c r="S155" t="n">
+        <v>19</v>
+      </c>
+      <c r="T155" t="n">
+        <v>18</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="W155" t="n">
+        <v>77</v>
+      </c>
+      <c r="X155" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1516666.666666667</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>23.77272727272727</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>184.3181818181818</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>65.04545454545455</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1237500</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>22.23809523809524</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>183.8571428571429</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>64.47619047619048</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1373809.523809524</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="BA155" t="inlineStr"/>
+      <c r="BB155" t="inlineStr"/>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
+      <c r="BI155" t="inlineStr"/>
+      <c r="BJ155" t="inlineStr"/>
+      <c r="BK155" t="inlineStr"/>
+      <c r="BL155" t="inlineStr"/>
+      <c r="BM155" t="inlineStr"/>
+      <c r="BN155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN155"/>
+  <dimension ref="A1:BN161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32675,6 +32675,1190 @@
       <c r="BM155" t="inlineStr"/>
       <c r="BN155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F156" t="n">
+        <v>29575</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M156" t="n">
+        <v>40</v>
+      </c>
+      <c r="N156" t="n">
+        <v>60</v>
+      </c>
+      <c r="O156" t="n">
+        <v>7</v>
+      </c>
+      <c r="P156" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>1</v>
+      </c>
+      <c r="R156" t="n">
+        <v>5</v>
+      </c>
+      <c r="S156" t="n">
+        <v>8</v>
+      </c>
+      <c r="T156" t="n">
+        <v>8</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="W156" t="n">
+        <v>77</v>
+      </c>
+      <c r="X156" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AC156" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>4955555.555555556</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>185.625</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>30562500</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>183.1875</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>70.3125</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>2892187.5</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>75.83333333333333</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>11708333.33333333</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>78.66666666666667</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>141</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>148</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>320</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F157" t="n">
+        <v>16365</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M157" t="n">
+        <v>47</v>
+      </c>
+      <c r="N157" t="n">
+        <v>53</v>
+      </c>
+      <c r="O157" t="n">
+        <v>11</v>
+      </c>
+      <c r="P157" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>5</v>
+      </c>
+      <c r="R157" t="n">
+        <v>4</v>
+      </c>
+      <c r="S157" t="n">
+        <v>12</v>
+      </c>
+      <c r="T157" t="n">
+        <v>10</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="W157" t="n">
+        <v>77</v>
+      </c>
+      <c r="X157" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC157" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>4990909.090909091</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>76.36363636363636</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>184.6296296296296</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>69.85185185185185</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>2369444.444444444</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>73.81481481481481</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>186.8571428571429</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>3926071.428571429</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>175</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>67</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>142</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F158" t="n">
+        <v>67517</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M158" t="n">
+        <v>73</v>
+      </c>
+      <c r="N158" t="n">
+        <v>27</v>
+      </c>
+      <c r="O158" t="n">
+        <v>26</v>
+      </c>
+      <c r="P158" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>7</v>
+      </c>
+      <c r="R158" t="n">
+        <v>4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="n">
+        <v>11</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="W158" t="n">
+        <v>77</v>
+      </c>
+      <c r="X158" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC158" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>24755555.55555556</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>81.11111111111111</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>3327272.727272727</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>76.72727272727273</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>23.94736842105263</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>180.3684210526316</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>74.73684210526316</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>12918421.05263158</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>80.36842105263158</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>181.9583333333333</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>68</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>2771458.333333333</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>75.04166666666667</v>
+      </c>
+      <c r="BA158" t="inlineStr"/>
+      <c r="BB158" t="inlineStr"/>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr"/>
+      <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>347</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F159" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M159" t="n">
+        <v>39</v>
+      </c>
+      <c r="N159" t="n">
+        <v>61</v>
+      </c>
+      <c r="O159" t="n">
+        <v>16</v>
+      </c>
+      <c r="P159" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>5</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2</v>
+      </c>
+      <c r="S159" t="n">
+        <v>11</v>
+      </c>
+      <c r="T159" t="n">
+        <v>17</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="W159" t="n">
+        <v>77</v>
+      </c>
+      <c r="X159" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC159" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>80.45454545454545</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>31700000</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>82.18181818181819</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>185.9090909090909</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>75.54545454545455</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>8472727.272727273</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>181.8666666666667</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>10781666.66666667</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>77.86666666666666</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>185.68</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>5754000</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="BA159" t="inlineStr"/>
+      <c r="BB159" t="inlineStr"/>
+      <c r="BC159" t="inlineStr"/>
+      <c r="BD159" t="inlineStr"/>
+      <c r="BE159" t="inlineStr"/>
+      <c r="BF159" t="inlineStr"/>
+      <c r="BG159" t="inlineStr"/>
+      <c r="BH159" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>216</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>45529.64583333334</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F160" t="n">
+        <v>11788</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>52</v>
+      </c>
+      <c r="N160" t="n">
+        <v>48</v>
+      </c>
+      <c r="O160" t="n">
+        <v>11</v>
+      </c>
+      <c r="P160" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>2</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2</v>
+      </c>
+      <c r="S160" t="n">
+        <v>14</v>
+      </c>
+      <c r="T160" t="n">
+        <v>9</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W160" t="n">
+        <v>77</v>
+      </c>
+      <c r="X160" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr"/>
+      <c r="AO160" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>184.2857142857143</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>65.71428571428571</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>70.57142857142857</v>
+      </c>
+      <c r="AU160" t="inlineStr"/>
+      <c r="AV160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr"/>
+      <c r="AX160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr"/>
+      <c r="BA160" t="inlineStr"/>
+      <c r="BB160" t="inlineStr"/>
+      <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="inlineStr"/>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr"/>
+      <c r="BH160" t="inlineStr"/>
+      <c r="BI160" t="inlineStr"/>
+      <c r="BJ160" t="inlineStr"/>
+      <c r="BK160" t="inlineStr"/>
+      <c r="BL160" t="inlineStr"/>
+      <c r="BM160" t="inlineStr"/>
+      <c r="BN160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>45529.64583333334</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>5423</v>
+      </c>
+      <c r="F161" t="n">
+        <v>8262</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>53</v>
+      </c>
+      <c r="N161" t="n">
+        <v>47</v>
+      </c>
+      <c r="O161" t="n">
+        <v>9</v>
+      </c>
+      <c r="P161" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>6</v>
+      </c>
+      <c r="R161" t="n">
+        <v>10</v>
+      </c>
+      <c r="S161" t="n">
+        <v>23</v>
+      </c>
+      <c r="T161" t="n">
+        <v>7</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W161" t="n">
+        <v>77</v>
+      </c>
+      <c r="X161" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1317500</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>30.14285714285714</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1157142.857142857</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="BA161" t="inlineStr"/>
+      <c r="BB161" t="inlineStr"/>
+      <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr"/>
+      <c r="BH161" t="inlineStr"/>
+      <c r="BI161" t="inlineStr"/>
+      <c r="BJ161" t="inlineStr"/>
+      <c r="BK161" t="inlineStr"/>
+      <c r="BL161" t="inlineStr"/>
+      <c r="BM161" t="inlineStr"/>
+      <c r="BN161" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN161"/>
+  <dimension ref="A1:BN173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33859,6 +33859,2230 @@
       <c r="BM161" t="inlineStr"/>
       <c r="BN161" t="inlineStr"/>
     </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M162" t="n">
+        <v>54</v>
+      </c>
+      <c r="N162" t="n">
+        <v>46</v>
+      </c>
+      <c r="O162" t="n">
+        <v>13</v>
+      </c>
+      <c r="P162" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>5</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>6</v>
+      </c>
+      <c r="T162" t="n">
+        <v>15</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="W162" t="n">
+        <v>77</v>
+      </c>
+      <c r="X162" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC162" t="n">
+        <v>28.81818181818182</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2.636363636363636</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>45181818.18181818</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>85.27272727272727</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>26.08333333333333</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>184.4166666666667</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>29945833.33333333</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>82.70833333333333</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>186.2307692307692</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>1.615384615384615</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>76.92307692307692</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>13420000</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>79.53846153846153</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>72</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>385</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>81300000</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M163" t="n">
+        <v>42</v>
+      </c>
+      <c r="N163" t="n">
+        <v>58</v>
+      </c>
+      <c r="O163" t="n">
+        <v>13</v>
+      </c>
+      <c r="P163" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>4</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6</v>
+      </c>
+      <c r="S163" t="n">
+        <v>7</v>
+      </c>
+      <c r="T163" t="n">
+        <v>15</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W163" t="n">
+        <v>77</v>
+      </c>
+      <c r="X163" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC163" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>184.9090909090909</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2709090.909090909</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>11237500</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>25.21052631578947</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>68.05263157894737</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1943157.894736842</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>73.89473684210526</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>183.6190476190476</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>5953571.428571428</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>76.38095238095238</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>47500000</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F164" t="n">
+        <v>11870</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="n">
+        <v>34</v>
+      </c>
+      <c r="N164" t="n">
+        <v>66</v>
+      </c>
+      <c r="O164" t="n">
+        <v>12</v>
+      </c>
+      <c r="P164" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>5</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="n">
+        <v>15</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W164" t="n">
+        <v>77</v>
+      </c>
+      <c r="X164" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>66.55555555555556</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1443750</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>183.1875</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>66.0625</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>1164062.5</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>69.6875</v>
+      </c>
+      <c r="BA164" t="inlineStr"/>
+      <c r="BB164" t="inlineStr"/>
+      <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr"/>
+      <c r="BH164" t="inlineStr"/>
+      <c r="BI164" t="inlineStr"/>
+      <c r="BJ164" t="inlineStr"/>
+      <c r="BK164" t="inlineStr"/>
+      <c r="BL164" t="inlineStr"/>
+      <c r="BM164" t="inlineStr"/>
+      <c r="BN164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F165" t="n">
+        <v>8006</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>61</v>
+      </c>
+      <c r="N165" t="n">
+        <v>39</v>
+      </c>
+      <c r="O165" t="n">
+        <v>14</v>
+      </c>
+      <c r="P165" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>2</v>
+      </c>
+      <c r="R165" t="n">
+        <v>4</v>
+      </c>
+      <c r="S165" t="n">
+        <v>13</v>
+      </c>
+      <c r="T165" t="n">
+        <v>13</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W165" t="n">
+        <v>77</v>
+      </c>
+      <c r="X165" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1495000</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>63.83333333333334</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1116666.666666667</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>1251250</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="BA165" t="inlineStr"/>
+      <c r="BB165" t="inlineStr"/>
+      <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr"/>
+      <c r="BH165" t="inlineStr"/>
+      <c r="BI165" t="inlineStr"/>
+      <c r="BJ165" t="inlineStr"/>
+      <c r="BK165" t="inlineStr"/>
+      <c r="BL165" t="inlineStr"/>
+      <c r="BM165" t="inlineStr"/>
+      <c r="BN165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio leonardo garilli
+  piacenza </t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>21668</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1480</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>33</v>
+      </c>
+      <c r="N166" t="n">
+        <v>67</v>
+      </c>
+      <c r="O166" t="n">
+        <v>6</v>
+      </c>
+      <c r="P166" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>3</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="n">
+        <v>26</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W166" t="n">
+        <v>77</v>
+      </c>
+      <c r="X166" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr"/>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr"/>
+      <c r="AO166" t="inlineStr"/>
+      <c r="AP166" t="inlineStr"/>
+      <c r="AQ166" t="inlineStr"/>
+      <c r="AR166" t="inlineStr"/>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AU166" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA166" t="inlineStr"/>
+      <c r="BB166" t="inlineStr"/>
+      <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr"/>
+      <c r="BH166" t="inlineStr"/>
+      <c r="BI166" t="inlineStr"/>
+      <c r="BJ166" t="inlineStr"/>
+      <c r="BK166" t="inlineStr"/>
+      <c r="BL166" t="inlineStr"/>
+      <c r="BM166" t="inlineStr"/>
+      <c r="BN166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F167" t="n">
+        <v>15733</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>57</v>
+      </c>
+      <c r="N167" t="n">
+        <v>43</v>
+      </c>
+      <c r="O167" t="n">
+        <v>26</v>
+      </c>
+      <c r="P167" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>4</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2</v>
+      </c>
+      <c r="S167" t="n">
+        <v>11</v>
+      </c>
+      <c r="T167" t="n">
+        <v>12</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W167" t="n">
+        <v>77</v>
+      </c>
+      <c r="X167" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC167" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1509090.909090909</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>3562500</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>25.73913043478261</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>177.9565217391304</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>64.52173913043478</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>996304.3478260869</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>69.1304347826087</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>1935000</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="BA167" t="inlineStr"/>
+      <c r="BB167" t="inlineStr"/>
+      <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr"/>
+      <c r="BH167" t="inlineStr"/>
+      <c r="BI167" t="inlineStr"/>
+      <c r="BJ167" t="inlineStr"/>
+      <c r="BK167" t="inlineStr"/>
+      <c r="BL167" t="inlineStr"/>
+      <c r="BM167" t="inlineStr"/>
+      <c r="BN167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monaldi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1987</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>50</v>
+      </c>
+      <c r="N168" t="n">
+        <v>50</v>
+      </c>
+      <c r="O168" t="n">
+        <v>12</v>
+      </c>
+      <c r="P168" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>3</v>
+      </c>
+      <c r="R168" t="n">
+        <v>4</v>
+      </c>
+      <c r="S168" t="n">
+        <v>16</v>
+      </c>
+      <c r="T168" t="n">
+        <v>13</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W168" t="n">
+        <v>77</v>
+      </c>
+      <c r="X168" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>903500</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>62.16666666666666</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>929166.6666666666</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>1346250</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA168" t="inlineStr"/>
+      <c r="BB168" t="inlineStr"/>
+      <c r="BC168" t="inlineStr"/>
+      <c r="BD168" t="inlineStr"/>
+      <c r="BE168" t="inlineStr"/>
+      <c r="BF168" t="inlineStr"/>
+      <c r="BG168" t="inlineStr"/>
+      <c r="BH168" t="inlineStr"/>
+      <c r="BI168" t="inlineStr"/>
+      <c r="BJ168" t="inlineStr"/>
+      <c r="BK168" t="inlineStr"/>
+      <c r="BL168" t="inlineStr"/>
+      <c r="BM168" t="inlineStr"/>
+      <c r="BN168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F169" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>52</v>
+      </c>
+      <c r="N169" t="n">
+        <v>48</v>
+      </c>
+      <c r="O169" t="n">
+        <v>9</v>
+      </c>
+      <c r="P169" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>4</v>
+      </c>
+      <c r="R169" t="n">
+        <v>1</v>
+      </c>
+      <c r="S169" t="n">
+        <v>14</v>
+      </c>
+      <c r="T169" t="n">
+        <v>18</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W169" t="n">
+        <v>77</v>
+      </c>
+      <c r="X169" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1790000</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>25.23809523809524</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>181.952380952381</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1007142.857142857</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>70.38095238095238</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>24.29166666666667</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>67.04166666666667</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>1760416.666666667</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>71.58333333333333</v>
+      </c>
+      <c r="BA169" t="inlineStr"/>
+      <c r="BB169" t="inlineStr"/>
+      <c r="BC169" t="inlineStr"/>
+      <c r="BD169" t="inlineStr"/>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
+      <c r="BG169" t="inlineStr"/>
+      <c r="BH169" t="inlineStr"/>
+      <c r="BI169" t="inlineStr"/>
+      <c r="BJ169" t="inlineStr"/>
+      <c r="BK169" t="inlineStr"/>
+      <c r="BL169" t="inlineStr"/>
+      <c r="BM169" t="inlineStr"/>
+      <c r="BN169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F170" t="n">
+        <v>9394</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>64</v>
+      </c>
+      <c r="N170" t="n">
+        <v>36</v>
+      </c>
+      <c r="O170" t="n">
+        <v>18</v>
+      </c>
+      <c r="P170" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>4</v>
+      </c>
+      <c r="R170" t="n">
+        <v>3</v>
+      </c>
+      <c r="S170" t="n">
+        <v>14</v>
+      </c>
+      <c r="T170" t="n">
+        <v>21</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W170" t="n">
+        <v>77</v>
+      </c>
+      <c r="X170" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC170" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>2818181.818181818</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1972000</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>181.4285714285714</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>69.95238095238095</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>2583333.333333333</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>74.0952380952381</v>
+      </c>
+      <c r="BA170" t="inlineStr"/>
+      <c r="BB170" t="inlineStr"/>
+      <c r="BC170" t="inlineStr"/>
+      <c r="BD170" t="inlineStr"/>
+      <c r="BE170" t="inlineStr"/>
+      <c r="BF170" t="inlineStr"/>
+      <c r="BG170" t="inlineStr"/>
+      <c r="BH170" t="inlineStr"/>
+      <c r="BI170" t="inlineStr"/>
+      <c r="BJ170" t="inlineStr"/>
+      <c r="BK170" t="inlineStr"/>
+      <c r="BL170" t="inlineStr"/>
+      <c r="BM170" t="inlineStr"/>
+      <c r="BN170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F171" t="n">
+        <v>9841</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>48</v>
+      </c>
+      <c r="N171" t="n">
+        <v>52</v>
+      </c>
+      <c r="O171" t="n">
+        <v>12</v>
+      </c>
+      <c r="P171" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>3</v>
+      </c>
+      <c r="S171" t="n">
+        <v>16</v>
+      </c>
+      <c r="T171" t="n">
+        <v>13</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W171" t="n">
+        <v>77</v>
+      </c>
+      <c r="X171" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1590000</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>21.82608695652174</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>185.0434782608696</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>64.1304347826087</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1358695.652173913</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>25.91304347826087</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>181.5652173913043</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>65.30434782608695</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>1058695.652173913</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>69.47826086956522</v>
+      </c>
+      <c r="BA171" t="inlineStr"/>
+      <c r="BB171" t="inlineStr"/>
+      <c r="BC171" t="inlineStr"/>
+      <c r="BD171" t="inlineStr"/>
+      <c r="BE171" t="inlineStr"/>
+      <c r="BF171" t="inlineStr"/>
+      <c r="BG171" t="inlineStr"/>
+      <c r="BH171" t="inlineStr"/>
+      <c r="BI171" t="inlineStr"/>
+      <c r="BJ171" t="inlineStr"/>
+      <c r="BK171" t="inlineStr"/>
+      <c r="BL171" t="inlineStr"/>
+      <c r="BM171" t="inlineStr"/>
+      <c r="BN171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F172" t="n">
+        <v>9252</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>39</v>
+      </c>
+      <c r="N172" t="n">
+        <v>61</v>
+      </c>
+      <c r="O172" t="n">
+        <v>11</v>
+      </c>
+      <c r="P172" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>5</v>
+      </c>
+      <c r="R172" t="n">
+        <v>4</v>
+      </c>
+      <c r="S172" t="n">
+        <v>16</v>
+      </c>
+      <c r="T172" t="n">
+        <v>14</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="W172" t="n">
+        <v>77</v>
+      </c>
+      <c r="X172" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AC172" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1063888.888888889</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>25.68421052631579</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>181.7894736842105</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>63.89473684210526</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1174736.842105263</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>24.19047619047619</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>182.7142857142857</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>64.76190476190476</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>1086904.761904762</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>71.47619047619048</v>
+      </c>
+      <c r="BA172" t="inlineStr"/>
+      <c r="BB172" t="inlineStr"/>
+      <c r="BC172" t="inlineStr"/>
+      <c r="BD172" t="inlineStr"/>
+      <c r="BE172" t="inlineStr"/>
+      <c r="BF172" t="inlineStr"/>
+      <c r="BG172" t="inlineStr"/>
+      <c r="BH172" t="inlineStr"/>
+      <c r="BI172" t="inlineStr"/>
+      <c r="BJ172" t="inlineStr"/>
+      <c r="BK172" t="inlineStr"/>
+      <c r="BL172" t="inlineStr"/>
+      <c r="BM172" t="inlineStr"/>
+      <c r="BN172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F173" t="n">
+        <v>15683</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>58</v>
+      </c>
+      <c r="N173" t="n">
+        <v>42</v>
+      </c>
+      <c r="O173" t="n">
+        <v>24</v>
+      </c>
+      <c r="P173" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>8</v>
+      </c>
+      <c r="R173" t="n">
+        <v>4</v>
+      </c>
+      <c r="S173" t="n">
+        <v>15</v>
+      </c>
+      <c r="T173" t="n">
+        <v>9</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="W173" t="n">
+        <v>77</v>
+      </c>
+      <c r="X173" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC173" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2131250</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>22.15384615384615</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>178.6153846153846</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>65.76923076923077</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1940384.615384615</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>75.53846153846153</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>67.08333333333333</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>1406041.666666667</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BA173" t="inlineStr"/>
+      <c r="BB173" t="inlineStr"/>
+      <c r="BC173" t="inlineStr"/>
+      <c r="BD173" t="inlineStr"/>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr"/>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
+      <c r="BI173" t="inlineStr"/>
+      <c r="BJ173" t="inlineStr"/>
+      <c r="BK173" t="inlineStr"/>
+      <c r="BL173" t="inlineStr"/>
+      <c r="BM173" t="inlineStr"/>
+      <c r="BN173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN173"/>
+  <dimension ref="A1:BN181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36083,6 +36083,1576 @@
       <c r="BM173" t="inlineStr"/>
       <c r="BN173" t="inlineStr"/>
     </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M174" t="n">
+        <v>47</v>
+      </c>
+      <c r="N174" t="n">
+        <v>53</v>
+      </c>
+      <c r="O174" t="n">
+        <v>5</v>
+      </c>
+      <c r="P174" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>4</v>
+      </c>
+      <c r="R174" t="n">
+        <v>3</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="n">
+        <v>5</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="W174" t="n">
+        <v>77</v>
+      </c>
+      <c r="X174" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AC174" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>20590000</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>35700000</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>9992500</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>185.2105263157895</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>1.684210526315789</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>78.78947368421052</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>37289473.68421052</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>84.10526315789474</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>315</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>89500000</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F175" t="n">
+        <v>25960</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M175" t="n">
+        <v>68</v>
+      </c>
+      <c r="N175" t="n">
+        <v>32</v>
+      </c>
+      <c r="O175" t="n">
+        <v>14</v>
+      </c>
+      <c r="P175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>3</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2</v>
+      </c>
+      <c r="S175" t="n">
+        <v>15</v>
+      </c>
+      <c r="T175" t="n">
+        <v>18</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="W175" t="n">
+        <v>77</v>
+      </c>
+      <c r="X175" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC175" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>2917272.727272727</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>4542000</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>22.8695652173913</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>69.60869565217391</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>3240217.391304348</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>75.91304347826087</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>442</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>58400000</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>476</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>352</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>16425000</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F176" t="n">
+        <v>26386</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M176" t="n">
+        <v>35</v>
+      </c>
+      <c r="N176" t="n">
+        <v>65</v>
+      </c>
+      <c r="O176" t="n">
+        <v>17</v>
+      </c>
+      <c r="P176" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>4</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="n">
+        <v>13</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="W176" t="n">
+        <v>77</v>
+      </c>
+      <c r="X176" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC176" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>5550000</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>4990909.090909091</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>76.36363636363636</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>23.35714285714286</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>183.6428571428571</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>68.35714285714286</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>3046428.571428571</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>183.3214285714286</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>1.357142857142857</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>70.10714285714286</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>2147321.428571429</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>73.42857142857143</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>215</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH176" t="inlineStr"/>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>45535.64583333334</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>21092</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="n">
+        <v>58</v>
+      </c>
+      <c r="N177" t="n">
+        <v>42</v>
+      </c>
+      <c r="O177" t="n">
+        <v>18</v>
+      </c>
+      <c r="P177" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>6</v>
+      </c>
+      <c r="R177" t="n">
+        <v>4</v>
+      </c>
+      <c r="S177" t="n">
+        <v>20</v>
+      </c>
+      <c r="T177" t="n">
+        <v>16</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W177" t="n">
+        <v>77</v>
+      </c>
+      <c r="X177" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC177" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>1467500</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>25.34782608695652</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>182.2173913043478</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.217391304347826</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>65.78260869565217</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1167391.304347826</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>70.43478260869566</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>181.1818181818182</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>64.81818181818181</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>1029545.454545455</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>70.72727272727273</v>
+      </c>
+      <c r="BA177" t="inlineStr"/>
+      <c r="BB177" t="inlineStr"/>
+      <c r="BC177" t="inlineStr"/>
+      <c r="BD177" t="inlineStr"/>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>45535.64583333334</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>35</v>
+      </c>
+      <c r="N178" t="n">
+        <v>65</v>
+      </c>
+      <c r="O178" t="n">
+        <v>15</v>
+      </c>
+      <c r="P178" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>5</v>
+      </c>
+      <c r="R178" t="n">
+        <v>5</v>
+      </c>
+      <c r="S178" t="n">
+        <v>12</v>
+      </c>
+      <c r="T178" t="n">
+        <v>17</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W178" t="n">
+        <v>77</v>
+      </c>
+      <c r="X178" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>185.3636363636364</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>1609090.909090909</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>182.9545454545455</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1394318.181818182</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>26.57894736842105</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>181.7368421052632</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>64.73684210526316</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>979210.5263157894</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>68.73684210526316</v>
+      </c>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>45535.64583333334</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>50</v>
+      </c>
+      <c r="N179" t="n">
+        <v>50</v>
+      </c>
+      <c r="O179" t="n">
+        <v>12</v>
+      </c>
+      <c r="P179" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>4</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6</v>
+      </c>
+      <c r="S179" t="n">
+        <v>15</v>
+      </c>
+      <c r="T179" t="n">
+        <v>10</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="W179" t="n">
+        <v>77</v>
+      </c>
+      <c r="X179" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC179" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>3277500</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>2210000</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>22.63157894736842</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>181.8947368421053</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>67.05263157894737</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>2115789.47368421</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>74.36842105263158</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>26.52173913043478</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>182.9565217391304</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>69.73913043478261</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>1930434.782608696</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>72.39130434782609</v>
+      </c>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr"/>
+      <c r="BM179" t="inlineStr"/>
+      <c r="BN179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>45535.64583333334</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>67</v>
+      </c>
+      <c r="N180" t="n">
+        <v>33</v>
+      </c>
+      <c r="O180" t="n">
+        <v>19</v>
+      </c>
+      <c r="P180" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>7</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2</v>
+      </c>
+      <c r="S180" t="n">
+        <v>13</v>
+      </c>
+      <c r="T180" t="n">
+        <v>15</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="W180" t="n">
+        <v>77</v>
+      </c>
+      <c r="X180" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AC180" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>1081000</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1408333.333333333</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1263095.238095238</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>71.04761904761905</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>23.41176470588235</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>181.7058823529412</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>64.17647058823529</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>1038235.294117647</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>71.11764705882354</v>
+      </c>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="inlineStr"/>
+      <c r="BM180" t="inlineStr"/>
+      <c r="BN180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>45535.54166666666</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>39</v>
+      </c>
+      <c r="N181" t="n">
+        <v>61</v>
+      </c>
+      <c r="O181" t="n">
+        <v>9</v>
+      </c>
+      <c r="P181" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>4</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7</v>
+      </c>
+      <c r="S181" t="n">
+        <v>11</v>
+      </c>
+      <c r="T181" t="n">
+        <v>11</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W181" t="n">
+        <v>77</v>
+      </c>
+      <c r="X181" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC181" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1962500</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>183</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1456800</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>25.10526315789474</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>182.9473684210526</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>65.10526315789474</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>1163947.368421053</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>69.42105263157895</v>
+      </c>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="inlineStr"/>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr"/>
+      <c r="BM181" t="inlineStr"/>
+      <c r="BN181" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN181"/>
+  <dimension ref="A1:BN191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37653,6 +37653,1930 @@
       <c r="BM181" t="inlineStr"/>
       <c r="BN181" t="inlineStr"/>
     </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F182" t="n">
+        <v>41375</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M182" t="n">
+        <v>50</v>
+      </c>
+      <c r="N182" t="n">
+        <v>50</v>
+      </c>
+      <c r="O182" t="n">
+        <v>8</v>
+      </c>
+      <c r="P182" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>1</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" t="n">
+        <v>11</v>
+      </c>
+      <c r="T182" t="n">
+        <v>12</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="W182" t="n">
+        <v>77</v>
+      </c>
+      <c r="X182" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC182" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>185.625</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>30562500</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>84</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>17991666.66666667</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>80.55555555555556</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>25.13333333333333</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>26583333.33333333</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>21997500</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>320</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>325</v>
+      </c>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="inlineStr"/>
+      <c r="BN182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F183" t="n">
+        <v>7020</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M183" t="n">
+        <v>44</v>
+      </c>
+      <c r="N183" t="n">
+        <v>56</v>
+      </c>
+      <c r="O183" t="n">
+        <v>10</v>
+      </c>
+      <c r="P183" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>3</v>
+      </c>
+      <c r="R183" t="n">
+        <v>4</v>
+      </c>
+      <c r="S183" t="n">
+        <v>16</v>
+      </c>
+      <c r="T183" t="n">
+        <v>9</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="W183" t="n">
+        <v>77</v>
+      </c>
+      <c r="X183" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC183" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>3910000</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AI183" t="inlineStr"/>
+      <c r="AJ183" t="inlineStr"/>
+      <c r="AK183" t="inlineStr"/>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>71.05555555555556</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>3255555.555555556</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>5085416.666666667</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>72.83333333333333</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>153</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F184" t="n">
+        <v>18376</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M184" t="n">
+        <v>68</v>
+      </c>
+      <c r="N184" t="n">
+        <v>32</v>
+      </c>
+      <c r="O184" t="n">
+        <v>15</v>
+      </c>
+      <c r="P184" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>5</v>
+      </c>
+      <c r="R184" t="n">
+        <v>3</v>
+      </c>
+      <c r="S184" t="n">
+        <v>11</v>
+      </c>
+      <c r="T184" t="n">
+        <v>21</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W184" t="n">
+        <v>77</v>
+      </c>
+      <c r="X184" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC184" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>12180000</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>5430000</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>181.76</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>11064000</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>27.30434782608696</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>183.1304347826087</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>1.565217391304348</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>72.39130434782609</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>3752173.913043478</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>75.95652173913044</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>79</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>152</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>16900000</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F185" t="n">
+        <v>30747</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M185" t="n">
+        <v>58</v>
+      </c>
+      <c r="N185" t="n">
+        <v>42</v>
+      </c>
+      <c r="O185" t="n">
+        <v>11</v>
+      </c>
+      <c r="P185" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>1</v>
+      </c>
+      <c r="R185" t="n">
+        <v>3</v>
+      </c>
+      <c r="S185" t="n">
+        <v>8</v>
+      </c>
+      <c r="T185" t="n">
+        <v>16</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="W185" t="n">
+        <v>77</v>
+      </c>
+      <c r="X185" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC185" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>5330000</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>27.42105263157895</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>183.5263157894737</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>4003947.368421053</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>72.94736842105263</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>183.5238095238095</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>3660714.285714286</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>75.57142857142857</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>344</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>22750000</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>394</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>185</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>141</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F186" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M186" t="n">
+        <v>54</v>
+      </c>
+      <c r="N186" t="n">
+        <v>46</v>
+      </c>
+      <c r="O186" t="n">
+        <v>29</v>
+      </c>
+      <c r="P186" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>7</v>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>12</v>
+      </c>
+      <c r="T186" t="n">
+        <v>6</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="W186" t="n">
+        <v>77</v>
+      </c>
+      <c r="X186" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC186" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>80.45454545454545</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>31700000</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>82.18181818181819</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>27.05882352941176</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>183.7058823529412</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>2.176470588235294</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>77.47058823529412</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>16913235.29411765</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>2602600</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F187" t="n">
+        <v>9348</v>
+      </c>
+      <c r="G187" t="n">
+        <v>3</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>46</v>
+      </c>
+      <c r="N187" t="n">
+        <v>54</v>
+      </c>
+      <c r="O187" t="n">
+        <v>17</v>
+      </c>
+      <c r="P187" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>8</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1</v>
+      </c>
+      <c r="S187" t="n">
+        <v>13</v>
+      </c>
+      <c r="T187" t="n">
+        <v>11</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W187" t="n">
+        <v>77</v>
+      </c>
+      <c r="X187" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>181</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>1057500</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI187" t="inlineStr"/>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr"/>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr"/>
+      <c r="AO187" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>183.6818181818182</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1277272.727272727</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>181.0833333333333</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>1143750</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA187" t="inlineStr"/>
+      <c r="BB187" t="inlineStr"/>
+      <c r="BC187" t="inlineStr"/>
+      <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="inlineStr"/>
+      <c r="BM187" t="inlineStr"/>
+      <c r="BN187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F188" t="n">
+        <v>10755</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>52</v>
+      </c>
+      <c r="N188" t="n">
+        <v>48</v>
+      </c>
+      <c r="O188" t="n">
+        <v>9</v>
+      </c>
+      <c r="P188" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>3</v>
+      </c>
+      <c r="R188" t="n">
+        <v>3</v>
+      </c>
+      <c r="S188" t="n">
+        <v>23</v>
+      </c>
+      <c r="T188" t="n">
+        <v>13</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W188" t="n">
+        <v>77</v>
+      </c>
+      <c r="X188" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>1561111.111111111</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI188" t="inlineStr"/>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr"/>
+      <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr"/>
+      <c r="AO188" t="n">
+        <v>23.22727272727273</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>67.31818181818181</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1904545.454545455</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>74.36363636363636</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>72</v>
+      </c>
+      <c r="BA188" t="inlineStr"/>
+      <c r="BB188" t="inlineStr"/>
+      <c r="BC188" t="inlineStr"/>
+      <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr"/>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="inlineStr"/>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>5423</v>
+      </c>
+      <c r="F189" t="n">
+        <v>8651</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>55</v>
+      </c>
+      <c r="N189" t="n">
+        <v>45</v>
+      </c>
+      <c r="O189" t="n">
+        <v>7</v>
+      </c>
+      <c r="P189" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>2</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2</v>
+      </c>
+      <c r="S189" t="n">
+        <v>16</v>
+      </c>
+      <c r="T189" t="n">
+        <v>16</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="W189" t="n">
+        <v>77</v>
+      </c>
+      <c r="X189" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr"/>
+      <c r="AL189" t="inlineStr"/>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr"/>
+      <c r="AO189" t="n">
+        <v>30.14285714285714</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1157142.857142857</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>1959722.222222222</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>72.94444444444444</v>
+      </c>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr"/>
+      <c r="BL189" t="inlineStr"/>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renzo barbera
+  palermo </t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>36349</v>
+      </c>
+      <c r="F190" t="n">
+        <v>25787</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>51</v>
+      </c>
+      <c r="N190" t="n">
+        <v>49</v>
+      </c>
+      <c r="O190" t="n">
+        <v>22</v>
+      </c>
+      <c r="P190" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>9</v>
+      </c>
+      <c r="R190" t="n">
+        <v>3</v>
+      </c>
+      <c r="S190" t="n">
+        <v>12</v>
+      </c>
+      <c r="T190" t="n">
+        <v>9</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W190" t="n">
+        <v>77</v>
+      </c>
+      <c r="X190" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC190" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1086111.111111111</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>24.34782608695652</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>184.3913043478261</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>2328260.869565217</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>74.47826086956522</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>66.38888888888889</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>1383333.333333333</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="BA190" t="inlineStr"/>
+      <c r="BB190" t="inlineStr"/>
+      <c r="BC190" t="inlineStr"/>
+      <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="inlineStr"/>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7573</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>46</v>
+      </c>
+      <c r="N191" t="n">
+        <v>54</v>
+      </c>
+      <c r="O191" t="n">
+        <v>11</v>
+      </c>
+      <c r="P191" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>3</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6</v>
+      </c>
+      <c r="S191" t="n">
+        <v>17</v>
+      </c>
+      <c r="T191" t="n">
+        <v>21</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W191" t="n">
+        <v>77</v>
+      </c>
+      <c r="X191" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>1430555.555555556</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AI191" t="inlineStr"/>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr"/>
+      <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr"/>
+      <c r="AO191" t="n">
+        <v>26.34782608695652</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>185.2608695652174</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>66.78260869565217</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1183695.652173913</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>69.78260869565217</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>2775000</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="inlineStr"/>
+      <c r="BM191" t="inlineStr"/>
+      <c r="BN191" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN191"/>
+  <dimension ref="A1:BN199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39671,6 +39671,1470 @@
       <c r="BM191" t="inlineStr"/>
       <c r="BN191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M192" t="n">
+        <v>34</v>
+      </c>
+      <c r="N192" t="n">
+        <v>66</v>
+      </c>
+      <c r="O192" t="n">
+        <v>5</v>
+      </c>
+      <c r="P192" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>3</v>
+      </c>
+      <c r="R192" t="n">
+        <v>3</v>
+      </c>
+      <c r="S192" t="n">
+        <v>11</v>
+      </c>
+      <c r="T192" t="n">
+        <v>11</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="W192" t="n">
+        <v>77</v>
+      </c>
+      <c r="X192" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AC192" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>184.7272727272727</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>69.81818181818181</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2917272.727272727</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>74.81818181818181</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>81.11111111111111</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>35333333.33333334</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>84.11111111111111</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>183.6470588235294</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>68.64705882352941</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>3054411.764705882</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>74.29411764705883</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>77</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>18890625</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>81.625</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>343</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>163</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>54500000</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M193" t="n">
+        <v>44</v>
+      </c>
+      <c r="N193" t="n">
+        <v>56</v>
+      </c>
+      <c r="O193" t="n">
+        <v>14</v>
+      </c>
+      <c r="P193" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>4</v>
+      </c>
+      <c r="R193" t="n">
+        <v>4</v>
+      </c>
+      <c r="S193" t="n">
+        <v>17</v>
+      </c>
+      <c r="T193" t="n">
+        <v>12</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="W193" t="n">
+        <v>77</v>
+      </c>
+      <c r="X193" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr"/>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>186.7272727272727</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>11609090.90909091</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>79.54545454545455</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>181.8846153846154</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>1.461538461538461</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>72.30769230769231</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>4776923.076923077</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>74.76923076923077</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>72.06666666666666</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>6048333.333333333</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>79.93333333333334</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>155</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>216</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>OGCsGku2</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F194" t="n">
+        <v>14003</v>
+      </c>
+      <c r="G194" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>30</v>
+      </c>
+      <c r="N194" t="n">
+        <v>70</v>
+      </c>
+      <c r="O194" t="n">
+        <v>13</v>
+      </c>
+      <c r="P194" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>2</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1</v>
+      </c>
+      <c r="S194" t="n">
+        <v>6</v>
+      </c>
+      <c r="T194" t="n">
+        <v>29</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W194" t="n">
+        <v>77</v>
+      </c>
+      <c r="X194" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI194" t="inlineStr"/>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="inlineStr"/>
+      <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr"/>
+      <c r="AO194" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1131000</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AU194" t="inlineStr"/>
+      <c r="AV194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr"/>
+      <c r="AX194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="inlineStr"/>
+      <c r="BN194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>jN4TwgX8</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F195" t="n">
+        <v>5715</v>
+      </c>
+      <c r="G195" t="n">
+        <v>4</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>48</v>
+      </c>
+      <c r="N195" t="n">
+        <v>52</v>
+      </c>
+      <c r="O195" t="n">
+        <v>14</v>
+      </c>
+      <c r="P195" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>7</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="n">
+        <v>15</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="W195" t="n">
+        <v>77</v>
+      </c>
+      <c r="X195" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC195" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>66.33333333333333</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1247222.222222222</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1819444.444444444</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>65.20833333333333</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1186458.333333333</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>72.29166666666667</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>22.17391304347826</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>185.4782608695652</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>64.52173913043478</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>1404347.826086957</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>74.43478260869566</v>
+      </c>
+      <c r="BA195" t="inlineStr"/>
+      <c r="BB195" t="inlineStr"/>
+      <c r="BC195" t="inlineStr"/>
+      <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr"/>
+      <c r="BI195" t="inlineStr"/>
+      <c r="BJ195" t="inlineStr"/>
+      <c r="BK195" t="inlineStr"/>
+      <c r="BL195" t="inlineStr"/>
+      <c r="BM195" t="inlineStr"/>
+      <c r="BN195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>OUiGUlfe</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2269</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>40</v>
+      </c>
+      <c r="N196" t="n">
+        <v>60</v>
+      </c>
+      <c r="O196" t="n">
+        <v>13</v>
+      </c>
+      <c r="P196" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>4</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2</v>
+      </c>
+      <c r="S196" t="n">
+        <v>12</v>
+      </c>
+      <c r="T196" t="n">
+        <v>17</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W196" t="n">
+        <v>77</v>
+      </c>
+      <c r="X196" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>179.5555555555555</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>64.83333333333333</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1116388.888888889</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>182.6190476190476</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>1319047.619047619</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>70.95238095238095</v>
+      </c>
+      <c r="BA196" t="inlineStr"/>
+      <c r="BB196" t="inlineStr"/>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr"/>
+      <c r="BL196" t="inlineStr"/>
+      <c r="BM196" t="inlineStr"/>
+      <c r="BN196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>CjYAjWGE</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>67</v>
+      </c>
+      <c r="N197" t="n">
+        <v>33</v>
+      </c>
+      <c r="O197" t="n">
+        <v>9</v>
+      </c>
+      <c r="P197" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>4</v>
+      </c>
+      <c r="R197" t="n">
+        <v>5</v>
+      </c>
+      <c r="S197" t="n">
+        <v>11</v>
+      </c>
+      <c r="T197" t="n">
+        <v>14</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W197" t="n">
+        <v>77</v>
+      </c>
+      <c r="X197" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC197" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1465000</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>25.21739130434782</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>184.6521739130435</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>69.04347826086956</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1947826.086956522</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>73.08695652173913</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>26.13636363636364</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>184.2272727272727</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>67.31818181818181</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>1448863.636363636</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="BA197" t="inlineStr"/>
+      <c r="BB197" t="inlineStr"/>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="inlineStr"/>
+      <c r="BL197" t="inlineStr"/>
+      <c r="BM197" t="inlineStr"/>
+      <c r="BN197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>b7WIlAoR</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>69</v>
+      </c>
+      <c r="N198" t="n">
+        <v>31</v>
+      </c>
+      <c r="O198" t="n">
+        <v>14</v>
+      </c>
+      <c r="P198" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>5</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6</v>
+      </c>
+      <c r="S198" t="n">
+        <v>17</v>
+      </c>
+      <c r="T198" t="n">
+        <v>15</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W198" t="n">
+        <v>77</v>
+      </c>
+      <c r="X198" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>2581818.181818182</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO198" t="inlineStr"/>
+      <c r="AP198" t="inlineStr"/>
+      <c r="AQ198" t="inlineStr"/>
+      <c r="AR198" t="inlineStr"/>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AU198" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>3306000</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="BA198" t="inlineStr"/>
+      <c r="BB198" t="inlineStr"/>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
+      <c r="BI198" t="inlineStr"/>
+      <c r="BJ198" t="inlineStr"/>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="inlineStr"/>
+      <c r="BM198" t="inlineStr"/>
+      <c r="BN198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>S2b7WAPr</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>45548.64583333334</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monaldi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F199" t="n">
+        <v>13974</v>
+      </c>
+      <c r="G199" t="n">
+        <v>2</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>59</v>
+      </c>
+      <c r="N199" t="n">
+        <v>41</v>
+      </c>
+      <c r="O199" t="n">
+        <v>12</v>
+      </c>
+      <c r="P199" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>4</v>
+      </c>
+      <c r="R199" t="n">
+        <v>4</v>
+      </c>
+      <c r="S199" t="n">
+        <v>11</v>
+      </c>
+      <c r="T199" t="n">
+        <v>11</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W199" t="n">
+        <v>77</v>
+      </c>
+      <c r="X199" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1655000</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>184.375</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>2471875</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>73</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>1133750</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA199" t="inlineStr"/>
+      <c r="BB199" t="inlineStr"/>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
+      <c r="BI199" t="inlineStr"/>
+      <c r="BJ199" t="inlineStr"/>
+      <c r="BK199" t="inlineStr"/>
+      <c r="BL199" t="inlineStr"/>
+      <c r="BM199" t="inlineStr"/>
+      <c r="BN199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN199"/>
+  <dimension ref="A1:BN211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41135,6 +41135,2472 @@
       <c r="BM199" t="inlineStr"/>
       <c r="BN199" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F200" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G200" t="n">
+        <v>2</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M200" t="n">
+        <v>55</v>
+      </c>
+      <c r="N200" t="n">
+        <v>45</v>
+      </c>
+      <c r="O200" t="n">
+        <v>14</v>
+      </c>
+      <c r="P200" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>7</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2</v>
+      </c>
+      <c r="S200" t="n">
+        <v>13</v>
+      </c>
+      <c r="T200" t="n">
+        <v>10</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="W200" t="n">
+        <v>77</v>
+      </c>
+      <c r="X200" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC200" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>77.81818181818181</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>19609090.90909091</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>81</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>4050000</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>182.64</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>10674000</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>184</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>2980681.818181818</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>142</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F201" t="n">
+        <v>17586</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M201" t="n">
+        <v>47</v>
+      </c>
+      <c r="N201" t="n">
+        <v>53</v>
+      </c>
+      <c r="O201" t="n">
+        <v>9</v>
+      </c>
+      <c r="P201" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>3</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6</v>
+      </c>
+      <c r="S201" t="n">
+        <v>8</v>
+      </c>
+      <c r="T201" t="n">
+        <v>18</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W201" t="n">
+        <v>77</v>
+      </c>
+      <c r="X201" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC201" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>187</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>4360000</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>23.04545454545455</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>66.18181818181819</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>2434772.727272727</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>25.34782608695652</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>183.304347826087</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>71.04347826086956</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>3195652.173913043</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>75.47826086956522</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>213</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>224</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>177</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>79</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F202" t="n">
+        <v>14541</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L202" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M202" t="n">
+        <v>40</v>
+      </c>
+      <c r="N202" t="n">
+        <v>60</v>
+      </c>
+      <c r="O202" t="n">
+        <v>5</v>
+      </c>
+      <c r="P202" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>2</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2</v>
+      </c>
+      <c r="S202" t="n">
+        <v>11</v>
+      </c>
+      <c r="T202" t="n">
+        <v>19</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W202" t="n">
+        <v>77</v>
+      </c>
+      <c r="X202" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC202" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>5430000</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>27.45454545454545</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>181.3636363636364</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>2.181818181818182</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>81.81818181818181</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>32681818.18181818</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>84.09090909090909</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>26.30769230769231</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>181.8461538461538</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>72.07692307692308</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>4440384.615384615</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>75.69230769230769</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>185.96</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>26080000</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>226</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>22900000</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F203" t="n">
+        <v>15733</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>4</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M203" t="n">
+        <v>51</v>
+      </c>
+      <c r="N203" t="n">
+        <v>49</v>
+      </c>
+      <c r="O203" t="n">
+        <v>16</v>
+      </c>
+      <c r="P203" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>3</v>
+      </c>
+      <c r="R203" t="n">
+        <v>5</v>
+      </c>
+      <c r="S203" t="n">
+        <v>22</v>
+      </c>
+      <c r="T203" t="n">
+        <v>11</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="W203" t="n">
+        <v>77</v>
+      </c>
+      <c r="X203" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC203" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>4781818.181818182</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>27.36363636363636</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>81.27272727272727</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>34109090.90909091</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>82.45454545454545</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>68.14814814814815</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>2123148.148148148</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>72.51851851851852</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>181.7916666666667</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>76.70833333333333</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>17009375</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>73</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>170</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F204" t="n">
+        <v>22705</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3</v>
+      </c>
+      <c r="H204" t="n">
+        <v>2</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M204" t="n">
+        <v>51</v>
+      </c>
+      <c r="N204" t="n">
+        <v>49</v>
+      </c>
+      <c r="O204" t="n">
+        <v>13</v>
+      </c>
+      <c r="P204" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>7</v>
+      </c>
+      <c r="R204" t="n">
+        <v>5</v>
+      </c>
+      <c r="S204" t="n">
+        <v>16</v>
+      </c>
+      <c r="T204" t="n">
+        <v>15</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W204" t="n">
+        <v>77</v>
+      </c>
+      <c r="X204" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC204" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>13411111.11111111</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>80.11111111111111</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>26.42105263157895</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>186.6842105263158</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>75.21052631578948</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>11618947.36842105</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>78.73684210526316</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>23.07407407407407</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>184.6296296296296</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>1.296296296296296</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>9445370.370370371</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>80.22222222222223</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>309</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>64200000</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>326</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>79</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F205" t="n">
+        <v>24277</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M205" t="n">
+        <v>53</v>
+      </c>
+      <c r="N205" t="n">
+        <v>47</v>
+      </c>
+      <c r="O205" t="n">
+        <v>5</v>
+      </c>
+      <c r="P205" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6</v>
+      </c>
+      <c r="S205" t="n">
+        <v>13</v>
+      </c>
+      <c r="T205" t="n">
+        <v>13</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="W205" t="n">
+        <v>77</v>
+      </c>
+      <c r="X205" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AC205" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>5228125</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>7209000</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>23.73684210526316</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>184.7368421052632</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>68</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>2302631.578947369</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>73.47368421052632</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>222</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>245</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>350</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>45550.3125</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F206" t="n">
+        <v>33009</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M206" t="n">
+        <v>49</v>
+      </c>
+      <c r="N206" t="n">
+        <v>51</v>
+      </c>
+      <c r="O206" t="n">
+        <v>20</v>
+      </c>
+      <c r="P206" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>8</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6</v>
+      </c>
+      <c r="S206" t="n">
+        <v>9</v>
+      </c>
+      <c r="T206" t="n">
+        <v>12</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="W206" t="n">
+        <v>77</v>
+      </c>
+      <c r="X206" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC206" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>4109090.909090909</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>22942500</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>25.61111111111111</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>184.3888888888889</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>5415277.777777778</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>75.05555555555556</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>25.95652173913043</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>181.7826086956522</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>1.608695652173913</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>77.82608695652173</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>20666304.34782609</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>80.78260869565217</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>350</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>29450000</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>397</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>173</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>77</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>45549.65625</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F207" t="n">
+        <v>71273</v>
+      </c>
+      <c r="G207" t="n">
+        <v>4</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M207" t="n">
+        <v>62</v>
+      </c>
+      <c r="N207" t="n">
+        <v>38</v>
+      </c>
+      <c r="O207" t="n">
+        <v>12</v>
+      </c>
+      <c r="P207" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>8</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1</v>
+      </c>
+      <c r="S207" t="n">
+        <v>12</v>
+      </c>
+      <c r="T207" t="n">
+        <v>12</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W207" t="n">
+        <v>77</v>
+      </c>
+      <c r="X207" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC207" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>35611111.11111111</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>83.88888888888889</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>183.3478260869565</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1.478260869565217</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>76.43478260869566</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>22591304.34782609</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>83.08695652173913</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>180.35</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>2212250</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>392</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>97900000</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>404</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>177</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>65</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F208" t="n">
+        <v>15083</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="n">
+        <v>3</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>70</v>
+      </c>
+      <c r="N208" t="n">
+        <v>30</v>
+      </c>
+      <c r="O208" t="n">
+        <v>12</v>
+      </c>
+      <c r="P208" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>7</v>
+      </c>
+      <c r="R208" t="n">
+        <v>5</v>
+      </c>
+      <c r="S208" t="n">
+        <v>8</v>
+      </c>
+      <c r="T208" t="n">
+        <v>17</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W208" t="n">
+        <v>77</v>
+      </c>
+      <c r="X208" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>186</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1756818.181818182</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>26.05555555555556</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>67.61111111111111</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1909722.222222222</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>184.55</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>1092500</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2777</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>41</v>
+      </c>
+      <c r="N209" t="n">
+        <v>59</v>
+      </c>
+      <c r="O209" t="n">
+        <v>14</v>
+      </c>
+      <c r="P209" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>3</v>
+      </c>
+      <c r="R209" t="n">
+        <v>7</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="n">
+        <v>14</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W209" t="n">
+        <v>77</v>
+      </c>
+      <c r="X209" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1012500</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>23.04347826086957</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>184.7826086956522</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>1.260869565217391</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>67.95652173913044</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>3011956.52173913</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>76.04347826086956</v>
+      </c>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F210" t="n">
+        <v>8171</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>45</v>
+      </c>
+      <c r="N210" t="n">
+        <v>55</v>
+      </c>
+      <c r="O210" t="n">
+        <v>11</v>
+      </c>
+      <c r="P210" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>6</v>
+      </c>
+      <c r="R210" t="n">
+        <v>3</v>
+      </c>
+      <c r="S210" t="n">
+        <v>17</v>
+      </c>
+      <c r="T210" t="n">
+        <v>17</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="W210" t="n">
+        <v>77</v>
+      </c>
+      <c r="X210" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC210" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>1227500</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>180.7083333333333</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>65.95833333333333</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1272916.666666667</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>72.16666666666667</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>2083125</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8665</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>3</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>59</v>
+      </c>
+      <c r="N211" t="n">
+        <v>41</v>
+      </c>
+      <c r="O211" t="n">
+        <v>22</v>
+      </c>
+      <c r="P211" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>6</v>
+      </c>
+      <c r="R211" t="n">
+        <v>4</v>
+      </c>
+      <c r="S211" t="n">
+        <v>15</v>
+      </c>
+      <c r="T211" t="n">
+        <v>12</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W211" t="n">
+        <v>77</v>
+      </c>
+      <c r="X211" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC211" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1434090.909090909</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1113500</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>27.44444444444444</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>959722.2222222222</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>65.61111111111111</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL230"/>
+  <dimension ref="A1:CL239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59991,6 +59991,2128 @@
         <v>65</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>45559.65625</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F231" t="n">
+        <v>22977</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2</v>
+      </c>
+      <c r="H231" t="n">
+        <v>3</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L231" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M231" t="n">
+        <v>59</v>
+      </c>
+      <c r="N231" t="n">
+        <v>41</v>
+      </c>
+      <c r="O231" t="n">
+        <v>8</v>
+      </c>
+      <c r="P231" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>5</v>
+      </c>
+      <c r="R231" t="n">
+        <v>7</v>
+      </c>
+      <c r="S231" t="n">
+        <v>3</v>
+      </c>
+      <c r="T231" t="n">
+        <v>4</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3</v>
+      </c>
+      <c r="W231" t="n">
+        <v>17</v>
+      </c>
+      <c r="X231" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>560</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>409</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>456</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>308</v>
+      </c>
+      <c r="AO231" t="inlineStr"/>
+      <c r="AP231" t="inlineStr"/>
+      <c r="AQ231" t="inlineStr"/>
+      <c r="AR231" t="inlineStr"/>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AT231" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AU231" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr"/>
+      <c r="BA231" t="inlineStr"/>
+      <c r="BB231" t="inlineStr"/>
+      <c r="BC231" t="inlineStr"/>
+      <c r="BD231" t="inlineStr"/>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr"/>
+      <c r="BI231" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="BJ231" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="BK231" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>187.2727272727273</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>44000</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="BQ231" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="BR231" t="n">
+        <v>29000</v>
+      </c>
+      <c r="BS231" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="BT231" t="n">
+        <v>184.1304347826087</v>
+      </c>
+      <c r="BU231" t="n">
+        <v>75.52173913043478</v>
+      </c>
+      <c r="BV231" t="n">
+        <v>33956.52173913043</v>
+      </c>
+      <c r="BW231" t="n">
+        <v>26.88235294117647</v>
+      </c>
+      <c r="BX231" t="n">
+        <v>182.7647058823529</v>
+      </c>
+      <c r="BY231" t="n">
+        <v>72.23529411764706</v>
+      </c>
+      <c r="BZ231" t="n">
+        <v>17588.23529411765</v>
+      </c>
+      <c r="CA231" t="inlineStr"/>
+      <c r="CB231" t="inlineStr"/>
+      <c r="CC231" t="inlineStr"/>
+      <c r="CD231" t="inlineStr"/>
+      <c r="CE231" t="inlineStr"/>
+      <c r="CF231" t="inlineStr"/>
+      <c r="CG231" t="inlineStr"/>
+      <c r="CH231" t="inlineStr"/>
+      <c r="CI231" t="inlineStr"/>
+      <c r="CJ231" t="inlineStr"/>
+      <c r="CK231" t="inlineStr"/>
+      <c r="CL231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>h8xCR9dC</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>5</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>65</v>
+      </c>
+      <c r="N232" t="n">
+        <v>35</v>
+      </c>
+      <c r="O232" t="n">
+        <v>16</v>
+      </c>
+      <c r="P232" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>7</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1</v>
+      </c>
+      <c r="S232" t="n">
+        <v>5</v>
+      </c>
+      <c r="T232" t="n">
+        <v>8</v>
+      </c>
+      <c r="U232" t="n">
+        <v>4</v>
+      </c>
+      <c r="V232" t="n">
+        <v>1</v>
+      </c>
+      <c r="W232" t="n">
+        <v>13</v>
+      </c>
+      <c r="X232" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>649</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>334</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>549</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>243</v>
+      </c>
+      <c r="AO232" t="inlineStr"/>
+      <c r="AP232" t="inlineStr"/>
+      <c r="AQ232" t="inlineStr"/>
+      <c r="AR232" t="inlineStr"/>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AT232" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AU232" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr"/>
+      <c r="BA232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BJ232" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="BK232" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>45800</v>
+      </c>
+      <c r="BO232" t="inlineStr"/>
+      <c r="BP232" t="inlineStr"/>
+      <c r="BQ232" t="inlineStr"/>
+      <c r="BR232" t="inlineStr"/>
+      <c r="BS232" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="BT232" t="n">
+        <v>184.36</v>
+      </c>
+      <c r="BU232" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="BV232" t="n">
+        <v>72880</v>
+      </c>
+      <c r="BW232" t="n">
+        <v>25.90476190476191</v>
+      </c>
+      <c r="BX232" t="n">
+        <v>182.4761904761905</v>
+      </c>
+      <c r="BY232" t="n">
+        <v>70.0952380952381</v>
+      </c>
+      <c r="BZ232" t="n">
+        <v>7095.238095238095</v>
+      </c>
+      <c r="CA232" t="inlineStr"/>
+      <c r="CB232" t="inlineStr"/>
+      <c r="CC232" t="inlineStr"/>
+      <c r="CD232" t="inlineStr"/>
+      <c r="CE232" t="inlineStr"/>
+      <c r="CF232" t="inlineStr"/>
+      <c r="CG232" t="inlineStr"/>
+      <c r="CH232" t="inlineStr"/>
+      <c r="CI232" t="inlineStr"/>
+      <c r="CJ232" t="inlineStr"/>
+      <c r="CK232" t="inlineStr"/>
+      <c r="CL232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>OE5MGhrf</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>45561.5625</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3782</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>58</v>
+      </c>
+      <c r="N233" t="n">
+        <v>42</v>
+      </c>
+      <c r="O233" t="n">
+        <v>19</v>
+      </c>
+      <c r="P233" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>8</v>
+      </c>
+      <c r="R233" t="n">
+        <v>3</v>
+      </c>
+      <c r="S233" t="n">
+        <v>6</v>
+      </c>
+      <c r="T233" t="n">
+        <v>8</v>
+      </c>
+      <c r="U233" t="n">
+        <v>5</v>
+      </c>
+      <c r="V233" t="n">
+        <v>2</v>
+      </c>
+      <c r="W233" t="n">
+        <v>16</v>
+      </c>
+      <c r="X233" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>634</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>446</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>531</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>359</v>
+      </c>
+      <c r="AO233" t="inlineStr"/>
+      <c r="AP233" t="inlineStr"/>
+      <c r="AQ233" t="inlineStr"/>
+      <c r="AR233" t="inlineStr"/>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AT233" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AU233" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr"/>
+      <c r="BA233" t="inlineStr"/>
+      <c r="BB233" t="inlineStr"/>
+      <c r="BC233" t="inlineStr"/>
+      <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
+      <c r="BI233" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="BJ233" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="BK233" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>182.7777777777778</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>72</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>29444.44444444445</v>
+      </c>
+      <c r="BO233" t="inlineStr"/>
+      <c r="BP233" t="inlineStr"/>
+      <c r="BQ233" t="inlineStr"/>
+      <c r="BR233" t="inlineStr"/>
+      <c r="BS233" t="n">
+        <v>26.05263157894737</v>
+      </c>
+      <c r="BT233" t="n">
+        <v>184.6315789473684</v>
+      </c>
+      <c r="BU233" t="n">
+        <v>72.10526315789474</v>
+      </c>
+      <c r="BV233" t="n">
+        <v>27315.78947368421</v>
+      </c>
+      <c r="BW233" t="inlineStr"/>
+      <c r="BX233" t="inlineStr"/>
+      <c r="BY233" t="inlineStr"/>
+      <c r="BZ233" t="inlineStr"/>
+      <c r="CA233" t="inlineStr"/>
+      <c r="CB233" t="inlineStr"/>
+      <c r="CC233" t="inlineStr"/>
+      <c r="CD233" t="inlineStr"/>
+      <c r="CE233" t="inlineStr"/>
+      <c r="CF233" t="inlineStr"/>
+      <c r="CG233" t="inlineStr"/>
+      <c r="CH233" t="inlineStr"/>
+      <c r="CI233" t="inlineStr"/>
+      <c r="CJ233" t="inlineStr"/>
+      <c r="CK233" t="inlineStr"/>
+      <c r="CL233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>baMp22np</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F234" t="n">
+        <v>28575</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>35</v>
+      </c>
+      <c r="N234" t="n">
+        <v>65</v>
+      </c>
+      <c r="O234" t="n">
+        <v>11</v>
+      </c>
+      <c r="P234" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3</v>
+      </c>
+      <c r="R234" t="n">
+        <v>4</v>
+      </c>
+      <c r="S234" t="n">
+        <v>5</v>
+      </c>
+      <c r="T234" t="n">
+        <v>7</v>
+      </c>
+      <c r="U234" t="n">
+        <v>3</v>
+      </c>
+      <c r="V234" t="n">
+        <v>3</v>
+      </c>
+      <c r="W234" t="n">
+        <v>12</v>
+      </c>
+      <c r="X234" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>288</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>524</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>182</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>388</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AT234" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AU234" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr"/>
+      <c r="BA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="BJ234" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="BK234" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>183.6363636363636</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>17818.18181818182</v>
+      </c>
+      <c r="BO234" t="inlineStr"/>
+      <c r="BP234" t="inlineStr"/>
+      <c r="BQ234" t="inlineStr"/>
+      <c r="BR234" t="inlineStr"/>
+      <c r="BS234" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="BT234" t="n">
+        <v>186.3913043478261</v>
+      </c>
+      <c r="BU234" t="n">
+        <v>69.78260869565217</v>
+      </c>
+      <c r="BV234" t="n">
+        <v>18782.60869565217</v>
+      </c>
+      <c r="BW234" t="n">
+        <v>26.47826086956522</v>
+      </c>
+      <c r="BX234" t="n">
+        <v>181.4347826086957</v>
+      </c>
+      <c r="BY234" t="n">
+        <v>68.82608695652173</v>
+      </c>
+      <c r="BZ234" t="inlineStr"/>
+      <c r="CA234" t="inlineStr"/>
+      <c r="CB234" t="inlineStr"/>
+      <c r="CC234" t="inlineStr"/>
+      <c r="CD234" t="inlineStr"/>
+      <c r="CE234" t="inlineStr"/>
+      <c r="CF234" t="inlineStr"/>
+      <c r="CG234" t="inlineStr"/>
+      <c r="CH234" t="inlineStr"/>
+      <c r="CI234" t="inlineStr"/>
+      <c r="CJ234" t="inlineStr"/>
+      <c r="CK234" t="inlineStr"/>
+      <c r="CL234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>xCj1xWPj</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>45560.5625</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4940</v>
+      </c>
+      <c r="G235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>54</v>
+      </c>
+      <c r="N235" t="n">
+        <v>46</v>
+      </c>
+      <c r="O235" t="n">
+        <v>15</v>
+      </c>
+      <c r="P235" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>4</v>
+      </c>
+      <c r="R235" t="n">
+        <v>3</v>
+      </c>
+      <c r="S235" t="n">
+        <v>7</v>
+      </c>
+      <c r="T235" t="n">
+        <v>3</v>
+      </c>
+      <c r="U235" t="n">
+        <v>4</v>
+      </c>
+      <c r="V235" t="n">
+        <v>7</v>
+      </c>
+      <c r="W235" t="n">
+        <v>15</v>
+      </c>
+      <c r="X235" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>537</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>496</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>433</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>390</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>86</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>84</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>35</v>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AT235" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AU235" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr"/>
+      <c r="BA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BJ235" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BK235" t="n">
+        <v>22.375</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>10125</v>
+      </c>
+      <c r="BO235" t="inlineStr"/>
+      <c r="BP235" t="inlineStr"/>
+      <c r="BQ235" t="inlineStr"/>
+      <c r="BR235" t="inlineStr"/>
+      <c r="BS235" t="n">
+        <v>24.73684210526316</v>
+      </c>
+      <c r="BT235" t="n">
+        <v>187.3684210526316</v>
+      </c>
+      <c r="BU235" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="BV235" t="n">
+        <v>14789.47368421053</v>
+      </c>
+      <c r="BW235" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="BX235" t="n">
+        <v>181.05</v>
+      </c>
+      <c r="BY235" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BZ235" t="n">
+        <v>12000</v>
+      </c>
+      <c r="CA235" t="inlineStr"/>
+      <c r="CB235" t="inlineStr"/>
+      <c r="CC235" t="inlineStr"/>
+      <c r="CD235" t="inlineStr"/>
+      <c r="CE235" t="inlineStr"/>
+      <c r="CF235" t="inlineStr"/>
+      <c r="CG235" t="inlineStr"/>
+      <c r="CH235" t="inlineStr"/>
+      <c r="CI235" t="inlineStr"/>
+      <c r="CJ235" t="inlineStr"/>
+      <c r="CK235" t="inlineStr"/>
+      <c r="CL235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>h2uVDr1f</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>45560.45833333334</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F236" t="n">
+        <v>3347</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>52</v>
+      </c>
+      <c r="N236" t="n">
+        <v>48</v>
+      </c>
+      <c r="O236" t="n">
+        <v>12</v>
+      </c>
+      <c r="P236" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>4</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6</v>
+      </c>
+      <c r="S236" t="n">
+        <v>5</v>
+      </c>
+      <c r="T236" t="n">
+        <v>8</v>
+      </c>
+      <c r="U236" t="n">
+        <v>3</v>
+      </c>
+      <c r="V236" t="n">
+        <v>1</v>
+      </c>
+      <c r="W236" t="n">
+        <v>20</v>
+      </c>
+      <c r="X236" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>495</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>474</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>354</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>324</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>105</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AT236" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AU236" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="inlineStr"/>
+      <c r="BD236" t="inlineStr"/>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
+      <c r="BI236" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+      <c r="BO236" t="inlineStr"/>
+      <c r="BP236" t="inlineStr"/>
+      <c r="BQ236" t="inlineStr"/>
+      <c r="BR236" t="inlineStr"/>
+      <c r="BS236" t="n">
+        <v>25.17647058823529</v>
+      </c>
+      <c r="BT236" t="n">
+        <v>186.4117647058823</v>
+      </c>
+      <c r="BU236" t="n">
+        <v>68.52941176470588</v>
+      </c>
+      <c r="BV236" t="n">
+        <v>3294.117647058823</v>
+      </c>
+      <c r="BW236" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BX236" t="n">
+        <v>187</v>
+      </c>
+      <c r="BY236" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="BZ236" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CA236" t="inlineStr"/>
+      <c r="CB236" t="inlineStr"/>
+      <c r="CC236" t="inlineStr"/>
+      <c r="CD236" t="inlineStr"/>
+      <c r="CE236" t="inlineStr"/>
+      <c r="CF236" t="inlineStr"/>
+      <c r="CG236" t="inlineStr"/>
+      <c r="CH236" t="inlineStr"/>
+      <c r="CI236" t="inlineStr"/>
+      <c r="CJ236" t="inlineStr"/>
+      <c r="CK236" t="inlineStr"/>
+      <c r="CL236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SG7bDmCr</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F237" t="n">
+        <v>12334</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>56</v>
+      </c>
+      <c r="N237" t="n">
+        <v>44</v>
+      </c>
+      <c r="O237" t="n">
+        <v>15</v>
+      </c>
+      <c r="P237" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>5</v>
+      </c>
+      <c r="R237" t="n">
+        <v>2</v>
+      </c>
+      <c r="S237" t="n">
+        <v>5</v>
+      </c>
+      <c r="T237" t="n">
+        <v>2</v>
+      </c>
+      <c r="U237" t="n">
+        <v>5</v>
+      </c>
+      <c r="V237" t="n">
+        <v>3</v>
+      </c>
+      <c r="W237" t="n">
+        <v>15</v>
+      </c>
+      <c r="X237" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>506</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>400</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>381</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>290</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>92</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>88</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>56</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AT237" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AU237" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="inlineStr"/>
+      <c r="BD237" t="inlineStr"/>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
+      <c r="BI237" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BJ237" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BK237" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>26700</v>
+      </c>
+      <c r="BO237" t="inlineStr"/>
+      <c r="BP237" t="inlineStr"/>
+      <c r="BQ237" t="inlineStr"/>
+      <c r="BR237" t="inlineStr"/>
+      <c r="BS237" t="n">
+        <v>24.23809523809524</v>
+      </c>
+      <c r="BT237" t="n">
+        <v>185.5238095238095</v>
+      </c>
+      <c r="BU237" t="n">
+        <v>72.52380952380952</v>
+      </c>
+      <c r="BV237" t="n">
+        <v>25714.28571428571</v>
+      </c>
+      <c r="BW237" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX237" t="n">
+        <v>185.5454545454545</v>
+      </c>
+      <c r="BY237" t="n">
+        <v>70.04545454545455</v>
+      </c>
+      <c r="BZ237" t="inlineStr"/>
+      <c r="CA237" t="inlineStr"/>
+      <c r="CB237" t="inlineStr"/>
+      <c r="CC237" t="inlineStr"/>
+      <c r="CD237" t="inlineStr"/>
+      <c r="CE237" t="inlineStr"/>
+      <c r="CF237" t="inlineStr"/>
+      <c r="CG237" t="inlineStr"/>
+      <c r="CH237" t="inlineStr"/>
+      <c r="CI237" t="inlineStr"/>
+      <c r="CJ237" t="inlineStr"/>
+      <c r="CK237" t="inlineStr"/>
+      <c r="CL237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>WjBv9U0S</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>45559.5625</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F238" t="n">
+        <v>11017</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>50</v>
+      </c>
+      <c r="N238" t="n">
+        <v>50</v>
+      </c>
+      <c r="O238" t="n">
+        <v>13</v>
+      </c>
+      <c r="P238" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>4</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>8</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1</v>
+      </c>
+      <c r="U238" t="n">
+        <v>1</v>
+      </c>
+      <c r="V238" t="n">
+        <v>2</v>
+      </c>
+      <c r="W238" t="n">
+        <v>19</v>
+      </c>
+      <c r="X238" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>469</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>502</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>422</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>118</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>77</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>70</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AT238" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AU238" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA238" t="inlineStr"/>
+      <c r="BB238" t="inlineStr"/>
+      <c r="BC238" t="inlineStr"/>
+      <c r="BD238" t="inlineStr"/>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="inlineStr"/>
+      <c r="BH238" t="inlineStr"/>
+      <c r="BI238" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BJ238" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="BK238" t="n">
+        <v>26</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>17000</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>23</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="BQ238" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="BR238" t="inlineStr"/>
+      <c r="BS238" t="n">
+        <v>25.52173913043478</v>
+      </c>
+      <c r="BT238" t="n">
+        <v>181.6086956521739</v>
+      </c>
+      <c r="BU238" t="n">
+        <v>70.43478260869566</v>
+      </c>
+      <c r="BV238" t="n">
+        <v>16652.17391304348</v>
+      </c>
+      <c r="BW238" t="n">
+        <v>28.23076923076923</v>
+      </c>
+      <c r="BX238" t="n">
+        <v>184.0769230769231</v>
+      </c>
+      <c r="BY238" t="n">
+        <v>71.23076923076923</v>
+      </c>
+      <c r="BZ238" t="inlineStr"/>
+      <c r="CA238" t="inlineStr"/>
+      <c r="CB238" t="inlineStr"/>
+      <c r="CC238" t="inlineStr"/>
+      <c r="CD238" t="inlineStr"/>
+      <c r="CE238" t="inlineStr"/>
+      <c r="CF238" t="inlineStr"/>
+      <c r="CG238" t="inlineStr"/>
+      <c r="CH238" t="inlineStr"/>
+      <c r="CI238" t="inlineStr"/>
+      <c r="CJ238" t="inlineStr"/>
+      <c r="CK238" t="inlineStr"/>
+      <c r="CL238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>O2Xm0vko</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>45559.45833333334</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F239" t="n">
+        <v>13951</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>62</v>
+      </c>
+      <c r="N239" t="n">
+        <v>38</v>
+      </c>
+      <c r="O239" t="n">
+        <v>14</v>
+      </c>
+      <c r="P239" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>7</v>
+      </c>
+      <c r="R239" t="n">
+        <v>5</v>
+      </c>
+      <c r="S239" t="n">
+        <v>6</v>
+      </c>
+      <c r="T239" t="n">
+        <v>6</v>
+      </c>
+      <c r="U239" t="n">
+        <v>1</v>
+      </c>
+      <c r="V239" t="n">
+        <v>2</v>
+      </c>
+      <c r="W239" t="n">
+        <v>17</v>
+      </c>
+      <c r="X239" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>599</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>339</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>531</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>263</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>143</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>83</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>72</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AT239" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AU239" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>773</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA239" t="inlineStr"/>
+      <c r="BB239" t="inlineStr"/>
+      <c r="BC239" t="inlineStr"/>
+      <c r="BD239" t="inlineStr"/>
+      <c r="BE239" t="inlineStr"/>
+      <c r="BF239" t="inlineStr"/>
+      <c r="BG239" t="inlineStr"/>
+      <c r="BH239" t="inlineStr"/>
+      <c r="BI239" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="BJ239" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="BK239" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="BN239" t="n">
+        <v>7444.444444444444</v>
+      </c>
+      <c r="BO239" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BP239" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="BQ239" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BR239" t="inlineStr"/>
+      <c r="BS239" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="BT239" t="n">
+        <v>183.1333333333333</v>
+      </c>
+      <c r="BU239" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BV239" t="inlineStr"/>
+      <c r="BW239" t="n">
+        <v>20.94444444444444</v>
+      </c>
+      <c r="BX239" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="BY239" t="n">
+        <v>67.83333333333333</v>
+      </c>
+      <c r="BZ239" t="n">
+        <v>5611.111111111111</v>
+      </c>
+      <c r="CA239" t="inlineStr"/>
+      <c r="CB239" t="inlineStr"/>
+      <c r="CC239" t="inlineStr"/>
+      <c r="CD239" t="inlineStr"/>
+      <c r="CE239" t="inlineStr"/>
+      <c r="CF239" t="inlineStr"/>
+      <c r="CG239" t="inlineStr"/>
+      <c r="CH239" t="inlineStr"/>
+      <c r="CI239" t="inlineStr"/>
+      <c r="CJ239" t="inlineStr"/>
+      <c r="CK239" t="inlineStr"/>
+      <c r="CL239" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL239"/>
+  <dimension ref="A1:CL247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62113,6 +62113,1856 @@
       <c r="CK239" t="inlineStr"/>
       <c r="CL239" t="inlineStr"/>
     </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F240" t="n">
+        <v>27126</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M240" t="n">
+        <v>36</v>
+      </c>
+      <c r="N240" t="n">
+        <v>64</v>
+      </c>
+      <c r="O240" t="n">
+        <v>5</v>
+      </c>
+      <c r="P240" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>1</v>
+      </c>
+      <c r="R240" t="n">
+        <v>5</v>
+      </c>
+      <c r="S240" t="n">
+        <v>1</v>
+      </c>
+      <c r="T240" t="n">
+        <v>11</v>
+      </c>
+      <c r="U240" t="n">
+        <v>3</v>
+      </c>
+      <c r="V240" t="n">
+        <v>7</v>
+      </c>
+      <c r="W240" t="n">
+        <v>16</v>
+      </c>
+      <c r="X240" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>296</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>522</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>225</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>454</v>
+      </c>
+      <c r="AO240" t="inlineStr"/>
+      <c r="AP240" t="inlineStr"/>
+      <c r="AQ240" t="inlineStr"/>
+      <c r="AR240" t="inlineStr"/>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AT240" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AU240" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr"/>
+      <c r="BA240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC240" t="inlineStr"/>
+      <c r="BD240" t="inlineStr"/>
+      <c r="BE240" t="inlineStr"/>
+      <c r="BF240" t="inlineStr"/>
+      <c r="BG240" t="inlineStr"/>
+      <c r="BH240" t="inlineStr"/>
+      <c r="BI240" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BJ240" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="BK240" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>26818.18181818182</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="BP240" t="n">
+        <v>186.5454545454545</v>
+      </c>
+      <c r="BQ240" t="n">
+        <v>77.45454545454545</v>
+      </c>
+      <c r="BR240" t="n">
+        <v>40272.72727272727</v>
+      </c>
+      <c r="BS240" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="BT240" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="BU240" t="n">
+        <v>71.86666666666666</v>
+      </c>
+      <c r="BV240" t="n">
+        <v>16766.66666666667</v>
+      </c>
+      <c r="BW240" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="BX240" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="BY240" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="BZ240" t="n">
+        <v>34160</v>
+      </c>
+      <c r="CA240" t="inlineStr"/>
+      <c r="CB240" t="inlineStr"/>
+      <c r="CC240" t="inlineStr"/>
+      <c r="CD240" t="inlineStr"/>
+      <c r="CE240" t="inlineStr"/>
+      <c r="CF240" t="inlineStr"/>
+      <c r="CG240" t="inlineStr"/>
+      <c r="CH240" t="inlineStr"/>
+      <c r="CI240" t="inlineStr"/>
+      <c r="CJ240" t="inlineStr"/>
+      <c r="CK240" t="inlineStr"/>
+      <c r="CL240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L241" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M241" t="n">
+        <v>34</v>
+      </c>
+      <c r="N241" t="n">
+        <v>66</v>
+      </c>
+      <c r="O241" t="n">
+        <v>7</v>
+      </c>
+      <c r="P241" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>2</v>
+      </c>
+      <c r="R241" t="n">
+        <v>3</v>
+      </c>
+      <c r="S241" t="n">
+        <v>1</v>
+      </c>
+      <c r="T241" t="n">
+        <v>7</v>
+      </c>
+      <c r="U241" t="n">
+        <v>4</v>
+      </c>
+      <c r="V241" t="n">
+        <v>2</v>
+      </c>
+      <c r="W241" t="n">
+        <v>15</v>
+      </c>
+      <c r="X241" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>355</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>697</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>267</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>577</v>
+      </c>
+      <c r="AO241" t="inlineStr"/>
+      <c r="AP241" t="inlineStr"/>
+      <c r="AQ241" t="inlineStr"/>
+      <c r="AR241" t="inlineStr"/>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AT241" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AU241" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV241" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr"/>
+      <c r="BA241" t="inlineStr"/>
+      <c r="BB241" t="inlineStr"/>
+      <c r="BC241" t="inlineStr"/>
+      <c r="BD241" t="inlineStr"/>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="inlineStr"/>
+      <c r="BH241" t="inlineStr"/>
+      <c r="BI241" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="BJ241" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="BK241" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BL241" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="BM241" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BN241" t="n">
+        <v>24700</v>
+      </c>
+      <c r="BO241" t="inlineStr"/>
+      <c r="BP241" t="inlineStr"/>
+      <c r="BQ241" t="inlineStr"/>
+      <c r="BR241" t="inlineStr"/>
+      <c r="BS241" t="n">
+        <v>24.23809523809524</v>
+      </c>
+      <c r="BT241" t="n">
+        <v>185.3809523809524</v>
+      </c>
+      <c r="BU241" t="n">
+        <v>68.76190476190476</v>
+      </c>
+      <c r="BV241" t="n">
+        <v>13952.38095238095</v>
+      </c>
+      <c r="BW241" t="n">
+        <v>24.3125</v>
+      </c>
+      <c r="BX241" t="n">
+        <v>184.625</v>
+      </c>
+      <c r="BY241" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="BZ241" t="n">
+        <v>64625</v>
+      </c>
+      <c r="CA241" t="inlineStr"/>
+      <c r="CB241" t="inlineStr"/>
+      <c r="CC241" t="inlineStr"/>
+      <c r="CD241" t="inlineStr"/>
+      <c r="CE241" t="inlineStr"/>
+      <c r="CF241" t="inlineStr"/>
+      <c r="CG241" t="inlineStr"/>
+      <c r="CH241" t="inlineStr"/>
+      <c r="CI241" t="inlineStr"/>
+      <c r="CJ241" t="inlineStr"/>
+      <c r="CK241" t="inlineStr"/>
+      <c r="CL241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F242" t="n">
+        <v>24611</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" t="n">
+        <v>3</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L242" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M242" t="n">
+        <v>40</v>
+      </c>
+      <c r="N242" t="n">
+        <v>60</v>
+      </c>
+      <c r="O242" t="n">
+        <v>10</v>
+      </c>
+      <c r="P242" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>3</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7</v>
+      </c>
+      <c r="S242" t="n">
+        <v>2</v>
+      </c>
+      <c r="T242" t="n">
+        <v>6</v>
+      </c>
+      <c r="U242" t="n">
+        <v>5</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3</v>
+      </c>
+      <c r="W242" t="n">
+        <v>10</v>
+      </c>
+      <c r="X242" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>416</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>648</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>346</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>583</v>
+      </c>
+      <c r="AO242" t="inlineStr"/>
+      <c r="AP242" t="inlineStr"/>
+      <c r="AQ242" t="inlineStr"/>
+      <c r="AR242" t="inlineStr"/>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AT242" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AU242" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr"/>
+      <c r="BA242" t="inlineStr"/>
+      <c r="BB242" t="inlineStr"/>
+      <c r="BC242" t="inlineStr"/>
+      <c r="BD242" t="inlineStr"/>
+      <c r="BE242" t="inlineStr"/>
+      <c r="BF242" t="inlineStr"/>
+      <c r="BG242" t="inlineStr"/>
+      <c r="BH242" t="inlineStr"/>
+      <c r="BI242" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BJ242" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="BK242" t="n">
+        <v>26</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="BM242" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="BN242" t="n">
+        <v>15888.88888888889</v>
+      </c>
+      <c r="BO242" t="n">
+        <v>28.09090909090909</v>
+      </c>
+      <c r="BP242" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="BQ242" t="n">
+        <v>82.90909090909091</v>
+      </c>
+      <c r="BR242" t="n">
+        <v>91545.45454545454</v>
+      </c>
+      <c r="BS242" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="BT242" t="n">
+        <v>185.4736842105263</v>
+      </c>
+      <c r="BU242" t="n">
+        <v>69.73684210526316</v>
+      </c>
+      <c r="BV242" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BW242" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="BX242" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="BY242" t="n">
+        <v>78.79166666666667</v>
+      </c>
+      <c r="BZ242" t="n">
+        <v>65291.66666666666</v>
+      </c>
+      <c r="CA242" t="inlineStr"/>
+      <c r="CB242" t="inlineStr"/>
+      <c r="CC242" t="inlineStr"/>
+      <c r="CD242" t="inlineStr"/>
+      <c r="CE242" t="inlineStr"/>
+      <c r="CF242" t="inlineStr"/>
+      <c r="CG242" t="inlineStr"/>
+      <c r="CH242" t="inlineStr"/>
+      <c r="CI242" t="inlineStr"/>
+      <c r="CJ242" t="inlineStr"/>
+      <c r="CK242" t="inlineStr"/>
+      <c r="CL242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F243" t="n">
+        <v>71103</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M243" t="n">
+        <v>57</v>
+      </c>
+      <c r="N243" t="n">
+        <v>43</v>
+      </c>
+      <c r="O243" t="n">
+        <v>15</v>
+      </c>
+      <c r="P243" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>6</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7</v>
+      </c>
+      <c r="S243" t="n">
+        <v>7</v>
+      </c>
+      <c r="T243" t="n">
+        <v>6</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2</v>
+      </c>
+      <c r="V243" t="n">
+        <v>3</v>
+      </c>
+      <c r="W243" t="n">
+        <v>13</v>
+      </c>
+      <c r="X243" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>497</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>368</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>458</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>328</v>
+      </c>
+      <c r="AO243" t="inlineStr"/>
+      <c r="AP243" t="inlineStr"/>
+      <c r="AQ243" t="inlineStr"/>
+      <c r="AR243" t="inlineStr"/>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AT243" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AU243" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr"/>
+      <c r="BA243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC243" t="inlineStr"/>
+      <c r="BD243" t="inlineStr"/>
+      <c r="BE243" t="inlineStr"/>
+      <c r="BF243" t="inlineStr"/>
+      <c r="BG243" t="inlineStr"/>
+      <c r="BH243" t="inlineStr"/>
+      <c r="BI243" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="BJ243" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="BK243" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="BN243" t="n">
+        <v>70200</v>
+      </c>
+      <c r="BO243" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="BP243" t="n">
+        <v>184.625</v>
+      </c>
+      <c r="BQ243" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BR243" t="n">
+        <v>11750</v>
+      </c>
+      <c r="BS243" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BT243" t="n">
+        <v>183.7083333333333</v>
+      </c>
+      <c r="BU243" t="n">
+        <v>75.70833333333333</v>
+      </c>
+      <c r="BV243" t="inlineStr"/>
+      <c r="BW243" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="BX243" t="n">
+        <v>180.9444444444445</v>
+      </c>
+      <c r="BY243" t="n">
+        <v>68.27777777777777</v>
+      </c>
+      <c r="BZ243" t="inlineStr"/>
+      <c r="CA243" t="inlineStr"/>
+      <c r="CB243" t="inlineStr"/>
+      <c r="CC243" t="inlineStr"/>
+      <c r="CD243" t="inlineStr"/>
+      <c r="CE243" t="inlineStr"/>
+      <c r="CF243" t="inlineStr"/>
+      <c r="CG243" t="inlineStr"/>
+      <c r="CH243" t="inlineStr"/>
+      <c r="CI243" t="inlineStr"/>
+      <c r="CJ243" t="inlineStr"/>
+      <c r="CK243" t="inlineStr"/>
+      <c r="CL243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>jwmmlzio</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F244" t="n">
+        <v>17538</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>49</v>
+      </c>
+      <c r="N244" t="n">
+        <v>51</v>
+      </c>
+      <c r="O244" t="n">
+        <v>12</v>
+      </c>
+      <c r="P244" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>1</v>
+      </c>
+      <c r="R244" t="n">
+        <v>4</v>
+      </c>
+      <c r="S244" t="n">
+        <v>4</v>
+      </c>
+      <c r="T244" t="n">
+        <v>3</v>
+      </c>
+      <c r="U244" t="n">
+        <v>7</v>
+      </c>
+      <c r="V244" t="n">
+        <v>4</v>
+      </c>
+      <c r="W244" t="n">
+        <v>12</v>
+      </c>
+      <c r="X244" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>328</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>329</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>266</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>267</v>
+      </c>
+      <c r="AO244" t="inlineStr"/>
+      <c r="AP244" t="inlineStr"/>
+      <c r="AQ244" t="inlineStr"/>
+      <c r="AR244" t="inlineStr"/>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AT244" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AU244" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr"/>
+      <c r="BA244" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC244" t="inlineStr"/>
+      <c r="BD244" t="inlineStr"/>
+      <c r="BE244" t="inlineStr"/>
+      <c r="BF244" t="inlineStr"/>
+      <c r="BG244" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI244" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="BJ244" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="BK244" t="inlineStr"/>
+      <c r="BL244" t="inlineStr"/>
+      <c r="BM244" t="inlineStr"/>
+      <c r="BN244" t="inlineStr"/>
+      <c r="BO244" t="inlineStr"/>
+      <c r="BP244" t="inlineStr"/>
+      <c r="BQ244" t="inlineStr"/>
+      <c r="BR244" t="inlineStr"/>
+      <c r="BS244" t="n">
+        <v>27.375</v>
+      </c>
+      <c r="BT244" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="BU244" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BV244" t="n">
+        <v>5625</v>
+      </c>
+      <c r="BW244" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BX244" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BY244" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="BZ244" t="n">
+        <v>9444.444444444445</v>
+      </c>
+      <c r="CA244" t="inlineStr"/>
+      <c r="CB244" t="inlineStr"/>
+      <c r="CC244" t="inlineStr"/>
+      <c r="CD244" t="inlineStr"/>
+      <c r="CE244" t="inlineStr"/>
+      <c r="CF244" t="inlineStr"/>
+      <c r="CG244" t="inlineStr"/>
+      <c r="CH244" t="inlineStr"/>
+      <c r="CI244" t="inlineStr"/>
+      <c r="CJ244" t="inlineStr"/>
+      <c r="CK244" t="inlineStr"/>
+      <c r="CL244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>vaTsAHD4</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F245" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="n">
+        <v>55</v>
+      </c>
+      <c r="N245" t="n">
+        <v>45</v>
+      </c>
+      <c r="O245" t="n">
+        <v>17</v>
+      </c>
+      <c r="P245" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>6</v>
+      </c>
+      <c r="R245" t="n">
+        <v>4</v>
+      </c>
+      <c r="S245" t="n">
+        <v>4</v>
+      </c>
+      <c r="T245" t="n">
+        <v>4</v>
+      </c>
+      <c r="U245" t="n">
+        <v>7</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2</v>
+      </c>
+      <c r="W245" t="n">
+        <v>17</v>
+      </c>
+      <c r="X245" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>444</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>357</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>357</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>265</v>
+      </c>
+      <c r="AO245" t="inlineStr"/>
+      <c r="AP245" t="inlineStr"/>
+      <c r="AQ245" t="inlineStr"/>
+      <c r="AR245" t="inlineStr"/>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AT245" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AU245" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr"/>
+      <c r="BA245" t="inlineStr"/>
+      <c r="BB245" t="inlineStr"/>
+      <c r="BC245" t="inlineStr"/>
+      <c r="BD245" t="inlineStr"/>
+      <c r="BE245" t="inlineStr"/>
+      <c r="BF245" t="inlineStr"/>
+      <c r="BG245" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI245" t="inlineStr"/>
+      <c r="BJ245" t="inlineStr"/>
+      <c r="BK245" t="inlineStr"/>
+      <c r="BL245" t="inlineStr"/>
+      <c r="BM245" t="inlineStr"/>
+      <c r="BN245" t="inlineStr"/>
+      <c r="BO245" t="inlineStr"/>
+      <c r="BP245" t="inlineStr"/>
+      <c r="BQ245" t="inlineStr"/>
+      <c r="BR245" t="inlineStr"/>
+      <c r="BS245" t="inlineStr"/>
+      <c r="BT245" t="inlineStr"/>
+      <c r="BU245" t="inlineStr"/>
+      <c r="BV245" t="inlineStr"/>
+      <c r="BW245" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="BX245" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="BY245" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ245" t="inlineStr"/>
+      <c r="CA245" t="inlineStr"/>
+      <c r="CB245" t="inlineStr"/>
+      <c r="CC245" t="inlineStr"/>
+      <c r="CD245" t="inlineStr"/>
+      <c r="CE245" t="inlineStr"/>
+      <c r="CF245" t="inlineStr"/>
+      <c r="CG245" t="inlineStr"/>
+      <c r="CH245" t="inlineStr"/>
+      <c r="CI245" t="inlineStr"/>
+      <c r="CJ245" t="inlineStr"/>
+      <c r="CK245" t="inlineStr"/>
+      <c r="CL245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>4USV4sgM</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F246" t="n">
+        <v>5405</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>59</v>
+      </c>
+      <c r="N246" t="n">
+        <v>41</v>
+      </c>
+      <c r="O246" t="n">
+        <v>12</v>
+      </c>
+      <c r="P246" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>3</v>
+      </c>
+      <c r="R246" t="n">
+        <v>1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>5</v>
+      </c>
+      <c r="T246" t="n">
+        <v>6</v>
+      </c>
+      <c r="U246" t="n">
+        <v>4</v>
+      </c>
+      <c r="V246" t="n">
+        <v>6</v>
+      </c>
+      <c r="W246" t="n">
+        <v>11</v>
+      </c>
+      <c r="X246" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>540</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>352</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>456</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>274</v>
+      </c>
+      <c r="AO246" t="inlineStr"/>
+      <c r="AP246" t="inlineStr"/>
+      <c r="AQ246" t="inlineStr"/>
+      <c r="AR246" t="inlineStr"/>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AT246" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AU246" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr"/>
+      <c r="BA246" t="inlineStr"/>
+      <c r="BB246" t="inlineStr"/>
+      <c r="BC246" t="inlineStr"/>
+      <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI246" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="BJ246" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="BK246" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BM246" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BN246" t="n">
+        <v>11000</v>
+      </c>
+      <c r="BO246" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BP246" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BQ246" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BR246" t="n">
+        <v>4875</v>
+      </c>
+      <c r="BS246" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="BT246" t="n">
+        <v>183.0555555555555</v>
+      </c>
+      <c r="BU246" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="BV246" t="inlineStr"/>
+      <c r="BW246" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="BX246" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="BY246" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="BZ246" t="n">
+        <v>3733.333333333333</v>
+      </c>
+      <c r="CA246" t="inlineStr"/>
+      <c r="CB246" t="inlineStr"/>
+      <c r="CC246" t="inlineStr"/>
+      <c r="CD246" t="inlineStr"/>
+      <c r="CE246" t="inlineStr"/>
+      <c r="CF246" t="inlineStr"/>
+      <c r="CG246" t="inlineStr"/>
+      <c r="CH246" t="inlineStr"/>
+      <c r="CI246" t="inlineStr"/>
+      <c r="CJ246" t="inlineStr"/>
+      <c r="CK246" t="inlineStr"/>
+      <c r="CL246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>8vLb6ZCT</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3204</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>49</v>
+      </c>
+      <c r="N247" t="n">
+        <v>51</v>
+      </c>
+      <c r="O247" t="n">
+        <v>12</v>
+      </c>
+      <c r="P247" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>4</v>
+      </c>
+      <c r="R247" t="n">
+        <v>5</v>
+      </c>
+      <c r="S247" t="n">
+        <v>7</v>
+      </c>
+      <c r="T247" t="n">
+        <v>6</v>
+      </c>
+      <c r="U247" t="n">
+        <v>1</v>
+      </c>
+      <c r="V247" t="n">
+        <v>6</v>
+      </c>
+      <c r="W247" t="n">
+        <v>12</v>
+      </c>
+      <c r="X247" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>372</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>396</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>268</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>307</v>
+      </c>
+      <c r="AO247" t="inlineStr"/>
+      <c r="AP247" t="inlineStr"/>
+      <c r="AQ247" t="inlineStr"/>
+      <c r="AR247" t="inlineStr"/>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AT247" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AU247" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr"/>
+      <c r="BA247" t="inlineStr"/>
+      <c r="BB247" t="inlineStr"/>
+      <c r="BC247" t="inlineStr"/>
+      <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>41</v>
+      </c>
+      <c r="BI247" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="BJ247" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="inlineStr"/>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
+      <c r="BO247" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="BP247" t="n">
+        <v>184.375</v>
+      </c>
+      <c r="BQ247" t="n">
+        <v>67</v>
+      </c>
+      <c r="BR247" t="n">
+        <v>4250</v>
+      </c>
+      <c r="BS247" t="inlineStr"/>
+      <c r="BT247" t="inlineStr"/>
+      <c r="BU247" t="inlineStr"/>
+      <c r="BV247" t="inlineStr"/>
+      <c r="BW247" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BX247" t="n">
+        <v>185.5833333333333</v>
+      </c>
+      <c r="BY247" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="BZ247" t="n">
+        <v>6833.333333333333</v>
+      </c>
+      <c r="CA247" t="inlineStr"/>
+      <c r="CB247" t="inlineStr"/>
+      <c r="CC247" t="inlineStr"/>
+      <c r="CD247" t="inlineStr"/>
+      <c r="CE247" t="inlineStr"/>
+      <c r="CF247" t="inlineStr"/>
+      <c r="CG247" t="inlineStr"/>
+      <c r="CH247" t="inlineStr"/>
+      <c r="CI247" t="inlineStr"/>
+      <c r="CJ247" t="inlineStr"/>
+      <c r="CK247" t="inlineStr"/>
+      <c r="CL247" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL247"/>
+  <dimension ref="A1:CL256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63963,6 +63963,2190 @@
       <c r="CK247" t="inlineStr"/>
       <c r="CL247" t="inlineStr"/>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F248" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G248" t="n">
+        <v>2</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M248" t="n">
+        <v>49</v>
+      </c>
+      <c r="N248" t="n">
+        <v>51</v>
+      </c>
+      <c r="O248" t="n">
+        <v>11</v>
+      </c>
+      <c r="P248" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>2</v>
+      </c>
+      <c r="R248" t="n">
+        <v>1</v>
+      </c>
+      <c r="S248" t="n">
+        <v>6</v>
+      </c>
+      <c r="T248" t="n">
+        <v>2</v>
+      </c>
+      <c r="U248" t="n">
+        <v>3</v>
+      </c>
+      <c r="V248" t="n">
+        <v>2</v>
+      </c>
+      <c r="W248" t="n">
+        <v>9</v>
+      </c>
+      <c r="X248" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>526</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>548</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>473</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>499</v>
+      </c>
+      <c r="AO248" t="inlineStr"/>
+      <c r="AP248" t="inlineStr"/>
+      <c r="AQ248" t="inlineStr"/>
+      <c r="AR248" t="inlineStr"/>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AT248" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AU248" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr"/>
+      <c r="BA248" t="inlineStr"/>
+      <c r="BB248" t="inlineStr"/>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BJ248" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="BK248" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="BL248" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="BM248" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="BN248" t="n">
+        <v>72545.45454545454</v>
+      </c>
+      <c r="BO248" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="BP248" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="BQ248" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="BR248" t="n">
+        <v>24666.66666666667</v>
+      </c>
+      <c r="BS248" t="n">
+        <v>25.79166666666667</v>
+      </c>
+      <c r="BT248" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BU248" t="n">
+        <v>76.41666666666667</v>
+      </c>
+      <c r="BV248" t="n">
+        <v>53125</v>
+      </c>
+      <c r="BW248" t="n">
+        <v>28.84615384615385</v>
+      </c>
+      <c r="BX248" t="n">
+        <v>180.6923076923077</v>
+      </c>
+      <c r="BY248" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="BZ248" t="n">
+        <v>35153.84615384616</v>
+      </c>
+      <c r="CA248" t="n">
+        <v>29</v>
+      </c>
+      <c r="CB248" t="n">
+        <v>181</v>
+      </c>
+      <c r="CC248" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="CD248" t="n">
+        <v>54500</v>
+      </c>
+      <c r="CE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF248" t="n">
+        <v>163</v>
+      </c>
+      <c r="CG248" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="CH248" t="n">
+        <v>181</v>
+      </c>
+      <c r="CI248" t="n">
+        <v>73</v>
+      </c>
+      <c r="CJ248" t="n">
+        <v>32250</v>
+      </c>
+      <c r="CK248" t="n">
+        <v>4</v>
+      </c>
+      <c r="CL248" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F249" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M249" t="n">
+        <v>37</v>
+      </c>
+      <c r="N249" t="n">
+        <v>63</v>
+      </c>
+      <c r="O249" t="n">
+        <v>8</v>
+      </c>
+      <c r="P249" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>1</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4</v>
+      </c>
+      <c r="T249" t="n">
+        <v>6</v>
+      </c>
+      <c r="U249" t="n">
+        <v>3</v>
+      </c>
+      <c r="V249" t="n">
+        <v>7</v>
+      </c>
+      <c r="W249" t="n">
+        <v>14</v>
+      </c>
+      <c r="X249" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>343</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>584</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>234</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>456</v>
+      </c>
+      <c r="AO249" t="inlineStr"/>
+      <c r="AP249" t="inlineStr"/>
+      <c r="AQ249" t="inlineStr"/>
+      <c r="AR249" t="inlineStr"/>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AT249" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AU249" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA249" t="inlineStr"/>
+      <c r="BB249" t="inlineStr"/>
+      <c r="BC249" t="inlineStr"/>
+      <c r="BD249" t="inlineStr"/>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
+      <c r="BI249" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BJ249" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BK249" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BM249" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BN249" t="inlineStr"/>
+      <c r="BO249" t="n">
+        <v>24</v>
+      </c>
+      <c r="BP249" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="BQ249" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="BR249" t="n">
+        <v>39000</v>
+      </c>
+      <c r="BS249" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="BT249" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="BU249" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="BV249" t="n">
+        <v>17050</v>
+      </c>
+      <c r="BW249" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="BX249" t="n">
+        <v>181.7037037037037</v>
+      </c>
+      <c r="BY249" t="n">
+        <v>75.07407407407408</v>
+      </c>
+      <c r="BZ249" t="inlineStr"/>
+      <c r="CA249" t="n">
+        <v>24</v>
+      </c>
+      <c r="CB249" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="CC249" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="CD249" t="n">
+        <v>8800</v>
+      </c>
+      <c r="CE249" t="n">
+        <v>5</v>
+      </c>
+      <c r="CF249" t="n">
+        <v>351</v>
+      </c>
+      <c r="CG249" t="n">
+        <v>25</v>
+      </c>
+      <c r="CH249" t="n">
+        <v>193</v>
+      </c>
+      <c r="CI249" t="n">
+        <v>76</v>
+      </c>
+      <c r="CJ249" t="n">
+        <v>15000</v>
+      </c>
+      <c r="CK249" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL249" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F250" t="n">
+        <v>62165</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M250" t="n">
+        <v>70</v>
+      </c>
+      <c r="N250" t="n">
+        <v>30</v>
+      </c>
+      <c r="O250" t="n">
+        <v>22</v>
+      </c>
+      <c r="P250" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>5</v>
+      </c>
+      <c r="R250" t="n">
+        <v>7</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="n">
+        <v>5</v>
+      </c>
+      <c r="U250" t="n">
+        <v>7</v>
+      </c>
+      <c r="V250" t="n">
+        <v>6</v>
+      </c>
+      <c r="W250" t="n">
+        <v>15</v>
+      </c>
+      <c r="X250" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>577</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>248</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>496</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>186</v>
+      </c>
+      <c r="AO250" t="inlineStr"/>
+      <c r="AP250" t="inlineStr"/>
+      <c r="AQ250" t="inlineStr"/>
+      <c r="AR250" t="inlineStr"/>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AT250" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AU250" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr"/>
+      <c r="BA250" t="inlineStr"/>
+      <c r="BB250" t="inlineStr"/>
+      <c r="BC250" t="inlineStr"/>
+      <c r="BD250" t="inlineStr"/>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr"/>
+      <c r="BH250" t="inlineStr"/>
+      <c r="BI250" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="BJ250" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="BK250" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BM250" t="n">
+        <v>77.88888888888889</v>
+      </c>
+      <c r="BN250" t="n">
+        <v>51555.55555555555</v>
+      </c>
+      <c r="BO250" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="BP250" t="n">
+        <v>182</v>
+      </c>
+      <c r="BQ250" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="BR250" t="n">
+        <v>11333.33333333333</v>
+      </c>
+      <c r="BS250" t="n">
+        <v>24.72222222222222</v>
+      </c>
+      <c r="BT250" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="BU250" t="n">
+        <v>75.83333333333333</v>
+      </c>
+      <c r="BV250" t="n">
+        <v>52277.77777777778</v>
+      </c>
+      <c r="BW250" t="n">
+        <v>25.58823529411765</v>
+      </c>
+      <c r="BX250" t="n">
+        <v>184.7058823529412</v>
+      </c>
+      <c r="BY250" t="n">
+        <v>67.70588235294117</v>
+      </c>
+      <c r="BZ250" t="inlineStr"/>
+      <c r="CA250" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CB250" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="CC250" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="CD250" t="n">
+        <v>45000</v>
+      </c>
+      <c r="CE250" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF250" t="n">
+        <v>155</v>
+      </c>
+      <c r="CG250" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CH250" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CI250" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="CJ250" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CK250" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL250" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F251" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M251" t="n">
+        <v>72</v>
+      </c>
+      <c r="N251" t="n">
+        <v>28</v>
+      </c>
+      <c r="O251" t="n">
+        <v>24</v>
+      </c>
+      <c r="P251" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>11</v>
+      </c>
+      <c r="R251" t="n">
+        <v>3</v>
+      </c>
+      <c r="S251" t="n">
+        <v>7</v>
+      </c>
+      <c r="T251" t="n">
+        <v>2</v>
+      </c>
+      <c r="U251" t="n">
+        <v>6</v>
+      </c>
+      <c r="V251" t="n">
+        <v>1</v>
+      </c>
+      <c r="W251" t="n">
+        <v>22</v>
+      </c>
+      <c r="X251" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>573</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>232</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>510</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>167</v>
+      </c>
+      <c r="AO251" t="inlineStr"/>
+      <c r="AP251" t="inlineStr"/>
+      <c r="AQ251" t="inlineStr"/>
+      <c r="AR251" t="inlineStr"/>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AT251" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AU251" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr"/>
+      <c r="BA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB251" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC251" t="inlineStr"/>
+      <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
+      <c r="BI251" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="BJ251" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BK251" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>29000</v>
+      </c>
+      <c r="BO251" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BP251" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BQ251" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="BR251" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="BS251" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BT251" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="BU251" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BV251" t="n">
+        <v>19850</v>
+      </c>
+      <c r="BW251" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BX251" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BY251" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BZ251" t="n">
+        <v>15050</v>
+      </c>
+      <c r="CA251" t="inlineStr"/>
+      <c r="CB251" t="inlineStr"/>
+      <c r="CC251" t="inlineStr"/>
+      <c r="CD251" t="inlineStr"/>
+      <c r="CE251" t="inlineStr"/>
+      <c r="CF251" t="inlineStr"/>
+      <c r="CG251" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="CH251" t="n">
+        <v>185</v>
+      </c>
+      <c r="CI251" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="CJ251" t="n">
+        <v>13200</v>
+      </c>
+      <c r="CK251" t="n">
+        <v>5</v>
+      </c>
+      <c r="CL251" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F252" t="n">
+        <v>23130</v>
+      </c>
+      <c r="G252" t="n">
+        <v>2</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M252" t="n">
+        <v>58</v>
+      </c>
+      <c r="N252" t="n">
+        <v>42</v>
+      </c>
+      <c r="O252" t="n">
+        <v>12</v>
+      </c>
+      <c r="P252" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>7</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4</v>
+      </c>
+      <c r="T252" t="n">
+        <v>5</v>
+      </c>
+      <c r="U252" t="n">
+        <v>1</v>
+      </c>
+      <c r="V252" t="n">
+        <v>1</v>
+      </c>
+      <c r="W252" t="n">
+        <v>14</v>
+      </c>
+      <c r="X252" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>485</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>360</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>408</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>277</v>
+      </c>
+      <c r="AO252" t="inlineStr"/>
+      <c r="AP252" t="inlineStr"/>
+      <c r="AQ252" t="inlineStr"/>
+      <c r="AR252" t="inlineStr"/>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AU252" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr"/>
+      <c r="BA252" t="inlineStr"/>
+      <c r="BB252" t="inlineStr"/>
+      <c r="BC252" t="inlineStr"/>
+      <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="inlineStr"/>
+      <c r="BI252" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BJ252" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="BK252" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>32625</v>
+      </c>
+      <c r="BO252" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="BQ252" t="n">
+        <v>77.81818181818181</v>
+      </c>
+      <c r="BR252" t="n">
+        <v>49454.54545454546</v>
+      </c>
+      <c r="BS252" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="BT252" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="BU252" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="BV252" t="n">
+        <v>30476.19047619048</v>
+      </c>
+      <c r="BW252" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BX252" t="n">
+        <v>182</v>
+      </c>
+      <c r="BY252" t="n">
+        <v>73.83333333333333</v>
+      </c>
+      <c r="BZ252" t="n">
+        <v>35458.33333333334</v>
+      </c>
+      <c r="CA252" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB252" t="n">
+        <v>183</v>
+      </c>
+      <c r="CC252" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="CD252" t="n">
+        <v>22000</v>
+      </c>
+      <c r="CE252" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF252" t="n">
+        <v>143</v>
+      </c>
+      <c r="CG252" t="n">
+        <v>29</v>
+      </c>
+      <c r="CH252" t="n">
+        <v>187</v>
+      </c>
+      <c r="CI252" t="n">
+        <v>78</v>
+      </c>
+      <c r="CJ252" t="n">
+        <v>38000</v>
+      </c>
+      <c r="CK252" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL252" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>nPWk8erH</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F253" t="n">
+        <v>12326</v>
+      </c>
+      <c r="G253" t="n">
+        <v>4</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="n">
+        <v>30</v>
+      </c>
+      <c r="N253" t="n">
+        <v>70</v>
+      </c>
+      <c r="O253" t="n">
+        <v>16</v>
+      </c>
+      <c r="P253" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>9</v>
+      </c>
+      <c r="R253" t="n">
+        <v>5</v>
+      </c>
+      <c r="S253" t="n">
+        <v>5</v>
+      </c>
+      <c r="T253" t="n">
+        <v>7</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2</v>
+      </c>
+      <c r="V253" t="n">
+        <v>4</v>
+      </c>
+      <c r="W253" t="n">
+        <v>11</v>
+      </c>
+      <c r="X253" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>239</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>545</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>196</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>491</v>
+      </c>
+      <c r="AO253" t="inlineStr"/>
+      <c r="AP253" t="inlineStr"/>
+      <c r="AQ253" t="inlineStr"/>
+      <c r="AR253" t="inlineStr"/>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AT253" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AU253" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr"/>
+      <c r="BA253" t="inlineStr"/>
+      <c r="BB253" t="inlineStr"/>
+      <c r="BC253" t="inlineStr"/>
+      <c r="BD253" t="inlineStr"/>
+      <c r="BE253" t="inlineStr"/>
+      <c r="BF253" t="inlineStr"/>
+      <c r="BG253" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI253" t="inlineStr"/>
+      <c r="BJ253" t="inlineStr"/>
+      <c r="BK253" t="inlineStr"/>
+      <c r="BL253" t="inlineStr"/>
+      <c r="BM253" t="inlineStr"/>
+      <c r="BN253" t="inlineStr"/>
+      <c r="BO253" t="inlineStr"/>
+      <c r="BP253" t="inlineStr"/>
+      <c r="BQ253" t="inlineStr"/>
+      <c r="BR253" t="inlineStr"/>
+      <c r="BS253" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="BT253" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="BU253" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="BV253" t="n">
+        <v>11875</v>
+      </c>
+      <c r="BW253" t="inlineStr"/>
+      <c r="BX253" t="inlineStr"/>
+      <c r="BY253" t="inlineStr"/>
+      <c r="BZ253" t="inlineStr"/>
+      <c r="CA253" t="inlineStr"/>
+      <c r="CB253" t="inlineStr"/>
+      <c r="CC253" t="inlineStr"/>
+      <c r="CD253" t="inlineStr"/>
+      <c r="CE253" t="inlineStr"/>
+      <c r="CF253" t="inlineStr"/>
+      <c r="CG253" t="inlineStr"/>
+      <c r="CH253" t="inlineStr"/>
+      <c r="CI253" t="inlineStr"/>
+      <c r="CJ253" t="inlineStr"/>
+      <c r="CK253" t="inlineStr"/>
+      <c r="CL253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>ID6U0Dzi</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F254" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G254" t="n">
+        <v>2</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>59</v>
+      </c>
+      <c r="N254" t="n">
+        <v>41</v>
+      </c>
+      <c r="O254" t="n">
+        <v>13</v>
+      </c>
+      <c r="P254" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>6</v>
+      </c>
+      <c r="R254" t="n">
+        <v>2</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4</v>
+      </c>
+      <c r="T254" t="n">
+        <v>3</v>
+      </c>
+      <c r="U254" t="n">
+        <v>3</v>
+      </c>
+      <c r="V254" t="n">
+        <v>3</v>
+      </c>
+      <c r="W254" t="n">
+        <v>25</v>
+      </c>
+      <c r="X254" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>417</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>276</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>324</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO254" t="inlineStr"/>
+      <c r="AP254" t="inlineStr"/>
+      <c r="AQ254" t="inlineStr"/>
+      <c r="AR254" t="inlineStr"/>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AT254" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AU254" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr"/>
+      <c r="BA254" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB254" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC254" t="inlineStr"/>
+      <c r="BD254" t="inlineStr"/>
+      <c r="BE254" t="inlineStr"/>
+      <c r="BF254" t="inlineStr"/>
+      <c r="BG254" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI254" t="inlineStr"/>
+      <c r="BJ254" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BK254" t="inlineStr"/>
+      <c r="BL254" t="inlineStr"/>
+      <c r="BM254" t="inlineStr"/>
+      <c r="BN254" t="inlineStr"/>
+      <c r="BO254" t="inlineStr"/>
+      <c r="BP254" t="inlineStr"/>
+      <c r="BQ254" t="inlineStr"/>
+      <c r="BR254" t="inlineStr"/>
+      <c r="BS254" t="inlineStr"/>
+      <c r="BT254" t="inlineStr"/>
+      <c r="BU254" t="inlineStr"/>
+      <c r="BV254" t="inlineStr"/>
+      <c r="BW254" t="n">
+        <v>22.36363636363636</v>
+      </c>
+      <c r="BX254" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="BY254" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="BZ254" t="inlineStr"/>
+      <c r="CA254" t="inlineStr"/>
+      <c r="CB254" t="inlineStr"/>
+      <c r="CC254" t="inlineStr"/>
+      <c r="CD254" t="inlineStr"/>
+      <c r="CE254" t="inlineStr"/>
+      <c r="CF254" t="inlineStr"/>
+      <c r="CG254" t="inlineStr"/>
+      <c r="CH254" t="inlineStr"/>
+      <c r="CI254" t="inlineStr"/>
+      <c r="CJ254" t="inlineStr"/>
+      <c r="CK254" t="inlineStr"/>
+      <c r="CL254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>zkyF8Pgc</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>21092</v>
+      </c>
+      <c r="F255" t="n">
+        <v>10101</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="n">
+        <v>3</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="n">
+        <v>44</v>
+      </c>
+      <c r="N255" t="n">
+        <v>56</v>
+      </c>
+      <c r="O255" t="n">
+        <v>8</v>
+      </c>
+      <c r="P255" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>4</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>5</v>
+      </c>
+      <c r="U255" t="n">
+        <v>4</v>
+      </c>
+      <c r="V255" t="n">
+        <v>2</v>
+      </c>
+      <c r="W255" t="n">
+        <v>14</v>
+      </c>
+      <c r="X255" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>295</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>367</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>311</v>
+      </c>
+      <c r="AO255" t="inlineStr"/>
+      <c r="AP255" t="inlineStr"/>
+      <c r="AQ255" t="inlineStr"/>
+      <c r="AR255" t="inlineStr"/>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AT255" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AU255" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr"/>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="inlineStr"/>
+      <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
+      <c r="BG255" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI255" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="BJ255" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="BK255" t="inlineStr"/>
+      <c r="BL255" t="inlineStr"/>
+      <c r="BM255" t="inlineStr"/>
+      <c r="BN255" t="inlineStr"/>
+      <c r="BO255" t="n">
+        <v>28.11111111111111</v>
+      </c>
+      <c r="BP255" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BQ255" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BR255" t="inlineStr"/>
+      <c r="BS255" t="inlineStr"/>
+      <c r="BT255" t="inlineStr"/>
+      <c r="BU255" t="inlineStr"/>
+      <c r="BV255" t="inlineStr"/>
+      <c r="BW255" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BX255" t="n">
+        <v>184.7333333333333</v>
+      </c>
+      <c r="BY255" t="n">
+        <v>68.06666666666666</v>
+      </c>
+      <c r="BZ255" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CA255" t="inlineStr"/>
+      <c r="CB255" t="inlineStr"/>
+      <c r="CC255" t="inlineStr"/>
+      <c r="CD255" t="inlineStr"/>
+      <c r="CE255" t="inlineStr"/>
+      <c r="CF255" t="inlineStr"/>
+      <c r="CG255" t="inlineStr"/>
+      <c r="CH255" t="inlineStr"/>
+      <c r="CI255" t="inlineStr"/>
+      <c r="CJ255" t="inlineStr"/>
+      <c r="CK255" t="inlineStr"/>
+      <c r="CL255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F256" t="n">
+        <v>14932</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>59</v>
+      </c>
+      <c r="N256" t="n">
+        <v>41</v>
+      </c>
+      <c r="O256" t="n">
+        <v>9</v>
+      </c>
+      <c r="P256" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>3</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>3</v>
+      </c>
+      <c r="T256" t="n">
+        <v>3</v>
+      </c>
+      <c r="U256" t="n">
+        <v>3</v>
+      </c>
+      <c r="V256" t="n">
+        <v>0</v>
+      </c>
+      <c r="W256" t="n">
+        <v>19</v>
+      </c>
+      <c r="X256" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>522</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>363</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>465</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO256" t="inlineStr"/>
+      <c r="AP256" t="inlineStr"/>
+      <c r="AQ256" t="inlineStr"/>
+      <c r="AR256" t="inlineStr"/>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AT256" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AU256" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr"/>
+      <c r="BA256" t="inlineStr"/>
+      <c r="BB256" t="inlineStr"/>
+      <c r="BC256" t="inlineStr"/>
+      <c r="BD256" t="inlineStr"/>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI256" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BJ256" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="BK256" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="BM256" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BN256" t="n">
+        <v>14875</v>
+      </c>
+      <c r="BO256" t="inlineStr"/>
+      <c r="BP256" t="inlineStr"/>
+      <c r="BQ256" t="inlineStr"/>
+      <c r="BR256" t="inlineStr"/>
+      <c r="BS256" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT256" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="BU256" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="BV256" t="n">
+        <v>9583.333333333334</v>
+      </c>
+      <c r="BW256" t="n">
+        <v>27.58333333333333</v>
+      </c>
+      <c r="BX256" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BY256" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="BZ256" t="inlineStr"/>
+      <c r="CA256" t="inlineStr"/>
+      <c r="CB256" t="inlineStr"/>
+      <c r="CC256" t="inlineStr"/>
+      <c r="CD256" t="inlineStr"/>
+      <c r="CE256" t="inlineStr"/>
+      <c r="CF256" t="inlineStr"/>
+      <c r="CG256" t="inlineStr"/>
+      <c r="CH256" t="inlineStr"/>
+      <c r="CI256" t="inlineStr"/>
+      <c r="CJ256" t="inlineStr"/>
+      <c r="CK256" t="inlineStr"/>
+      <c r="CL256" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ259"/>
+  <dimension ref="A1:CZ268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77683,6 +77683,2656 @@
       <c r="CY259" t="inlineStr"/>
       <c r="CZ259" t="inlineStr"/>
     </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>45570.54166666666</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="n">
+        <v>5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M260" t="n">
+        <v>67</v>
+      </c>
+      <c r="N260" t="n">
+        <v>33</v>
+      </c>
+      <c r="O260" t="n">
+        <v>22</v>
+      </c>
+      <c r="P260" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>10</v>
+      </c>
+      <c r="R260" t="n">
+        <v>3</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1</v>
+      </c>
+      <c r="U260" t="n">
+        <v>4</v>
+      </c>
+      <c r="V260" t="n">
+        <v>3</v>
+      </c>
+      <c r="W260" t="n">
+        <v>15</v>
+      </c>
+      <c r="X260" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI260" t="inlineStr"/>
+      <c r="AJ260" t="inlineStr"/>
+      <c r="AK260" t="n">
+        <v>613</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>362</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>567</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AQ260" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU260" t="inlineStr"/>
+      <c r="AV260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr"/>
+      <c r="AX260" t="inlineStr"/>
+      <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr"/>
+      <c r="BA260" t="inlineStr"/>
+      <c r="BB260" t="inlineStr"/>
+      <c r="BC260" t="inlineStr"/>
+      <c r="BD260" t="inlineStr"/>
+      <c r="BE260" t="inlineStr"/>
+      <c r="BF260" t="inlineStr"/>
+      <c r="BG260" t="inlineStr"/>
+      <c r="BH260" t="inlineStr"/>
+      <c r="BI260" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>60909.09090909091</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>20818181.81818182</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="BQ260" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="BR260" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="BS260" t="n">
+        <v>33636.36363636364</v>
+      </c>
+      <c r="BT260" t="n">
+        <v>4454545.454545454</v>
+      </c>
+      <c r="BU260" t="n">
+        <v>76.81818181818181</v>
+      </c>
+      <c r="BV260" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BW260" t="n">
+        <v>23.63157894736842</v>
+      </c>
+      <c r="BX260" t="n">
+        <v>185</v>
+      </c>
+      <c r="BY260" t="n">
+        <v>71.78947368421052</v>
+      </c>
+      <c r="BZ260" t="n">
+        <v>36947.36842105263</v>
+      </c>
+      <c r="CA260" t="n">
+        <v>12145789.47368421</v>
+      </c>
+      <c r="CB260" t="n">
+        <v>78.78947368421052</v>
+      </c>
+      <c r="CC260" t="n">
+        <v>1.368421052631579</v>
+      </c>
+      <c r="CD260" t="n">
+        <v>24.47619047619047</v>
+      </c>
+      <c r="CE260" t="n">
+        <v>184.8095238095238</v>
+      </c>
+      <c r="CF260" t="n">
+        <v>66.0952380952381</v>
+      </c>
+      <c r="CG260" t="n">
+        <v>25142.85714285714</v>
+      </c>
+      <c r="CH260" t="n">
+        <v>1808333.333333333</v>
+      </c>
+      <c r="CI260" t="n">
+        <v>71.57142857142857</v>
+      </c>
+      <c r="CJ260" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK260" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="CL260" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="CM260" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN260" t="n">
+        <v>377</v>
+      </c>
+      <c r="CO260" t="n">
+        <v>205000</v>
+      </c>
+      <c r="CP260" t="n">
+        <v>72800000</v>
+      </c>
+      <c r="CQ260" t="n">
+        <v>407</v>
+      </c>
+      <c r="CR260" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS260" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="CT260" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="CU260" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV260" t="n">
+        <v>371</v>
+      </c>
+      <c r="CW260" t="n">
+        <v>185000</v>
+      </c>
+      <c r="CX260" t="n">
+        <v>24950000</v>
+      </c>
+      <c r="CY260" t="n">
+        <v>375</v>
+      </c>
+      <c r="CZ260" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F261" t="n">
+        <v>21441</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M261" t="n">
+        <v>56</v>
+      </c>
+      <c r="N261" t="n">
+        <v>44</v>
+      </c>
+      <c r="O261" t="n">
+        <v>13</v>
+      </c>
+      <c r="P261" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>4</v>
+      </c>
+      <c r="R261" t="n">
+        <v>3</v>
+      </c>
+      <c r="S261" t="n">
+        <v>5</v>
+      </c>
+      <c r="T261" t="n">
+        <v>5</v>
+      </c>
+      <c r="U261" t="n">
+        <v>4</v>
+      </c>
+      <c r="V261" t="n">
+        <v>1</v>
+      </c>
+      <c r="W261" t="n">
+        <v>22</v>
+      </c>
+      <c r="X261" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>459</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>371</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>272</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AQ261" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU261" t="inlineStr"/>
+      <c r="AV261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr"/>
+      <c r="AX261" t="inlineStr"/>
+      <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr"/>
+      <c r="BA261" t="inlineStr"/>
+      <c r="BB261" t="inlineStr"/>
+      <c r="BC261" t="inlineStr"/>
+      <c r="BD261" t="inlineStr"/>
+      <c r="BE261" t="inlineStr"/>
+      <c r="BF261" t="inlineStr"/>
+      <c r="BG261" t="inlineStr"/>
+      <c r="BH261" t="inlineStr"/>
+      <c r="BI261" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>186</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>14875</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BQ261" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BR261" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BS261" t="n">
+        <v>12250</v>
+      </c>
+      <c r="BT261" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="BU261" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="BV261" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW261" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX261" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BY261" t="n">
+        <v>68.77777777777777</v>
+      </c>
+      <c r="BZ261" t="n">
+        <v>14055.55555555555</v>
+      </c>
+      <c r="CA261" t="n">
+        <v>2065277.777777778</v>
+      </c>
+      <c r="CB261" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="CC261" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD261" t="n">
+        <v>25.06666666666667</v>
+      </c>
+      <c r="CE261" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="CF261" t="n">
+        <v>68</v>
+      </c>
+      <c r="CG261" t="n">
+        <v>10200</v>
+      </c>
+      <c r="CH261" t="n">
+        <v>2090000</v>
+      </c>
+      <c r="CI261" t="n">
+        <v>72.86666666666666</v>
+      </c>
+      <c r="CJ261" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK261" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="CL261" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="CM261" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN261" t="n">
+        <v>295</v>
+      </c>
+      <c r="CO261" t="n">
+        <v>70000</v>
+      </c>
+      <c r="CP261" t="n">
+        <v>28200000</v>
+      </c>
+      <c r="CQ261" t="n">
+        <v>311</v>
+      </c>
+      <c r="CR261" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS261" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT261" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="CU261" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV261" t="n">
+        <v>343</v>
+      </c>
+      <c r="CW261" t="n">
+        <v>48000</v>
+      </c>
+      <c r="CX261" t="n">
+        <v>14850000</v>
+      </c>
+      <c r="CY261" t="n">
+        <v>387</v>
+      </c>
+      <c r="CZ261" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F262" t="n">
+        <v>25979</v>
+      </c>
+      <c r="G262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L262" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M262" t="n">
+        <v>50</v>
+      </c>
+      <c r="N262" t="n">
+        <v>50</v>
+      </c>
+      <c r="O262" t="n">
+        <v>20</v>
+      </c>
+      <c r="P262" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>3</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="n">
+        <v>8</v>
+      </c>
+      <c r="U262" t="n">
+        <v>7</v>
+      </c>
+      <c r="V262" t="n">
+        <v>4</v>
+      </c>
+      <c r="W262" t="n">
+        <v>5</v>
+      </c>
+      <c r="X262" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>281</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>292</v>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AQ262" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU262" t="inlineStr"/>
+      <c r="AV262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr"/>
+      <c r="AX262" t="inlineStr"/>
+      <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr"/>
+      <c r="BA262" t="inlineStr"/>
+      <c r="BB262" t="inlineStr"/>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+      <c r="BI262" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>12375</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>4175000</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="BQ262" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="BR262" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BS262" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BT262" t="n">
+        <v>2970000</v>
+      </c>
+      <c r="BU262" t="n">
+        <v>75</v>
+      </c>
+      <c r="BV262" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW262" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="BX262" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BY262" t="n">
+        <v>69.71428571428571</v>
+      </c>
+      <c r="BZ262" t="n">
+        <v>8500</v>
+      </c>
+      <c r="CA262" t="n">
+        <v>3120000</v>
+      </c>
+      <c r="CB262" t="n">
+        <v>75.35714285714286</v>
+      </c>
+      <c r="CC262" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD262" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="CE262" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="CF262" t="n">
+        <v>68.68181818181819</v>
+      </c>
+      <c r="CG262" t="n">
+        <v>14136.36363636364</v>
+      </c>
+      <c r="CH262" t="n">
+        <v>2061590.909090909</v>
+      </c>
+      <c r="CI262" t="n">
+        <v>74.09090909090909</v>
+      </c>
+      <c r="CJ262" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK262" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="CL262" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="CM262" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN262" t="n">
+        <v>363</v>
+      </c>
+      <c r="CO262" t="n">
+        <v>76000</v>
+      </c>
+      <c r="CP262" t="n">
+        <v>29600000</v>
+      </c>
+      <c r="CQ262" t="n">
+        <v>381</v>
+      </c>
+      <c r="CR262" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS262" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="CT262" t="n">
+        <v>179</v>
+      </c>
+      <c r="CU262" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV262" t="n">
+        <v>139</v>
+      </c>
+      <c r="CW262" t="n">
+        <v>22000</v>
+      </c>
+      <c r="CX262" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="CY262" t="n">
+        <v>145</v>
+      </c>
+      <c r="CZ262" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45569.5625</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F263" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G263" t="n">
+        <v>3</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M263" t="n">
+        <v>41</v>
+      </c>
+      <c r="N263" t="n">
+        <v>59</v>
+      </c>
+      <c r="O263" t="n">
+        <v>9</v>
+      </c>
+      <c r="P263" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>6</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>8</v>
+      </c>
+      <c r="U263" t="n">
+        <v>3</v>
+      </c>
+      <c r="V263" t="n">
+        <v>1</v>
+      </c>
+      <c r="W263" t="n">
+        <v>8</v>
+      </c>
+      <c r="X263" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>469</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>681</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>394</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>620</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AQ263" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU263" t="inlineStr"/>
+      <c r="AV263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr"/>
+      <c r="AX263" t="inlineStr"/>
+      <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr"/>
+      <c r="BA263" t="inlineStr"/>
+      <c r="BB263" t="inlineStr"/>
+      <c r="BC263" t="inlineStr"/>
+      <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
+      <c r="BI263" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>106900</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>26450000</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BP263" t="inlineStr"/>
+      <c r="BQ263" t="inlineStr"/>
+      <c r="BR263" t="inlineStr"/>
+      <c r="BS263" t="inlineStr"/>
+      <c r="BT263" t="inlineStr"/>
+      <c r="BU263" t="inlineStr"/>
+      <c r="BV263" t="inlineStr"/>
+      <c r="BW263" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX263" t="n">
+        <v>181.65</v>
+      </c>
+      <c r="BY263" t="n">
+        <v>76.45</v>
+      </c>
+      <c r="BZ263" t="n">
+        <v>89450</v>
+      </c>
+      <c r="CA263" t="n">
+        <v>14463750</v>
+      </c>
+      <c r="CB263" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="CC263" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CD263" t="n">
+        <v>29.35294117647059</v>
+      </c>
+      <c r="CE263" t="n">
+        <v>179.1176470588235</v>
+      </c>
+      <c r="CF263" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="CG263" t="n">
+        <v>25470.58823529412</v>
+      </c>
+      <c r="CH263" t="n">
+        <v>5489705.882352941</v>
+      </c>
+      <c r="CI263" t="n">
+        <v>74.64705882352941</v>
+      </c>
+      <c r="CJ263" t="n">
+        <v>1.470588235294118</v>
+      </c>
+      <c r="CK263" t="n">
+        <v>30</v>
+      </c>
+      <c r="CL263" t="n">
+        <v>181</v>
+      </c>
+      <c r="CM263" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN263" t="n">
+        <v>160</v>
+      </c>
+      <c r="CO263" t="n">
+        <v>169000</v>
+      </c>
+      <c r="CP263" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="CQ263" t="n">
+        <v>162</v>
+      </c>
+      <c r="CR263" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS263" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT263" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="CU263" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV263" t="n">
+        <v>139</v>
+      </c>
+      <c r="CW263" t="n">
+        <v>43000</v>
+      </c>
+      <c r="CX263" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="CY263" t="n">
+        <v>139</v>
+      </c>
+      <c r="CZ263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>xd6CHKxS</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="n">
+        <v>58</v>
+      </c>
+      <c r="N264" t="n">
+        <v>42</v>
+      </c>
+      <c r="O264" t="n">
+        <v>15</v>
+      </c>
+      <c r="P264" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>3</v>
+      </c>
+      <c r="R264" t="n">
+        <v>3</v>
+      </c>
+      <c r="S264" t="n">
+        <v>9</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1</v>
+      </c>
+      <c r="U264" t="n">
+        <v>3</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>17</v>
+      </c>
+      <c r="X264" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>437</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>314</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>365</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>229</v>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AQ264" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU264" t="inlineStr"/>
+      <c r="AV264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr"/>
+      <c r="AX264" t="inlineStr"/>
+      <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr"/>
+      <c r="BA264" t="inlineStr"/>
+      <c r="BB264" t="inlineStr"/>
+      <c r="BC264" t="inlineStr"/>
+      <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
+      <c r="BI264" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>11100</v>
+      </c>
+      <c r="BM264" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="BN264" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="BO264" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP264" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="BQ264" t="n">
+        <v>180.5454545454545</v>
+      </c>
+      <c r="BR264" t="n">
+        <v>64.81818181818181</v>
+      </c>
+      <c r="BS264" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BT264" t="n">
+        <v>1045454.545454545</v>
+      </c>
+      <c r="BU264" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="BV264" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW264" t="n">
+        <v>23.95454545454545</v>
+      </c>
+      <c r="BX264" t="n">
+        <v>182.8636363636364</v>
+      </c>
+      <c r="BY264" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="BZ264" t="n">
+        <v>9772.727272727272</v>
+      </c>
+      <c r="CA264" t="n">
+        <v>1595000</v>
+      </c>
+      <c r="CB264" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="CC264" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD264" t="n">
+        <v>26.34782608695652</v>
+      </c>
+      <c r="CE264" t="n">
+        <v>179.8260869565217</v>
+      </c>
+      <c r="CF264" t="n">
+        <v>64.8695652173913</v>
+      </c>
+      <c r="CG264" t="n">
+        <v>3347.826086956522</v>
+      </c>
+      <c r="CH264" t="n">
+        <v>972608.6956521739</v>
+      </c>
+      <c r="CI264" t="n">
+        <v>67.78260869565217</v>
+      </c>
+      <c r="CJ264" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK264" t="n">
+        <v>22</v>
+      </c>
+      <c r="CL264" t="n">
+        <v>191.25</v>
+      </c>
+      <c r="CM264" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN264" t="n">
+        <v>260</v>
+      </c>
+      <c r="CO264" t="n">
+        <v>83000</v>
+      </c>
+      <c r="CP264" t="n">
+        <v>5875000</v>
+      </c>
+      <c r="CQ264" t="n">
+        <v>294</v>
+      </c>
+      <c r="CR264" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS264" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="CT264" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="CU264" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV264" t="n">
+        <v>187</v>
+      </c>
+      <c r="CW264" t="n">
+        <v>30000</v>
+      </c>
+      <c r="CX264" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="CY264" t="n">
+        <v>210</v>
+      </c>
+      <c r="CZ264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>8xjWXuN8</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="n">
+        <v>3</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="n">
+        <v>39</v>
+      </c>
+      <c r="N265" t="n">
+        <v>61</v>
+      </c>
+      <c r="O265" t="n">
+        <v>14</v>
+      </c>
+      <c r="P265" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>7</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2</v>
+      </c>
+      <c r="S265" t="n">
+        <v>3</v>
+      </c>
+      <c r="T265" t="n">
+        <v>4</v>
+      </c>
+      <c r="U265" t="n">
+        <v>4</v>
+      </c>
+      <c r="V265" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" t="n">
+        <v>10</v>
+      </c>
+      <c r="X265" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>196</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>303</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>143</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>253</v>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AQ265" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU265" t="inlineStr"/>
+      <c r="AV265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr"/>
+      <c r="AX265" t="inlineStr"/>
+      <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr"/>
+      <c r="BA265" t="inlineStr"/>
+      <c r="BB265" t="inlineStr"/>
+      <c r="BC265" t="inlineStr"/>
+      <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
+      <c r="BI265" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>3700</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>1277500</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BQ265" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="BR265" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BS265" t="n">
+        <v>2900</v>
+      </c>
+      <c r="BT265" t="n">
+        <v>1312500</v>
+      </c>
+      <c r="BU265" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BV265" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW265" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="BX265" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BY265" t="n">
+        <v>66.05555555555556</v>
+      </c>
+      <c r="BZ265" t="n">
+        <v>7666.666666666667</v>
+      </c>
+      <c r="CA265" t="n">
+        <v>1404166.666666667</v>
+      </c>
+      <c r="CB265" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="CC265" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD265" t="n">
+        <v>25.61904761904762</v>
+      </c>
+      <c r="CE265" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="CF265" t="n">
+        <v>67.28571428571429</v>
+      </c>
+      <c r="CG265" t="n">
+        <v>4904.761904761905</v>
+      </c>
+      <c r="CH265" t="n">
+        <v>1555952.380952381</v>
+      </c>
+      <c r="CI265" t="n">
+        <v>71.38095238095238</v>
+      </c>
+      <c r="CJ265" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK265" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="CL265" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="CM265" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN265" t="n">
+        <v>207</v>
+      </c>
+      <c r="CO265" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CP265" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="CQ265" t="n">
+        <v>227</v>
+      </c>
+      <c r="CR265" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS265" t="inlineStr"/>
+      <c r="CT265" t="inlineStr"/>
+      <c r="CU265" t="inlineStr"/>
+      <c r="CV265" t="inlineStr"/>
+      <c r="CW265" t="inlineStr"/>
+      <c r="CX265" t="inlineStr"/>
+      <c r="CY265" t="inlineStr"/>
+      <c r="CZ265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>8zBCDByf</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="n">
+        <v>6</v>
+      </c>
+      <c r="H266" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="n">
+        <v>58</v>
+      </c>
+      <c r="N266" t="n">
+        <v>42</v>
+      </c>
+      <c r="O266" t="n">
+        <v>19</v>
+      </c>
+      <c r="P266" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>13</v>
+      </c>
+      <c r="R266" t="n">
+        <v>4</v>
+      </c>
+      <c r="S266" t="n">
+        <v>2</v>
+      </c>
+      <c r="T266" t="n">
+        <v>5</v>
+      </c>
+      <c r="U266" t="n">
+        <v>4</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2</v>
+      </c>
+      <c r="W266" t="n">
+        <v>13</v>
+      </c>
+      <c r="X266" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>504</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>350</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>428</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>274</v>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AQ266" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU266" t="inlineStr"/>
+      <c r="AV266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr"/>
+      <c r="AX266" t="inlineStr"/>
+      <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr"/>
+      <c r="BA266" t="inlineStr"/>
+      <c r="BB266" t="inlineStr"/>
+      <c r="BC266" t="inlineStr"/>
+      <c r="BD266" t="inlineStr"/>
+      <c r="BE266" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG266" t="inlineStr"/>
+      <c r="BH266" t="inlineStr"/>
+      <c r="BI266" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>4260000</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="BQ266" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="BR266" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="BS266" t="n">
+        <v>2375</v>
+      </c>
+      <c r="BT266" t="n">
+        <v>953125</v>
+      </c>
+      <c r="BU266" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="BV266" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW266" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="BX266" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="BY266" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BZ266" t="n">
+        <v>4360</v>
+      </c>
+      <c r="CA266" t="n">
+        <v>6354000</v>
+      </c>
+      <c r="CB266" t="n">
+        <v>75.28</v>
+      </c>
+      <c r="CC266" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CD266" t="n">
+        <v>24.05555555555556</v>
+      </c>
+      <c r="CE266" t="n">
+        <v>180.6111111111111</v>
+      </c>
+      <c r="CF266" t="n">
+        <v>64.38888888888889</v>
+      </c>
+      <c r="CG266" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="CH266" t="n">
+        <v>1210833.333333333</v>
+      </c>
+      <c r="CI266" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="CJ266" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK266" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL266" t="n">
+        <v>188</v>
+      </c>
+      <c r="CM266" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN266" t="n">
+        <v>71</v>
+      </c>
+      <c r="CO266" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CP266" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="CQ266" t="n">
+        <v>80</v>
+      </c>
+      <c r="CR266" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS266" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT266" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="CU266" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV266" t="n">
+        <v>244</v>
+      </c>
+      <c r="CW266" t="inlineStr"/>
+      <c r="CX266" t="n">
+        <v>2670000</v>
+      </c>
+      <c r="CY266" t="n">
+        <v>273</v>
+      </c>
+      <c r="CZ266" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>tl9KBk66</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>42</v>
+      </c>
+      <c r="N267" t="n">
+        <v>58</v>
+      </c>
+      <c r="O267" t="n">
+        <v>12</v>
+      </c>
+      <c r="P267" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>2</v>
+      </c>
+      <c r="R267" t="n">
+        <v>3</v>
+      </c>
+      <c r="S267" t="n">
+        <v>6</v>
+      </c>
+      <c r="T267" t="n">
+        <v>6</v>
+      </c>
+      <c r="U267" t="n">
+        <v>4</v>
+      </c>
+      <c r="V267" t="n">
+        <v>6</v>
+      </c>
+      <c r="W267" t="n">
+        <v>19</v>
+      </c>
+      <c r="X267" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>329</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>444</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>233</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>346</v>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AQ267" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU267" t="inlineStr"/>
+      <c r="AV267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr"/>
+      <c r="AX267" t="inlineStr"/>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr"/>
+      <c r="BA267" t="inlineStr"/>
+      <c r="BB267" t="inlineStr"/>
+      <c r="BC267" t="inlineStr"/>
+      <c r="BD267" t="inlineStr"/>
+      <c r="BE267" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG267" t="inlineStr"/>
+      <c r="BH267" t="inlineStr"/>
+      <c r="BI267" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>186.2222222222222</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>7222.222222222223</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BQ267" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="BR267" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="BS267" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BT267" t="n">
+        <v>2260000</v>
+      </c>
+      <c r="BU267" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BV267" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW267" t="n">
+        <v>24.47826086956522</v>
+      </c>
+      <c r="BX267" t="n">
+        <v>184</v>
+      </c>
+      <c r="BY267" t="n">
+        <v>65.56521739130434</v>
+      </c>
+      <c r="BZ267" t="inlineStr"/>
+      <c r="CA267" t="n">
+        <v>1667391.304347826</v>
+      </c>
+      <c r="CB267" t="n">
+        <v>72.21739130434783</v>
+      </c>
+      <c r="CC267" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD267" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="CE267" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="CF267" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="CG267" t="inlineStr"/>
+      <c r="CH267" t="n">
+        <v>1460800</v>
+      </c>
+      <c r="CI267" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="CJ267" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK267" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CL267" t="n">
+        <v>187</v>
+      </c>
+      <c r="CM267" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN267" t="n">
+        <v>119</v>
+      </c>
+      <c r="CO267" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CP267" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="CQ267" t="n">
+        <v>129</v>
+      </c>
+      <c r="CR267" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS267" t="inlineStr"/>
+      <c r="CT267" t="inlineStr"/>
+      <c r="CU267" t="inlineStr"/>
+      <c r="CV267" t="inlineStr"/>
+      <c r="CW267" t="inlineStr"/>
+      <c r="CX267" t="inlineStr"/>
+      <c r="CY267" t="inlineStr"/>
+      <c r="CZ267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>EyI3FX6s</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="n">
+        <v>52</v>
+      </c>
+      <c r="N268" t="n">
+        <v>48</v>
+      </c>
+      <c r="O268" t="n">
+        <v>16</v>
+      </c>
+      <c r="P268" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>4</v>
+      </c>
+      <c r="R268" t="n">
+        <v>3</v>
+      </c>
+      <c r="S268" t="n">
+        <v>9</v>
+      </c>
+      <c r="T268" t="n">
+        <v>3</v>
+      </c>
+      <c r="U268" t="n">
+        <v>3</v>
+      </c>
+      <c r="V268" t="n">
+        <v>1</v>
+      </c>
+      <c r="W268" t="n">
+        <v>27</v>
+      </c>
+      <c r="X268" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>369</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>331</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>269</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>228</v>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AQ268" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU268" t="inlineStr"/>
+      <c r="AV268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr"/>
+      <c r="AX268" t="inlineStr"/>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr"/>
+      <c r="BA268" t="inlineStr"/>
+      <c r="BB268" t="inlineStr"/>
+      <c r="BC268" t="inlineStr"/>
+      <c r="BD268" t="inlineStr"/>
+      <c r="BE268" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG268" t="inlineStr"/>
+      <c r="BH268" t="inlineStr"/>
+      <c r="BI268" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>4272.727272727273</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2343181.818181818</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>73.81818181818181</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="BQ268" t="n">
+        <v>185.2222222222222</v>
+      </c>
+      <c r="BR268" t="n">
+        <v>63.88888888888889</v>
+      </c>
+      <c r="BS268" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BT268" t="n">
+        <v>922222.2222222222</v>
+      </c>
+      <c r="BU268" t="n">
+        <v>68.77777777777777</v>
+      </c>
+      <c r="BV268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW268" t="n">
+        <v>26.07692307692308</v>
+      </c>
+      <c r="BX268" t="n">
+        <v>183.0769230769231</v>
+      </c>
+      <c r="BY268" t="n">
+        <v>68.57692307692308</v>
+      </c>
+      <c r="BZ268" t="n">
+        <v>7769.23076923077</v>
+      </c>
+      <c r="CA268" t="n">
+        <v>1950961.538461538</v>
+      </c>
+      <c r="CB268" t="n">
+        <v>73.61538461538461</v>
+      </c>
+      <c r="CC268" t="n">
+        <v>1.115384615384615</v>
+      </c>
+      <c r="CD268" t="n">
+        <v>24.29411764705882</v>
+      </c>
+      <c r="CE268" t="n">
+        <v>182</v>
+      </c>
+      <c r="CF268" t="n">
+        <v>63.58823529411764</v>
+      </c>
+      <c r="CG268" t="n">
+        <v>9352.941176470587</v>
+      </c>
+      <c r="CH268" t="n">
+        <v>947058.8235294118</v>
+      </c>
+      <c r="CI268" t="n">
+        <v>68.88235294117646</v>
+      </c>
+      <c r="CJ268" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK268" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL268" t="n">
+        <v>189</v>
+      </c>
+      <c r="CM268" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN268" t="n">
+        <v>142</v>
+      </c>
+      <c r="CO268" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CP268" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="CQ268" t="n">
+        <v>157</v>
+      </c>
+      <c r="CR268" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS268" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT268" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="CU268" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV268" t="n">
+        <v>194</v>
+      </c>
+      <c r="CW268" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CX268" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="CY268" t="n">
+        <v>203</v>
+      </c>
+      <c r="CZ268" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ268"/>
+  <dimension ref="A1:CZ279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80333,6 +80333,3204 @@
         <v>3</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F269" t="n">
+        <v>21923</v>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="K269" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L269" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M269" t="n">
+        <v>40</v>
+      </c>
+      <c r="N269" t="n">
+        <v>60</v>
+      </c>
+      <c r="O269" t="n">
+        <v>12</v>
+      </c>
+      <c r="P269" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>3</v>
+      </c>
+      <c r="R269" t="n">
+        <v>8</v>
+      </c>
+      <c r="S269" t="n">
+        <v>8</v>
+      </c>
+      <c r="T269" t="n">
+        <v>5</v>
+      </c>
+      <c r="U269" t="n">
+        <v>1</v>
+      </c>
+      <c r="V269" t="n">
+        <v>3</v>
+      </c>
+      <c r="W269" t="n">
+        <v>22</v>
+      </c>
+      <c r="X269" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>328</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>477</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>379</v>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AQ269" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU269" t="inlineStr"/>
+      <c r="AV269" t="inlineStr"/>
+      <c r="AW269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr"/>
+      <c r="BA269" t="inlineStr"/>
+      <c r="BB269" t="inlineStr"/>
+      <c r="BC269" t="inlineStr"/>
+      <c r="BD269" t="inlineStr"/>
+      <c r="BE269" t="inlineStr"/>
+      <c r="BF269" t="inlineStr"/>
+      <c r="BG269" t="inlineStr"/>
+      <c r="BH269" t="inlineStr"/>
+      <c r="BI269" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>41888.88888888889</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>14011111.11111111</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="BQ269" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="BR269" t="n">
+        <v>82.88888888888889</v>
+      </c>
+      <c r="BS269" t="n">
+        <v>145111.1111111111</v>
+      </c>
+      <c r="BT269" t="n">
+        <v>48777777.77777778</v>
+      </c>
+      <c r="BU269" t="n">
+        <v>85.33333333333333</v>
+      </c>
+      <c r="BV269" t="n">
+        <v>3</v>
+      </c>
+      <c r="BW269" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="BX269" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="BY269" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="BZ269" t="n">
+        <v>41500</v>
+      </c>
+      <c r="CA269" t="n">
+        <v>10803750</v>
+      </c>
+      <c r="CB269" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="CC269" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CD269" t="n">
+        <v>23</v>
+      </c>
+      <c r="CE269" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="CF269" t="n">
+        <v>76.69230769230769</v>
+      </c>
+      <c r="CG269" t="n">
+        <v>102384.6153846154</v>
+      </c>
+      <c r="CH269" t="n">
+        <v>26884615.38461538</v>
+      </c>
+      <c r="CI269" t="n">
+        <v>83.61538461538461</v>
+      </c>
+      <c r="CJ269" t="n">
+        <v>1.384615384615385</v>
+      </c>
+      <c r="CK269" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="CL269" t="n">
+        <v>188</v>
+      </c>
+      <c r="CM269" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN269" t="n">
+        <v>152</v>
+      </c>
+      <c r="CO269" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CP269" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="CQ269" t="n">
+        <v>158</v>
+      </c>
+      <c r="CR269" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS269" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="CT269" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="CU269" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV269" t="n">
+        <v>383</v>
+      </c>
+      <c r="CW269" t="n">
+        <v>509000</v>
+      </c>
+      <c r="CX269" t="n">
+        <v>96475000</v>
+      </c>
+      <c r="CY269" t="n">
+        <v>403</v>
+      </c>
+      <c r="CZ269" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F270" t="n">
+        <v>12021</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K270" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M270" t="n">
+        <v>35</v>
+      </c>
+      <c r="N270" t="n">
+        <v>65</v>
+      </c>
+      <c r="O270" t="n">
+        <v>3</v>
+      </c>
+      <c r="P270" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>3</v>
+      </c>
+      <c r="R270" t="n">
+        <v>4</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>7</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" t="n">
+        <v>4</v>
+      </c>
+      <c r="W270" t="n">
+        <v>21</v>
+      </c>
+      <c r="X270" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>337</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>654</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>234</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>518</v>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AQ270" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW270" t="inlineStr"/>
+      <c r="AX270" t="inlineStr"/>
+      <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr"/>
+      <c r="BA270" t="inlineStr"/>
+      <c r="BB270" t="inlineStr"/>
+      <c r="BC270" t="inlineStr"/>
+      <c r="BD270" t="inlineStr"/>
+      <c r="BE270" t="inlineStr"/>
+      <c r="BF270" t="inlineStr"/>
+      <c r="BG270" t="inlineStr"/>
+      <c r="BH270" t="inlineStr"/>
+      <c r="BI270" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>21000</v>
+      </c>
+      <c r="BM270" t="n">
+        <v>4670000</v>
+      </c>
+      <c r="BN270" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="BO270" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP270" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="BQ270" t="n">
+        <v>182</v>
+      </c>
+      <c r="BR270" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="BS270" t="n">
+        <v>37125</v>
+      </c>
+      <c r="BT270" t="n">
+        <v>18875000</v>
+      </c>
+      <c r="BU270" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="BV270" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BW270" t="n">
+        <v>27.88235294117647</v>
+      </c>
+      <c r="BX270" t="n">
+        <v>182</v>
+      </c>
+      <c r="BY270" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ270" t="n">
+        <v>43588.23529411765</v>
+      </c>
+      <c r="CA270" t="n">
+        <v>8538235.294117646</v>
+      </c>
+      <c r="CB270" t="n">
+        <v>76.76470588235294</v>
+      </c>
+      <c r="CC270" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="CD270" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="CE270" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="CF270" t="n">
+        <v>74.38888888888889</v>
+      </c>
+      <c r="CG270" t="n">
+        <v>28444.44444444445</v>
+      </c>
+      <c r="CH270" t="n">
+        <v>12516666.66666667</v>
+      </c>
+      <c r="CI270" t="n">
+        <v>80.16666666666667</v>
+      </c>
+      <c r="CJ270" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CK270" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="CL270" t="n">
+        <v>180</v>
+      </c>
+      <c r="CM270" t="n">
+        <v>6</v>
+      </c>
+      <c r="CN270" t="n">
+        <v>432</v>
+      </c>
+      <c r="CO270" t="n">
+        <v>133000</v>
+      </c>
+      <c r="CP270" t="n">
+        <v>29900000</v>
+      </c>
+      <c r="CQ270" t="n">
+        <v>453</v>
+      </c>
+      <c r="CR270" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS270" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="CT270" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="CU270" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV270" t="n">
+        <v>165</v>
+      </c>
+      <c r="CW270" t="n">
+        <v>180000</v>
+      </c>
+      <c r="CX270" t="n">
+        <v>94500000</v>
+      </c>
+      <c r="CY270" t="n">
+        <v>167</v>
+      </c>
+      <c r="CZ270" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F271" t="n">
+        <v>28400</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="K271" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M271" t="n">
+        <v>71</v>
+      </c>
+      <c r="N271" t="n">
+        <v>29</v>
+      </c>
+      <c r="O271" t="n">
+        <v>19</v>
+      </c>
+      <c r="P271" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>3</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2</v>
+      </c>
+      <c r="S271" t="n">
+        <v>9</v>
+      </c>
+      <c r="T271" t="n">
+        <v>5</v>
+      </c>
+      <c r="U271" t="n">
+        <v>7</v>
+      </c>
+      <c r="V271" t="n">
+        <v>6</v>
+      </c>
+      <c r="W271" t="n">
+        <v>16</v>
+      </c>
+      <c r="X271" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>630</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>246</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>493</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>161</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AQ271" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr"/>
+      <c r="BA271" t="inlineStr"/>
+      <c r="BB271" t="inlineStr"/>
+      <c r="BC271" t="inlineStr"/>
+      <c r="BD271" t="inlineStr"/>
+      <c r="BE271" t="inlineStr"/>
+      <c r="BF271" t="inlineStr"/>
+      <c r="BG271" t="inlineStr"/>
+      <c r="BH271" t="inlineStr"/>
+      <c r="BI271" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>186.3636363636364</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>44000</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>9263636.363636363</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>78.54545454545455</v>
+      </c>
+      <c r="BO271" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="BP271" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BQ271" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="BR271" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="BS271" t="n">
+        <v>26700</v>
+      </c>
+      <c r="BT271" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="BU271" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="BV271" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW271" t="n">
+        <v>23.95833333333333</v>
+      </c>
+      <c r="BX271" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="BY271" t="n">
+        <v>73.45833333333333</v>
+      </c>
+      <c r="BZ271" t="n">
+        <v>39791.66666666666</v>
+      </c>
+      <c r="CA271" t="n">
+        <v>7797916.666666667</v>
+      </c>
+      <c r="CB271" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="CC271" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="CD271" t="n">
+        <v>24</v>
+      </c>
+      <c r="CE271" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="CF271" t="n">
+        <v>68.09090909090909</v>
+      </c>
+      <c r="CG271" t="n">
+        <v>21954.54545454546</v>
+      </c>
+      <c r="CH271" t="n">
+        <v>2779545.454545455</v>
+      </c>
+      <c r="CI271" t="n">
+        <v>73.95454545454545</v>
+      </c>
+      <c r="CJ271" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK271" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL271" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="CM271" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN271" t="n">
+        <v>374</v>
+      </c>
+      <c r="CO271" t="n">
+        <v>245000</v>
+      </c>
+      <c r="CP271" t="n">
+        <v>51200000</v>
+      </c>
+      <c r="CQ271" t="n">
+        <v>395</v>
+      </c>
+      <c r="CR271" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS271" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="CT271" t="n">
+        <v>187.3333333333333</v>
+      </c>
+      <c r="CU271" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV271" t="n">
+        <v>217</v>
+      </c>
+      <c r="CW271" t="n">
+        <v>72000</v>
+      </c>
+      <c r="CX271" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="CY271" t="n">
+        <v>233</v>
+      </c>
+      <c r="CZ271" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F272" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G272" t="n">
+        <v>2</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K272" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M272" t="n">
+        <v>59</v>
+      </c>
+      <c r="N272" t="n">
+        <v>41</v>
+      </c>
+      <c r="O272" t="n">
+        <v>16</v>
+      </c>
+      <c r="P272" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>6</v>
+      </c>
+      <c r="R272" t="n">
+        <v>2</v>
+      </c>
+      <c r="S272" t="n">
+        <v>8</v>
+      </c>
+      <c r="T272" t="n">
+        <v>3</v>
+      </c>
+      <c r="U272" t="n">
+        <v>2</v>
+      </c>
+      <c r="V272" t="n">
+        <v>2</v>
+      </c>
+      <c r="W272" t="n">
+        <v>19</v>
+      </c>
+      <c r="X272" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>453</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>317</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>218</v>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AQ272" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW272" t="inlineStr"/>
+      <c r="AX272" t="inlineStr"/>
+      <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr"/>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="inlineStr"/>
+      <c r="BD272" t="inlineStr"/>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="inlineStr"/>
+      <c r="BH272" t="inlineStr"/>
+      <c r="BI272" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>49800</v>
+      </c>
+      <c r="BM272" t="n">
+        <v>24100000</v>
+      </c>
+      <c r="BN272" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="BO272" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP272" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="BQ272" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="BR272" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BS272" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BT272" t="n">
+        <v>2722500</v>
+      </c>
+      <c r="BU272" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="BV272" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW272" t="n">
+        <v>27.52173913043478</v>
+      </c>
+      <c r="BX272" t="n">
+        <v>182.9130434782609</v>
+      </c>
+      <c r="BY272" t="n">
+        <v>75.78260869565217</v>
+      </c>
+      <c r="BZ272" t="n">
+        <v>40217.39130434782</v>
+      </c>
+      <c r="CA272" t="n">
+        <v>9761956.521739131</v>
+      </c>
+      <c r="CB272" t="n">
+        <v>78.82608695652173</v>
+      </c>
+      <c r="CC272" t="n">
+        <v>1.652173913043478</v>
+      </c>
+      <c r="CD272" t="n">
+        <v>24.47826086956522</v>
+      </c>
+      <c r="CE272" t="n">
+        <v>183.1304347826087</v>
+      </c>
+      <c r="CF272" t="n">
+        <v>69.43478260869566</v>
+      </c>
+      <c r="CG272" t="n">
+        <v>29478.26086956522</v>
+      </c>
+      <c r="CH272" t="n">
+        <v>3345652.173913043</v>
+      </c>
+      <c r="CI272" t="n">
+        <v>74.91304347826087</v>
+      </c>
+      <c r="CJ272" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="CK272" t="inlineStr"/>
+      <c r="CL272" t="inlineStr"/>
+      <c r="CM272" t="inlineStr"/>
+      <c r="CN272" t="inlineStr"/>
+      <c r="CO272" t="inlineStr"/>
+      <c r="CP272" t="inlineStr"/>
+      <c r="CQ272" t="inlineStr"/>
+      <c r="CR272" t="inlineStr"/>
+      <c r="CS272" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT272" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="CU272" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV272" t="n">
+        <v>356</v>
+      </c>
+      <c r="CW272" t="n">
+        <v>60000</v>
+      </c>
+      <c r="CX272" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="CY272" t="n">
+        <v>373</v>
+      </c>
+      <c r="CZ272" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F273" t="n">
+        <v>40557</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="K273" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M273" t="n">
+        <v>74</v>
+      </c>
+      <c r="N273" t="n">
+        <v>26</v>
+      </c>
+      <c r="O273" t="n">
+        <v>21</v>
+      </c>
+      <c r="P273" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>9</v>
+      </c>
+      <c r="R273" t="n">
+        <v>2</v>
+      </c>
+      <c r="S273" t="n">
+        <v>7</v>
+      </c>
+      <c r="T273" t="n">
+        <v>4</v>
+      </c>
+      <c r="U273" t="n">
+        <v>5</v>
+      </c>
+      <c r="V273" t="n">
+        <v>3</v>
+      </c>
+      <c r="W273" t="n">
+        <v>12</v>
+      </c>
+      <c r="X273" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>752</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>259</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>652</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AQ273" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr"/>
+      <c r="BA273" t="inlineStr"/>
+      <c r="BB273" t="inlineStr"/>
+      <c r="BC273" t="inlineStr"/>
+      <c r="BD273" t="inlineStr"/>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="inlineStr"/>
+      <c r="BH273" t="inlineStr"/>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
+      <c r="BO273" t="inlineStr"/>
+      <c r="BP273" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="BQ273" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="BR273" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="BS273" t="n">
+        <v>17636.36363636364</v>
+      </c>
+      <c r="BT273" t="n">
+        <v>3654545.454545455</v>
+      </c>
+      <c r="BU273" t="n">
+        <v>75.54545454545455</v>
+      </c>
+      <c r="BV273" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BW273" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="BX273" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="BY273" t="n">
+        <v>77.54545454545455</v>
+      </c>
+      <c r="BZ273" t="n">
+        <v>84090.90909090909</v>
+      </c>
+      <c r="CA273" t="n">
+        <v>18218181.81818182</v>
+      </c>
+      <c r="CB273" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="CC273" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="CD273" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="CE273" t="n">
+        <v>180.84</v>
+      </c>
+      <c r="CF273" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="CG273" t="n">
+        <v>20040</v>
+      </c>
+      <c r="CH273" t="n">
+        <v>3535000</v>
+      </c>
+      <c r="CI273" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="CJ273" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK273" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="CL273" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="CM273" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN273" t="n">
+        <v>403</v>
+      </c>
+      <c r="CO273" t="n">
+        <v>554000</v>
+      </c>
+      <c r="CP273" t="n">
+        <v>163000000</v>
+      </c>
+      <c r="CQ273" t="n">
+        <v>412</v>
+      </c>
+      <c r="CR273" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS273" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT273" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="CU273" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV273" t="n">
+        <v>286</v>
+      </c>
+      <c r="CW273" t="n">
+        <v>58000</v>
+      </c>
+      <c r="CX273" t="n">
+        <v>6575000</v>
+      </c>
+      <c r="CY273" t="n">
+        <v>288</v>
+      </c>
+      <c r="CZ273" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>45570.65625</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F274" t="n">
+        <v>73348</v>
+      </c>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L274" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M274" t="n">
+        <v>80</v>
+      </c>
+      <c r="N274" t="n">
+        <v>20</v>
+      </c>
+      <c r="O274" t="n">
+        <v>29</v>
+      </c>
+      <c r="P274" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>8</v>
+      </c>
+      <c r="R274" t="n">
+        <v>5</v>
+      </c>
+      <c r="S274" t="n">
+        <v>13</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1</v>
+      </c>
+      <c r="U274" t="n">
+        <v>8</v>
+      </c>
+      <c r="V274" t="n">
+        <v>1</v>
+      </c>
+      <c r="W274" t="n">
+        <v>11</v>
+      </c>
+      <c r="X274" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>740</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>192</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>688</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>127</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AQ274" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU274" t="inlineStr"/>
+      <c r="AV274" t="inlineStr"/>
+      <c r="AW274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr"/>
+      <c r="BA274" t="inlineStr"/>
+      <c r="BB274" t="inlineStr"/>
+      <c r="BC274" t="inlineStr"/>
+      <c r="BD274" t="inlineStr"/>
+      <c r="BE274" t="inlineStr"/>
+      <c r="BF274" t="inlineStr"/>
+      <c r="BG274" t="inlineStr"/>
+      <c r="BH274" t="inlineStr"/>
+      <c r="BI274" t="n">
+        <v>29.09090909090909</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>83.81818181818181</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>108181.8181818182</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>85.27272727272727</v>
+      </c>
+      <c r="BO274" t="n">
+        <v>3.272727272727273</v>
+      </c>
+      <c r="BP274" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="BQ274" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="BR274" t="n">
+        <v>74</v>
+      </c>
+      <c r="BS274" t="n">
+        <v>34750</v>
+      </c>
+      <c r="BT274" t="n">
+        <v>9137500</v>
+      </c>
+      <c r="BU274" t="n">
+        <v>78.875</v>
+      </c>
+      <c r="BV274" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BW274" t="n">
+        <v>28.8695652173913</v>
+      </c>
+      <c r="BX274" t="n">
+        <v>186.4782608695652</v>
+      </c>
+      <c r="BY274" t="n">
+        <v>80.60869565217391</v>
+      </c>
+      <c r="BZ274" t="n">
+        <v>91869.56521739131</v>
+      </c>
+      <c r="CA274" t="n">
+        <v>24686956.52173913</v>
+      </c>
+      <c r="CB274" t="n">
+        <v>81.69565217391305</v>
+      </c>
+      <c r="CC274" t="n">
+        <v>2.521739130434783</v>
+      </c>
+      <c r="CD274" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="CE274" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="CF274" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="CG274" t="n">
+        <v>35750</v>
+      </c>
+      <c r="CH274" t="n">
+        <v>7907500</v>
+      </c>
+      <c r="CI274" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="CJ274" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CK274" t="n">
+        <v>26</v>
+      </c>
+      <c r="CL274" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="CM274" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN274" t="n">
+        <v>161</v>
+      </c>
+      <c r="CO274" t="n">
+        <v>210000</v>
+      </c>
+      <c r="CP274" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="CQ274" t="n">
+        <v>163</v>
+      </c>
+      <c r="CR274" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS274" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT274" t="n">
+        <v>182</v>
+      </c>
+      <c r="CU274" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV274" t="n">
+        <v>205</v>
+      </c>
+      <c r="CW274" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CX274" t="n">
+        <v>26400000</v>
+      </c>
+      <c r="CY274" t="n">
+        <v>242</v>
+      </c>
+      <c r="CZ274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>tAM9caod</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F275" t="n">
+        <v>8394</v>
+      </c>
+      <c r="G275" t="n">
+        <v>2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>57</v>
+      </c>
+      <c r="N275" t="n">
+        <v>43</v>
+      </c>
+      <c r="O275" t="n">
+        <v>9</v>
+      </c>
+      <c r="P275" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>5</v>
+      </c>
+      <c r="R275" t="n">
+        <v>3</v>
+      </c>
+      <c r="S275" t="n">
+        <v>3</v>
+      </c>
+      <c r="T275" t="n">
+        <v>3</v>
+      </c>
+      <c r="U275" t="n">
+        <v>1</v>
+      </c>
+      <c r="V275" t="n">
+        <v>1</v>
+      </c>
+      <c r="W275" t="n">
+        <v>28</v>
+      </c>
+      <c r="X275" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>385</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>303</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>204</v>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AQ275" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU275" t="inlineStr"/>
+      <c r="AV275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr"/>
+      <c r="AX275" t="inlineStr"/>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr"/>
+      <c r="BA275" t="inlineStr"/>
+      <c r="BB275" t="inlineStr"/>
+      <c r="BC275" t="inlineStr"/>
+      <c r="BD275" t="inlineStr"/>
+      <c r="BE275" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG275" t="inlineStr"/>
+      <c r="BH275" t="inlineStr"/>
+      <c r="BI275" t="n">
+        <v>27.81818181818182</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>181.7272727272727</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>2454.545454545455</v>
+      </c>
+      <c r="BM275" t="n">
+        <v>1079545.454545455</v>
+      </c>
+      <c r="BN275" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="BO275" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP275" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BQ275" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BR275" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="BS275" t="n">
+        <v>4600</v>
+      </c>
+      <c r="BT275" t="n">
+        <v>1645000</v>
+      </c>
+      <c r="BU275" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BV275" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW275" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BX275" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="BY275" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="BZ275" t="n">
+        <v>11333.33333333333</v>
+      </c>
+      <c r="CA275" t="n">
+        <v>998541.6666666666</v>
+      </c>
+      <c r="CB275" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="CC275" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD275" t="n">
+        <v>27.23809523809524</v>
+      </c>
+      <c r="CE275" t="n">
+        <v>186.5238095238095</v>
+      </c>
+      <c r="CF275" t="n">
+        <v>66.76190476190476</v>
+      </c>
+      <c r="CG275" t="inlineStr"/>
+      <c r="CH275" t="n">
+        <v>1003809.523809524</v>
+      </c>
+      <c r="CI275" t="n">
+        <v>71.04761904761905</v>
+      </c>
+      <c r="CJ275" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK275" t="inlineStr"/>
+      <c r="CL275" t="inlineStr"/>
+      <c r="CM275" t="inlineStr"/>
+      <c r="CN275" t="inlineStr"/>
+      <c r="CO275" t="inlineStr"/>
+      <c r="CP275" t="inlineStr"/>
+      <c r="CQ275" t="inlineStr"/>
+      <c r="CR275" t="inlineStr"/>
+      <c r="CS275" t="inlineStr"/>
+      <c r="CT275" t="inlineStr"/>
+      <c r="CU275" t="inlineStr"/>
+      <c r="CV275" t="inlineStr"/>
+      <c r="CW275" t="inlineStr"/>
+      <c r="CX275" t="inlineStr"/>
+      <c r="CY275" t="inlineStr"/>
+      <c r="CZ275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>8GEeL2w3</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F276" t="n">
+        <v>6771</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>2</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>64</v>
+      </c>
+      <c r="N276" t="n">
+        <v>36</v>
+      </c>
+      <c r="O276" t="n">
+        <v>32</v>
+      </c>
+      <c r="P276" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>6</v>
+      </c>
+      <c r="R276" t="n">
+        <v>4</v>
+      </c>
+      <c r="S276" t="n">
+        <v>18</v>
+      </c>
+      <c r="T276" t="n">
+        <v>5</v>
+      </c>
+      <c r="U276" t="n">
+        <v>8</v>
+      </c>
+      <c r="V276" t="n">
+        <v>1</v>
+      </c>
+      <c r="W276" t="n">
+        <v>14</v>
+      </c>
+      <c r="X276" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>488</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>286</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>414</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>188</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AQ276" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU276" t="inlineStr"/>
+      <c r="AV276" t="inlineStr"/>
+      <c r="AW276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr"/>
+      <c r="BA276" t="inlineStr"/>
+      <c r="BB276" t="inlineStr"/>
+      <c r="BC276" t="inlineStr"/>
+      <c r="BD276" t="inlineStr"/>
+      <c r="BE276" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG276" t="inlineStr"/>
+      <c r="BH276" t="inlineStr"/>
+      <c r="BI276" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="BK276" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BL276" t="n">
+        <v>4900</v>
+      </c>
+      <c r="BM276" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="BN276" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BO276" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP276" t="n">
+        <v>29.81818181818182</v>
+      </c>
+      <c r="BQ276" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="BR276" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="BS276" t="n">
+        <v>2636.363636363636</v>
+      </c>
+      <c r="BT276" t="n">
+        <v>1160000</v>
+      </c>
+      <c r="BU276" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="BV276" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW276" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="BX276" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="BY276" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="BZ276" t="n">
+        <v>2520</v>
+      </c>
+      <c r="CA276" t="n">
+        <v>1053000</v>
+      </c>
+      <c r="CB276" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="CC276" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD276" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="CE276" t="n">
+        <v>184.95</v>
+      </c>
+      <c r="CF276" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="CG276" t="n">
+        <v>4600</v>
+      </c>
+      <c r="CH276" t="n">
+        <v>1201250</v>
+      </c>
+      <c r="CI276" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="CJ276" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK276" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL276" t="n">
+        <v>180</v>
+      </c>
+      <c r="CM276" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN276" t="n">
+        <v>127</v>
+      </c>
+      <c r="CO276" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CP276" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="CQ276" t="n">
+        <v>144</v>
+      </c>
+      <c r="CR276" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS276" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="CT276" t="n">
+        <v>180</v>
+      </c>
+      <c r="CU276" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV276" t="n">
+        <v>201</v>
+      </c>
+      <c r="CW276" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CX276" t="n">
+        <v>2275000</v>
+      </c>
+      <c r="CY276" t="n">
+        <v>208</v>
+      </c>
+      <c r="CZ276" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>4r84Jt8F</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F277" t="n">
+        <v>9942</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>56</v>
+      </c>
+      <c r="N277" t="n">
+        <v>44</v>
+      </c>
+      <c r="O277" t="n">
+        <v>19</v>
+      </c>
+      <c r="P277" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>6</v>
+      </c>
+      <c r="R277" t="n">
+        <v>4</v>
+      </c>
+      <c r="S277" t="n">
+        <v>11</v>
+      </c>
+      <c r="T277" t="n">
+        <v>7</v>
+      </c>
+      <c r="U277" t="n">
+        <v>2</v>
+      </c>
+      <c r="V277" t="n">
+        <v>3</v>
+      </c>
+      <c r="W277" t="n">
+        <v>19</v>
+      </c>
+      <c r="X277" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>445</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>338</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>375</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>264</v>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AQ277" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU277" t="inlineStr"/>
+      <c r="AV277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr"/>
+      <c r="AX277" t="inlineStr"/>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr"/>
+      <c r="BA277" t="inlineStr"/>
+      <c r="BB277" t="inlineStr"/>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF277" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
+      <c r="BI277" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="BJ277" t="n">
+        <v>184</v>
+      </c>
+      <c r="BK277" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BL277" t="n">
+        <v>5272.727272727273</v>
+      </c>
+      <c r="BM277" t="n">
+        <v>2027272.727272727</v>
+      </c>
+      <c r="BN277" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="BO277" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP277" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="BQ277" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="BR277" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="BS277" t="n">
+        <v>7272.727272727273</v>
+      </c>
+      <c r="BT277" t="n">
+        <v>1309090.909090909</v>
+      </c>
+      <c r="BU277" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BV277" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW277" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="BX277" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="BY277" t="n">
+        <v>68.84615384615384</v>
+      </c>
+      <c r="BZ277" t="n">
+        <v>4115.384615384615</v>
+      </c>
+      <c r="CA277" t="n">
+        <v>1906730.769230769</v>
+      </c>
+      <c r="CB277" t="n">
+        <v>73.30769230769231</v>
+      </c>
+      <c r="CC277" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD277" t="n">
+        <v>27.3125</v>
+      </c>
+      <c r="CE277" t="n">
+        <v>184.5625</v>
+      </c>
+      <c r="CF277" t="n">
+        <v>66.8125</v>
+      </c>
+      <c r="CG277" t="n">
+        <v>11375</v>
+      </c>
+      <c r="CH277" t="n">
+        <v>1146875</v>
+      </c>
+      <c r="CI277" t="n">
+        <v>68.8125</v>
+      </c>
+      <c r="CJ277" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK277" t="inlineStr"/>
+      <c r="CL277" t="inlineStr"/>
+      <c r="CM277" t="inlineStr"/>
+      <c r="CN277" t="inlineStr"/>
+      <c r="CO277" t="inlineStr"/>
+      <c r="CP277" t="inlineStr"/>
+      <c r="CQ277" t="inlineStr"/>
+      <c r="CR277" t="inlineStr"/>
+      <c r="CS277" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT277" t="n">
+        <v>188</v>
+      </c>
+      <c r="CU277" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV277" t="n">
+        <v>66</v>
+      </c>
+      <c r="CW277" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CX277" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="CY277" t="n">
+        <v>72</v>
+      </c>
+      <c r="CZ277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>KG9yCb0k</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>5423</v>
+      </c>
+      <c r="F278" t="n">
+        <v>10317</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>70</v>
+      </c>
+      <c r="N278" t="n">
+        <v>30</v>
+      </c>
+      <c r="O278" t="n">
+        <v>21</v>
+      </c>
+      <c r="P278" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>7</v>
+      </c>
+      <c r="R278" t="n">
+        <v>4</v>
+      </c>
+      <c r="S278" t="n">
+        <v>7</v>
+      </c>
+      <c r="T278" t="n">
+        <v>5</v>
+      </c>
+      <c r="U278" t="n">
+        <v>7</v>
+      </c>
+      <c r="V278" t="n">
+        <v>1</v>
+      </c>
+      <c r="W278" t="n">
+        <v>27</v>
+      </c>
+      <c r="X278" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>570</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>231</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>523</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>177</v>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AQ278" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU278" t="inlineStr"/>
+      <c r="AV278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr"/>
+      <c r="AX278" t="inlineStr"/>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr"/>
+      <c r="BA278" t="inlineStr"/>
+      <c r="BB278" t="inlineStr"/>
+      <c r="BC278" t="inlineStr"/>
+      <c r="BD278" t="inlineStr"/>
+      <c r="BE278" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF278" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG278" t="inlineStr"/>
+      <c r="BH278" t="inlineStr"/>
+      <c r="BI278" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="BK278" t="n">
+        <v>64.77777777777777</v>
+      </c>
+      <c r="BL278" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="BM278" t="n">
+        <v>983333.3333333334</v>
+      </c>
+      <c r="BN278" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="BO278" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP278" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="BQ278" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="BR278" t="n">
+        <v>66.55555555555556</v>
+      </c>
+      <c r="BS278" t="n">
+        <v>2888.888888888889</v>
+      </c>
+      <c r="BT278" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="BU278" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="BV278" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW278" t="n">
+        <v>27.10526315789474</v>
+      </c>
+      <c r="BX278" t="n">
+        <v>181.2105263157895</v>
+      </c>
+      <c r="BY278" t="n">
+        <v>65.89473684210526</v>
+      </c>
+      <c r="BZ278" t="inlineStr"/>
+      <c r="CA278" t="n">
+        <v>1048421.052631579</v>
+      </c>
+      <c r="CB278" t="n">
+        <v>69.89473684210526</v>
+      </c>
+      <c r="CC278" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD278" t="n">
+        <v>24.73913043478261</v>
+      </c>
+      <c r="CE278" t="n">
+        <v>180.6521739130435</v>
+      </c>
+      <c r="CF278" t="n">
+        <v>64.47826086956522</v>
+      </c>
+      <c r="CG278" t="n">
+        <v>3304.347826086957</v>
+      </c>
+      <c r="CH278" t="n">
+        <v>1089130.434782609</v>
+      </c>
+      <c r="CI278" t="n">
+        <v>71.39130434782609</v>
+      </c>
+      <c r="CJ278" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK278" t="inlineStr"/>
+      <c r="CL278" t="inlineStr"/>
+      <c r="CM278" t="inlineStr"/>
+      <c r="CN278" t="inlineStr"/>
+      <c r="CO278" t="inlineStr"/>
+      <c r="CP278" t="inlineStr"/>
+      <c r="CQ278" t="inlineStr"/>
+      <c r="CR278" t="inlineStr"/>
+      <c r="CS278" t="inlineStr"/>
+      <c r="CT278" t="inlineStr"/>
+      <c r="CU278" t="inlineStr"/>
+      <c r="CV278" t="inlineStr"/>
+      <c r="CW278" t="inlineStr"/>
+      <c r="CX278" t="inlineStr"/>
+      <c r="CY278" t="inlineStr"/>
+      <c r="CZ278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>StDqAxV1</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renzo barbera
+  palermo </t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>36349</v>
+      </c>
+      <c r="F279" t="n">
+        <v>25460</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>51</v>
+      </c>
+      <c r="N279" t="n">
+        <v>49</v>
+      </c>
+      <c r="O279" t="n">
+        <v>16</v>
+      </c>
+      <c r="P279" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>5</v>
+      </c>
+      <c r="R279" t="n">
+        <v>4</v>
+      </c>
+      <c r="S279" t="n">
+        <v>5</v>
+      </c>
+      <c r="T279" t="n">
+        <v>3</v>
+      </c>
+      <c r="U279" t="n">
+        <v>6</v>
+      </c>
+      <c r="V279" t="n">
+        <v>2</v>
+      </c>
+      <c r="W279" t="n">
+        <v>22</v>
+      </c>
+      <c r="X279" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>439</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>438</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>374</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>367</v>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AQ279" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU279" t="inlineStr"/>
+      <c r="AV279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr"/>
+      <c r="AX279" t="inlineStr"/>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr"/>
+      <c r="BA279" t="inlineStr"/>
+      <c r="BB279" t="inlineStr"/>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF279" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="inlineStr"/>
+      <c r="BI279" t="inlineStr"/>
+      <c r="BJ279" t="inlineStr"/>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="inlineStr"/>
+      <c r="BM279" t="inlineStr"/>
+      <c r="BN279" t="inlineStr"/>
+      <c r="BO279" t="inlineStr"/>
+      <c r="BP279" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="BQ279" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="BR279" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="BS279" t="n">
+        <v>6200</v>
+      </c>
+      <c r="BT279" t="n">
+        <v>1262500</v>
+      </c>
+      <c r="BU279" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BV279" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BW279" t="n">
+        <v>28.08333333333333</v>
+      </c>
+      <c r="BX279" t="n">
+        <v>181.9583333333333</v>
+      </c>
+      <c r="BY279" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="BZ279" t="n">
+        <v>5958.333333333333</v>
+      </c>
+      <c r="CA279" t="n">
+        <v>2623958.333333333</v>
+      </c>
+      <c r="CB279" t="n">
+        <v>73</v>
+      </c>
+      <c r="CC279" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD279" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="CE279" t="n">
+        <v>181.4761904761905</v>
+      </c>
+      <c r="CF279" t="n">
+        <v>67.14285714285714</v>
+      </c>
+      <c r="CG279" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CH279" t="n">
+        <v>1280714.285714286</v>
+      </c>
+      <c r="CI279" t="n">
+        <v>70.52380952380952</v>
+      </c>
+      <c r="CJ279" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="CK279" t="inlineStr"/>
+      <c r="CL279" t="inlineStr"/>
+      <c r="CM279" t="inlineStr"/>
+      <c r="CN279" t="inlineStr"/>
+      <c r="CO279" t="inlineStr"/>
+      <c r="CP279" t="inlineStr"/>
+      <c r="CQ279" t="inlineStr"/>
+      <c r="CR279" t="inlineStr"/>
+      <c r="CS279" t="inlineStr"/>
+      <c r="CT279" t="inlineStr"/>
+      <c r="CU279" t="inlineStr"/>
+      <c r="CV279" t="inlineStr"/>
+      <c r="CW279" t="inlineStr"/>
+      <c r="CX279" t="inlineStr"/>
+      <c r="CY279" t="inlineStr"/>
+      <c r="CZ279" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ279"/>
+  <dimension ref="A1:DB288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,16 @@
       <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
         </is>
       </c>
     </row>
@@ -1250,6 +1260,8 @@
       <c r="CZ2" t="n">
         <v>4</v>
       </c>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1552,6 +1564,8 @@
       <c r="CZ3" t="n">
         <v>5</v>
       </c>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1858,6 +1872,8 @@
       <c r="CZ4" t="n">
         <v>1</v>
       </c>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2160,6 +2176,8 @@
       <c r="CZ5" t="n">
         <v>2</v>
       </c>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2436,6 +2454,8 @@
       <c r="CZ6" t="n">
         <v>5</v>
       </c>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2722,6 +2742,8 @@
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="inlineStr"/>
       <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -3028,6 +3050,8 @@
       <c r="CZ8" t="n">
         <v>5</v>
       </c>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -3314,6 +3338,8 @@
       <c r="CZ9" t="n">
         <v>8</v>
       </c>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3616,6 +3642,8 @@
       <c r="CZ10" t="n">
         <v>5</v>
       </c>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3922,6 +3950,8 @@
       <c r="CZ11" t="n">
         <v>5</v>
       </c>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -4210,6 +4240,8 @@
       <c r="CZ12" t="n">
         <v>1</v>
       </c>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -4512,6 +4544,8 @@
       <c r="CZ13" t="n">
         <v>7</v>
       </c>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -4818,6 +4852,8 @@
       <c r="CZ14" t="n">
         <v>3</v>
       </c>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -5120,6 +5156,8 @@
       <c r="CZ15" t="n">
         <v>4</v>
       </c>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -5406,6 +5444,8 @@
       <c r="CZ16" t="n">
         <v>3</v>
       </c>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -5712,6 +5752,8 @@
       <c r="CZ17" t="n">
         <v>4</v>
       </c>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -6014,6 +6056,8 @@
       <c r="CZ18" t="n">
         <v>2</v>
       </c>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -6320,6 +6364,8 @@
       <c r="CZ19" t="n">
         <v>3</v>
       </c>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -6626,6 +6672,8 @@
       <c r="CZ20" t="n">
         <v>3</v>
       </c>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -6928,6 +6976,8 @@
       <c r="CZ21" t="n">
         <v>6</v>
       </c>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -7222,6 +7272,8 @@
       <c r="CZ22" t="n">
         <v>3</v>
       </c>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -7536,6 +7588,8 @@
       <c r="CZ23" t="n">
         <v>3</v>
       </c>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -7846,6 +7900,8 @@
       <c r="CZ24" t="n">
         <v>1</v>
       </c>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8156,6 +8212,8 @@
       <c r="CZ25" t="n">
         <v>2</v>
       </c>
+      <c r="DA25" t="inlineStr"/>
+      <c r="DB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -8466,6 +8524,8 @@
       <c r="CZ26" t="n">
         <v>1</v>
       </c>
+      <c r="DA26" t="inlineStr"/>
+      <c r="DB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -8762,6 +8822,8 @@
       <c r="CZ27" t="n">
         <v>5</v>
       </c>
+      <c r="DA27" t="inlineStr"/>
+      <c r="DB27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -9056,6 +9118,8 @@
       <c r="CX28" t="inlineStr"/>
       <c r="CY28" t="inlineStr"/>
       <c r="CZ28" t="inlineStr"/>
+      <c r="DA28" t="inlineStr"/>
+      <c r="DB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -9370,6 +9434,8 @@
       <c r="CZ29" t="n">
         <v>1</v>
       </c>
+      <c r="DA29" t="inlineStr"/>
+      <c r="DB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -9680,6 +9746,8 @@
       <c r="CZ30" t="n">
         <v>7</v>
       </c>
+      <c r="DA30" t="inlineStr"/>
+      <c r="DB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -9976,6 +10044,8 @@
       <c r="CZ31" t="n">
         <v>3</v>
       </c>
+      <c r="DA31" t="inlineStr"/>
+      <c r="DB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -10270,6 +10340,8 @@
       <c r="CX32" t="inlineStr"/>
       <c r="CY32" t="inlineStr"/>
       <c r="CZ32" t="inlineStr"/>
+      <c r="DA32" t="inlineStr"/>
+      <c r="DB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -10566,6 +10638,8 @@
       <c r="CZ33" t="n">
         <v>1</v>
       </c>
+      <c r="DA33" t="inlineStr"/>
+      <c r="DB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -10876,6 +10950,8 @@
       <c r="CZ34" t="n">
         <v>2</v>
       </c>
+      <c r="DA34" t="inlineStr"/>
+      <c r="DB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -11186,6 +11262,8 @@
       <c r="CZ35" t="n">
         <v>3</v>
       </c>
+      <c r="DA35" t="inlineStr"/>
+      <c r="DB35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -11500,6 +11578,8 @@
       <c r="CZ36" t="n">
         <v>10</v>
       </c>
+      <c r="DA36" t="inlineStr"/>
+      <c r="DB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -11802,6 +11882,8 @@
       <c r="CZ37" t="n">
         <v>2</v>
       </c>
+      <c r="DA37" t="inlineStr"/>
+      <c r="DB37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -12116,6 +12198,8 @@
       <c r="CZ38" t="n">
         <v>6</v>
       </c>
+      <c r="DA38" t="inlineStr"/>
+      <c r="DB38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -12418,6 +12502,8 @@
       <c r="CX39" t="inlineStr"/>
       <c r="CY39" t="inlineStr"/>
       <c r="CZ39" t="inlineStr"/>
+      <c r="DA39" t="inlineStr"/>
+      <c r="DB39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -12728,6 +12814,8 @@
       <c r="CZ40" t="n">
         <v>9</v>
       </c>
+      <c r="DA40" t="inlineStr"/>
+      <c r="DB40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -13042,6 +13130,8 @@
       <c r="CZ41" t="n">
         <v>2</v>
       </c>
+      <c r="DA41" t="inlineStr"/>
+      <c r="DB41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -13352,6 +13442,8 @@
       <c r="CZ42" t="n">
         <v>11</v>
       </c>
+      <c r="DA42" t="inlineStr"/>
+      <c r="DB42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -13662,6 +13754,8 @@
       <c r="CZ43" t="n">
         <v>2</v>
       </c>
+      <c r="DA43" t="inlineStr"/>
+      <c r="DB43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -13956,6 +14050,8 @@
       <c r="CZ44" t="n">
         <v>5</v>
       </c>
+      <c r="DA44" t="inlineStr"/>
+      <c r="DB44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -14250,6 +14346,8 @@
       <c r="CZ45" t="n">
         <v>3</v>
       </c>
+      <c r="DA45" t="inlineStr"/>
+      <c r="DB45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -14560,6 +14658,8 @@
       <c r="CZ46" t="n">
         <v>4</v>
       </c>
+      <c r="DA46" t="inlineStr"/>
+      <c r="DB46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -14870,6 +14970,8 @@
       <c r="CZ47" t="n">
         <v>6</v>
       </c>
+      <c r="DA47" t="inlineStr"/>
+      <c r="DB47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -15180,6 +15282,8 @@
       <c r="CZ48" t="n">
         <v>3</v>
       </c>
+      <c r="DA48" t="inlineStr"/>
+      <c r="DB48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -15490,6 +15594,8 @@
       <c r="CZ49" t="n">
         <v>2</v>
       </c>
+      <c r="DA49" t="inlineStr"/>
+      <c r="DB49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -15800,6 +15906,8 @@
       <c r="CZ50" t="n">
         <v>5</v>
       </c>
+      <c r="DA50" t="inlineStr"/>
+      <c r="DB50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -16114,6 +16222,8 @@
       <c r="CZ51" t="n">
         <v>2</v>
       </c>
+      <c r="DA51" t="inlineStr"/>
+      <c r="DB51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -16424,6 +16534,8 @@
       <c r="CZ52" t="n">
         <v>1</v>
       </c>
+      <c r="DA52" t="inlineStr"/>
+      <c r="DB52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -16734,6 +16846,8 @@
       <c r="CZ53" t="n">
         <v>8</v>
       </c>
+      <c r="DA53" t="inlineStr"/>
+      <c r="DB53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -17044,6 +17158,8 @@
       <c r="CZ54" t="n">
         <v>3</v>
       </c>
+      <c r="DA54" t="inlineStr"/>
+      <c r="DB54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -17354,6 +17470,8 @@
       <c r="CZ55" t="n">
         <v>6</v>
       </c>
+      <c r="DA55" t="inlineStr"/>
+      <c r="DB55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -17664,6 +17782,8 @@
       <c r="CZ56" t="n">
         <v>4</v>
       </c>
+      <c r="DA56" t="inlineStr"/>
+      <c r="DB56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -17958,6 +18078,8 @@
       <c r="CX57" t="inlineStr"/>
       <c r="CY57" t="inlineStr"/>
       <c r="CZ57" t="inlineStr"/>
+      <c r="DA57" t="inlineStr"/>
+      <c r="DB57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -18268,6 +18390,8 @@
       <c r="CZ58" t="n">
         <v>3</v>
       </c>
+      <c r="DA58" t="inlineStr"/>
+      <c r="DB58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -18578,6 +18702,8 @@
       <c r="CZ59" t="n">
         <v>3</v>
       </c>
+      <c r="DA59" t="inlineStr"/>
+      <c r="DB59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -18888,6 +19014,8 @@
       <c r="CZ60" t="n">
         <v>7</v>
       </c>
+      <c r="DA60" t="inlineStr"/>
+      <c r="DB60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -19202,6 +19330,8 @@
       <c r="CZ61" t="n">
         <v>1</v>
       </c>
+      <c r="DA61" t="inlineStr"/>
+      <c r="DB61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -19518,6 +19648,8 @@
       <c r="CZ62" t="n">
         <v>3</v>
       </c>
+      <c r="DA62" t="inlineStr"/>
+      <c r="DB62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -19834,6 +19966,8 @@
       <c r="CZ63" t="n">
         <v>10</v>
       </c>
+      <c r="DA63" t="inlineStr"/>
+      <c r="DB63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -20150,6 +20284,8 @@
       <c r="CZ64" t="n">
         <v>7</v>
       </c>
+      <c r="DA64" t="inlineStr"/>
+      <c r="DB64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -20462,6 +20598,8 @@
       <c r="CZ65" t="n">
         <v>5</v>
       </c>
+      <c r="DA65" t="inlineStr"/>
+      <c r="DB65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -20764,6 +20902,8 @@
       <c r="CX66" t="inlineStr"/>
       <c r="CY66" t="inlineStr"/>
       <c r="CZ66" t="inlineStr"/>
+      <c r="DA66" t="inlineStr"/>
+      <c r="DB66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -21082,6 +21222,8 @@
       <c r="CZ67" t="n">
         <v>2</v>
       </c>
+      <c r="DA67" t="inlineStr"/>
+      <c r="DB67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -21392,6 +21534,8 @@
       <c r="CZ68" t="n">
         <v>5</v>
       </c>
+      <c r="DA68" t="inlineStr"/>
+      <c r="DB68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -21710,6 +21854,8 @@
       <c r="CZ69" t="n">
         <v>16</v>
       </c>
+      <c r="DA69" t="inlineStr"/>
+      <c r="DB69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -22032,6 +22178,8 @@
       <c r="CZ70" t="n">
         <v>4</v>
       </c>
+      <c r="DA70" t="inlineStr"/>
+      <c r="DB70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -22334,6 +22482,8 @@
       <c r="CZ71" t="n">
         <v>2</v>
       </c>
+      <c r="DA71" t="inlineStr"/>
+      <c r="DB71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -22650,6 +22800,8 @@
       <c r="CZ72" t="n">
         <v>1</v>
       </c>
+      <c r="DA72" t="inlineStr"/>
+      <c r="DB72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -22968,6 +23120,8 @@
       <c r="CZ73" t="n">
         <v>6</v>
       </c>
+      <c r="DA73" t="inlineStr"/>
+      <c r="DB73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -23282,6 +23436,8 @@
       <c r="CZ74" t="n">
         <v>3</v>
       </c>
+      <c r="DA74" t="inlineStr"/>
+      <c r="DB74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -23604,6 +23760,8 @@
       <c r="CZ75" t="n">
         <v>1</v>
       </c>
+      <c r="DA75" t="inlineStr"/>
+      <c r="DB75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -23904,6 +24062,8 @@
       <c r="CZ76" t="n">
         <v>3</v>
       </c>
+      <c r="DA76" t="inlineStr"/>
+      <c r="DB76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -24220,6 +24380,8 @@
       <c r="CZ77" t="n">
         <v>3</v>
       </c>
+      <c r="DA77" t="inlineStr"/>
+      <c r="DB77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -24540,6 +24702,8 @@
       <c r="CZ78" t="n">
         <v>3</v>
       </c>
+      <c r="DA78" t="inlineStr"/>
+      <c r="DB78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -24860,6 +25024,8 @@
       <c r="CZ79" t="n">
         <v>3</v>
       </c>
+      <c r="DA79" t="inlineStr"/>
+      <c r="DB79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -25176,6 +25342,8 @@
       <c r="CZ80" t="n">
         <v>6</v>
       </c>
+      <c r="DA80" t="inlineStr"/>
+      <c r="DB80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -25492,6 +25660,8 @@
       <c r="CZ81" t="n">
         <v>8</v>
       </c>
+      <c r="DA81" t="inlineStr"/>
+      <c r="DB81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -25806,6 +25976,8 @@
       <c r="CZ82" t="n">
         <v>10</v>
       </c>
+      <c r="DA82" t="inlineStr"/>
+      <c r="DB82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -26122,6 +26294,8 @@
       <c r="CZ83" t="n">
         <v>3</v>
       </c>
+      <c r="DA83" t="inlineStr"/>
+      <c r="DB83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -26438,6 +26612,8 @@
       <c r="CZ84" t="n">
         <v>7</v>
       </c>
+      <c r="DA84" t="inlineStr"/>
+      <c r="DB84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -26756,6 +26932,8 @@
       <c r="CZ85" t="n">
         <v>6</v>
       </c>
+      <c r="DA85" t="inlineStr"/>
+      <c r="DB85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -27074,6 +27252,8 @@
       <c r="CZ86" t="n">
         <v>15</v>
       </c>
+      <c r="DA86" t="inlineStr"/>
+      <c r="DB86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -27390,6 +27570,8 @@
       <c r="CZ87" t="n">
         <v>6</v>
       </c>
+      <c r="DA87" t="inlineStr"/>
+      <c r="DB87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -27712,6 +27894,8 @@
       <c r="CZ88" t="n">
         <v>3</v>
       </c>
+      <c r="DA88" t="inlineStr"/>
+      <c r="DB88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -28026,6 +28210,8 @@
       <c r="CZ89" t="n">
         <v>3</v>
       </c>
+      <c r="DA89" t="inlineStr"/>
+      <c r="DB89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -28344,6 +28530,8 @@
       <c r="CZ90" t="n">
         <v>5</v>
       </c>
+      <c r="DA90" t="inlineStr"/>
+      <c r="DB90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -28660,6 +28848,8 @@
       <c r="CZ91" t="n">
         <v>2</v>
       </c>
+      <c r="DA91" t="inlineStr"/>
+      <c r="DB91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -28972,6 +29162,8 @@
       <c r="CZ92" t="n">
         <v>3</v>
       </c>
+      <c r="DA92" t="inlineStr"/>
+      <c r="DB92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -29284,6 +29476,8 @@
       <c r="CZ93" t="n">
         <v>11</v>
       </c>
+      <c r="DA93" t="inlineStr"/>
+      <c r="DB93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -29602,6 +29796,8 @@
       <c r="CZ94" t="n">
         <v>3</v>
       </c>
+      <c r="DA94" t="inlineStr"/>
+      <c r="DB94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -29904,6 +30100,8 @@
       <c r="CZ95" t="n">
         <v>8</v>
       </c>
+      <c r="DA95" t="inlineStr"/>
+      <c r="DB95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -30220,6 +30418,8 @@
       <c r="CZ96" t="n">
         <v>7</v>
       </c>
+      <c r="DA96" t="inlineStr"/>
+      <c r="DB96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -30534,6 +30734,8 @@
       <c r="CZ97" t="n">
         <v>4</v>
       </c>
+      <c r="DA97" t="inlineStr"/>
+      <c r="DB97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -30852,6 +31054,8 @@
       <c r="CZ98" t="n">
         <v>1</v>
       </c>
+      <c r="DA98" t="inlineStr"/>
+      <c r="DB98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -31172,6 +31376,8 @@
       <c r="CZ99" t="n">
         <v>3</v>
       </c>
+      <c r="DA99" t="inlineStr"/>
+      <c r="DB99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -31486,6 +31692,8 @@
       <c r="CZ100" t="n">
         <v>3</v>
       </c>
+      <c r="DA100" t="inlineStr"/>
+      <c r="DB100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -31804,6 +32012,8 @@
       <c r="CZ101" t="n">
         <v>1</v>
       </c>
+      <c r="DA101" t="inlineStr"/>
+      <c r="DB101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -32122,6 +32332,8 @@
       <c r="CZ102" t="n">
         <v>3</v>
       </c>
+      <c r="DA102" t="inlineStr"/>
+      <c r="DB102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -32440,6 +32652,8 @@
       <c r="CZ103" t="n">
         <v>8</v>
       </c>
+      <c r="DA103" t="inlineStr"/>
+      <c r="DB103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -32754,6 +32968,8 @@
       <c r="CZ104" t="n">
         <v>7</v>
       </c>
+      <c r="DA104" t="inlineStr"/>
+      <c r="DB104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -33070,6 +33286,8 @@
       <c r="CZ105" t="n">
         <v>5</v>
       </c>
+      <c r="DA105" t="inlineStr"/>
+      <c r="DB105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -33370,6 +33588,8 @@
       <c r="CZ106" t="n">
         <v>12</v>
       </c>
+      <c r="DA106" t="inlineStr"/>
+      <c r="DB106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -33692,6 +33912,8 @@
       <c r="CZ107" t="n">
         <v>6</v>
       </c>
+      <c r="DA107" t="inlineStr"/>
+      <c r="DB107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -34010,6 +34232,8 @@
       <c r="CZ108" t="n">
         <v>5</v>
       </c>
+      <c r="DA108" t="inlineStr"/>
+      <c r="DB108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -34326,6 +34550,8 @@
       <c r="CZ109" t="n">
         <v>2</v>
       </c>
+      <c r="DA109" t="inlineStr"/>
+      <c r="DB109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -34642,6 +34868,8 @@
       <c r="CZ110" t="n">
         <v>14</v>
       </c>
+      <c r="DA110" t="inlineStr"/>
+      <c r="DB110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -34958,6 +35186,8 @@
       <c r="CZ111" t="n">
         <v>2</v>
       </c>
+      <c r="DA111" t="inlineStr"/>
+      <c r="DB111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -35276,6 +35506,8 @@
       <c r="CZ112" t="n">
         <v>14</v>
       </c>
+      <c r="DA112" t="inlineStr"/>
+      <c r="DB112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -35570,6 +35802,8 @@
       <c r="CX113" t="inlineStr"/>
       <c r="CY113" t="inlineStr"/>
       <c r="CZ113" t="inlineStr"/>
+      <c r="DA113" t="inlineStr"/>
+      <c r="DB113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -35876,6 +36110,8 @@
       <c r="CX114" t="inlineStr"/>
       <c r="CY114" t="inlineStr"/>
       <c r="CZ114" t="inlineStr"/>
+      <c r="DA114" t="inlineStr"/>
+      <c r="DB114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -36194,6 +36430,8 @@
       <c r="CZ115" t="n">
         <v>3</v>
       </c>
+      <c r="DA115" t="inlineStr"/>
+      <c r="DB115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -36508,6 +36746,8 @@
       <c r="CZ116" t="n">
         <v>1</v>
       </c>
+      <c r="DA116" t="inlineStr"/>
+      <c r="DB116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -36822,6 +37062,8 @@
       <c r="CZ117" t="n">
         <v>10</v>
       </c>
+      <c r="DA117" t="inlineStr"/>
+      <c r="DB117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -37140,6 +37382,8 @@
       <c r="CZ118" t="n">
         <v>5</v>
       </c>
+      <c r="DA118" t="inlineStr"/>
+      <c r="DB118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -37454,6 +37698,8 @@
       <c r="CZ119" t="n">
         <v>5</v>
       </c>
+      <c r="DA119" t="inlineStr"/>
+      <c r="DB119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -37772,6 +38018,8 @@
       <c r="CZ120" t="n">
         <v>6</v>
       </c>
+      <c r="DA120" t="inlineStr"/>
+      <c r="DB120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -38084,6 +38332,8 @@
       <c r="CZ121" t="n">
         <v>4</v>
       </c>
+      <c r="DA121" t="inlineStr"/>
+      <c r="DB121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -38402,6 +38652,8 @@
       <c r="CZ122" t="n">
         <v>8</v>
       </c>
+      <c r="DA122" t="inlineStr"/>
+      <c r="DB122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -38718,6 +38970,8 @@
       <c r="CZ123" t="n">
         <v>8</v>
       </c>
+      <c r="DA123" t="inlineStr"/>
+      <c r="DB123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -39036,6 +39290,8 @@
       <c r="CZ124" t="n">
         <v>6</v>
       </c>
+      <c r="DA124" t="inlineStr"/>
+      <c r="DB124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -39352,6 +39608,8 @@
       <c r="CZ125" t="n">
         <v>5</v>
       </c>
+      <c r="DA125" t="inlineStr"/>
+      <c r="DB125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -39670,6 +39928,8 @@
       <c r="CZ126" t="n">
         <v>8</v>
       </c>
+      <c r="DA126" t="inlineStr"/>
+      <c r="DB126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -39986,6 +40246,8 @@
       <c r="CZ127" t="n">
         <v>6</v>
       </c>
+      <c r="DA127" t="inlineStr"/>
+      <c r="DB127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -40306,6 +40568,8 @@
       <c r="CZ128" t="n">
         <v>6</v>
       </c>
+      <c r="DA128" t="inlineStr"/>
+      <c r="DB128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -40624,6 +40888,8 @@
       <c r="CZ129" t="n">
         <v>6</v>
       </c>
+      <c r="DA129" t="inlineStr"/>
+      <c r="DB129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -40946,6 +41212,8 @@
       <c r="CZ130" t="n">
         <v>8</v>
       </c>
+      <c r="DA130" t="inlineStr"/>
+      <c r="DB130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -41260,6 +41528,8 @@
       <c r="CZ131" t="n">
         <v>4</v>
       </c>
+      <c r="DA131" t="inlineStr"/>
+      <c r="DB131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -41574,6 +41844,8 @@
       <c r="CZ132" t="n">
         <v>3</v>
       </c>
+      <c r="DA132" t="inlineStr"/>
+      <c r="DB132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -41892,6 +42164,8 @@
       <c r="CZ133" t="n">
         <v>8</v>
       </c>
+      <c r="DA133" t="inlineStr"/>
+      <c r="DB133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -42194,6 +42468,8 @@
       <c r="CX134" t="inlineStr"/>
       <c r="CY134" t="inlineStr"/>
       <c r="CZ134" t="inlineStr"/>
+      <c r="DA134" t="inlineStr"/>
+      <c r="DB134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -42512,6 +42788,8 @@
       <c r="CZ135" t="n">
         <v>1</v>
       </c>
+      <c r="DA135" t="inlineStr"/>
+      <c r="DB135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -42830,6 +43108,8 @@
       <c r="CZ136" t="n">
         <v>7</v>
       </c>
+      <c r="DA136" t="inlineStr"/>
+      <c r="DB136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -43146,6 +43426,8 @@
       <c r="CZ137" t="n">
         <v>2</v>
       </c>
+      <c r="DA137" t="inlineStr"/>
+      <c r="DB137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -43464,6 +43746,8 @@
       <c r="CZ138" t="n">
         <v>3</v>
       </c>
+      <c r="DA138" t="inlineStr"/>
+      <c r="DB138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -43780,6 +44064,8 @@
       <c r="CZ139" t="n">
         <v>4</v>
       </c>
+      <c r="DA139" t="inlineStr"/>
+      <c r="DB139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -44096,6 +44382,8 @@
       <c r="CZ140" t="n">
         <v>4</v>
       </c>
+      <c r="DA140" t="inlineStr"/>
+      <c r="DB140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -44414,6 +44702,8 @@
       <c r="CZ141" t="n">
         <v>2</v>
       </c>
+      <c r="DA141" t="inlineStr"/>
+      <c r="DB141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -44728,6 +45018,8 @@
       <c r="CZ142" t="n">
         <v>3</v>
       </c>
+      <c r="DA142" t="inlineStr"/>
+      <c r="DB142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -45044,6 +45336,8 @@
       <c r="CZ143" t="n">
         <v>6</v>
       </c>
+      <c r="DA143" t="inlineStr"/>
+      <c r="DB143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -45360,6 +45654,8 @@
       <c r="CZ144" t="n">
         <v>8</v>
       </c>
+      <c r="DA144" t="inlineStr"/>
+      <c r="DB144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -45678,6 +45974,8 @@
       <c r="CZ145" t="n">
         <v>4</v>
       </c>
+      <c r="DA145" t="inlineStr"/>
+      <c r="DB145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -45994,6 +46292,8 @@
       <c r="CZ146" t="n">
         <v>4</v>
       </c>
+      <c r="DA146" t="inlineStr"/>
+      <c r="DB146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -46312,6 +46612,8 @@
       <c r="CZ147" t="n">
         <v>4</v>
       </c>
+      <c r="DA147" t="inlineStr"/>
+      <c r="DB147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -46626,6 +46928,8 @@
       <c r="CZ148" t="n">
         <v>9</v>
       </c>
+      <c r="DA148" t="inlineStr"/>
+      <c r="DB148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -46942,6 +47246,8 @@
       <c r="CZ149" t="n">
         <v>17</v>
       </c>
+      <c r="DA149" t="inlineStr"/>
+      <c r="DB149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -47260,6 +47566,8 @@
       <c r="CZ150" t="n">
         <v>4</v>
       </c>
+      <c r="DA150" t="inlineStr"/>
+      <c r="DB150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -47582,6 +47890,8 @@
       <c r="CZ151" t="n">
         <v>5</v>
       </c>
+      <c r="DA151" t="inlineStr"/>
+      <c r="DB151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -47898,6 +48208,8 @@
       <c r="CZ152" t="n">
         <v>1</v>
       </c>
+      <c r="DA152" t="inlineStr"/>
+      <c r="DB152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -48198,6 +48510,8 @@
       <c r="CX153" t="inlineStr"/>
       <c r="CY153" t="inlineStr"/>
       <c r="CZ153" t="inlineStr"/>
+      <c r="DA153" t="inlineStr"/>
+      <c r="DB153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -48514,6 +48828,8 @@
       <c r="CZ154" t="n">
         <v>6</v>
       </c>
+      <c r="DA154" t="inlineStr"/>
+      <c r="DB154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -48832,6 +49148,8 @@
       <c r="CZ155" t="n">
         <v>1</v>
       </c>
+      <c r="DA155" t="inlineStr"/>
+      <c r="DB155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -49154,6 +49472,8 @@
       <c r="CZ156" t="n">
         <v>4</v>
       </c>
+      <c r="DA156" t="inlineStr"/>
+      <c r="DB156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -49470,6 +49790,8 @@
       <c r="CZ157" t="n">
         <v>3</v>
       </c>
+      <c r="DA157" t="inlineStr"/>
+      <c r="DB157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -49784,6 +50106,8 @@
       <c r="CZ158" t="n">
         <v>3</v>
       </c>
+      <c r="DA158" t="inlineStr"/>
+      <c r="DB158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -50102,6 +50426,8 @@
       <c r="CZ159" t="n">
         <v>8</v>
       </c>
+      <c r="DA159" t="inlineStr"/>
+      <c r="DB159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -50420,6 +50746,8 @@
       <c r="CZ160" t="n">
         <v>4</v>
       </c>
+      <c r="DA160" t="inlineStr"/>
+      <c r="DB160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -50736,6 +51064,8 @@
       <c r="CZ161" t="n">
         <v>4</v>
       </c>
+      <c r="DA161" t="inlineStr"/>
+      <c r="DB161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -51006,6 +51336,8 @@
       <c r="CX162" t="inlineStr"/>
       <c r="CY162" t="inlineStr"/>
       <c r="CZ162" t="inlineStr"/>
+      <c r="DA162" t="inlineStr"/>
+      <c r="DB162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -51272,6 +51604,8 @@
       <c r="CX163" t="inlineStr"/>
       <c r="CY163" t="inlineStr"/>
       <c r="CZ163" t="inlineStr"/>
+      <c r="DA163" t="inlineStr"/>
+      <c r="DB163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -51550,6 +51884,8 @@
       <c r="CX164" t="inlineStr"/>
       <c r="CY164" t="inlineStr"/>
       <c r="CZ164" t="inlineStr"/>
+      <c r="DA164" t="inlineStr"/>
+      <c r="DB164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -51828,6 +52164,8 @@
       <c r="CX165" t="inlineStr"/>
       <c r="CY165" t="inlineStr"/>
       <c r="CZ165" t="inlineStr"/>
+      <c r="DA165" t="inlineStr"/>
+      <c r="DB165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -52090,6 +52428,8 @@
       <c r="CX166" t="inlineStr"/>
       <c r="CY166" t="inlineStr"/>
       <c r="CZ166" t="inlineStr"/>
+      <c r="DA166" t="inlineStr"/>
+      <c r="DB166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -52354,6 +52694,8 @@
       <c r="CX167" t="inlineStr"/>
       <c r="CY167" t="inlineStr"/>
       <c r="CZ167" t="inlineStr"/>
+      <c r="DA167" t="inlineStr"/>
+      <c r="DB167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -52632,6 +52974,8 @@
       <c r="CX168" t="inlineStr"/>
       <c r="CY168" t="inlineStr"/>
       <c r="CZ168" t="inlineStr"/>
+      <c r="DA168" t="inlineStr"/>
+      <c r="DB168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -52896,6 +53240,8 @@
       <c r="CX169" t="inlineStr"/>
       <c r="CY169" t="inlineStr"/>
       <c r="CZ169" t="inlineStr"/>
+      <c r="DA169" t="inlineStr"/>
+      <c r="DB169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -53176,6 +53522,8 @@
       <c r="CX170" t="inlineStr"/>
       <c r="CY170" t="inlineStr"/>
       <c r="CZ170" t="inlineStr"/>
+      <c r="DA170" t="inlineStr"/>
+      <c r="DB170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -53456,6 +53804,8 @@
       <c r="CX171" t="inlineStr"/>
       <c r="CY171" t="inlineStr"/>
       <c r="CZ171" t="inlineStr"/>
+      <c r="DA171" t="inlineStr"/>
+      <c r="DB171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -53734,6 +54084,8 @@
       <c r="CX172" t="inlineStr"/>
       <c r="CY172" t="inlineStr"/>
       <c r="CZ172" t="inlineStr"/>
+      <c r="DA172" t="inlineStr"/>
+      <c r="DB172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -54014,6 +54366,8 @@
       <c r="CX173" t="inlineStr"/>
       <c r="CY173" t="inlineStr"/>
       <c r="CZ173" t="inlineStr"/>
+      <c r="DA173" t="inlineStr"/>
+      <c r="DB173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -54294,6 +54648,8 @@
       <c r="CX174" t="inlineStr"/>
       <c r="CY174" t="inlineStr"/>
       <c r="CZ174" t="inlineStr"/>
+      <c r="DA174" t="inlineStr"/>
+      <c r="DB174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -54576,6 +54932,8 @@
       <c r="CX175" t="inlineStr"/>
       <c r="CY175" t="inlineStr"/>
       <c r="CZ175" t="inlineStr"/>
+      <c r="DA175" t="inlineStr"/>
+      <c r="DB175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -54854,6 +55212,8 @@
       <c r="CX176" t="inlineStr"/>
       <c r="CY176" t="inlineStr"/>
       <c r="CZ176" t="inlineStr"/>
+      <c r="DA176" t="inlineStr"/>
+      <c r="DB176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -55132,6 +55492,8 @@
       <c r="CX177" t="inlineStr"/>
       <c r="CY177" t="inlineStr"/>
       <c r="CZ177" t="inlineStr"/>
+      <c r="DA177" t="inlineStr"/>
+      <c r="DB177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -55408,6 +55770,8 @@
       <c r="CX178" t="inlineStr"/>
       <c r="CY178" t="inlineStr"/>
       <c r="CZ178" t="inlineStr"/>
+      <c r="DA178" t="inlineStr"/>
+      <c r="DB178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -55682,6 +56046,8 @@
       <c r="CX179" t="inlineStr"/>
       <c r="CY179" t="inlineStr"/>
       <c r="CZ179" t="inlineStr"/>
+      <c r="DA179" t="inlineStr"/>
+      <c r="DB179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -55958,6 +56324,8 @@
       <c r="CX180" t="inlineStr"/>
       <c r="CY180" t="inlineStr"/>
       <c r="CZ180" t="inlineStr"/>
+      <c r="DA180" t="inlineStr"/>
+      <c r="DB180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -56234,6 +56602,8 @@
       <c r="CX181" t="inlineStr"/>
       <c r="CY181" t="inlineStr"/>
       <c r="CZ181" t="inlineStr"/>
+      <c r="DA181" t="inlineStr"/>
+      <c r="DB181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -56512,6 +56882,8 @@
       <c r="CX182" t="inlineStr"/>
       <c r="CY182" t="inlineStr"/>
       <c r="CZ182" t="inlineStr"/>
+      <c r="DA182" t="inlineStr"/>
+      <c r="DB182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -56780,6 +57152,8 @@
       <c r="CX183" t="inlineStr"/>
       <c r="CY183" t="inlineStr"/>
       <c r="CZ183" t="inlineStr"/>
+      <c r="DA183" t="inlineStr"/>
+      <c r="DB183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -57018,6 +57392,8 @@
       <c r="CX184" t="inlineStr"/>
       <c r="CY184" t="inlineStr"/>
       <c r="CZ184" t="inlineStr"/>
+      <c r="DA184" t="inlineStr"/>
+      <c r="DB184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -57278,6 +57654,8 @@
       <c r="CX185" t="inlineStr"/>
       <c r="CY185" t="inlineStr"/>
       <c r="CZ185" t="inlineStr"/>
+      <c r="DA185" t="inlineStr"/>
+      <c r="DB185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -57459,6 +57837,8 @@
       <c r="CX186" t="inlineStr"/>
       <c r="CY186" t="inlineStr"/>
       <c r="CZ186" t="inlineStr"/>
+      <c r="DA186" t="inlineStr"/>
+      <c r="DB186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -57626,6 +58006,8 @@
       <c r="CX187" t="inlineStr"/>
       <c r="CY187" t="inlineStr"/>
       <c r="CZ187" t="inlineStr"/>
+      <c r="DA187" t="inlineStr"/>
+      <c r="DB187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -57805,6 +58187,8 @@
       <c r="CX188" t="inlineStr"/>
       <c r="CY188" t="inlineStr"/>
       <c r="CZ188" t="inlineStr"/>
+      <c r="DA188" t="inlineStr"/>
+      <c r="DB188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -57974,6 +58358,8 @@
       <c r="CX189" t="inlineStr"/>
       <c r="CY189" t="inlineStr"/>
       <c r="CZ189" t="inlineStr"/>
+      <c r="DA189" t="inlineStr"/>
+      <c r="DB189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -58244,6 +58630,8 @@
       <c r="CX190" t="inlineStr"/>
       <c r="CY190" t="inlineStr"/>
       <c r="CZ190" t="inlineStr"/>
+      <c r="DA190" t="inlineStr"/>
+      <c r="DB190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -58514,6 +58902,8 @@
       <c r="CX191" t="inlineStr"/>
       <c r="CY191" t="inlineStr"/>
       <c r="CZ191" t="inlineStr"/>
+      <c r="DA191" t="inlineStr"/>
+      <c r="DB191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -58782,6 +59172,8 @@
       <c r="CX192" t="inlineStr"/>
       <c r="CY192" t="inlineStr"/>
       <c r="CZ192" t="inlineStr"/>
+      <c r="DA192" t="inlineStr"/>
+      <c r="DB192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -59056,6 +59448,8 @@
       <c r="CX193" t="inlineStr"/>
       <c r="CY193" t="inlineStr"/>
       <c r="CZ193" t="inlineStr"/>
+      <c r="DA193" t="inlineStr"/>
+      <c r="DB193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -59324,6 +59718,8 @@
       <c r="CX194" t="inlineStr"/>
       <c r="CY194" t="inlineStr"/>
       <c r="CZ194" t="inlineStr"/>
+      <c r="DA194" t="inlineStr"/>
+      <c r="DB194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -59594,6 +59990,8 @@
       <c r="CX195" t="inlineStr"/>
       <c r="CY195" t="inlineStr"/>
       <c r="CZ195" t="inlineStr"/>
+      <c r="DA195" t="inlineStr"/>
+      <c r="DB195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -59868,6 +60266,8 @@
       <c r="CX196" t="inlineStr"/>
       <c r="CY196" t="inlineStr"/>
       <c r="CZ196" t="inlineStr"/>
+      <c r="DA196" t="inlineStr"/>
+      <c r="DB196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -60136,6 +60536,8 @@
       <c r="CX197" t="inlineStr"/>
       <c r="CY197" t="inlineStr"/>
       <c r="CZ197" t="inlineStr"/>
+      <c r="DA197" t="inlineStr"/>
+      <c r="DB197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -60420,6 +60822,8 @@
       <c r="CX198" t="inlineStr"/>
       <c r="CY198" t="inlineStr"/>
       <c r="CZ198" t="inlineStr"/>
+      <c r="DA198" t="inlineStr"/>
+      <c r="DB198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -60690,6 +61094,8 @@
       <c r="CX199" t="inlineStr"/>
       <c r="CY199" t="inlineStr"/>
       <c r="CZ199" t="inlineStr"/>
+      <c r="DA199" t="inlineStr"/>
+      <c r="DB199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -60972,6 +61378,8 @@
       <c r="CX200" t="inlineStr"/>
       <c r="CY200" t="inlineStr"/>
       <c r="CZ200" t="inlineStr"/>
+      <c r="DA200" t="inlineStr"/>
+      <c r="DB200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -61254,6 +61662,8 @@
       <c r="CX201" t="inlineStr"/>
       <c r="CY201" t="inlineStr"/>
       <c r="CZ201" t="inlineStr"/>
+      <c r="DA201" t="inlineStr"/>
+      <c r="DB201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -61534,6 +61944,8 @@
       <c r="CX202" t="inlineStr"/>
       <c r="CY202" t="inlineStr"/>
       <c r="CZ202" t="inlineStr"/>
+      <c r="DA202" t="inlineStr"/>
+      <c r="DB202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -61814,6 +62226,8 @@
       <c r="CX203" t="inlineStr"/>
       <c r="CY203" t="inlineStr"/>
       <c r="CZ203" t="inlineStr"/>
+      <c r="DA203" t="inlineStr"/>
+      <c r="DB203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -62112,6 +62526,8 @@
       <c r="CZ204" t="n">
         <v>3</v>
       </c>
+      <c r="DA204" t="inlineStr"/>
+      <c r="DB204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -62394,6 +62810,8 @@
       <c r="CX205" t="inlineStr"/>
       <c r="CY205" t="inlineStr"/>
       <c r="CZ205" t="inlineStr"/>
+      <c r="DA205" t="inlineStr"/>
+      <c r="DB205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -62676,6 +63094,8 @@
       <c r="CX206" t="inlineStr"/>
       <c r="CY206" t="inlineStr"/>
       <c r="CZ206" t="inlineStr"/>
+      <c r="DA206" t="inlineStr"/>
+      <c r="DB206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -62956,6 +63376,8 @@
       <c r="CX207" t="inlineStr"/>
       <c r="CY207" t="inlineStr"/>
       <c r="CZ207" t="inlineStr"/>
+      <c r="DA207" t="inlineStr"/>
+      <c r="DB207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -63238,6 +63660,8 @@
       <c r="CX208" t="inlineStr"/>
       <c r="CY208" t="inlineStr"/>
       <c r="CZ208" t="inlineStr"/>
+      <c r="DA208" t="inlineStr"/>
+      <c r="DB208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -63520,6 +63944,8 @@
       <c r="CX209" t="inlineStr"/>
       <c r="CY209" t="inlineStr"/>
       <c r="CZ209" t="inlineStr"/>
+      <c r="DA209" t="inlineStr"/>
+      <c r="DB209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -63802,6 +64228,8 @@
       <c r="CX210" t="inlineStr"/>
       <c r="CY210" t="inlineStr"/>
       <c r="CZ210" t="inlineStr"/>
+      <c r="DA210" t="inlineStr"/>
+      <c r="DB210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -64100,6 +64528,8 @@
       <c r="CZ211" t="n">
         <v>3</v>
       </c>
+      <c r="DA211" t="inlineStr"/>
+      <c r="DB211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -64382,6 +64812,8 @@
       <c r="CX212" t="inlineStr"/>
       <c r="CY212" t="inlineStr"/>
       <c r="CZ212" t="inlineStr"/>
+      <c r="DA212" t="inlineStr"/>
+      <c r="DB212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -64664,6 +65096,8 @@
       <c r="CX213" t="inlineStr"/>
       <c r="CY213" t="inlineStr"/>
       <c r="CZ213" t="inlineStr"/>
+      <c r="DA213" t="inlineStr"/>
+      <c r="DB213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -64948,6 +65382,8 @@
       <c r="CX214" t="inlineStr"/>
       <c r="CY214" t="inlineStr"/>
       <c r="CZ214" t="inlineStr"/>
+      <c r="DA214" t="inlineStr"/>
+      <c r="DB214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -65234,6 +65670,8 @@
       <c r="CX215" t="inlineStr"/>
       <c r="CY215" t="inlineStr"/>
       <c r="CZ215" t="inlineStr"/>
+      <c r="DA215" t="inlineStr"/>
+      <c r="DB215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -65516,6 +65954,8 @@
       <c r="CX216" t="inlineStr"/>
       <c r="CY216" t="inlineStr"/>
       <c r="CZ216" t="inlineStr"/>
+      <c r="DA216" t="inlineStr"/>
+      <c r="DB216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -65796,6 +66236,8 @@
       <c r="CX217" t="inlineStr"/>
       <c r="CY217" t="inlineStr"/>
       <c r="CZ217" t="inlineStr"/>
+      <c r="DA217" t="inlineStr"/>
+      <c r="DB217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -66078,6 +66520,8 @@
       <c r="CX218" t="inlineStr"/>
       <c r="CY218" t="inlineStr"/>
       <c r="CZ218" t="inlineStr"/>
+      <c r="DA218" t="inlineStr"/>
+      <c r="DB218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -66362,6 +66806,8 @@
       <c r="CX219" t="inlineStr"/>
       <c r="CY219" t="inlineStr"/>
       <c r="CZ219" t="inlineStr"/>
+      <c r="DA219" t="inlineStr"/>
+      <c r="DB219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -66644,6 +67090,8 @@
       <c r="CX220" t="inlineStr"/>
       <c r="CY220" t="inlineStr"/>
       <c r="CZ220" t="inlineStr"/>
+      <c r="DA220" t="inlineStr"/>
+      <c r="DB220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -66930,6 +67378,8 @@
       <c r="CX221" t="inlineStr"/>
       <c r="CY221" t="inlineStr"/>
       <c r="CZ221" t="inlineStr"/>
+      <c r="DA221" t="inlineStr"/>
+      <c r="DB221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -67210,6 +67660,8 @@
       <c r="CX222" t="inlineStr"/>
       <c r="CY222" t="inlineStr"/>
       <c r="CZ222" t="inlineStr"/>
+      <c r="DA222" t="inlineStr"/>
+      <c r="DB222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -67492,6 +67944,8 @@
       <c r="CX223" t="inlineStr"/>
       <c r="CY223" t="inlineStr"/>
       <c r="CZ223" t="inlineStr"/>
+      <c r="DA223" t="inlineStr"/>
+      <c r="DB223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -67772,6 +68226,8 @@
       <c r="CX224" t="inlineStr"/>
       <c r="CY224" t="inlineStr"/>
       <c r="CZ224" t="inlineStr"/>
+      <c r="DA224" t="inlineStr"/>
+      <c r="DB224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -68052,6 +68508,8 @@
       <c r="CX225" t="inlineStr"/>
       <c r="CY225" t="inlineStr"/>
       <c r="CZ225" t="inlineStr"/>
+      <c r="DA225" t="inlineStr"/>
+      <c r="DB225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -68346,6 +68804,8 @@
       <c r="CX226" t="inlineStr"/>
       <c r="CY226" t="inlineStr"/>
       <c r="CZ226" t="inlineStr"/>
+      <c r="DA226" t="inlineStr"/>
+      <c r="DB226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -68644,6 +69104,8 @@
       <c r="CX227" t="inlineStr"/>
       <c r="CY227" t="inlineStr"/>
       <c r="CZ227" t="inlineStr"/>
+      <c r="DA227" t="inlineStr"/>
+      <c r="DB227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -68926,6 +69388,8 @@
       <c r="CX228" t="inlineStr"/>
       <c r="CY228" t="inlineStr"/>
       <c r="CZ228" t="inlineStr"/>
+      <c r="DA228" t="inlineStr"/>
+      <c r="DB228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -69212,6 +69676,8 @@
       <c r="CX229" t="inlineStr"/>
       <c r="CY229" t="inlineStr"/>
       <c r="CZ229" t="inlineStr"/>
+      <c r="DA229" t="inlineStr"/>
+      <c r="DB229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -69494,6 +69960,8 @@
       <c r="CX230" t="inlineStr"/>
       <c r="CY230" t="inlineStr"/>
       <c r="CZ230" t="inlineStr"/>
+      <c r="DA230" t="inlineStr"/>
+      <c r="DB230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -69772,6 +70240,8 @@
       <c r="CX231" t="inlineStr"/>
       <c r="CY231" t="inlineStr"/>
       <c r="CZ231" t="inlineStr"/>
+      <c r="DA231" t="inlineStr"/>
+      <c r="DB231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -70052,6 +70522,8 @@
       <c r="CX232" t="inlineStr"/>
       <c r="CY232" t="inlineStr"/>
       <c r="CZ232" t="inlineStr"/>
+      <c r="DA232" t="inlineStr"/>
+      <c r="DB232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -70352,6 +70824,8 @@
       <c r="CZ233" t="n">
         <v>3</v>
       </c>
+      <c r="DA233" t="inlineStr"/>
+      <c r="DB233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -70634,6 +71108,8 @@
       <c r="CX234" t="inlineStr"/>
       <c r="CY234" t="inlineStr"/>
       <c r="CZ234" t="inlineStr"/>
+      <c r="DA234" t="inlineStr"/>
+      <c r="DB234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -70912,6 +71388,8 @@
       <c r="CX235" t="inlineStr"/>
       <c r="CY235" t="inlineStr"/>
       <c r="CZ235" t="inlineStr"/>
+      <c r="DA235" t="inlineStr"/>
+      <c r="DB235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -71194,6 +71672,8 @@
       <c r="CX236" t="inlineStr"/>
       <c r="CY236" t="inlineStr"/>
       <c r="CZ236" t="inlineStr"/>
+      <c r="DA236" t="inlineStr"/>
+      <c r="DB236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -71474,6 +71954,8 @@
       <c r="CX237" t="inlineStr"/>
       <c r="CY237" t="inlineStr"/>
       <c r="CZ237" t="inlineStr"/>
+      <c r="DA237" t="inlineStr"/>
+      <c r="DB237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -71754,6 +72236,8 @@
       <c r="CX238" t="inlineStr"/>
       <c r="CY238" t="inlineStr"/>
       <c r="CZ238" t="inlineStr"/>
+      <c r="DA238" t="inlineStr"/>
+      <c r="DB238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -72040,6 +72524,8 @@
       <c r="CX239" t="inlineStr"/>
       <c r="CY239" t="inlineStr"/>
       <c r="CZ239" t="inlineStr"/>
+      <c r="DA239" t="inlineStr"/>
+      <c r="DB239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -72320,6 +72806,8 @@
       <c r="CX240" t="inlineStr"/>
       <c r="CY240" t="inlineStr"/>
       <c r="CZ240" t="inlineStr"/>
+      <c r="DA240" t="inlineStr"/>
+      <c r="DB240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -72598,6 +73086,8 @@
       <c r="CX241" t="inlineStr"/>
       <c r="CY241" t="inlineStr"/>
       <c r="CZ241" t="inlineStr"/>
+      <c r="DA241" t="inlineStr"/>
+      <c r="DB241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -72882,6 +73372,8 @@
       <c r="CX242" t="inlineStr"/>
       <c r="CY242" t="inlineStr"/>
       <c r="CZ242" t="inlineStr"/>
+      <c r="DA242" t="inlineStr"/>
+      <c r="DB242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -73168,6 +73660,8 @@
       <c r="CX243" t="inlineStr"/>
       <c r="CY243" t="inlineStr"/>
       <c r="CZ243" t="inlineStr"/>
+      <c r="DA243" t="inlineStr"/>
+      <c r="DB243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -73448,6 +73942,8 @@
       <c r="CX244" t="inlineStr"/>
       <c r="CY244" t="inlineStr"/>
       <c r="CZ244" t="inlineStr"/>
+      <c r="DA244" t="inlineStr"/>
+      <c r="DB244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -73728,6 +74224,8 @@
       <c r="CX245" t="inlineStr"/>
       <c r="CY245" t="inlineStr"/>
       <c r="CZ245" t="inlineStr"/>
+      <c r="DA245" t="inlineStr"/>
+      <c r="DB245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -74018,6 +74516,8 @@
       <c r="CX246" t="inlineStr"/>
       <c r="CY246" t="inlineStr"/>
       <c r="CZ246" t="inlineStr"/>
+      <c r="DA246" t="inlineStr"/>
+      <c r="DB246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -74298,6 +74798,8 @@
       <c r="CX247" t="inlineStr"/>
       <c r="CY247" t="inlineStr"/>
       <c r="CZ247" t="inlineStr"/>
+      <c r="DA247" t="inlineStr"/>
+      <c r="DB247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -74580,6 +75082,8 @@
       <c r="CX248" t="inlineStr"/>
       <c r="CY248" t="inlineStr"/>
       <c r="CZ248" t="inlineStr"/>
+      <c r="DA248" t="inlineStr"/>
+      <c r="DB248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -74858,6 +75362,8 @@
       <c r="CX249" t="inlineStr"/>
       <c r="CY249" t="inlineStr"/>
       <c r="CZ249" t="inlineStr"/>
+      <c r="DA249" t="inlineStr"/>
+      <c r="DB249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -75154,6 +75660,8 @@
       <c r="CZ250" t="n">
         <v>3</v>
       </c>
+      <c r="DA250" t="inlineStr"/>
+      <c r="DB250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -75436,6 +75944,8 @@
       <c r="CX251" t="inlineStr"/>
       <c r="CY251" t="inlineStr"/>
       <c r="CZ251" t="inlineStr"/>
+      <c r="DA251" t="inlineStr"/>
+      <c r="DB251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -75716,6 +76226,8 @@
       <c r="CX252" t="inlineStr"/>
       <c r="CY252" t="inlineStr"/>
       <c r="CZ252" t="inlineStr"/>
+      <c r="DA252" t="inlineStr"/>
+      <c r="DB252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -76002,6 +76514,8 @@
       <c r="CX253" t="inlineStr"/>
       <c r="CY253" t="inlineStr"/>
       <c r="CZ253" t="inlineStr"/>
+      <c r="DA253" t="inlineStr"/>
+      <c r="DB253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -76280,6 +76794,8 @@
       <c r="CX254" t="inlineStr"/>
       <c r="CY254" t="inlineStr"/>
       <c r="CZ254" t="inlineStr"/>
+      <c r="DA254" t="inlineStr"/>
+      <c r="DB254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -76560,6 +77076,8 @@
       <c r="CX255" t="inlineStr"/>
       <c r="CY255" t="inlineStr"/>
       <c r="CZ255" t="inlineStr"/>
+      <c r="DA255" t="inlineStr"/>
+      <c r="DB255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -76840,6 +77358,8 @@
       <c r="CX256" t="inlineStr"/>
       <c r="CY256" t="inlineStr"/>
       <c r="CZ256" t="inlineStr"/>
+      <c r="DA256" t="inlineStr"/>
+      <c r="DB256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -77120,6 +77640,8 @@
       <c r="CX257" t="inlineStr"/>
       <c r="CY257" t="inlineStr"/>
       <c r="CZ257" t="inlineStr"/>
+      <c r="DA257" t="inlineStr"/>
+      <c r="DB257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -77400,6 +77922,8 @@
       <c r="CX258" t="inlineStr"/>
       <c r="CY258" t="inlineStr"/>
       <c r="CZ258" t="inlineStr"/>
+      <c r="DA258" t="inlineStr"/>
+      <c r="DB258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -77682,6 +78206,8 @@
       <c r="CX259" t="inlineStr"/>
       <c r="CY259" t="inlineStr"/>
       <c r="CZ259" t="inlineStr"/>
+      <c r="DA259" t="inlineStr"/>
+      <c r="DB259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -77978,6 +78504,8 @@
       <c r="CZ260" t="n">
         <v>7</v>
       </c>
+      <c r="DA260" t="inlineStr"/>
+      <c r="DB260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -78280,6 +78808,8 @@
       <c r="CZ261" t="n">
         <v>5</v>
       </c>
+      <c r="DA261" t="inlineStr"/>
+      <c r="DB261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -78582,6 +79112,8 @@
       <c r="CZ262" t="n">
         <v>3</v>
       </c>
+      <c r="DA262" t="inlineStr"/>
+      <c r="DB262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -78870,6 +79402,8 @@
       <c r="CZ263" t="n">
         <v>2</v>
       </c>
+      <c r="DA263" t="inlineStr"/>
+      <c r="DB263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -79170,6 +79704,8 @@
       <c r="CZ264" t="n">
         <v>3</v>
       </c>
+      <c r="DA264" t="inlineStr"/>
+      <c r="DB264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -79454,6 +79990,8 @@
       <c r="CX265" t="inlineStr"/>
       <c r="CY265" t="inlineStr"/>
       <c r="CZ265" t="inlineStr"/>
+      <c r="DA265" t="inlineStr"/>
+      <c r="DB265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -79752,6 +80290,8 @@
       <c r="CZ266" t="n">
         <v>4</v>
       </c>
+      <c r="DA266" t="inlineStr"/>
+      <c r="DB266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -80032,6 +80572,8 @@
       <c r="CX267" t="inlineStr"/>
       <c r="CY267" t="inlineStr"/>
       <c r="CZ267" t="inlineStr"/>
+      <c r="DA267" t="inlineStr"/>
+      <c r="DB267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -80332,6 +80874,8 @@
       <c r="CZ268" t="n">
         <v>3</v>
       </c>
+      <c r="DA268" t="inlineStr"/>
+      <c r="DB268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -80638,6 +81182,8 @@
       <c r="CZ269" t="n">
         <v>11</v>
       </c>
+      <c r="DA269" t="inlineStr"/>
+      <c r="DB269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -80944,6 +81490,8 @@
       <c r="CZ270" t="n">
         <v>5</v>
       </c>
+      <c r="DA270" t="inlineStr"/>
+      <c r="DB270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -81254,6 +81802,8 @@
       <c r="CZ271" t="n">
         <v>3</v>
       </c>
+      <c r="DA271" t="inlineStr"/>
+      <c r="DB271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -81544,6 +82094,8 @@
       <c r="CZ272" t="n">
         <v>5</v>
       </c>
+      <c r="DA272" t="inlineStr"/>
+      <c r="DB272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -81840,6 +82392,8 @@
       <c r="CZ273" t="n">
         <v>4</v>
       </c>
+      <c r="DA273" t="inlineStr"/>
+      <c r="DB273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -82146,6 +82700,8 @@
       <c r="CZ274" t="n">
         <v>3</v>
       </c>
+      <c r="DA274" t="inlineStr"/>
+      <c r="DB274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -82414,6 +82970,8 @@
       <c r="CX275" t="inlineStr"/>
       <c r="CY275" t="inlineStr"/>
       <c r="CZ275" t="inlineStr"/>
+      <c r="DA275" t="inlineStr"/>
+      <c r="DB275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -82720,6 +83278,8 @@
       <c r="CZ276" t="n">
         <v>3</v>
       </c>
+      <c r="DA276" t="inlineStr"/>
+      <c r="DB276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -83006,6 +83566,8 @@
       <c r="CZ277" t="n">
         <v>1</v>
       </c>
+      <c r="DA277" t="inlineStr"/>
+      <c r="DB277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -83274,6 +83836,8 @@
       <c r="CX278" t="inlineStr"/>
       <c r="CY278" t="inlineStr"/>
       <c r="CZ278" t="inlineStr"/>
+      <c r="DA278" t="inlineStr"/>
+      <c r="DB278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -83530,6 +84094,2664 @@
       <c r="CX279" t="inlineStr"/>
       <c r="CY279" t="inlineStr"/>
       <c r="CZ279" t="inlineStr"/>
+      <c r="DA279" t="inlineStr"/>
+      <c r="DB279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>45584.54166666666</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M280" t="n">
+        <v>44</v>
+      </c>
+      <c r="N280" t="n">
+        <v>56</v>
+      </c>
+      <c r="O280" t="n">
+        <v>10</v>
+      </c>
+      <c r="P280" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>5</v>
+      </c>
+      <c r="R280" t="n">
+        <v>1</v>
+      </c>
+      <c r="S280" t="n">
+        <v>1</v>
+      </c>
+      <c r="T280" t="n">
+        <v>11</v>
+      </c>
+      <c r="U280" t="n">
+        <v>4</v>
+      </c>
+      <c r="V280" t="n">
+        <v>1</v>
+      </c>
+      <c r="W280" t="n">
+        <v>14</v>
+      </c>
+      <c r="X280" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>335</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>411</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>278</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>367</v>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AQ280" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr"/>
+      <c r="BA280" t="inlineStr"/>
+      <c r="BB280" t="inlineStr"/>
+      <c r="BC280" t="inlineStr"/>
+      <c r="BD280" t="inlineStr"/>
+      <c r="BE280" t="inlineStr"/>
+      <c r="BF280" t="inlineStr"/>
+      <c r="BG280" t="inlineStr"/>
+      <c r="BH280" t="inlineStr"/>
+      <c r="BI280" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BJ280" t="n">
+        <v>184.375</v>
+      </c>
+      <c r="BK280" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="BL280" t="n">
+        <v>122625</v>
+      </c>
+      <c r="BM280" t="n">
+        <v>33650000</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BO280" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="BP280" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="BQ280" t="n">
+        <v>186.625</v>
+      </c>
+      <c r="BR280" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BS280" t="n">
+        <v>14875</v>
+      </c>
+      <c r="BT280" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="BU280" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="BV280" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW280" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="BX280" t="n">
+        <v>186.65</v>
+      </c>
+      <c r="BY280" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ280" t="n">
+        <v>98550</v>
+      </c>
+      <c r="CA280" t="n">
+        <v>25003750</v>
+      </c>
+      <c r="CB280" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="CC280" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CD280" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="CE280" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="CF280" t="n">
+        <v>71</v>
+      </c>
+      <c r="CG280" t="n">
+        <v>15150</v>
+      </c>
+      <c r="CH280" t="n">
+        <v>2681250</v>
+      </c>
+      <c r="CI280" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="CJ280" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK280" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="CL280" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="CM280" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN280" t="n">
+        <v>250</v>
+      </c>
+      <c r="CO280" t="n">
+        <v>480000</v>
+      </c>
+      <c r="CP280" t="n">
+        <v>155500000</v>
+      </c>
+      <c r="CQ280" t="n">
+        <v>256</v>
+      </c>
+      <c r="CR280" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS280" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="CT280" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="CU280" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV280" t="n">
+        <v>221</v>
+      </c>
+      <c r="CW280" t="n">
+        <v>57000</v>
+      </c>
+      <c r="CX280" t="n">
+        <v>22800000</v>
+      </c>
+      <c r="CY280" t="n">
+        <v>232</v>
+      </c>
+      <c r="CZ280" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA280" t="n">
+        <v>5</v>
+      </c>
+      <c r="DB280" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F281" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="K281" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M281" t="n">
+        <v>61</v>
+      </c>
+      <c r="N281" t="n">
+        <v>39</v>
+      </c>
+      <c r="O281" t="n">
+        <v>11</v>
+      </c>
+      <c r="P281" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>3</v>
+      </c>
+      <c r="R281" t="n">
+        <v>3</v>
+      </c>
+      <c r="S281" t="n">
+        <v>4</v>
+      </c>
+      <c r="T281" t="n">
+        <v>6</v>
+      </c>
+      <c r="U281" t="n">
+        <v>4</v>
+      </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="n">
+        <v>10</v>
+      </c>
+      <c r="X281" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>586</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>362</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>511</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>298</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AQ281" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW281" t="inlineStr"/>
+      <c r="AX281" t="inlineStr"/>
+      <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr"/>
+      <c r="BA281" t="inlineStr"/>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="inlineStr"/>
+      <c r="BI281" t="inlineStr"/>
+      <c r="BJ281" t="inlineStr"/>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="inlineStr"/>
+      <c r="BM281" t="inlineStr"/>
+      <c r="BN281" t="inlineStr"/>
+      <c r="BO281" t="inlineStr"/>
+      <c r="BP281" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BQ281" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="BR281" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BS281" t="n">
+        <v>25200</v>
+      </c>
+      <c r="BT281" t="n">
+        <v>5342500</v>
+      </c>
+      <c r="BU281" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BV281" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW281" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="BX281" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="BY281" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="BZ281" t="n">
+        <v>23150</v>
+      </c>
+      <c r="CA281" t="n">
+        <v>4151250</v>
+      </c>
+      <c r="CB281" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="CC281" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CD281" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="CE281" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="CF281" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="CG281" t="n">
+        <v>22950</v>
+      </c>
+      <c r="CH281" t="n">
+        <v>3038750</v>
+      </c>
+      <c r="CI281" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="CJ281" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK281" t="n">
+        <v>28</v>
+      </c>
+      <c r="CL281" t="n">
+        <v>194</v>
+      </c>
+      <c r="CM281" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN281" t="n">
+        <v>67</v>
+      </c>
+      <c r="CO281" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CP281" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CQ281" t="n">
+        <v>67</v>
+      </c>
+      <c r="CR281" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS281" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT281" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="CU281" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV281" t="n">
+        <v>289</v>
+      </c>
+      <c r="CW281" t="n">
+        <v>97000</v>
+      </c>
+      <c r="CX281" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="CY281" t="n">
+        <v>310</v>
+      </c>
+      <c r="CZ281" t="n">
+        <v>4</v>
+      </c>
+      <c r="DA281" t="n">
+        <v>9</v>
+      </c>
+      <c r="DB281" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F282" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L282" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M282" t="n">
+        <v>38</v>
+      </c>
+      <c r="N282" t="n">
+        <v>62</v>
+      </c>
+      <c r="O282" t="n">
+        <v>10</v>
+      </c>
+      <c r="P282" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>4</v>
+      </c>
+      <c r="R282" t="n">
+        <v>7</v>
+      </c>
+      <c r="S282" t="n">
+        <v>2</v>
+      </c>
+      <c r="T282" t="n">
+        <v>1</v>
+      </c>
+      <c r="U282" t="n">
+        <v>4</v>
+      </c>
+      <c r="V282" t="n">
+        <v>4</v>
+      </c>
+      <c r="W282" t="n">
+        <v>12</v>
+      </c>
+      <c r="X282" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>270</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>450</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>186</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>366</v>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AQ282" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW282" t="inlineStr"/>
+      <c r="AX282" t="inlineStr"/>
+      <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr"/>
+      <c r="BA282" t="inlineStr"/>
+      <c r="BB282" t="inlineStr"/>
+      <c r="BC282" t="inlineStr"/>
+      <c r="BD282" t="inlineStr"/>
+      <c r="BE282" t="inlineStr"/>
+      <c r="BF282" t="inlineStr"/>
+      <c r="BG282" t="inlineStr"/>
+      <c r="BH282" t="inlineStr"/>
+      <c r="BI282" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="BJ282" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="BK282" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BL282" t="n">
+        <v>28090.90909090909</v>
+      </c>
+      <c r="BM282" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BO282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP282" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BQ282" t="n">
+        <v>186.5555555555555</v>
+      </c>
+      <c r="BR282" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="BS282" t="n">
+        <v>46222.22222222222</v>
+      </c>
+      <c r="BT282" t="n">
+        <v>11588888.88888889</v>
+      </c>
+      <c r="BU282" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="BV282" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="BW282" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="BX282" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BY282" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="BZ282" t="n">
+        <v>29550</v>
+      </c>
+      <c r="CA282" t="n">
+        <v>2356250</v>
+      </c>
+      <c r="CB282" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="CC282" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CD282" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="CE282" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="CF282" t="n">
+        <v>73.55</v>
+      </c>
+      <c r="CG282" t="n">
+        <v>39550</v>
+      </c>
+      <c r="CH282" t="n">
+        <v>7602500</v>
+      </c>
+      <c r="CI282" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="CJ282" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CK282" t="n">
+        <v>28.42857142857143</v>
+      </c>
+      <c r="CL282" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="CM282" t="n">
+        <v>7</v>
+      </c>
+      <c r="CN282" t="n">
+        <v>516</v>
+      </c>
+      <c r="CO282" t="n">
+        <v>255000</v>
+      </c>
+      <c r="CP282" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="CQ282" t="n">
+        <v>534</v>
+      </c>
+      <c r="CR282" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS282" t="n">
+        <v>23.71428571428572</v>
+      </c>
+      <c r="CT282" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="CU282" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV282" t="n">
+        <v>519</v>
+      </c>
+      <c r="CW282" t="n">
+        <v>300000</v>
+      </c>
+      <c r="CX282" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="CY282" t="n">
+        <v>553</v>
+      </c>
+      <c r="CZ282" t="n">
+        <v>7</v>
+      </c>
+      <c r="DA282" t="n">
+        <v>5</v>
+      </c>
+      <c r="DB282" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>4MfFXWSP</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>45584.51041666666</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="n">
+        <v>2</v>
+      </c>
+      <c r="H283" t="n">
+        <v>5</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="n">
+        <v>49</v>
+      </c>
+      <c r="N283" t="n">
+        <v>51</v>
+      </c>
+      <c r="O283" t="n">
+        <v>20</v>
+      </c>
+      <c r="P283" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>8</v>
+      </c>
+      <c r="R283" t="n">
+        <v>8</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="n">
+        <v>8</v>
+      </c>
+      <c r="U283" t="n">
+        <v>2</v>
+      </c>
+      <c r="V283" t="n">
+        <v>5</v>
+      </c>
+      <c r="W283" t="n">
+        <v>18</v>
+      </c>
+      <c r="X283" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>445</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>466</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>407</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AQ283" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU283" t="inlineStr"/>
+      <c r="AV283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr"/>
+      <c r="AX283" t="inlineStr"/>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr"/>
+      <c r="BA283" t="inlineStr"/>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="n">
+        <v>25</v>
+      </c>
+      <c r="BF283" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="inlineStr"/>
+      <c r="BI283" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="BK283" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="BL283" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="BM283" t="n">
+        <v>1097222.222222222</v>
+      </c>
+      <c r="BN283" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BO283" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP283" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BQ283" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="BR283" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS283" t="n">
+        <v>5900</v>
+      </c>
+      <c r="BT283" t="n">
+        <v>4197500</v>
+      </c>
+      <c r="BU283" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="BV283" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW283" t="n">
+        <v>26.05555555555556</v>
+      </c>
+      <c r="BX283" t="n">
+        <v>180.2777777777778</v>
+      </c>
+      <c r="BY283" t="n">
+        <v>65.38888888888889</v>
+      </c>
+      <c r="BZ283" t="n">
+        <v>2611.111111111111</v>
+      </c>
+      <c r="CA283" t="n">
+        <v>972222.2222222222</v>
+      </c>
+      <c r="CB283" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="CC283" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD283" t="n">
+        <v>25.26086956521739</v>
+      </c>
+      <c r="CE283" t="n">
+        <v>183.695652173913</v>
+      </c>
+      <c r="CF283" t="n">
+        <v>69.30434782608695</v>
+      </c>
+      <c r="CG283" t="n">
+        <v>3217.391304347826</v>
+      </c>
+      <c r="CH283" t="n">
+        <v>6610869.565217392</v>
+      </c>
+      <c r="CI283" t="n">
+        <v>73.82608695652173</v>
+      </c>
+      <c r="CJ283" t="n">
+        <v>1.260869565217391</v>
+      </c>
+      <c r="CK283" t="inlineStr"/>
+      <c r="CL283" t="inlineStr"/>
+      <c r="CM283" t="inlineStr"/>
+      <c r="CN283" t="inlineStr"/>
+      <c r="CO283" t="inlineStr"/>
+      <c r="CP283" t="inlineStr"/>
+      <c r="CQ283" t="inlineStr"/>
+      <c r="CR283" t="inlineStr"/>
+      <c r="CS283" t="inlineStr"/>
+      <c r="CT283" t="inlineStr"/>
+      <c r="CU283" t="inlineStr"/>
+      <c r="CV283" t="inlineStr"/>
+      <c r="CW283" t="inlineStr"/>
+      <c r="CX283" t="inlineStr"/>
+      <c r="CY283" t="inlineStr"/>
+      <c r="CZ283" t="inlineStr"/>
+      <c r="DA283" t="inlineStr"/>
+      <c r="DB283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Imw2OSkC</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>60</v>
+      </c>
+      <c r="N284" t="n">
+        <v>40</v>
+      </c>
+      <c r="O284" t="n">
+        <v>21</v>
+      </c>
+      <c r="P284" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>5</v>
+      </c>
+      <c r="R284" t="n">
+        <v>2</v>
+      </c>
+      <c r="S284" t="n">
+        <v>8</v>
+      </c>
+      <c r="T284" t="n">
+        <v>3</v>
+      </c>
+      <c r="U284" t="n">
+        <v>8</v>
+      </c>
+      <c r="V284" t="n">
+        <v>5</v>
+      </c>
+      <c r="W284" t="n">
+        <v>24</v>
+      </c>
+      <c r="X284" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>426</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>276</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>358</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>202</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AQ284" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR284" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU284" t="inlineStr"/>
+      <c r="AV284" t="inlineStr"/>
+      <c r="AW284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr"/>
+      <c r="BA284" t="inlineStr"/>
+      <c r="BB284" t="inlineStr"/>
+      <c r="BC284" t="inlineStr"/>
+      <c r="BD284" t="inlineStr"/>
+      <c r="BE284" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF284" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG284" t="inlineStr"/>
+      <c r="BH284" t="inlineStr"/>
+      <c r="BI284" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="BM284" t="n">
+        <v>1063888.888888889</v>
+      </c>
+      <c r="BN284" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="BO284" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP284" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="BQ284" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="BR284" t="n">
+        <v>66.45454545454545</v>
+      </c>
+      <c r="BS284" t="n">
+        <v>4363.636363636364</v>
+      </c>
+      <c r="BT284" t="n">
+        <v>1386363.636363636</v>
+      </c>
+      <c r="BU284" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="BV284" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW284" t="n">
+        <v>24.36842105263158</v>
+      </c>
+      <c r="BX284" t="n">
+        <v>180</v>
+      </c>
+      <c r="BY284" t="n">
+        <v>64.42105263157895</v>
+      </c>
+      <c r="BZ284" t="n">
+        <v>2315.78947368421</v>
+      </c>
+      <c r="CA284" t="n">
+        <v>1183947.368421053</v>
+      </c>
+      <c r="CB284" t="n">
+        <v>70.68421052631579</v>
+      </c>
+      <c r="CC284" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD284" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="CE284" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="CF284" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="CG284" t="n">
+        <v>3500</v>
+      </c>
+      <c r="CH284" t="n">
+        <v>1256250</v>
+      </c>
+      <c r="CI284" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="CJ284" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK284" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CL284" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="CM284" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN284" t="n">
+        <v>113</v>
+      </c>
+      <c r="CO284" t="inlineStr"/>
+      <c r="CP284" t="n">
+        <v>770000</v>
+      </c>
+      <c r="CQ284" t="n">
+        <v>135</v>
+      </c>
+      <c r="CR284" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS284" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT284" t="n">
+        <v>180</v>
+      </c>
+      <c r="CU284" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV284" t="n">
+        <v>127</v>
+      </c>
+      <c r="CW284" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CX284" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="CY284" t="n">
+        <v>144</v>
+      </c>
+      <c r="CZ284" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA284" t="inlineStr"/>
+      <c r="DB284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>UR6KtA5t</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>21092</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="n">
+        <v>41</v>
+      </c>
+      <c r="N285" t="n">
+        <v>59</v>
+      </c>
+      <c r="O285" t="n">
+        <v>16</v>
+      </c>
+      <c r="P285" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>4</v>
+      </c>
+      <c r="R285" t="n">
+        <v>5</v>
+      </c>
+      <c r="S285" t="n">
+        <v>8</v>
+      </c>
+      <c r="T285" t="n">
+        <v>5</v>
+      </c>
+      <c r="U285" t="n">
+        <v>4</v>
+      </c>
+      <c r="V285" t="n">
+        <v>2</v>
+      </c>
+      <c r="W285" t="n">
+        <v>14</v>
+      </c>
+      <c r="X285" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>337</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>474</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>385</v>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AQ285" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU285" t="inlineStr"/>
+      <c r="AV285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr"/>
+      <c r="AX285" t="inlineStr"/>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr"/>
+      <c r="BA285" t="inlineStr"/>
+      <c r="BB285" t="inlineStr"/>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF285" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG285" t="inlineStr"/>
+      <c r="BH285" t="inlineStr"/>
+      <c r="BI285" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="BK285" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="BL285" t="n">
+        <v>5300</v>
+      </c>
+      <c r="BM285" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="BN285" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BO285" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP285" t="n">
+        <v>27.11111111111111</v>
+      </c>
+      <c r="BQ285" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="BR285" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="BS285" t="n">
+        <v>5444.444444444444</v>
+      </c>
+      <c r="BT285" t="n">
+        <v>2622222.222222222</v>
+      </c>
+      <c r="BU285" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BV285" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW285" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="BX285" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="BY285" t="n">
+        <v>66.29166666666667</v>
+      </c>
+      <c r="BZ285" t="inlineStr"/>
+      <c r="CA285" t="n">
+        <v>1047083.333333333</v>
+      </c>
+      <c r="CB285" t="n">
+        <v>69.04166666666667</v>
+      </c>
+      <c r="CC285" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD285" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="CE285" t="n">
+        <v>183.6875</v>
+      </c>
+      <c r="CF285" t="n">
+        <v>70.5625</v>
+      </c>
+      <c r="CG285" t="n">
+        <v>4687.5</v>
+      </c>
+      <c r="CH285" t="n">
+        <v>3060937.5</v>
+      </c>
+      <c r="CI285" t="n">
+        <v>76.3125</v>
+      </c>
+      <c r="CJ285" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK285" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL285" t="n">
+        <v>179</v>
+      </c>
+      <c r="CM285" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN285" t="n">
+        <v>209</v>
+      </c>
+      <c r="CO285" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CP285" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="CQ285" t="n">
+        <v>219</v>
+      </c>
+      <c r="CR285" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS285" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="CT285" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="CU285" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV285" t="n">
+        <v>345</v>
+      </c>
+      <c r="CW285" t="n">
+        <v>18000</v>
+      </c>
+      <c r="CX285" t="n">
+        <v>9725000</v>
+      </c>
+      <c r="CY285" t="n">
+        <v>367</v>
+      </c>
+      <c r="CZ285" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA285" t="inlineStr"/>
+      <c r="DB285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>dvbywS45</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="n">
+        <v>61</v>
+      </c>
+      <c r="N286" t="n">
+        <v>39</v>
+      </c>
+      <c r="O286" t="n">
+        <v>18</v>
+      </c>
+      <c r="P286" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>5</v>
+      </c>
+      <c r="R286" t="n">
+        <v>4</v>
+      </c>
+      <c r="S286" t="n">
+        <v>8</v>
+      </c>
+      <c r="T286" t="n">
+        <v>7</v>
+      </c>
+      <c r="U286" t="n">
+        <v>5</v>
+      </c>
+      <c r="V286" t="n">
+        <v>3</v>
+      </c>
+      <c r="W286" t="n">
+        <v>10</v>
+      </c>
+      <c r="X286" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>517</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>315</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>448</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>242</v>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AQ286" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU286" t="inlineStr"/>
+      <c r="AV286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr"/>
+      <c r="AX286" t="inlineStr"/>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr"/>
+      <c r="BA286" t="inlineStr"/>
+      <c r="BB286" t="inlineStr"/>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF286" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG286" t="inlineStr"/>
+      <c r="BH286" t="inlineStr"/>
+      <c r="BI286" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>183</v>
+      </c>
+      <c r="BK286" t="n">
+        <v>70</v>
+      </c>
+      <c r="BL286" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BM286" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="BN286" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO286" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BP286" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ286" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="BR286" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="BS286" t="n">
+        <v>6900</v>
+      </c>
+      <c r="BT286" t="n">
+        <v>1770000</v>
+      </c>
+      <c r="BU286" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BV286" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW286" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="BX286" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="BY286" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="BZ286" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CA286" t="n">
+        <v>1119750</v>
+      </c>
+      <c r="CB286" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="CC286" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CD286" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="CE286" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="CF286" t="n">
+        <v>65.54166666666667</v>
+      </c>
+      <c r="CG286" t="inlineStr"/>
+      <c r="CH286" t="n">
+        <v>1232083.333333333</v>
+      </c>
+      <c r="CI286" t="n">
+        <v>70.58333333333333</v>
+      </c>
+      <c r="CJ286" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK286" t="inlineStr"/>
+      <c r="CL286" t="inlineStr"/>
+      <c r="CM286" t="inlineStr"/>
+      <c r="CN286" t="inlineStr"/>
+      <c r="CO286" t="inlineStr"/>
+      <c r="CP286" t="inlineStr"/>
+      <c r="CQ286" t="inlineStr"/>
+      <c r="CR286" t="inlineStr"/>
+      <c r="CS286" t="inlineStr"/>
+      <c r="CT286" t="inlineStr"/>
+      <c r="CU286" t="inlineStr"/>
+      <c r="CV286" t="inlineStr"/>
+      <c r="CW286" t="inlineStr"/>
+      <c r="CX286" t="inlineStr"/>
+      <c r="CY286" t="inlineStr"/>
+      <c r="CZ286" t="inlineStr"/>
+      <c r="DA286" t="inlineStr"/>
+      <c r="DB286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>441qy6ZH</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="n">
+        <v>54</v>
+      </c>
+      <c r="N287" t="n">
+        <v>46</v>
+      </c>
+      <c r="O287" t="n">
+        <v>7</v>
+      </c>
+      <c r="P287" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>3</v>
+      </c>
+      <c r="R287" t="n">
+        <v>2</v>
+      </c>
+      <c r="S287" t="n">
+        <v>3</v>
+      </c>
+      <c r="T287" t="n">
+        <v>3</v>
+      </c>
+      <c r="U287" t="n">
+        <v>1</v>
+      </c>
+      <c r="V287" t="n">
+        <v>6</v>
+      </c>
+      <c r="W287" t="n">
+        <v>20</v>
+      </c>
+      <c r="X287" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK287" t="n">
+        <v>420</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>337</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>321</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>246</v>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AQ287" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU287" t="inlineStr"/>
+      <c r="AV287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr"/>
+      <c r="AX287" t="inlineStr"/>
+      <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr"/>
+      <c r="BA287" t="inlineStr"/>
+      <c r="BB287" t="inlineStr"/>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF287" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG287" t="inlineStr"/>
+      <c r="BH287" t="inlineStr"/>
+      <c r="BI287" t="n">
+        <v>30.45454545454545</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="BK287" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="BL287" t="n">
+        <v>3363.636363636364</v>
+      </c>
+      <c r="BM287" t="n">
+        <v>1216818.181818182</v>
+      </c>
+      <c r="BN287" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="BO287" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP287" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="BQ287" t="n">
+        <v>185.7777777777778</v>
+      </c>
+      <c r="BR287" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BS287" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="BT287" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="BU287" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="BV287" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW287" t="n">
+        <v>23.60869565217391</v>
+      </c>
+      <c r="BX287" t="n">
+        <v>183.3913043478261</v>
+      </c>
+      <c r="BY287" t="n">
+        <v>65.26086956521739</v>
+      </c>
+      <c r="BZ287" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CA287" t="n">
+        <v>1248913.043478261</v>
+      </c>
+      <c r="CB287" t="n">
+        <v>71.52173913043478</v>
+      </c>
+      <c r="CC287" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD287" t="n">
+        <v>23.95833333333333</v>
+      </c>
+      <c r="CE287" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="CF287" t="n">
+        <v>66.45833333333333</v>
+      </c>
+      <c r="CG287" t="n">
+        <v>5125</v>
+      </c>
+      <c r="CH287" t="n">
+        <v>1666666.666666667</v>
+      </c>
+      <c r="CI287" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="CJ287" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK287" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="CL287" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="CM287" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN287" t="n">
+        <v>201</v>
+      </c>
+      <c r="CO287" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CP287" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="CQ287" t="n">
+        <v>208</v>
+      </c>
+      <c r="CR287" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS287" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT287" t="n">
+        <v>183</v>
+      </c>
+      <c r="CU287" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV287" t="n">
+        <v>137</v>
+      </c>
+      <c r="CW287" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CX287" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="CY287" t="n">
+        <v>148</v>
+      </c>
+      <c r="CZ287" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA287" t="inlineStr"/>
+      <c r="DB287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>xG2T9TzJ</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F288" t="n">
+        <v>18615</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="n">
+        <v>42</v>
+      </c>
+      <c r="N288" t="n">
+        <v>58</v>
+      </c>
+      <c r="O288" t="n">
+        <v>16</v>
+      </c>
+      <c r="P288" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>5</v>
+      </c>
+      <c r="R288" t="n">
+        <v>7</v>
+      </c>
+      <c r="S288" t="n">
+        <v>6</v>
+      </c>
+      <c r="T288" t="n">
+        <v>8</v>
+      </c>
+      <c r="U288" t="n">
+        <v>5</v>
+      </c>
+      <c r="V288" t="n">
+        <v>3</v>
+      </c>
+      <c r="W288" t="n">
+        <v>19</v>
+      </c>
+      <c r="X288" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>368</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>486</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>306</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>435</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AQ288" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU288" t="inlineStr"/>
+      <c r="AV288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr"/>
+      <c r="AX288" t="inlineStr"/>
+      <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr"/>
+      <c r="BA288" t="inlineStr"/>
+      <c r="BB288" t="inlineStr"/>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="n">
+        <v>25</v>
+      </c>
+      <c r="BF288" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG288" t="inlineStr"/>
+      <c r="BH288" t="inlineStr"/>
+      <c r="BI288" t="n">
+        <v>28.27272727272727</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>180.8181818181818</v>
+      </c>
+      <c r="BK288" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="BL288" t="n">
+        <v>6818.181818181818</v>
+      </c>
+      <c r="BM288" t="n">
+        <v>1318181.818181818</v>
+      </c>
+      <c r="BN288" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="BO288" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP288" t="n">
+        <v>28.27272727272727</v>
+      </c>
+      <c r="BQ288" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="BR288" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="BS288" t="n">
+        <v>6636.363636363636</v>
+      </c>
+      <c r="BT288" t="n">
+        <v>968181.8181818182</v>
+      </c>
+      <c r="BU288" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="BV288" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW288" t="n">
+        <v>26.38095238095238</v>
+      </c>
+      <c r="BX288" t="n">
+        <v>183.8571428571429</v>
+      </c>
+      <c r="BY288" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="BZ288" t="n">
+        <v>9333.333333333334</v>
+      </c>
+      <c r="CA288" t="n">
+        <v>1128571.428571429</v>
+      </c>
+      <c r="CB288" t="n">
+        <v>69.14285714285714</v>
+      </c>
+      <c r="CC288" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD288" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="CE288" t="n">
+        <v>180.44</v>
+      </c>
+      <c r="CF288" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="CG288" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CH288" t="n">
+        <v>1307000</v>
+      </c>
+      <c r="CI288" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="CJ288" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK288" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL288" t="n">
+        <v>187</v>
+      </c>
+      <c r="CM288" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN288" t="n">
+        <v>126</v>
+      </c>
+      <c r="CO288" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CP288" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="CQ288" t="n">
+        <v>136</v>
+      </c>
+      <c r="CR288" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS288" t="inlineStr"/>
+      <c r="CT288" t="inlineStr"/>
+      <c r="CU288" t="inlineStr"/>
+      <c r="CV288" t="inlineStr"/>
+      <c r="CW288" t="inlineStr"/>
+      <c r="CX288" t="inlineStr"/>
+      <c r="CY288" t="inlineStr"/>
+      <c r="CZ288" t="inlineStr"/>
+      <c r="DA288" t="inlineStr"/>
+      <c r="DB288" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB288"/>
+  <dimension ref="A1:DB299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86753,6 +86753,3360 @@
       <c r="DA288" t="inlineStr"/>
       <c r="DB288" t="inlineStr"/>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K289" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M289" t="n">
+        <v>55</v>
+      </c>
+      <c r="N289" t="n">
+        <v>45</v>
+      </c>
+      <c r="O289" t="n">
+        <v>14</v>
+      </c>
+      <c r="P289" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>3</v>
+      </c>
+      <c r="R289" t="n">
+        <v>6</v>
+      </c>
+      <c r="S289" t="n">
+        <v>5</v>
+      </c>
+      <c r="T289" t="n">
+        <v>4</v>
+      </c>
+      <c r="U289" t="n">
+        <v>6</v>
+      </c>
+      <c r="V289" t="n">
+        <v>1</v>
+      </c>
+      <c r="W289" t="n">
+        <v>13</v>
+      </c>
+      <c r="X289" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>487</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>400</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>336</v>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AQ289" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW289" t="inlineStr"/>
+      <c r="AX289" t="inlineStr"/>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr"/>
+      <c r="BA289" t="inlineStr"/>
+      <c r="BB289" t="inlineStr"/>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr"/>
+      <c r="BH289" t="inlineStr"/>
+      <c r="BI289" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>79.625</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>42500</v>
+      </c>
+      <c r="BM289" t="n">
+        <v>26437500</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BO289" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP289" t="n">
+        <v>29.81818181818182</v>
+      </c>
+      <c r="BQ289" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="BR289" t="n">
+        <v>85</v>
+      </c>
+      <c r="BS289" t="n">
+        <v>120545.4545454545</v>
+      </c>
+      <c r="BT289" t="n">
+        <v>46409090.90909091</v>
+      </c>
+      <c r="BU289" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="BV289" t="n">
+        <v>3.545454545454545</v>
+      </c>
+      <c r="BW289" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BX289" t="n">
+        <v>177.1333333333333</v>
+      </c>
+      <c r="BY289" t="n">
+        <v>75.06666666666666</v>
+      </c>
+      <c r="BZ289" t="n">
+        <v>29666.66666666667</v>
+      </c>
+      <c r="CA289" t="n">
+        <v>18013333.33333333</v>
+      </c>
+      <c r="CB289" t="n">
+        <v>82.53333333333333</v>
+      </c>
+      <c r="CC289" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CD289" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="CE289" t="n">
+        <v>187.0416666666667</v>
+      </c>
+      <c r="CF289" t="n">
+        <v>80.08333333333333</v>
+      </c>
+      <c r="CG289" t="n">
+        <v>88916.66666666667</v>
+      </c>
+      <c r="CH289" t="n">
+        <v>27383333.33333333</v>
+      </c>
+      <c r="CI289" t="n">
+        <v>81.95833333333333</v>
+      </c>
+      <c r="CJ289" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="CK289" t="n">
+        <v>28</v>
+      </c>
+      <c r="CL289" t="n">
+        <v>179</v>
+      </c>
+      <c r="CM289" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN289" t="n">
+        <v>157</v>
+      </c>
+      <c r="CO289" t="n">
+        <v>142000</v>
+      </c>
+      <c r="CP289" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="CQ289" t="n">
+        <v>159</v>
+      </c>
+      <c r="CR289" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS289" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="CT289" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="CU289" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV289" t="n">
+        <v>230</v>
+      </c>
+      <c r="CW289" t="n">
+        <v>201000</v>
+      </c>
+      <c r="CX289" t="n">
+        <v>40500000</v>
+      </c>
+      <c r="CY289" t="n">
+        <v>239</v>
+      </c>
+      <c r="CZ289" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA289" t="n">
+        <v>5</v>
+      </c>
+      <c r="DB289" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>45585.54166666666</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F290" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G290" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M290" t="n">
+        <v>42</v>
+      </c>
+      <c r="N290" t="n">
+        <v>58</v>
+      </c>
+      <c r="O290" t="n">
+        <v>18</v>
+      </c>
+      <c r="P290" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>5</v>
+      </c>
+      <c r="R290" t="n">
+        <v>5</v>
+      </c>
+      <c r="S290" t="n">
+        <v>7</v>
+      </c>
+      <c r="T290" t="n">
+        <v>8</v>
+      </c>
+      <c r="U290" t="n">
+        <v>6</v>
+      </c>
+      <c r="V290" t="n">
+        <v>4</v>
+      </c>
+      <c r="W290" t="n">
+        <v>8</v>
+      </c>
+      <c r="X290" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>335</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>471</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>286</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>415</v>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AQ290" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW290" t="inlineStr"/>
+      <c r="AX290" t="inlineStr"/>
+      <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr"/>
+      <c r="BA290" t="inlineStr"/>
+      <c r="BB290" t="inlineStr"/>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr"/>
+      <c r="BH290" t="inlineStr"/>
+      <c r="BI290" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>184.7272727272727</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>18181.81818181818</v>
+      </c>
+      <c r="BM290" t="n">
+        <v>4027272.727272727</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="BO290" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BP290" t="n">
+        <v>27.125</v>
+      </c>
+      <c r="BQ290" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BR290" t="n">
+        <v>73.875</v>
+      </c>
+      <c r="BS290" t="n">
+        <v>35250</v>
+      </c>
+      <c r="BT290" t="n">
+        <v>7337500</v>
+      </c>
+      <c r="BU290" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="BV290" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW290" t="n">
+        <v>27.65384615384615</v>
+      </c>
+      <c r="BX290" t="n">
+        <v>182.9230769230769</v>
+      </c>
+      <c r="BY290" t="n">
+        <v>71.65384615384616</v>
+      </c>
+      <c r="BZ290" t="n">
+        <v>20846.15384615385</v>
+      </c>
+      <c r="CA290" t="n">
+        <v>3218269.230769231</v>
+      </c>
+      <c r="CB290" t="n">
+        <v>74.69230769230769</v>
+      </c>
+      <c r="CC290" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="CD290" t="n">
+        <v>23.46666666666667</v>
+      </c>
+      <c r="CE290" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="CF290" t="n">
+        <v>66.86666666666666</v>
+      </c>
+      <c r="CG290" t="n">
+        <v>24133.33333333333</v>
+      </c>
+      <c r="CH290" t="n">
+        <v>2028333.333333333</v>
+      </c>
+      <c r="CI290" t="n">
+        <v>74.86666666666666</v>
+      </c>
+      <c r="CJ290" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK290" t="n">
+        <v>28</v>
+      </c>
+      <c r="CL290" t="n">
+        <v>186</v>
+      </c>
+      <c r="CM290" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN290" t="n">
+        <v>210</v>
+      </c>
+      <c r="CO290" t="n">
+        <v>36000</v>
+      </c>
+      <c r="CP290" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="CQ290" t="n">
+        <v>219</v>
+      </c>
+      <c r="CR290" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS290" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT290" t="n">
+        <v>185</v>
+      </c>
+      <c r="CU290" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV290" t="n">
+        <v>303</v>
+      </c>
+      <c r="CW290" t="n">
+        <v>182000</v>
+      </c>
+      <c r="CX290" t="n">
+        <v>71900000</v>
+      </c>
+      <c r="CY290" t="n">
+        <v>331</v>
+      </c>
+      <c r="CZ290" t="n">
+        <v>6</v>
+      </c>
+      <c r="DA290" t="n">
+        <v>6</v>
+      </c>
+      <c r="DB290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F291" t="n">
+        <v>25124</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>6</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K291" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L291" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M291" t="n">
+        <v>39</v>
+      </c>
+      <c r="N291" t="n">
+        <v>61</v>
+      </c>
+      <c r="O291" t="n">
+        <v>5</v>
+      </c>
+      <c r="P291" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>2</v>
+      </c>
+      <c r="R291" t="n">
+        <v>11</v>
+      </c>
+      <c r="S291" t="n">
+        <v>2</v>
+      </c>
+      <c r="T291" t="n">
+        <v>4</v>
+      </c>
+      <c r="U291" t="n">
+        <v>1</v>
+      </c>
+      <c r="V291" t="n">
+        <v>4</v>
+      </c>
+      <c r="W291" t="n">
+        <v>14</v>
+      </c>
+      <c r="X291" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>353</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>567</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>279</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>511</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AQ291" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT291" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr"/>
+      <c r="BA291" t="inlineStr"/>
+      <c r="BB291" t="inlineStr"/>
+      <c r="BC291" t="inlineStr"/>
+      <c r="BD291" t="inlineStr"/>
+      <c r="BE291" t="inlineStr"/>
+      <c r="BF291" t="inlineStr"/>
+      <c r="BG291" t="inlineStr"/>
+      <c r="BH291" t="inlineStr"/>
+      <c r="BI291" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ291" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="BK291" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="BL291" t="n">
+        <v>12250</v>
+      </c>
+      <c r="BM291" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BO291" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP291" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="BQ291" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BR291" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="BS291" t="n">
+        <v>41888.88888888889</v>
+      </c>
+      <c r="BT291" t="n">
+        <v>14011111.11111111</v>
+      </c>
+      <c r="BU291" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="BV291" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="BW291" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX291" t="n">
+        <v>179.8235294117647</v>
+      </c>
+      <c r="BY291" t="n">
+        <v>70.17647058823529</v>
+      </c>
+      <c r="BZ291" t="n">
+        <v>10529.41176470588</v>
+      </c>
+      <c r="CA291" t="n">
+        <v>3251470.588235294</v>
+      </c>
+      <c r="CB291" t="n">
+        <v>75.17647058823529</v>
+      </c>
+      <c r="CC291" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD291" t="n">
+        <v>24.8695652173913</v>
+      </c>
+      <c r="CE291" t="n">
+        <v>181.4347826086957</v>
+      </c>
+      <c r="CF291" t="n">
+        <v>75.73913043478261</v>
+      </c>
+      <c r="CG291" t="n">
+        <v>41260.86956521739</v>
+      </c>
+      <c r="CH291" t="n">
+        <v>11846739.13043478</v>
+      </c>
+      <c r="CI291" t="n">
+        <v>80.52173913043478</v>
+      </c>
+      <c r="CJ291" t="n">
+        <v>1.304347826086957</v>
+      </c>
+      <c r="CK291" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="CL291" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="CM291" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN291" t="n">
+        <v>262</v>
+      </c>
+      <c r="CO291" t="n">
+        <v>35000</v>
+      </c>
+      <c r="CP291" t="n">
+        <v>7225000</v>
+      </c>
+      <c r="CQ291" t="n">
+        <v>305</v>
+      </c>
+      <c r="CR291" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS291" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="CT291" t="n">
+        <v>188</v>
+      </c>
+      <c r="CU291" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV291" t="n">
+        <v>152</v>
+      </c>
+      <c r="CW291" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CX291" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="CY291" t="n">
+        <v>158</v>
+      </c>
+      <c r="CZ291" t="n">
+        <v>3</v>
+      </c>
+      <c r="DA291" t="n">
+        <v>6</v>
+      </c>
+      <c r="DB291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F292" t="n">
+        <v>11979</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K292" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M292" t="n">
+        <v>42</v>
+      </c>
+      <c r="N292" t="n">
+        <v>58</v>
+      </c>
+      <c r="O292" t="n">
+        <v>12</v>
+      </c>
+      <c r="P292" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>4</v>
+      </c>
+      <c r="R292" t="n">
+        <v>7</v>
+      </c>
+      <c r="S292" t="n">
+        <v>7</v>
+      </c>
+      <c r="T292" t="n">
+        <v>8</v>
+      </c>
+      <c r="U292" t="n">
+        <v>1</v>
+      </c>
+      <c r="V292" t="n">
+        <v>1</v>
+      </c>
+      <c r="W292" t="n">
+        <v>6</v>
+      </c>
+      <c r="X292" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>370</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>503</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>292</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>413</v>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AQ292" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW292" t="inlineStr"/>
+      <c r="AX292" t="inlineStr"/>
+      <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr"/>
+      <c r="BA292" t="inlineStr"/>
+      <c r="BB292" t="inlineStr"/>
+      <c r="BC292" t="inlineStr"/>
+      <c r="BD292" t="inlineStr"/>
+      <c r="BE292" t="inlineStr"/>
+      <c r="BF292" t="inlineStr"/>
+      <c r="BG292" t="inlineStr"/>
+      <c r="BH292" t="inlineStr"/>
+      <c r="BI292" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BK292" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BL292" t="n">
+        <v>11600</v>
+      </c>
+      <c r="BM292" t="n">
+        <v>2810000</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="BO292" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BP292" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="BQ292" t="n">
+        <v>186.3636363636364</v>
+      </c>
+      <c r="BR292" t="n">
+        <v>79</v>
+      </c>
+      <c r="BS292" t="n">
+        <v>60363.63636363636</v>
+      </c>
+      <c r="BT292" t="n">
+        <v>20590909.09090909</v>
+      </c>
+      <c r="BU292" t="n">
+        <v>81.90909090909091</v>
+      </c>
+      <c r="BV292" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="BW292" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="BX292" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="BY292" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="BZ292" t="n">
+        <v>12200</v>
+      </c>
+      <c r="CA292" t="n">
+        <v>2602750</v>
+      </c>
+      <c r="CB292" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="CC292" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD292" t="n">
+        <v>24.86363636363636</v>
+      </c>
+      <c r="CE292" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="CF292" t="n">
+        <v>74.40909090909091</v>
+      </c>
+      <c r="CG292" t="n">
+        <v>39545.45454545454</v>
+      </c>
+      <c r="CH292" t="n">
+        <v>12287727.27272727</v>
+      </c>
+      <c r="CI292" t="n">
+        <v>80.31818181818181</v>
+      </c>
+      <c r="CJ292" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CK292" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL292" t="n">
+        <v>180</v>
+      </c>
+      <c r="CM292" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN292" t="n">
+        <v>65</v>
+      </c>
+      <c r="CO292" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CP292" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="CQ292" t="n">
+        <v>71</v>
+      </c>
+      <c r="CR292" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS292" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT292" t="n">
+        <v>190</v>
+      </c>
+      <c r="CU292" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV292" t="n">
+        <v>305</v>
+      </c>
+      <c r="CW292" t="n">
+        <v>180000</v>
+      </c>
+      <c r="CX292" t="n">
+        <v>68300000</v>
+      </c>
+      <c r="CY292" t="n">
+        <v>326</v>
+      </c>
+      <c r="CZ292" t="n">
+        <v>7</v>
+      </c>
+      <c r="DA292" t="n">
+        <v>7</v>
+      </c>
+      <c r="DB292" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>45585.3125</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F293" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K293" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M293" t="n">
+        <v>50</v>
+      </c>
+      <c r="N293" t="n">
+        <v>50</v>
+      </c>
+      <c r="O293" t="n">
+        <v>11</v>
+      </c>
+      <c r="P293" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>4</v>
+      </c>
+      <c r="R293" t="n">
+        <v>1</v>
+      </c>
+      <c r="S293" t="n">
+        <v>2</v>
+      </c>
+      <c r="T293" t="n">
+        <v>4</v>
+      </c>
+      <c r="U293" t="n">
+        <v>5</v>
+      </c>
+      <c r="V293" t="n">
+        <v>4</v>
+      </c>
+      <c r="W293" t="n">
+        <v>13</v>
+      </c>
+      <c r="X293" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>393</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>400</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>329</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>338</v>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AQ293" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT293" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW293" t="inlineStr"/>
+      <c r="AX293" t="inlineStr"/>
+      <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr"/>
+      <c r="BA293" t="inlineStr"/>
+      <c r="BB293" t="inlineStr"/>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
+      <c r="BI293" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BJ293" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="BK293" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BL293" t="n">
+        <v>22700</v>
+      </c>
+      <c r="BM293" t="n">
+        <v>3062500</v>
+      </c>
+      <c r="BN293" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="BO293" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP293" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="BQ293" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BR293" t="n">
+        <v>80.22222222222223</v>
+      </c>
+      <c r="BS293" t="n">
+        <v>107555.5555555556</v>
+      </c>
+      <c r="BT293" t="n">
+        <v>26444444.44444444</v>
+      </c>
+      <c r="BU293" t="n">
+        <v>82.44444444444444</v>
+      </c>
+      <c r="BV293" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW293" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="BX293" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="BY293" t="n">
+        <v>67.80952380952381</v>
+      </c>
+      <c r="BZ293" t="n">
+        <v>18095.2380952381</v>
+      </c>
+      <c r="CA293" t="n">
+        <v>2260714.285714286</v>
+      </c>
+      <c r="CB293" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="CC293" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="CD293" t="n">
+        <v>27.42105263157895</v>
+      </c>
+      <c r="CE293" t="n">
+        <v>182.0526315789474</v>
+      </c>
+      <c r="CF293" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="CG293" t="n">
+        <v>85052.63157894737</v>
+      </c>
+      <c r="CH293" t="n">
+        <v>13356578.94736842</v>
+      </c>
+      <c r="CI293" t="n">
+        <v>77.26315789473684</v>
+      </c>
+      <c r="CJ293" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="CK293" t="n">
+        <v>25</v>
+      </c>
+      <c r="CL293" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="CM293" t="n">
+        <v>6</v>
+      </c>
+      <c r="CN293" t="n">
+        <v>428</v>
+      </c>
+      <c r="CO293" t="n">
+        <v>71000</v>
+      </c>
+      <c r="CP293" t="n">
+        <v>18800000</v>
+      </c>
+      <c r="CQ293" t="n">
+        <v>448</v>
+      </c>
+      <c r="CR293" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS293" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="CT293" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="CU293" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV293" t="n">
+        <v>242</v>
+      </c>
+      <c r="CW293" t="n">
+        <v>294000</v>
+      </c>
+      <c r="CX293" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="CY293" t="n">
+        <v>244</v>
+      </c>
+      <c r="CZ293" t="n">
+        <v>8</v>
+      </c>
+      <c r="DA293" t="n">
+        <v>10</v>
+      </c>
+      <c r="DB293" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>45584.65625</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F294" t="n">
+        <v>40800</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="K294" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M294" t="n">
+        <v>69</v>
+      </c>
+      <c r="N294" t="n">
+        <v>31</v>
+      </c>
+      <c r="O294" t="n">
+        <v>16</v>
+      </c>
+      <c r="P294" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>3</v>
+      </c>
+      <c r="R294" t="n">
+        <v>1</v>
+      </c>
+      <c r="S294" t="n">
+        <v>10</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>3</v>
+      </c>
+      <c r="V294" t="n">
+        <v>1</v>
+      </c>
+      <c r="W294" t="n">
+        <v>9</v>
+      </c>
+      <c r="X294" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>604</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>268</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>545</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>209</v>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AQ294" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT294" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr"/>
+      <c r="BA294" t="inlineStr"/>
+      <c r="BB294" t="inlineStr"/>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
+      <c r="BI294" t="inlineStr"/>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+      <c r="BM294" t="inlineStr"/>
+      <c r="BN294" t="inlineStr"/>
+      <c r="BO294" t="inlineStr"/>
+      <c r="BP294" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BQ294" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BR294" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BS294" t="n">
+        <v>49800</v>
+      </c>
+      <c r="BT294" t="n">
+        <v>23850000</v>
+      </c>
+      <c r="BU294" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="BV294" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW294" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BX294" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="BY294" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="BZ294" t="n">
+        <v>73600</v>
+      </c>
+      <c r="CA294" t="n">
+        <v>13640000</v>
+      </c>
+      <c r="CB294" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="CC294" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CD294" t="n">
+        <v>28.04347826086957</v>
+      </c>
+      <c r="CE294" t="n">
+        <v>184.1739130434783</v>
+      </c>
+      <c r="CF294" t="n">
+        <v>75.8695652173913</v>
+      </c>
+      <c r="CG294" t="n">
+        <v>40391.30434782609</v>
+      </c>
+      <c r="CH294" t="n">
+        <v>10044565.2173913</v>
+      </c>
+      <c r="CI294" t="n">
+        <v>78.65217391304348</v>
+      </c>
+      <c r="CJ294" t="n">
+        <v>1.652173913043478</v>
+      </c>
+      <c r="CK294" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="CL294" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CM294" t="n">
+        <v>6</v>
+      </c>
+      <c r="CN294" t="n">
+        <v>490</v>
+      </c>
+      <c r="CO294" t="n">
+        <v>720000</v>
+      </c>
+      <c r="CP294" t="n">
+        <v>216500000</v>
+      </c>
+      <c r="CQ294" t="n">
+        <v>497</v>
+      </c>
+      <c r="CR294" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS294" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT294" t="n">
+        <v>174</v>
+      </c>
+      <c r="CU294" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV294" t="n">
+        <v>79</v>
+      </c>
+      <c r="CW294" t="n">
+        <v>50000</v>
+      </c>
+      <c r="CX294" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="CY294" t="n">
+        <v>79</v>
+      </c>
+      <c r="CZ294" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA294" t="n">
+        <v>4</v>
+      </c>
+      <c r="DB294" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>MLqgQlLa</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>45585.51041666666</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F295" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" t="n">
+        <v>5</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="n">
+        <v>52</v>
+      </c>
+      <c r="N295" t="n">
+        <v>48</v>
+      </c>
+      <c r="O295" t="n">
+        <v>10</v>
+      </c>
+      <c r="P295" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>5</v>
+      </c>
+      <c r="R295" t="n">
+        <v>6</v>
+      </c>
+      <c r="S295" t="n">
+        <v>2</v>
+      </c>
+      <c r="T295" t="n">
+        <v>6</v>
+      </c>
+      <c r="U295" t="n">
+        <v>3</v>
+      </c>
+      <c r="V295" t="n">
+        <v>2</v>
+      </c>
+      <c r="W295" t="n">
+        <v>22</v>
+      </c>
+      <c r="X295" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>448</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>407</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>388</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>341</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AQ295" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU295" t="inlineStr"/>
+      <c r="AV295" t="inlineStr"/>
+      <c r="AW295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr"/>
+      <c r="BA295" t="inlineStr"/>
+      <c r="BB295" t="inlineStr"/>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF295" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
+      <c r="BI295" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BJ295" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="BK295" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BL295" t="n">
+        <v>2700</v>
+      </c>
+      <c r="BM295" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="BN295" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BO295" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP295" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="BQ295" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BR295" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BS295" t="n">
+        <v>4400</v>
+      </c>
+      <c r="BT295" t="n">
+        <v>1997500</v>
+      </c>
+      <c r="BU295" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BV295" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW295" t="n">
+        <v>24.78947368421053</v>
+      </c>
+      <c r="BX295" t="n">
+        <v>181.3157894736842</v>
+      </c>
+      <c r="BY295" t="n">
+        <v>67.05263157894737</v>
+      </c>
+      <c r="BZ295" t="n">
+        <v>4263.157894736843</v>
+      </c>
+      <c r="CA295" t="n">
+        <v>1517105.263157895</v>
+      </c>
+      <c r="CB295" t="n">
+        <v>71.52631578947368</v>
+      </c>
+      <c r="CC295" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD295" t="n">
+        <v>24.96153846153846</v>
+      </c>
+      <c r="CE295" t="n">
+        <v>183.3076923076923</v>
+      </c>
+      <c r="CF295" t="n">
+        <v>69.19230769230769</v>
+      </c>
+      <c r="CG295" t="n">
+        <v>7653.846153846154</v>
+      </c>
+      <c r="CH295" t="n">
+        <v>2248076.923076923</v>
+      </c>
+      <c r="CI295" t="n">
+        <v>74.84615384615384</v>
+      </c>
+      <c r="CJ295" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK295" t="inlineStr"/>
+      <c r="CL295" t="inlineStr"/>
+      <c r="CM295" t="inlineStr"/>
+      <c r="CN295" t="inlineStr"/>
+      <c r="CO295" t="inlineStr"/>
+      <c r="CP295" t="inlineStr"/>
+      <c r="CQ295" t="inlineStr"/>
+      <c r="CR295" t="inlineStr"/>
+      <c r="CS295" t="n">
+        <v>34</v>
+      </c>
+      <c r="CT295" t="n">
+        <v>193</v>
+      </c>
+      <c r="CU295" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV295" t="n">
+        <v>71</v>
+      </c>
+      <c r="CW295" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CX295" t="n">
+        <v>600000</v>
+      </c>
+      <c r="CY295" t="n">
+        <v>71</v>
+      </c>
+      <c r="CZ295" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA295" t="inlineStr"/>
+      <c r="DB295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>lfWoSAjm</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monaldi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="n">
+        <v>35</v>
+      </c>
+      <c r="N296" t="n">
+        <v>65</v>
+      </c>
+      <c r="O296" t="n">
+        <v>16</v>
+      </c>
+      <c r="P296" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>5</v>
+      </c>
+      <c r="R296" t="n">
+        <v>2</v>
+      </c>
+      <c r="S296" t="n">
+        <v>5</v>
+      </c>
+      <c r="T296" t="n">
+        <v>3</v>
+      </c>
+      <c r="U296" t="n">
+        <v>6</v>
+      </c>
+      <c r="V296" t="n">
+        <v>4</v>
+      </c>
+      <c r="W296" t="n">
+        <v>20</v>
+      </c>
+      <c r="X296" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>266</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>513</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>433</v>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AQ296" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU296" t="inlineStr"/>
+      <c r="AV296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr"/>
+      <c r="AX296" t="inlineStr"/>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr"/>
+      <c r="BA296" t="inlineStr"/>
+      <c r="BB296" t="inlineStr"/>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF296" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG296" t="inlineStr"/>
+      <c r="BH296" t="inlineStr"/>
+      <c r="BI296" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="BK296" t="n">
+        <v>65.90909090909091</v>
+      </c>
+      <c r="BL296" t="n">
+        <v>6090.909090909091</v>
+      </c>
+      <c r="BM296" t="n">
+        <v>1127272.727272727</v>
+      </c>
+      <c r="BN296" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="BO296" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP296" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="BQ296" t="n">
+        <v>182</v>
+      </c>
+      <c r="BR296" t="n">
+        <v>65.875</v>
+      </c>
+      <c r="BS296" t="n">
+        <v>2375</v>
+      </c>
+      <c r="BT296" t="n">
+        <v>914375</v>
+      </c>
+      <c r="BU296" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="BV296" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW296" t="n">
+        <v>25.8695652173913</v>
+      </c>
+      <c r="BX296" t="n">
+        <v>179.304347826087</v>
+      </c>
+      <c r="BY296" t="n">
+        <v>63.73913043478261</v>
+      </c>
+      <c r="BZ296" t="n">
+        <v>4608.695652173913</v>
+      </c>
+      <c r="CA296" t="n">
+        <v>888043.4782608695</v>
+      </c>
+      <c r="CB296" t="n">
+        <v>67.69565217391305</v>
+      </c>
+      <c r="CC296" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD296" t="n">
+        <v>25.63157894736842</v>
+      </c>
+      <c r="CE296" t="n">
+        <v>181.2105263157895</v>
+      </c>
+      <c r="CF296" t="n">
+        <v>65</v>
+      </c>
+      <c r="CG296" t="inlineStr"/>
+      <c r="CH296" t="n">
+        <v>1021315.789473684</v>
+      </c>
+      <c r="CI296" t="n">
+        <v>70.36842105263158</v>
+      </c>
+      <c r="CJ296" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK296" t="n">
+        <v>21</v>
+      </c>
+      <c r="CL296" t="n">
+        <v>181</v>
+      </c>
+      <c r="CM296" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN296" t="n">
+        <v>62</v>
+      </c>
+      <c r="CO296" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CP296" t="n">
+        <v>975000</v>
+      </c>
+      <c r="CQ296" t="n">
+        <v>74</v>
+      </c>
+      <c r="CR296" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS296" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT296" t="n">
+        <v>182</v>
+      </c>
+      <c r="CU296" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV296" t="n">
+        <v>127</v>
+      </c>
+      <c r="CW296" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CX296" t="n">
+        <v>925000</v>
+      </c>
+      <c r="CY296" t="n">
+        <v>127</v>
+      </c>
+      <c r="CZ296" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA296" t="inlineStr"/>
+      <c r="DB296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>j1yAM6KO</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="n">
+        <v>1</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="n">
+        <v>54</v>
+      </c>
+      <c r="N297" t="n">
+        <v>46</v>
+      </c>
+      <c r="O297" t="n">
+        <v>15</v>
+      </c>
+      <c r="P297" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>4</v>
+      </c>
+      <c r="R297" t="n">
+        <v>6</v>
+      </c>
+      <c r="S297" t="n">
+        <v>6</v>
+      </c>
+      <c r="T297" t="n">
+        <v>4</v>
+      </c>
+      <c r="U297" t="n">
+        <v>5</v>
+      </c>
+      <c r="V297" t="n">
+        <v>6</v>
+      </c>
+      <c r="W297" t="n">
+        <v>16</v>
+      </c>
+      <c r="X297" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK297" t="n">
+        <v>398</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>343</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>264</v>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>AgMBZSTl</t>
+        </is>
+      </c>
+      <c r="AQ297" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR297" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT297" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU297" t="inlineStr"/>
+      <c r="AV297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr"/>
+      <c r="AX297" t="inlineStr"/>
+      <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr"/>
+      <c r="BA297" t="inlineStr"/>
+      <c r="BB297" t="inlineStr"/>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF297" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG297" t="inlineStr"/>
+      <c r="BH297" t="inlineStr"/>
+      <c r="BI297" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BJ297" t="n">
+        <v>185</v>
+      </c>
+      <c r="BK297" t="n">
+        <v>63.44444444444444</v>
+      </c>
+      <c r="BL297" t="n">
+        <v>4111.111111111111</v>
+      </c>
+      <c r="BM297" t="n">
+        <v>863888.8888888889</v>
+      </c>
+      <c r="BN297" t="n">
+        <v>68.44444444444444</v>
+      </c>
+      <c r="BO297" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP297" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BQ297" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="BR297" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BS297" t="n">
+        <v>5600</v>
+      </c>
+      <c r="BT297" t="n">
+        <v>2230000</v>
+      </c>
+      <c r="BU297" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="BV297" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW297" t="n">
+        <v>25.47826086956522</v>
+      </c>
+      <c r="BX297" t="n">
+        <v>182.2173913043478</v>
+      </c>
+      <c r="BY297" t="n">
+        <v>64.08695652173913</v>
+      </c>
+      <c r="BZ297" t="n">
+        <v>5869.565217391304</v>
+      </c>
+      <c r="CA297" t="n">
+        <v>840217.3913043478</v>
+      </c>
+      <c r="CB297" t="n">
+        <v>67.82608695652173</v>
+      </c>
+      <c r="CC297" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD297" t="n">
+        <v>25.23076923076923</v>
+      </c>
+      <c r="CE297" t="n">
+        <v>182.0769230769231</v>
+      </c>
+      <c r="CF297" t="n">
+        <v>67.34615384615384</v>
+      </c>
+      <c r="CG297" t="n">
+        <v>4076.923076923077</v>
+      </c>
+      <c r="CH297" t="n">
+        <v>1562500</v>
+      </c>
+      <c r="CI297" t="n">
+        <v>73.03846153846153</v>
+      </c>
+      <c r="CJ297" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK297" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL297" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="CM297" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN297" t="n">
+        <v>128</v>
+      </c>
+      <c r="CO297" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CP297" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="CQ297" t="n">
+        <v>137</v>
+      </c>
+      <c r="CR297" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS297" t="inlineStr"/>
+      <c r="CT297" t="inlineStr"/>
+      <c r="CU297" t="inlineStr"/>
+      <c r="CV297" t="inlineStr"/>
+      <c r="CW297" t="inlineStr"/>
+      <c r="CX297" t="inlineStr"/>
+      <c r="CY297" t="inlineStr"/>
+      <c r="CZ297" t="inlineStr"/>
+      <c r="DA297" t="inlineStr"/>
+      <c r="DB297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>zP9Svlzg</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F298" t="n">
+        <v>8459</v>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="n">
+        <v>43</v>
+      </c>
+      <c r="N298" t="n">
+        <v>57</v>
+      </c>
+      <c r="O298" t="n">
+        <v>8</v>
+      </c>
+      <c r="P298" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>6</v>
+      </c>
+      <c r="R298" t="n">
+        <v>3</v>
+      </c>
+      <c r="S298" t="n">
+        <v>2</v>
+      </c>
+      <c r="T298" t="n">
+        <v>7</v>
+      </c>
+      <c r="U298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V298" t="n">
+        <v>3</v>
+      </c>
+      <c r="W298" t="n">
+        <v>21</v>
+      </c>
+      <c r="X298" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>350</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>432</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>274</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>348</v>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AQ298" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT298" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU298" t="inlineStr"/>
+      <c r="AV298" t="inlineStr"/>
+      <c r="AW298" t="inlineStr"/>
+      <c r="AX298" t="inlineStr"/>
+      <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr"/>
+      <c r="BA298" t="inlineStr"/>
+      <c r="BB298" t="inlineStr"/>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="n">
+        <v>31</v>
+      </c>
+      <c r="BF298" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
+      <c r="BI298" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ298" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="BK298" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="BL298" t="n">
+        <v>14700</v>
+      </c>
+      <c r="BM298" t="n">
+        <v>2247500</v>
+      </c>
+      <c r="BN298" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BO298" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP298" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="BQ298" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="BR298" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="BS298" t="n">
+        <v>9909.09090909091</v>
+      </c>
+      <c r="BT298" t="n">
+        <v>1547727.272727273</v>
+      </c>
+      <c r="BU298" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="BV298" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW298" t="n">
+        <v>25.17391304347826</v>
+      </c>
+      <c r="BX298" t="n">
+        <v>181.6521739130435</v>
+      </c>
+      <c r="BY298" t="n">
+        <v>64.65217391304348</v>
+      </c>
+      <c r="BZ298" t="inlineStr"/>
+      <c r="CA298" t="n">
+        <v>1459347.826086957</v>
+      </c>
+      <c r="CB298" t="n">
+        <v>69.30434782608695</v>
+      </c>
+      <c r="CC298" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD298" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="CE298" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="CF298" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="CG298" t="n">
+        <v>7500</v>
+      </c>
+      <c r="CH298" t="n">
+        <v>1524500</v>
+      </c>
+      <c r="CI298" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="CJ298" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK298" t="n">
+        <v>31</v>
+      </c>
+      <c r="CL298" t="n">
+        <v>189</v>
+      </c>
+      <c r="CM298" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN298" t="n">
+        <v>65</v>
+      </c>
+      <c r="CO298" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CP298" t="n">
+        <v>500000</v>
+      </c>
+      <c r="CQ298" t="n">
+        <v>65</v>
+      </c>
+      <c r="CR298" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS298" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="CT298" t="n">
+        <v>191.6666666666667</v>
+      </c>
+      <c r="CU298" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV298" t="n">
+        <v>199</v>
+      </c>
+      <c r="CW298" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CX298" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="CY298" t="n">
+        <v>222</v>
+      </c>
+      <c r="CZ298" t="n">
+        <v>3</v>
+      </c>
+      <c r="DA298" t="inlineStr"/>
+      <c r="DB298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>McP0d8Q7</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>45586.65625</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>3</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K299" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M299" t="n">
+        <v>59</v>
+      </c>
+      <c r="N299" t="n">
+        <v>41</v>
+      </c>
+      <c r="O299" t="n">
+        <v>16</v>
+      </c>
+      <c r="P299" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>4</v>
+      </c>
+      <c r="R299" t="n">
+        <v>4</v>
+      </c>
+      <c r="S299" t="n">
+        <v>8</v>
+      </c>
+      <c r="T299" t="n">
+        <v>3</v>
+      </c>
+      <c r="U299" t="n">
+        <v>4</v>
+      </c>
+      <c r="V299" t="n">
+        <v>3</v>
+      </c>
+      <c r="W299" t="n">
+        <v>13</v>
+      </c>
+      <c r="X299" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH299" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK299" t="n">
+        <v>480</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>347</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AQ299" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR299" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT299" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU299" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW299" t="inlineStr"/>
+      <c r="AX299" t="inlineStr"/>
+      <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr"/>
+      <c r="BA299" t="inlineStr"/>
+      <c r="BB299" t="inlineStr"/>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
+      <c r="BI299" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BJ299" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BK299" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="BL299" t="n">
+        <v>12555.55555555555</v>
+      </c>
+      <c r="BM299" t="n">
+        <v>4766666.666666667</v>
+      </c>
+      <c r="BN299" t="n">
+        <v>77</v>
+      </c>
+      <c r="BO299" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP299" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BQ299" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BR299" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BS299" t="n">
+        <v>22500</v>
+      </c>
+      <c r="BT299" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="BU299" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="BV299" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BW299" t="n">
+        <v>26.52631578947368</v>
+      </c>
+      <c r="BX299" t="n">
+        <v>182.5263157894737</v>
+      </c>
+      <c r="BY299" t="n">
+        <v>71.73684210526316</v>
+      </c>
+      <c r="BZ299" t="n">
+        <v>11684.21052631579</v>
+      </c>
+      <c r="CA299" t="n">
+        <v>4867368.421052632</v>
+      </c>
+      <c r="CB299" t="n">
+        <v>75.52631578947368</v>
+      </c>
+      <c r="CC299" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="CD299" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="CE299" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="CF299" t="n">
+        <v>70.58333333333333</v>
+      </c>
+      <c r="CG299" t="n">
+        <v>34958.33333333334</v>
+      </c>
+      <c r="CH299" t="n">
+        <v>5843750</v>
+      </c>
+      <c r="CI299" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="CJ299" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="CK299" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="CL299" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="CM299" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN299" t="n">
+        <v>212</v>
+      </c>
+      <c r="CO299" t="n">
+        <v>42000</v>
+      </c>
+      <c r="CP299" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="CQ299" t="n">
+        <v>221</v>
+      </c>
+      <c r="CR299" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS299" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="CT299" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="CU299" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV299" t="n">
+        <v>297</v>
+      </c>
+      <c r="CW299" t="n">
+        <v>95000</v>
+      </c>
+      <c r="CX299" t="n">
+        <v>25300000</v>
+      </c>
+      <c r="CY299" t="n">
+        <v>307</v>
+      </c>
+      <c r="CZ299" t="n">
+        <v>4</v>
+      </c>
+      <c r="DA299" t="n">
+        <v>6</v>
+      </c>
+      <c r="DB299" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB299"/>
+  <dimension ref="A1:DB318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90107,6 +90107,5702 @@
         <v>8</v>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>45591.65625</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F300" t="n">
+        <v>23015</v>
+      </c>
+      <c r="G300" t="n">
+        <v>6</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="K300" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M300" t="n">
+        <v>69</v>
+      </c>
+      <c r="N300" t="n">
+        <v>31</v>
+      </c>
+      <c r="O300" t="n">
+        <v>19</v>
+      </c>
+      <c r="P300" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>10</v>
+      </c>
+      <c r="R300" t="n">
+        <v>2</v>
+      </c>
+      <c r="S300" t="n">
+        <v>6</v>
+      </c>
+      <c r="T300" t="n">
+        <v>2</v>
+      </c>
+      <c r="U300" t="n">
+        <v>3</v>
+      </c>
+      <c r="V300" t="n">
+        <v>0</v>
+      </c>
+      <c r="W300" t="n">
+        <v>15</v>
+      </c>
+      <c r="X300" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>785</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>349</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>714</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO300" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AP300" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AQ300" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT300" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW300" t="inlineStr"/>
+      <c r="AX300" t="inlineStr"/>
+      <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr"/>
+      <c r="BA300" t="inlineStr"/>
+      <c r="BB300" t="inlineStr"/>
+      <c r="BC300" t="inlineStr"/>
+      <c r="BD300" t="inlineStr"/>
+      <c r="BE300" t="inlineStr"/>
+      <c r="BF300" t="inlineStr"/>
+      <c r="BG300" t="inlineStr"/>
+      <c r="BH300" t="inlineStr"/>
+      <c r="BI300" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="BJ300" t="n">
+        <v>185.8181818181818</v>
+      </c>
+      <c r="BK300" t="n">
+        <v>78.63636363636364</v>
+      </c>
+      <c r="BL300" t="n">
+        <v>58636.36363636364</v>
+      </c>
+      <c r="BM300" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="BN300" t="n">
+        <v>81.90909090909091</v>
+      </c>
+      <c r="BO300" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="BP300" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="BQ300" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="BR300" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="BS300" t="n">
+        <v>11000</v>
+      </c>
+      <c r="BT300" t="n">
+        <v>5166666.666666667</v>
+      </c>
+      <c r="BU300" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="BV300" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BW300" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="BX300" t="n">
+        <v>185.5652173913043</v>
+      </c>
+      <c r="BY300" t="n">
+        <v>73.60869565217391</v>
+      </c>
+      <c r="BZ300" t="n">
+        <v>44565.21739130434</v>
+      </c>
+      <c r="CA300" t="n">
+        <v>13120434.7826087</v>
+      </c>
+      <c r="CB300" t="n">
+        <v>78.69565217391305</v>
+      </c>
+      <c r="CC300" t="n">
+        <v>1.652173913043478</v>
+      </c>
+      <c r="CD300" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="CE300" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="CF300" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="CG300" t="n">
+        <v>10937.5</v>
+      </c>
+      <c r="CH300" t="n">
+        <v>5184375</v>
+      </c>
+      <c r="CI300" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="CJ300" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="CK300" t="n">
+        <v>23</v>
+      </c>
+      <c r="CL300" t="n">
+        <v>192.3333333333333</v>
+      </c>
+      <c r="CM300" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN300" t="n">
+        <v>226</v>
+      </c>
+      <c r="CO300" t="n">
+        <v>114000</v>
+      </c>
+      <c r="CP300" t="n">
+        <v>56300000</v>
+      </c>
+      <c r="CQ300" t="n">
+        <v>247</v>
+      </c>
+      <c r="CR300" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS300" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT300" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CU300" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV300" t="n">
+        <v>286</v>
+      </c>
+      <c r="CW300" t="n">
+        <v>59000</v>
+      </c>
+      <c r="CX300" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="CY300" t="n">
+        <v>295</v>
+      </c>
+      <c r="CZ300" t="n">
+        <v>4</v>
+      </c>
+      <c r="DA300" t="n">
+        <v>6</v>
+      </c>
+      <c r="DB300" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F301" t="n">
+        <v>51103</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K301" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M301" t="n">
+        <v>65</v>
+      </c>
+      <c r="N301" t="n">
+        <v>35</v>
+      </c>
+      <c r="O301" t="n">
+        <v>24</v>
+      </c>
+      <c r="P301" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>8</v>
+      </c>
+      <c r="R301" t="n">
+        <v>2</v>
+      </c>
+      <c r="S301" t="n">
+        <v>7</v>
+      </c>
+      <c r="T301" t="n">
+        <v>4</v>
+      </c>
+      <c r="U301" t="n">
+        <v>9</v>
+      </c>
+      <c r="V301" t="n">
+        <v>5</v>
+      </c>
+      <c r="W301" t="n">
+        <v>7</v>
+      </c>
+      <c r="X301" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>493</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>272</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>423</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>198</v>
+      </c>
+      <c r="AO301" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AP301" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AQ301" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT301" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU301" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW301" t="inlineStr"/>
+      <c r="AX301" t="inlineStr"/>
+      <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr"/>
+      <c r="BA301" t="inlineStr"/>
+      <c r="BB301" t="inlineStr"/>
+      <c r="BC301" t="inlineStr"/>
+      <c r="BD301" t="inlineStr"/>
+      <c r="BE301" t="inlineStr"/>
+      <c r="BF301" t="inlineStr"/>
+      <c r="BG301" t="inlineStr"/>
+      <c r="BH301" t="inlineStr"/>
+      <c r="BI301" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="BJ301" t="n">
+        <v>186.875</v>
+      </c>
+      <c r="BK301" t="n">
+        <v>79.375</v>
+      </c>
+      <c r="BL301" t="n">
+        <v>96375</v>
+      </c>
+      <c r="BM301" t="n">
+        <v>19662500</v>
+      </c>
+      <c r="BN301" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BO301" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BP301" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="BQ301" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="BR301" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="BS301" t="n">
+        <v>11333.33333333333</v>
+      </c>
+      <c r="BT301" t="n">
+        <v>5222222.222222222</v>
+      </c>
+      <c r="BU301" t="n">
+        <v>77</v>
+      </c>
+      <c r="BV301" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW301" t="n">
+        <v>26.31578947368421</v>
+      </c>
+      <c r="BX301" t="n">
+        <v>180.1052631578947</v>
+      </c>
+      <c r="BY301" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="BZ301" t="n">
+        <v>94578.94736842105</v>
+      </c>
+      <c r="CA301" t="n">
+        <v>23321052.63157895</v>
+      </c>
+      <c r="CB301" t="n">
+        <v>80.73684210526316</v>
+      </c>
+      <c r="CC301" t="n">
+        <v>1.789473684210526</v>
+      </c>
+      <c r="CD301" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="CE301" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="CF301" t="n">
+        <v>70.8125</v>
+      </c>
+      <c r="CG301" t="n">
+        <v>11750</v>
+      </c>
+      <c r="CH301" t="n">
+        <v>3210937.5</v>
+      </c>
+      <c r="CI301" t="n">
+        <v>73.9375</v>
+      </c>
+      <c r="CJ301" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK301" t="n">
+        <v>31</v>
+      </c>
+      <c r="CL301" t="n">
+        <v>170</v>
+      </c>
+      <c r="CM301" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN301" t="n">
+        <v>161</v>
+      </c>
+      <c r="CO301" t="n">
+        <v>225000</v>
+      </c>
+      <c r="CP301" t="n">
+        <v>38500000</v>
+      </c>
+      <c r="CQ301" t="n">
+        <v>161</v>
+      </c>
+      <c r="CR301" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS301" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="CT301" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="CU301" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV301" t="n">
+        <v>336</v>
+      </c>
+      <c r="CW301" t="n">
+        <v>46000</v>
+      </c>
+      <c r="CX301" t="n">
+        <v>13225000</v>
+      </c>
+      <c r="CY301" t="n">
+        <v>385</v>
+      </c>
+      <c r="CZ301" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA301" t="n">
+        <v>7</v>
+      </c>
+      <c r="DB301" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>45590.65625</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F302" t="n">
+        <v>23571</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K302" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L302" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M302" t="n">
+        <v>31</v>
+      </c>
+      <c r="N302" t="n">
+        <v>69</v>
+      </c>
+      <c r="O302" t="n">
+        <v>8</v>
+      </c>
+      <c r="P302" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>2</v>
+      </c>
+      <c r="R302" t="n">
+        <v>6</v>
+      </c>
+      <c r="S302" t="n">
+        <v>3</v>
+      </c>
+      <c r="T302" t="n">
+        <v>6</v>
+      </c>
+      <c r="U302" t="n">
+        <v>3</v>
+      </c>
+      <c r="V302" t="n">
+        <v>8</v>
+      </c>
+      <c r="W302" t="n">
+        <v>12</v>
+      </c>
+      <c r="X302" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>628</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>211</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>552</v>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AP302" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AQ302" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR302" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT302" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU302" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW302" t="inlineStr"/>
+      <c r="AX302" t="inlineStr"/>
+      <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr"/>
+      <c r="BA302" t="inlineStr"/>
+      <c r="BB302" t="inlineStr"/>
+      <c r="BC302" t="inlineStr"/>
+      <c r="BD302" t="inlineStr"/>
+      <c r="BE302" t="inlineStr"/>
+      <c r="BF302" t="inlineStr"/>
+      <c r="BG302" t="inlineStr"/>
+      <c r="BH302" t="inlineStr"/>
+      <c r="BI302" t="inlineStr"/>
+      <c r="BJ302" t="inlineStr"/>
+      <c r="BK302" t="inlineStr"/>
+      <c r="BL302" t="inlineStr"/>
+      <c r="BM302" t="inlineStr"/>
+      <c r="BN302" t="inlineStr"/>
+      <c r="BO302" t="inlineStr"/>
+      <c r="BP302" t="inlineStr"/>
+      <c r="BQ302" t="inlineStr"/>
+      <c r="BR302" t="inlineStr"/>
+      <c r="BS302" t="inlineStr"/>
+      <c r="BT302" t="inlineStr"/>
+      <c r="BU302" t="inlineStr"/>
+      <c r="BV302" t="inlineStr"/>
+      <c r="BW302" t="n">
+        <v>25.04761904761905</v>
+      </c>
+      <c r="BX302" t="n">
+        <v>185.4285714285714</v>
+      </c>
+      <c r="BY302" t="n">
+        <v>68.71428571428571</v>
+      </c>
+      <c r="BZ302" t="n">
+        <v>27190.47619047619</v>
+      </c>
+      <c r="CA302" t="n">
+        <v>2844047.619047619</v>
+      </c>
+      <c r="CB302" t="n">
+        <v>74.9047619047619</v>
+      </c>
+      <c r="CC302" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD302" t="n">
+        <v>27.73684210526316</v>
+      </c>
+      <c r="CE302" t="n">
+        <v>180.1578947368421</v>
+      </c>
+      <c r="CF302" t="n">
+        <v>73.57894736842105</v>
+      </c>
+      <c r="CG302" t="n">
+        <v>24263.15789473684</v>
+      </c>
+      <c r="CH302" t="n">
+        <v>5685526.315789473</v>
+      </c>
+      <c r="CI302" t="n">
+        <v>75.78947368421052</v>
+      </c>
+      <c r="CJ302" t="n">
+        <v>1.421052631578947</v>
+      </c>
+      <c r="CK302" t="n">
+        <v>25</v>
+      </c>
+      <c r="CL302" t="n">
+        <v>185</v>
+      </c>
+      <c r="CM302" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN302" t="n">
+        <v>303</v>
+      </c>
+      <c r="CO302" t="n">
+        <v>182000</v>
+      </c>
+      <c r="CP302" t="n">
+        <v>71900000</v>
+      </c>
+      <c r="CQ302" t="n">
+        <v>331</v>
+      </c>
+      <c r="CR302" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS302" t="inlineStr"/>
+      <c r="CT302" t="inlineStr"/>
+      <c r="CU302" t="inlineStr"/>
+      <c r="CV302" t="inlineStr"/>
+      <c r="CW302" t="inlineStr"/>
+      <c r="CX302" t="inlineStr"/>
+      <c r="CY302" t="inlineStr"/>
+      <c r="CZ302" t="inlineStr"/>
+      <c r="DA302" t="n">
+        <v>10</v>
+      </c>
+      <c r="DB302" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>I5fXHFho</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>45590.5625</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F303" t="n">
+        <v>21095</v>
+      </c>
+      <c r="G303" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="K303" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M303" t="n">
+        <v>64</v>
+      </c>
+      <c r="N303" t="n">
+        <v>36</v>
+      </c>
+      <c r="O303" t="n">
+        <v>13</v>
+      </c>
+      <c r="P303" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>4</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>7</v>
+      </c>
+      <c r="T303" t="n">
+        <v>3</v>
+      </c>
+      <c r="U303" t="n">
+        <v>2</v>
+      </c>
+      <c r="V303" t="n">
+        <v>0</v>
+      </c>
+      <c r="W303" t="n">
+        <v>9</v>
+      </c>
+      <c r="X303" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>532</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>293</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>484</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>234</v>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AP303" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AQ303" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr"/>
+      <c r="BA303" t="inlineStr"/>
+      <c r="BB303" t="inlineStr"/>
+      <c r="BC303" t="inlineStr"/>
+      <c r="BD303" t="inlineStr"/>
+      <c r="BE303" t="inlineStr"/>
+      <c r="BF303" t="inlineStr"/>
+      <c r="BG303" t="inlineStr"/>
+      <c r="BH303" t="inlineStr"/>
+      <c r="BI303" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>187.1111111111111</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>15777.77777777778</v>
+      </c>
+      <c r="BM303" t="n">
+        <v>3444444.444444444</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="BO303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP303" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="BQ303" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="BR303" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="BS303" t="n">
+        <v>22818.18181818182</v>
+      </c>
+      <c r="BT303" t="n">
+        <v>4272727.272727272</v>
+      </c>
+      <c r="BU303" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="BV303" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BW303" t="n">
+        <v>26.63157894736842</v>
+      </c>
+      <c r="BX303" t="n">
+        <v>181.7894736842105</v>
+      </c>
+      <c r="BY303" t="n">
+        <v>70.15789473684211</v>
+      </c>
+      <c r="BZ303" t="n">
+        <v>14157.8947368421</v>
+      </c>
+      <c r="CA303" t="n">
+        <v>2248684.210526316</v>
+      </c>
+      <c r="CB303" t="n">
+        <v>73.89473684210526</v>
+      </c>
+      <c r="CC303" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD303" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="CE303" t="n">
+        <v>181.3703703703704</v>
+      </c>
+      <c r="CF303" t="n">
+        <v>70.85185185185185</v>
+      </c>
+      <c r="CG303" t="n">
+        <v>16703.7037037037</v>
+      </c>
+      <c r="CH303" t="n">
+        <v>3276851.851851852</v>
+      </c>
+      <c r="CI303" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="CJ303" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK303" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="CL303" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="CM303" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN303" t="n">
+        <v>221</v>
+      </c>
+      <c r="CO303" t="n">
+        <v>57000</v>
+      </c>
+      <c r="CP303" t="n">
+        <v>22800000</v>
+      </c>
+      <c r="CQ303" t="n">
+        <v>232</v>
+      </c>
+      <c r="CR303" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS303" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="CT303" t="n">
+        <v>186</v>
+      </c>
+      <c r="CU303" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV303" t="n">
+        <v>141</v>
+      </c>
+      <c r="CW303" t="n">
+        <v>27000</v>
+      </c>
+      <c r="CX303" t="n">
+        <v>2575000</v>
+      </c>
+      <c r="CY303" t="n">
+        <v>141</v>
+      </c>
+      <c r="CZ303" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA303" t="n">
+        <v>8</v>
+      </c>
+      <c r="DB303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>0WfhZq4U</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>45591.51041666666</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="n">
+        <v>3</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="n">
+        <v>59</v>
+      </c>
+      <c r="N304" t="n">
+        <v>41</v>
+      </c>
+      <c r="O304" t="n">
+        <v>9</v>
+      </c>
+      <c r="P304" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>4</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2</v>
+      </c>
+      <c r="S304" t="n">
+        <v>3</v>
+      </c>
+      <c r="T304" t="n">
+        <v>10</v>
+      </c>
+      <c r="U304" t="n">
+        <v>2</v>
+      </c>
+      <c r="V304" t="n">
+        <v>8</v>
+      </c>
+      <c r="W304" t="n">
+        <v>8</v>
+      </c>
+      <c r="X304" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>561</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>361</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>464</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>286</v>
+      </c>
+      <c r="AO304" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AP304" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AQ304" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU304" t="inlineStr"/>
+      <c r="AV304" t="inlineStr"/>
+      <c r="AW304" t="inlineStr"/>
+      <c r="AX304" t="inlineStr"/>
+      <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr"/>
+      <c r="BA304" t="inlineStr"/>
+      <c r="BB304" t="inlineStr"/>
+      <c r="BC304" t="inlineStr"/>
+      <c r="BD304" t="inlineStr"/>
+      <c r="BE304" t="n">
+        <v>25</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG304" t="inlineStr"/>
+      <c r="BH304" t="inlineStr"/>
+      <c r="BI304" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>4300</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>827500</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="BO304" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP304" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BQ304" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="BR304" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BS304" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BT304" t="n">
+        <v>1247500</v>
+      </c>
+      <c r="BU304" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BV304" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW304" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="BX304" t="n">
+        <v>180</v>
+      </c>
+      <c r="BY304" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="BZ304" t="n">
+        <v>6200</v>
+      </c>
+      <c r="CA304" t="n">
+        <v>1155800</v>
+      </c>
+      <c r="CB304" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="CC304" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD304" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="CE304" t="n">
+        <v>181.1578947368421</v>
+      </c>
+      <c r="CF304" t="n">
+        <v>62.63157894736842</v>
+      </c>
+      <c r="CG304" t="n">
+        <v>2263.157894736842</v>
+      </c>
+      <c r="CH304" t="n">
+        <v>870789.4736842106</v>
+      </c>
+      <c r="CI304" t="n">
+        <v>69.10526315789474</v>
+      </c>
+      <c r="CJ304" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK304" t="inlineStr"/>
+      <c r="CL304" t="inlineStr"/>
+      <c r="CM304" t="inlineStr"/>
+      <c r="CN304" t="inlineStr"/>
+      <c r="CO304" t="inlineStr"/>
+      <c r="CP304" t="inlineStr"/>
+      <c r="CQ304" t="inlineStr"/>
+      <c r="CR304" t="inlineStr"/>
+      <c r="CS304" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT304" t="n">
+        <v>176</v>
+      </c>
+      <c r="CU304" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV304" t="n">
+        <v>53</v>
+      </c>
+      <c r="CW304" t="inlineStr"/>
+      <c r="CX304" t="n">
+        <v>220000</v>
+      </c>
+      <c r="CY304" t="n">
+        <v>65</v>
+      </c>
+      <c r="CZ304" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA304" t="inlineStr"/>
+      <c r="DB304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>4vIh2rYG</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>45591.51041666666</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="n">
+        <v>2</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="n">
+        <v>52</v>
+      </c>
+      <c r="N305" t="n">
+        <v>48</v>
+      </c>
+      <c r="O305" t="n">
+        <v>12</v>
+      </c>
+      <c r="P305" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>5</v>
+      </c>
+      <c r="R305" t="n">
+        <v>5</v>
+      </c>
+      <c r="S305" t="n">
+        <v>3</v>
+      </c>
+      <c r="T305" t="n">
+        <v>5</v>
+      </c>
+      <c r="U305" t="n">
+        <v>4</v>
+      </c>
+      <c r="V305" t="n">
+        <v>4</v>
+      </c>
+      <c r="W305" t="n">
+        <v>9</v>
+      </c>
+      <c r="X305" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>489</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>456</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>431</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>381</v>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AP305" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AQ305" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU305" t="inlineStr"/>
+      <c r="AV305" t="inlineStr"/>
+      <c r="AW305" t="inlineStr"/>
+      <c r="AX305" t="inlineStr"/>
+      <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr"/>
+      <c r="BA305" t="inlineStr"/>
+      <c r="BB305" t="inlineStr"/>
+      <c r="BC305" t="inlineStr"/>
+      <c r="BD305" t="inlineStr"/>
+      <c r="BE305" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG305" t="inlineStr"/>
+      <c r="BH305" t="inlineStr"/>
+      <c r="BI305" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>5800</v>
+      </c>
+      <c r="BM305" t="n">
+        <v>3782500</v>
+      </c>
+      <c r="BN305" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BO305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP305" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ305" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="BR305" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BS305" t="n">
+        <v>4600</v>
+      </c>
+      <c r="BT305" t="n">
+        <v>1585000</v>
+      </c>
+      <c r="BU305" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BV305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW305" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="BX305" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="BY305" t="n">
+        <v>69.16</v>
+      </c>
+      <c r="BZ305" t="n">
+        <v>3080</v>
+      </c>
+      <c r="CA305" t="n">
+        <v>6362000</v>
+      </c>
+      <c r="CB305" t="n">
+        <v>75</v>
+      </c>
+      <c r="CC305" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CD305" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="CE305" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="CF305" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="CG305" t="inlineStr"/>
+      <c r="CH305" t="n">
+        <v>1370200</v>
+      </c>
+      <c r="CI305" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="CJ305" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK305" t="inlineStr"/>
+      <c r="CL305" t="inlineStr"/>
+      <c r="CM305" t="inlineStr"/>
+      <c r="CN305" t="inlineStr"/>
+      <c r="CO305" t="inlineStr"/>
+      <c r="CP305" t="inlineStr"/>
+      <c r="CQ305" t="inlineStr"/>
+      <c r="CR305" t="inlineStr"/>
+      <c r="CS305" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT305" t="n">
+        <v>186</v>
+      </c>
+      <c r="CU305" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV305" t="n">
+        <v>67</v>
+      </c>
+      <c r="CW305" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX305" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="CY305" t="n">
+        <v>74</v>
+      </c>
+      <c r="CZ305" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA305" t="inlineStr"/>
+      <c r="DB305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>zoo3iRJb</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="n">
+        <v>44</v>
+      </c>
+      <c r="N306" t="n">
+        <v>56</v>
+      </c>
+      <c r="O306" t="n">
+        <v>15</v>
+      </c>
+      <c r="P306" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>5</v>
+      </c>
+      <c r="R306" t="n">
+        <v>2</v>
+      </c>
+      <c r="S306" t="n">
+        <v>6</v>
+      </c>
+      <c r="T306" t="n">
+        <v>11</v>
+      </c>
+      <c r="U306" t="n">
+        <v>4</v>
+      </c>
+      <c r="V306" t="n">
+        <v>4</v>
+      </c>
+      <c r="W306" t="n">
+        <v>16</v>
+      </c>
+      <c r="X306" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>334</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>424</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>267</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>355</v>
+      </c>
+      <c r="AO306" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AP306" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AQ306" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU306" t="inlineStr"/>
+      <c r="AV306" t="inlineStr"/>
+      <c r="AW306" t="inlineStr"/>
+      <c r="AX306" t="inlineStr"/>
+      <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr"/>
+      <c r="BA306" t="inlineStr"/>
+      <c r="BB306" t="inlineStr"/>
+      <c r="BC306" t="inlineStr"/>
+      <c r="BD306" t="inlineStr"/>
+      <c r="BE306" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG306" t="inlineStr"/>
+      <c r="BH306" t="inlineStr"/>
+      <c r="BI306" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>3700</v>
+      </c>
+      <c r="BM306" t="n">
+        <v>1362500</v>
+      </c>
+      <c r="BN306" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BO306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP306" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="BQ306" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="BR306" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="BS306" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="BT306" t="n">
+        <v>1141666.666666667</v>
+      </c>
+      <c r="BU306" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="BV306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW306" t="n">
+        <v>23.70588235294118</v>
+      </c>
+      <c r="BX306" t="n">
+        <v>181.1176470588235</v>
+      </c>
+      <c r="BY306" t="n">
+        <v>66.64705882352941</v>
+      </c>
+      <c r="BZ306" t="n">
+        <v>3352.941176470588</v>
+      </c>
+      <c r="CA306" t="n">
+        <v>1539705.882352941</v>
+      </c>
+      <c r="CB306" t="n">
+        <v>71.88235294117646</v>
+      </c>
+      <c r="CC306" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD306" t="n">
+        <v>24.68181818181818</v>
+      </c>
+      <c r="CE306" t="n">
+        <v>181.0454545454545</v>
+      </c>
+      <c r="CF306" t="n">
+        <v>63.40909090909091</v>
+      </c>
+      <c r="CG306" t="n">
+        <v>3318.181818181818</v>
+      </c>
+      <c r="CH306" t="n">
+        <v>838636.3636363636</v>
+      </c>
+      <c r="CI306" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="CJ306" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK306" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL306" t="n">
+        <v>172</v>
+      </c>
+      <c r="CM306" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN306" t="n">
+        <v>66</v>
+      </c>
+      <c r="CO306" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CP306" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="CQ306" t="n">
+        <v>70</v>
+      </c>
+      <c r="CR306" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS306" t="inlineStr"/>
+      <c r="CT306" t="inlineStr"/>
+      <c r="CU306" t="inlineStr"/>
+      <c r="CV306" t="inlineStr"/>
+      <c r="CW306" t="inlineStr"/>
+      <c r="CX306" t="inlineStr"/>
+      <c r="CY306" t="inlineStr"/>
+      <c r="CZ306" t="inlineStr"/>
+      <c r="DA306" t="inlineStr"/>
+      <c r="DB306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>rBlBk5lB</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="n">
+        <v>47</v>
+      </c>
+      <c r="N307" t="n">
+        <v>53</v>
+      </c>
+      <c r="O307" t="n">
+        <v>13</v>
+      </c>
+      <c r="P307" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>5</v>
+      </c>
+      <c r="R307" t="n">
+        <v>3</v>
+      </c>
+      <c r="S307" t="n">
+        <v>6</v>
+      </c>
+      <c r="T307" t="n">
+        <v>5</v>
+      </c>
+      <c r="U307" t="n">
+        <v>2</v>
+      </c>
+      <c r="V307" t="n">
+        <v>2</v>
+      </c>
+      <c r="W307" t="n">
+        <v>20</v>
+      </c>
+      <c r="X307" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>249</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>283</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>166</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>197</v>
+      </c>
+      <c r="AO307" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AP307" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AQ307" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU307" t="inlineStr"/>
+      <c r="AV307" t="inlineStr"/>
+      <c r="AW307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr"/>
+      <c r="BA307" t="inlineStr"/>
+      <c r="BB307" t="inlineStr"/>
+      <c r="BC307" t="inlineStr"/>
+      <c r="BD307" t="inlineStr"/>
+      <c r="BE307" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG307" t="inlineStr"/>
+      <c r="BH307" t="inlineStr"/>
+      <c r="BI307" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>3900</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BO307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP307" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="BQ307" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="BR307" t="n">
+        <v>63.88888888888889</v>
+      </c>
+      <c r="BS307" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BT307" t="n">
+        <v>919444.4444444445</v>
+      </c>
+      <c r="BU307" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="BV307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW307" t="n">
+        <v>24.65217391304348</v>
+      </c>
+      <c r="BX307" t="n">
+        <v>180.7391304347826</v>
+      </c>
+      <c r="BY307" t="n">
+        <v>65.17391304347827</v>
+      </c>
+      <c r="BZ307" t="inlineStr"/>
+      <c r="CA307" t="n">
+        <v>1216956.52173913</v>
+      </c>
+      <c r="CB307" t="n">
+        <v>70.17391304347827</v>
+      </c>
+      <c r="CC307" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD307" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="CE307" t="n">
+        <v>181.65</v>
+      </c>
+      <c r="CF307" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="CG307" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CH307" t="n">
+        <v>718750</v>
+      </c>
+      <c r="CI307" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="CJ307" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK307" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="CL307" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="CM307" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN307" t="n">
+        <v>194</v>
+      </c>
+      <c r="CO307" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CP307" t="n">
+        <v>2875000</v>
+      </c>
+      <c r="CQ307" t="n">
+        <v>215</v>
+      </c>
+      <c r="CR307" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS307" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT307" t="n">
+        <v>179</v>
+      </c>
+      <c r="CU307" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV307" t="n">
+        <v>130</v>
+      </c>
+      <c r="CW307" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CX307" t="n">
+        <v>2025000</v>
+      </c>
+      <c r="CY307" t="n">
+        <v>140</v>
+      </c>
+      <c r="CZ307" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA307" t="inlineStr"/>
+      <c r="DB307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>4QxKmqJN</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="n">
+        <v>2</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="n">
+        <v>43</v>
+      </c>
+      <c r="N308" t="n">
+        <v>57</v>
+      </c>
+      <c r="O308" t="n">
+        <v>9</v>
+      </c>
+      <c r="P308" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>3</v>
+      </c>
+      <c r="R308" t="n">
+        <v>3</v>
+      </c>
+      <c r="S308" t="n">
+        <v>3</v>
+      </c>
+      <c r="T308" t="n">
+        <v>1</v>
+      </c>
+      <c r="U308" t="n">
+        <v>3</v>
+      </c>
+      <c r="V308" t="n">
+        <v>2</v>
+      </c>
+      <c r="W308" t="n">
+        <v>15</v>
+      </c>
+      <c r="X308" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>428</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>568</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>356</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>475</v>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>AgMBZSTl</t>
+        </is>
+      </c>
+      <c r="AP308" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AQ308" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU308" t="inlineStr"/>
+      <c r="AV308" t="inlineStr"/>
+      <c r="AW308" t="inlineStr"/>
+      <c r="AX308" t="inlineStr"/>
+      <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr"/>
+      <c r="BA308" t="inlineStr"/>
+      <c r="BB308" t="inlineStr"/>
+      <c r="BC308" t="inlineStr"/>
+      <c r="BD308" t="inlineStr"/>
+      <c r="BE308" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG308" t="inlineStr"/>
+      <c r="BH308" t="inlineStr"/>
+      <c r="BI308" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="BK308" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BL308" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BM308" t="n">
+        <v>2290000</v>
+      </c>
+      <c r="BN308" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="BO308" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP308" t="n">
+        <v>29.22222222222222</v>
+      </c>
+      <c r="BQ308" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BR308" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="BS308" t="n">
+        <v>5777.777777777777</v>
+      </c>
+      <c r="BT308" t="n">
+        <v>1121666.666666667</v>
+      </c>
+      <c r="BU308" t="n">
+        <v>70</v>
+      </c>
+      <c r="BV308" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BW308" t="n">
+        <v>26.14814814814815</v>
+      </c>
+      <c r="BX308" t="n">
+        <v>182.7037037037037</v>
+      </c>
+      <c r="BY308" t="n">
+        <v>67.70370370370371</v>
+      </c>
+      <c r="BZ308" t="n">
+        <v>5074.074074074074</v>
+      </c>
+      <c r="CA308" t="n">
+        <v>1500925.925925926</v>
+      </c>
+      <c r="CB308" t="n">
+        <v>72.51851851851852</v>
+      </c>
+      <c r="CC308" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD308" t="n">
+        <v>25.95238095238095</v>
+      </c>
+      <c r="CE308" t="n">
+        <v>180.4761904761905</v>
+      </c>
+      <c r="CF308" t="n">
+        <v>67.76190476190476</v>
+      </c>
+      <c r="CG308" t="n">
+        <v>6952.380952380952</v>
+      </c>
+      <c r="CH308" t="n">
+        <v>1859523.809523809</v>
+      </c>
+      <c r="CI308" t="n">
+        <v>71.52380952380952</v>
+      </c>
+      <c r="CJ308" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="CK308" t="inlineStr"/>
+      <c r="CL308" t="inlineStr"/>
+      <c r="CM308" t="inlineStr"/>
+      <c r="CN308" t="inlineStr"/>
+      <c r="CO308" t="inlineStr"/>
+      <c r="CP308" t="inlineStr"/>
+      <c r="CQ308" t="inlineStr"/>
+      <c r="CR308" t="inlineStr"/>
+      <c r="CS308" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT308" t="n">
+        <v>185</v>
+      </c>
+      <c r="CU308" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV308" t="n">
+        <v>73</v>
+      </c>
+      <c r="CW308" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX308" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CY308" t="n">
+        <v>73</v>
+      </c>
+      <c r="CZ308" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA308" t="inlineStr"/>
+      <c r="DB308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>zaQy6QYi</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renzo barbera
+  palermo </t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>36349</v>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="n">
+        <v>52</v>
+      </c>
+      <c r="N309" t="n">
+        <v>48</v>
+      </c>
+      <c r="O309" t="n">
+        <v>19</v>
+      </c>
+      <c r="P309" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>4</v>
+      </c>
+      <c r="R309" t="n">
+        <v>3</v>
+      </c>
+      <c r="S309" t="n">
+        <v>8</v>
+      </c>
+      <c r="T309" t="n">
+        <v>2</v>
+      </c>
+      <c r="U309" t="n">
+        <v>7</v>
+      </c>
+      <c r="V309" t="n">
+        <v>1</v>
+      </c>
+      <c r="W309" t="n">
+        <v>20</v>
+      </c>
+      <c r="X309" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>426</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>397</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>363</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>317</v>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AP309" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AQ309" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT309" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU309" t="inlineStr"/>
+      <c r="AV309" t="inlineStr"/>
+      <c r="AW309" t="inlineStr"/>
+      <c r="AX309" t="inlineStr"/>
+      <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr"/>
+      <c r="BA309" t="inlineStr"/>
+      <c r="BB309" t="inlineStr"/>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF309" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
+      <c r="BI309" t="n">
+        <v>27.11111111111111</v>
+      </c>
+      <c r="BJ309" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="BK309" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="BL309" t="n">
+        <v>5444.444444444444</v>
+      </c>
+      <c r="BM309" t="n">
+        <v>2622222.222222222</v>
+      </c>
+      <c r="BN309" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BO309" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP309" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ309" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="BR309" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="BS309" t="n">
+        <v>14700</v>
+      </c>
+      <c r="BT309" t="n">
+        <v>2247500</v>
+      </c>
+      <c r="BU309" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BV309" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW309" t="n">
+        <v>24.86363636363636</v>
+      </c>
+      <c r="BX309" t="n">
+        <v>185.6818181818182</v>
+      </c>
+      <c r="BY309" t="n">
+        <v>69.22727272727273</v>
+      </c>
+      <c r="BZ309" t="n">
+        <v>4136.363636363636</v>
+      </c>
+      <c r="CA309" t="n">
+        <v>2344318.181818182</v>
+      </c>
+      <c r="CB309" t="n">
+        <v>75.40909090909091</v>
+      </c>
+      <c r="CC309" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD309" t="n">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="CE309" t="n">
+        <v>182.304347826087</v>
+      </c>
+      <c r="CF309" t="n">
+        <v>65.43478260869566</v>
+      </c>
+      <c r="CG309" t="inlineStr"/>
+      <c r="CH309" t="n">
+        <v>1495217.391304348</v>
+      </c>
+      <c r="CI309" t="n">
+        <v>70.30434782608695</v>
+      </c>
+      <c r="CJ309" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK309" t="n">
+        <v>28</v>
+      </c>
+      <c r="CL309" t="n">
+        <v>186</v>
+      </c>
+      <c r="CM309" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN309" t="n">
+        <v>210</v>
+      </c>
+      <c r="CO309" t="n">
+        <v>12000</v>
+      </c>
+      <c r="CP309" t="n">
+        <v>4725000</v>
+      </c>
+      <c r="CQ309" t="n">
+        <v>211</v>
+      </c>
+      <c r="CR309" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS309" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT309" t="n">
+        <v>189</v>
+      </c>
+      <c r="CU309" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV309" t="n">
+        <v>65</v>
+      </c>
+      <c r="CW309" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CX309" t="n">
+        <v>500000</v>
+      </c>
+      <c r="CY309" t="n">
+        <v>65</v>
+      </c>
+      <c r="CZ309" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA309" t="inlineStr"/>
+      <c r="DB309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>AwpQqzIk</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>45590.64583333334</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F310" t="n">
+        <v>7460</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="n">
+        <v>59</v>
+      </c>
+      <c r="N310" t="n">
+        <v>41</v>
+      </c>
+      <c r="O310" t="n">
+        <v>16</v>
+      </c>
+      <c r="P310" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>5</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>7</v>
+      </c>
+      <c r="T310" t="n">
+        <v>4</v>
+      </c>
+      <c r="U310" t="n">
+        <v>4</v>
+      </c>
+      <c r="V310" t="n">
+        <v>0</v>
+      </c>
+      <c r="W310" t="n">
+        <v>24</v>
+      </c>
+      <c r="X310" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>430</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>306</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>353</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>219</v>
+      </c>
+      <c r="AO310" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AP310" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AQ310" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU310" t="inlineStr"/>
+      <c r="AV310" t="inlineStr"/>
+      <c r="AW310" t="inlineStr"/>
+      <c r="AX310" t="inlineStr"/>
+      <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr"/>
+      <c r="BA310" t="inlineStr"/>
+      <c r="BB310" t="inlineStr"/>
+      <c r="BC310" t="inlineStr"/>
+      <c r="BD310" t="inlineStr"/>
+      <c r="BE310" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF310" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG310" t="inlineStr"/>
+      <c r="BH310" t="inlineStr"/>
+      <c r="BI310" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ310" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="BK310" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="BL310" t="n">
+        <v>6800</v>
+      </c>
+      <c r="BM310" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="BN310" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BO310" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP310" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ310" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BR310" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="BS310" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BT310" t="n">
+        <v>1307500</v>
+      </c>
+      <c r="BU310" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BV310" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW310" t="n">
+        <v>25.04347826086957</v>
+      </c>
+      <c r="BX310" t="n">
+        <v>184.2173913043478</v>
+      </c>
+      <c r="BY310" t="n">
+        <v>64.56521739130434</v>
+      </c>
+      <c r="BZ310" t="inlineStr"/>
+      <c r="CA310" t="n">
+        <v>1197826.086956522</v>
+      </c>
+      <c r="CB310" t="n">
+        <v>70.08695652173913</v>
+      </c>
+      <c r="CC310" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD310" t="n">
+        <v>27.30434782608696</v>
+      </c>
+      <c r="CE310" t="n">
+        <v>183.2173913043478</v>
+      </c>
+      <c r="CF310" t="n">
+        <v>66.47826086956522</v>
+      </c>
+      <c r="CG310" t="n">
+        <v>9391.304347826086</v>
+      </c>
+      <c r="CH310" t="n">
+        <v>1072826.086956522</v>
+      </c>
+      <c r="CI310" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="CJ310" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK310" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL310" t="n">
+        <v>190</v>
+      </c>
+      <c r="CM310" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN310" t="n">
+        <v>65</v>
+      </c>
+      <c r="CO310" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CP310" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CQ310" t="n">
+        <v>69</v>
+      </c>
+      <c r="CR310" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS310" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT310" t="n">
+        <v>186</v>
+      </c>
+      <c r="CU310" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV310" t="n">
+        <v>60</v>
+      </c>
+      <c r="CW310" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX310" t="n">
+        <v>300000</v>
+      </c>
+      <c r="CY310" t="n">
+        <v>64</v>
+      </c>
+      <c r="CZ310" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA310" t="inlineStr"/>
+      <c r="DB310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F311" t="n">
+        <v>20440</v>
+      </c>
+      <c r="G311" t="n">
+        <v>5</v>
+      </c>
+      <c r="H311" t="n">
+        <v>1</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K311" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M311" t="n">
+        <v>38</v>
+      </c>
+      <c r="N311" t="n">
+        <v>62</v>
+      </c>
+      <c r="O311" t="n">
+        <v>21</v>
+      </c>
+      <c r="P311" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>10</v>
+      </c>
+      <c r="R311" t="n">
+        <v>5</v>
+      </c>
+      <c r="S311" t="n">
+        <v>8</v>
+      </c>
+      <c r="T311" t="n">
+        <v>1</v>
+      </c>
+      <c r="U311" t="n">
+        <v>3</v>
+      </c>
+      <c r="V311" t="n">
+        <v>8</v>
+      </c>
+      <c r="W311" t="n">
+        <v>11</v>
+      </c>
+      <c r="X311" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>343</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>547</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>304</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>503</v>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AQ311" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr"/>
+      <c r="BA311" t="inlineStr"/>
+      <c r="BB311" t="inlineStr"/>
+      <c r="BC311" t="inlineStr"/>
+      <c r="BD311" t="inlineStr"/>
+      <c r="BE311" t="inlineStr"/>
+      <c r="BF311" t="inlineStr"/>
+      <c r="BG311" t="inlineStr"/>
+      <c r="BH311" t="inlineStr"/>
+      <c r="BI311" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BJ311" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="BK311" t="n">
+        <v>75.22222222222223</v>
+      </c>
+      <c r="BL311" t="n">
+        <v>39333.33333333334</v>
+      </c>
+      <c r="BM311" t="n">
+        <v>12733333.33333333</v>
+      </c>
+      <c r="BN311" t="n">
+        <v>81</v>
+      </c>
+      <c r="BO311" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="BP311" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BQ311" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="BR311" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="BS311" t="n">
+        <v>40500</v>
+      </c>
+      <c r="BT311" t="n">
+        <v>23975000</v>
+      </c>
+      <c r="BU311" t="n">
+        <v>81</v>
+      </c>
+      <c r="BV311" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BW311" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BX311" t="n">
+        <v>181.8181818181818</v>
+      </c>
+      <c r="BY311" t="n">
+        <v>75.72727272727273</v>
+      </c>
+      <c r="BZ311" t="n">
+        <v>42272.72727272727</v>
+      </c>
+      <c r="CA311" t="n">
+        <v>10771590.90909091</v>
+      </c>
+      <c r="CB311" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="CC311" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="CD311" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="CE311" t="n">
+        <v>177.4166666666667</v>
+      </c>
+      <c r="CF311" t="n">
+        <v>78</v>
+      </c>
+      <c r="CG311" t="n">
+        <v>36416.66666666666</v>
+      </c>
+      <c r="CH311" t="n">
+        <v>22191666.66666667</v>
+      </c>
+      <c r="CI311" t="n">
+        <v>81.58333333333333</v>
+      </c>
+      <c r="CJ311" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="CK311" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="CL311" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="CM311" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN311" t="n">
+        <v>232</v>
+      </c>
+      <c r="CO311" t="n">
+        <v>142000</v>
+      </c>
+      <c r="CP311" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="CQ311" t="n">
+        <v>238</v>
+      </c>
+      <c r="CR311" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS311" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT311" t="n">
+        <v>179</v>
+      </c>
+      <c r="CU311" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV311" t="n">
+        <v>157</v>
+      </c>
+      <c r="CW311" t="n">
+        <v>142000</v>
+      </c>
+      <c r="CX311" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="CY311" t="n">
+        <v>159</v>
+      </c>
+      <c r="CZ311" t="n">
+        <v>4</v>
+      </c>
+      <c r="DA311" t="n">
+        <v>4</v>
+      </c>
+      <c r="DB311" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F312" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G312" t="n">
+        <v>4</v>
+      </c>
+      <c r="H312" t="n">
+        <v>4</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L312" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M312" t="n">
+        <v>47</v>
+      </c>
+      <c r="N312" t="n">
+        <v>53</v>
+      </c>
+      <c r="O312" t="n">
+        <v>18</v>
+      </c>
+      <c r="P312" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>9</v>
+      </c>
+      <c r="R312" t="n">
+        <v>5</v>
+      </c>
+      <c r="S312" t="n">
+        <v>4</v>
+      </c>
+      <c r="T312" t="n">
+        <v>3</v>
+      </c>
+      <c r="U312" t="n">
+        <v>5</v>
+      </c>
+      <c r="V312" t="n">
+        <v>2</v>
+      </c>
+      <c r="W312" t="n">
+        <v>16</v>
+      </c>
+      <c r="X312" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>383</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>445</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>327</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>392</v>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AQ312" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT312" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW312" t="inlineStr"/>
+      <c r="AX312" t="inlineStr"/>
+      <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr"/>
+      <c r="BA312" t="inlineStr"/>
+      <c r="BB312" t="inlineStr"/>
+      <c r="BC312" t="inlineStr"/>
+      <c r="BD312" t="inlineStr"/>
+      <c r="BE312" t="inlineStr"/>
+      <c r="BF312" t="inlineStr"/>
+      <c r="BG312" t="inlineStr"/>
+      <c r="BH312" t="inlineStr"/>
+      <c r="BI312" t="n">
+        <v>28.90909090909091</v>
+      </c>
+      <c r="BJ312" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="BK312" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="BL312" t="n">
+        <v>118363.6363636364</v>
+      </c>
+      <c r="BM312" t="n">
+        <v>46545454.54545455</v>
+      </c>
+      <c r="BN312" t="n">
+        <v>84.90909090909091</v>
+      </c>
+      <c r="BO312" t="n">
+        <v>3.454545454545455</v>
+      </c>
+      <c r="BP312" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="BQ312" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BR312" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="BS312" t="n">
+        <v>83250</v>
+      </c>
+      <c r="BT312" t="n">
+        <v>23687500</v>
+      </c>
+      <c r="BU312" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="BV312" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BW312" t="n">
+        <v>27.36842105263158</v>
+      </c>
+      <c r="BX312" t="n">
+        <v>185.4736842105263</v>
+      </c>
+      <c r="BY312" t="n">
+        <v>78.78947368421052</v>
+      </c>
+      <c r="BZ312" t="n">
+        <v>77210.52631578948</v>
+      </c>
+      <c r="CA312" t="n">
+        <v>20542105.26315789</v>
+      </c>
+      <c r="CB312" t="n">
+        <v>81.47368421052632</v>
+      </c>
+      <c r="CC312" t="n">
+        <v>2.157894736842105</v>
+      </c>
+      <c r="CD312" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="CE312" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="CF312" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="CG312" t="n">
+        <v>83888.88888888889</v>
+      </c>
+      <c r="CH312" t="n">
+        <v>17822222.22222222</v>
+      </c>
+      <c r="CI312" t="n">
+        <v>80.88888888888889</v>
+      </c>
+      <c r="CJ312" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="CK312" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="CL312" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="CM312" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN312" t="n">
+        <v>249</v>
+      </c>
+      <c r="CO312" t="n">
+        <v>313000</v>
+      </c>
+      <c r="CP312" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="CQ312" t="n">
+        <v>252</v>
+      </c>
+      <c r="CR312" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS312" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CT312" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="CU312" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV312" t="n">
+        <v>412</v>
+      </c>
+      <c r="CW312" t="n">
+        <v>630000</v>
+      </c>
+      <c r="CX312" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="CY312" t="n">
+        <v>417</v>
+      </c>
+      <c r="CZ312" t="n">
+        <v>16</v>
+      </c>
+      <c r="DA312" t="n">
+        <v>5</v>
+      </c>
+      <c r="DB312" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F313" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M313" t="n">
+        <v>61</v>
+      </c>
+      <c r="N313" t="n">
+        <v>39</v>
+      </c>
+      <c r="O313" t="n">
+        <v>18</v>
+      </c>
+      <c r="P313" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>4</v>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="n">
+        <v>10</v>
+      </c>
+      <c r="T313" t="n">
+        <v>4</v>
+      </c>
+      <c r="U313" t="n">
+        <v>4</v>
+      </c>
+      <c r="V313" t="n">
+        <v>0</v>
+      </c>
+      <c r="W313" t="n">
+        <v>6</v>
+      </c>
+      <c r="X313" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>550</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>352</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>486</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>276</v>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AQ313" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT313" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU313" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW313" t="inlineStr"/>
+      <c r="AX313" t="inlineStr"/>
+      <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr"/>
+      <c r="BA313" t="inlineStr"/>
+      <c r="BB313" t="inlineStr"/>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr"/>
+      <c r="BE313" t="inlineStr"/>
+      <c r="BF313" t="inlineStr"/>
+      <c r="BG313" t="inlineStr"/>
+      <c r="BH313" t="inlineStr"/>
+      <c r="BI313" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BJ313" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BK313" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BL313" t="n">
+        <v>43500</v>
+      </c>
+      <c r="BM313" t="n">
+        <v>18800000</v>
+      </c>
+      <c r="BN313" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO313" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BP313" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="BQ313" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="BR313" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="BS313" t="n">
+        <v>30818.18181818182</v>
+      </c>
+      <c r="BT313" t="n">
+        <v>3822727.272727273</v>
+      </c>
+      <c r="BU313" t="n">
+        <v>75.63636363636364</v>
+      </c>
+      <c r="BV313" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW313" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="BX313" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BY313" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="BZ313" t="n">
+        <v>34700</v>
+      </c>
+      <c r="CA313" t="n">
+        <v>9306250</v>
+      </c>
+      <c r="CB313" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="CC313" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CD313" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="CE313" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="CF313" t="n">
+        <v>66</v>
+      </c>
+      <c r="CG313" t="n">
+        <v>26850</v>
+      </c>
+      <c r="CH313" t="n">
+        <v>1436250</v>
+      </c>
+      <c r="CI313" t="n">
+        <v>71</v>
+      </c>
+      <c r="CJ313" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CK313" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="CL313" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CM313" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN313" t="n">
+        <v>162</v>
+      </c>
+      <c r="CO313" t="n">
+        <v>117000</v>
+      </c>
+      <c r="CP313" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="CQ313" t="n">
+        <v>162</v>
+      </c>
+      <c r="CR313" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS313" t="n">
+        <v>28.42857142857143</v>
+      </c>
+      <c r="CT313" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="CU313" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV313" t="n">
+        <v>516</v>
+      </c>
+      <c r="CW313" t="n">
+        <v>255000</v>
+      </c>
+      <c r="CX313" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="CY313" t="n">
+        <v>534</v>
+      </c>
+      <c r="CZ313" t="n">
+        <v>10</v>
+      </c>
+      <c r="DA313" t="n">
+        <v>7</v>
+      </c>
+      <c r="DB313" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F314" t="n">
+        <v>10141</v>
+      </c>
+      <c r="G314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" t="n">
+        <v>2</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M314" t="n">
+        <v>46</v>
+      </c>
+      <c r="N314" t="n">
+        <v>54</v>
+      </c>
+      <c r="O314" t="n">
+        <v>13</v>
+      </c>
+      <c r="P314" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>2</v>
+      </c>
+      <c r="R314" t="n">
+        <v>2</v>
+      </c>
+      <c r="S314" t="n">
+        <v>8</v>
+      </c>
+      <c r="T314" t="n">
+        <v>2</v>
+      </c>
+      <c r="U314" t="n">
+        <v>3</v>
+      </c>
+      <c r="V314" t="n">
+        <v>2</v>
+      </c>
+      <c r="W314" t="n">
+        <v>16</v>
+      </c>
+      <c r="X314" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>347</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>416</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>273</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>338</v>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AQ314" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU314" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr"/>
+      <c r="BA314" t="inlineStr"/>
+      <c r="BB314" t="inlineStr"/>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr"/>
+      <c r="BE314" t="inlineStr"/>
+      <c r="BF314" t="inlineStr"/>
+      <c r="BG314" t="inlineStr"/>
+      <c r="BH314" t="inlineStr"/>
+      <c r="BI314" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BJ314" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BK314" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BL314" t="n">
+        <v>22500</v>
+      </c>
+      <c r="BM314" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="BN314" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="BO314" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP314" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="BQ314" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="BR314" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="BS314" t="n">
+        <v>11818.18181818182</v>
+      </c>
+      <c r="BT314" t="n">
+        <v>3054545.454545455</v>
+      </c>
+      <c r="BU314" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="BV314" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BW314" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="BX314" t="n">
+        <v>182.6818181818182</v>
+      </c>
+      <c r="BY314" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="BZ314" t="n">
+        <v>36363.63636363636</v>
+      </c>
+      <c r="CA314" t="n">
+        <v>6665909.090909091</v>
+      </c>
+      <c r="CB314" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="CC314" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="CD314" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="CE314" t="n">
+        <v>184.5909090909091</v>
+      </c>
+      <c r="CF314" t="n">
+        <v>69.31818181818181</v>
+      </c>
+      <c r="CG314" t="n">
+        <v>13545.45454545455</v>
+      </c>
+      <c r="CH314" t="n">
+        <v>2384318.181818182</v>
+      </c>
+      <c r="CI314" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="CJ314" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="CK314" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="CL314" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="CM314" t="n">
+        <v>5</v>
+      </c>
+      <c r="CN314" t="n">
+        <v>373</v>
+      </c>
+      <c r="CO314" t="n">
+        <v>120000</v>
+      </c>
+      <c r="CP314" t="n">
+        <v>29300000</v>
+      </c>
+      <c r="CQ314" t="n">
+        <v>378</v>
+      </c>
+      <c r="CR314" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS314" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT314" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CU314" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV314" t="n">
+        <v>132</v>
+      </c>
+      <c r="CW314" t="n">
+        <v>17000</v>
+      </c>
+      <c r="CX314" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="CY314" t="n">
+        <v>143</v>
+      </c>
+      <c r="CZ314" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA314" t="n">
+        <v>11</v>
+      </c>
+      <c r="DB314" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>45592.35416666666</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F315" t="n">
+        <v>17802</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M315" t="n">
+        <v>60</v>
+      </c>
+      <c r="N315" t="n">
+        <v>40</v>
+      </c>
+      <c r="O315" t="n">
+        <v>17</v>
+      </c>
+      <c r="P315" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>4</v>
+      </c>
+      <c r="R315" t="n">
+        <v>2</v>
+      </c>
+      <c r="S315" t="n">
+        <v>8</v>
+      </c>
+      <c r="T315" t="n">
+        <v>4</v>
+      </c>
+      <c r="U315" t="n">
+        <v>5</v>
+      </c>
+      <c r="V315" t="n">
+        <v>0</v>
+      </c>
+      <c r="W315" t="n">
+        <v>17</v>
+      </c>
+      <c r="X315" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>527</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>350</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>456</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>279</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AQ315" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR315" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT315" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW315" t="inlineStr"/>
+      <c r="AX315" t="inlineStr"/>
+      <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr"/>
+      <c r="BA315" t="inlineStr"/>
+      <c r="BB315" t="inlineStr"/>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr"/>
+      <c r="BE315" t="inlineStr"/>
+      <c r="BF315" t="inlineStr"/>
+      <c r="BG315" t="inlineStr"/>
+      <c r="BH315" t="inlineStr"/>
+      <c r="BI315" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BJ315" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="BK315" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="BL315" t="n">
+        <v>26700</v>
+      </c>
+      <c r="BM315" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="BN315" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="BO315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP315" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BQ315" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="BR315" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="BS315" t="n">
+        <v>21000</v>
+      </c>
+      <c r="BT315" t="n">
+        <v>2872500</v>
+      </c>
+      <c r="BU315" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="BV315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW315" t="n">
+        <v>24.04347826086957</v>
+      </c>
+      <c r="BX315" t="n">
+        <v>183.1304347826087</v>
+      </c>
+      <c r="BY315" t="n">
+        <v>69.04347826086956</v>
+      </c>
+      <c r="BZ315" t="n">
+        <v>22565.21739130435</v>
+      </c>
+      <c r="CA315" t="n">
+        <v>3069565.217391304</v>
+      </c>
+      <c r="CB315" t="n">
+        <v>74.60869565217391</v>
+      </c>
+      <c r="CC315" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD315" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="CE315" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="CF315" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="CG315" t="n">
+        <v>17458.33333333333</v>
+      </c>
+      <c r="CH315" t="n">
+        <v>2272916.666666667</v>
+      </c>
+      <c r="CI315" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="CJ315" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="CK315" t="n">
+        <v>25</v>
+      </c>
+      <c r="CL315" t="n">
+        <v>188</v>
+      </c>
+      <c r="CM315" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN315" t="n">
+        <v>145</v>
+      </c>
+      <c r="CO315" t="n">
+        <v>48000</v>
+      </c>
+      <c r="CP315" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="CQ315" t="n">
+        <v>154</v>
+      </c>
+      <c r="CR315" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS315" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="CT315" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="CU315" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV315" t="n">
+        <v>361</v>
+      </c>
+      <c r="CW315" t="n">
+        <v>95000</v>
+      </c>
+      <c r="CX315" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="CY315" t="n">
+        <v>380</v>
+      </c>
+      <c r="CZ315" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA315" t="n">
+        <v>7</v>
+      </c>
+      <c r="DB315" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>GrV1gmkn</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">santoro a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="n">
+        <v>54</v>
+      </c>
+      <c r="N316" t="n">
+        <v>46</v>
+      </c>
+      <c r="O316" t="n">
+        <v>10</v>
+      </c>
+      <c r="P316" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>6</v>
+      </c>
+      <c r="R316" t="n">
+        <v>1</v>
+      </c>
+      <c r="S316" t="n">
+        <v>2</v>
+      </c>
+      <c r="T316" t="n">
+        <v>8</v>
+      </c>
+      <c r="U316" t="n">
+        <v>2</v>
+      </c>
+      <c r="V316" t="n">
+        <v>2</v>
+      </c>
+      <c r="W316" t="n">
+        <v>13</v>
+      </c>
+      <c r="X316" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>497</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>383</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>442</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>343</v>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AQ316" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR316" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT316" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU316" t="inlineStr"/>
+      <c r="AV316" t="inlineStr"/>
+      <c r="AW316" t="inlineStr"/>
+      <c r="AX316" t="inlineStr"/>
+      <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr"/>
+      <c r="BA316" t="inlineStr"/>
+      <c r="BB316" t="inlineStr"/>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr"/>
+      <c r="BE316" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF316" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG316" t="inlineStr"/>
+      <c r="BH316" t="inlineStr"/>
+      <c r="BI316" t="n">
+        <v>29.72727272727273</v>
+      </c>
+      <c r="BJ316" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="BK316" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="BL316" t="n">
+        <v>2545.454545454545</v>
+      </c>
+      <c r="BM316" t="n">
+        <v>972727.2727272727</v>
+      </c>
+      <c r="BN316" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="BO316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP316" t="n">
+        <v>27.36363636363636</v>
+      </c>
+      <c r="BQ316" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="BR316" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="BS316" t="n">
+        <v>3181.818181818182</v>
+      </c>
+      <c r="BT316" t="n">
+        <v>1252272.727272727</v>
+      </c>
+      <c r="BU316" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="BV316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW316" t="n">
+        <v>25.56521739130435</v>
+      </c>
+      <c r="BX316" t="n">
+        <v>182.3478260869565</v>
+      </c>
+      <c r="BY316" t="n">
+        <v>65.82608695652173</v>
+      </c>
+      <c r="BZ316" t="n">
+        <v>6391.304347826087</v>
+      </c>
+      <c r="CA316" t="n">
+        <v>1170652.173913043</v>
+      </c>
+      <c r="CB316" t="n">
+        <v>70.78260869565217</v>
+      </c>
+      <c r="CC316" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD316" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="CE316" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="CF316" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="CG316" t="inlineStr"/>
+      <c r="CH316" t="n">
+        <v>1212250</v>
+      </c>
+      <c r="CI316" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="CJ316" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK316" t="inlineStr"/>
+      <c r="CL316" t="inlineStr"/>
+      <c r="CM316" t="inlineStr"/>
+      <c r="CN316" t="inlineStr"/>
+      <c r="CO316" t="inlineStr"/>
+      <c r="CP316" t="inlineStr"/>
+      <c r="CQ316" t="inlineStr"/>
+      <c r="CR316" t="inlineStr"/>
+      <c r="CS316" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="CT316" t="n">
+        <v>182</v>
+      </c>
+      <c r="CU316" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV316" t="n">
+        <v>270</v>
+      </c>
+      <c r="CW316" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CX316" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="CY316" t="n">
+        <v>277</v>
+      </c>
+      <c r="CZ316" t="n">
+        <v>4</v>
+      </c>
+      <c r="DA316" t="inlineStr"/>
+      <c r="DB316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>z9TkrNto</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="n">
+        <v>31</v>
+      </c>
+      <c r="N317" t="n">
+        <v>69</v>
+      </c>
+      <c r="O317" t="n">
+        <v>11</v>
+      </c>
+      <c r="P317" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>3</v>
+      </c>
+      <c r="R317" t="n">
+        <v>4</v>
+      </c>
+      <c r="S317" t="n">
+        <v>6</v>
+      </c>
+      <c r="T317" t="n">
+        <v>11</v>
+      </c>
+      <c r="U317" t="n">
+        <v>2</v>
+      </c>
+      <c r="V317" t="n">
+        <v>5</v>
+      </c>
+      <c r="W317" t="n">
+        <v>19</v>
+      </c>
+      <c r="X317" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>227</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>485</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>142</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>423</v>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AQ317" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT317" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU317" t="inlineStr"/>
+      <c r="AV317" t="inlineStr"/>
+      <c r="AW317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr"/>
+      <c r="BA317" t="inlineStr"/>
+      <c r="BB317" t="inlineStr"/>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr"/>
+      <c r="BE317" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF317" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
+      <c r="BI317" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BJ317" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BK317" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BL317" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BM317" t="n">
+        <v>1191500</v>
+      </c>
+      <c r="BN317" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BO317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP317" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="BQ317" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="BR317" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BS317" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="BT317" t="n">
+        <v>1297222.222222222</v>
+      </c>
+      <c r="BU317" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="BV317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW317" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX317" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BY317" t="n">
+        <v>65.61111111111111</v>
+      </c>
+      <c r="BZ317" t="n">
+        <v>7833.333333333333</v>
+      </c>
+      <c r="CA317" t="n">
+        <v>1495833.333333333</v>
+      </c>
+      <c r="CB317" t="n">
+        <v>73</v>
+      </c>
+      <c r="CC317" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD317" t="n">
+        <v>24.43478260869565</v>
+      </c>
+      <c r="CE317" t="n">
+        <v>183.1739130434783</v>
+      </c>
+      <c r="CF317" t="n">
+        <v>66.95652173913044</v>
+      </c>
+      <c r="CG317" t="n">
+        <v>5260.869565217391</v>
+      </c>
+      <c r="CH317" t="n">
+        <v>1783695.652173913</v>
+      </c>
+      <c r="CI317" t="n">
+        <v>72.34782608695652</v>
+      </c>
+      <c r="CJ317" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK317" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="CL317" t="n">
+        <v>191.6666666666667</v>
+      </c>
+      <c r="CM317" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN317" t="n">
+        <v>199</v>
+      </c>
+      <c r="CO317" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CP317" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="CQ317" t="n">
+        <v>222</v>
+      </c>
+      <c r="CR317" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS317" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT317" t="n">
+        <v>183</v>
+      </c>
+      <c r="CU317" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV317" t="n">
+        <v>137</v>
+      </c>
+      <c r="CW317" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CX317" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="CY317" t="n">
+        <v>148</v>
+      </c>
+      <c r="CZ317" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA317" t="inlineStr"/>
+      <c r="DB317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>8COq4434</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="n">
+        <v>30</v>
+      </c>
+      <c r="N318" t="n">
+        <v>70</v>
+      </c>
+      <c r="O318" t="n">
+        <v>20</v>
+      </c>
+      <c r="P318" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>7</v>
+      </c>
+      <c r="R318" t="n">
+        <v>5</v>
+      </c>
+      <c r="S318" t="n">
+        <v>9</v>
+      </c>
+      <c r="T318" t="n">
+        <v>2</v>
+      </c>
+      <c r="U318" t="n">
+        <v>4</v>
+      </c>
+      <c r="V318" t="n">
+        <v>4</v>
+      </c>
+      <c r="W318" t="n">
+        <v>13</v>
+      </c>
+      <c r="X318" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>258</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>616</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>189</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>555</v>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AQ318" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT318" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU318" t="inlineStr"/>
+      <c r="AV318" t="inlineStr"/>
+      <c r="AW318" t="inlineStr"/>
+      <c r="AX318" t="inlineStr"/>
+      <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr"/>
+      <c r="BA318" t="inlineStr"/>
+      <c r="BB318" t="inlineStr"/>
+      <c r="BC318" t="inlineStr"/>
+      <c r="BD318" t="inlineStr"/>
+      <c r="BE318" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF318" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG318" t="inlineStr"/>
+      <c r="BH318" t="inlineStr"/>
+      <c r="BI318" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="BJ318" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="BK318" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BL318" t="n">
+        <v>5300</v>
+      </c>
+      <c r="BM318" t="n">
+        <v>1722500</v>
+      </c>
+      <c r="BN318" t="n">
+        <v>72</v>
+      </c>
+      <c r="BO318" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP318" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="BQ318" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="BR318" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="BS318" t="n">
+        <v>2125</v>
+      </c>
+      <c r="BT318" t="n">
+        <v>989375</v>
+      </c>
+      <c r="BU318" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BV318" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW318" t="n">
+        <v>25.23076923076923</v>
+      </c>
+      <c r="BX318" t="n">
+        <v>184</v>
+      </c>
+      <c r="BY318" t="n">
+        <v>69.84615384615384</v>
+      </c>
+      <c r="BZ318" t="n">
+        <v>7038.461538461538</v>
+      </c>
+      <c r="CA318" t="n">
+        <v>2426923.076923077</v>
+      </c>
+      <c r="CB318" t="n">
+        <v>75.80769230769231</v>
+      </c>
+      <c r="CC318" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="CD318" t="n">
+        <v>27.78947368421053</v>
+      </c>
+      <c r="CE318" t="n">
+        <v>181.0526315789474</v>
+      </c>
+      <c r="CF318" t="n">
+        <v>66.21052631578948</v>
+      </c>
+      <c r="CG318" t="inlineStr"/>
+      <c r="CH318" t="n">
+        <v>1039736.842105263</v>
+      </c>
+      <c r="CI318" t="n">
+        <v>69.15789473684211</v>
+      </c>
+      <c r="CJ318" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK318" t="inlineStr"/>
+      <c r="CL318" t="inlineStr"/>
+      <c r="CM318" t="inlineStr"/>
+      <c r="CN318" t="inlineStr"/>
+      <c r="CO318" t="inlineStr"/>
+      <c r="CP318" t="inlineStr"/>
+      <c r="CQ318" t="inlineStr"/>
+      <c r="CR318" t="inlineStr"/>
+      <c r="CS318" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT318" t="n">
+        <v>186</v>
+      </c>
+      <c r="CU318" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV318" t="n">
+        <v>65</v>
+      </c>
+      <c r="CW318" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX318" t="n">
+        <v>575000</v>
+      </c>
+      <c r="CY318" t="n">
+        <v>65</v>
+      </c>
+      <c r="CZ318" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA318" t="inlineStr"/>
+      <c r="DB318" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
